--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05 05:23:56</t>
+          <t xml:space="preserve">2026-08-05 06:13:17</t>
         </is>
       </c>
     </row>
@@ -650,331 +650,331 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="33.0" customHeight="1">
+    <row r="19" ht="49.5" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">11-2</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代交代した旧イメージ (dangling) の回収</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定で有効。無効化は --no-reclaim-old-image)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66.0" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11-3</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時のビルドキャッシュ削除・使用量の計測</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--prune-build-cache / --prune-build-cache-keep / --disk-usage-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33.0" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss マスターパスワードの伝搬検証 (取得元 → 実行時の値)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-jboss-password</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="33.0" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="22" ht="33.0" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CloudWatch Agent (cwagent) の設定ファイルチェックとコンテナ内設定の照合 (送達レポートは --cwagent-delivery-report 指定時のみ)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(compose.yml に cwagent があれば自動)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="99.0" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="23" ht="99.0" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">WAR デプロイ時 Java 例外エラー解析 (原因分析・対処提案の Excel / テキスト出力)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(起動確認時に自動。ファイル出力は --report-dir / --deploy-exception-excel / --deploy-exception-text 指定時)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《できること》</t>
         </is>
       </c>
-      <c r="B22" s="8"/>
-    </row>
-    <row r="23" ht="33.0" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="B24" s="8"/>
+    </row>
+    <row r="25" ht="33.0" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup も --verify-url も指定しなければ、純粋にビルドのみを行って終了します
 (従来の build_and_push.sh --build-only 相当)。</t>
         </is>
       </c>
-      <c r="B23" s="3"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《行わないこと》</t>
-        </is>
-      </c>
-      <c r="B24" s="8"/>
-    </row>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ECR 権限チェック / ECR ログイン / タグ付け / プッシュ / imagedefinition.json の出力。</t>
-        </is>
-      </c>
       <c r="B25" s="3"/>
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">《行わないこと》</t>
+        </is>
+      </c>
+      <c r="B26" s="8"/>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECR 権限チェック / ECR ログイン / タグ付け / プッシュ / imagedefinition.json の出力。</t>
+        </is>
+      </c>
+      <c r="B27" s="3"/>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B26" s="8"/>
-    </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="B28" s="8"/>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">前提</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">必須コマンド</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">docker、docker compose または docker-compose</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="33.0" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">追加で必要</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">curl (--verify-url / --keep-container-mode http 時)、aws (--jboss-password-param 時)、Python 3 (送達診断の JSON 整形時)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">必須コマンド</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker、docker compose または docker-compose</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="33.0" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">追加で必要</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curl (--verify-url / --keep-container-mode http 時)、aws (--jboss-password-param 時)、Python 3 (送達診断の JSON 整形時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">AWS 認証</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--jboss-password-param を使う場合のみ必要 (aws login --remote 済み)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B31" s="8"/>
-    </row>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B33" s="8"/>
+    </row>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B32" s="3"/>
-    </row>
-    <row r="33" ht="9.0" customHeight="1">
-      <c r="A33" s="0"/>
-    </row>
-    <row r="34" ht="24.0" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" ht="9.0" customHeight="1">
+      <c r="A35" s="0"/>
+    </row>
+    <row r="36" ht="24.0" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2. 全体構成</t>
         </is>
       </c>
-      <c r="B34" s="5"/>
-    </row>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.1 ファイル内のセクション構成》</t>
         </is>
       </c>
-      <c r="B35" s="8"/>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="B37" s="8"/>
+    </row>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">位置</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">セクション</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="33.0" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="39" ht="33.0" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">冒頭</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ヘッダーコメント</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">目的・機能一覧・使い方</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="33.0" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="40" ht="33.0" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示タイムゾーン設定</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示・保存する時刻をすべて JST に固定</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="82.5" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="41" ht="82.5" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="49.5" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="42" ht="49.5" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ用ヘルパ</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / run / JST 変換ヘルパ</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">usage()</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--help の本文</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="66.0" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="44" ht="66.0" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数パース</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">append_services によるカンマ区切り分割、need_value による値欠落検出</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="49.5" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中盤</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力値の検証</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">数値・モード・排他関係・サービス指定の整合性</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中盤</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">依存コマンド / AWS 認証 / compose 判定</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実行環境の確認</t>
         </is>
       </c>
     </row>
@@ -986,16 +986,16 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット準備・一時ファイルコピー</t>
+          <t xml:space="preserve">入力値の検証</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepare_jboss_password / prepare_copy_files</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="82.5" customHeight="1">
+          <t xml:space="preserve">数値・モード・排他関係・サービス指定の整合性</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">依存コマンド / AWS 認証 / compose 判定</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">危険文字の分析、段ごとの比較、compose.yml と standalone.xml の解析、CredentialStore の開封確認</t>
+          <t xml:space="preserve">実行環境の確認</t>
         </is>
       </c>
     </row>
@@ -1020,480 +1020,498 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">シークレット準備・一時ファイルコピー</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prepare_jboss_password / prepare_copy_files</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="82.5" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中盤</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">マスターパスワードの伝搬検証</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">危険文字の分析、段ごとの比較、compose.yml と standalone.xml の解析、CredentialStore の開封確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="49.5" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中盤</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">起動確認・ログ表示ヘルパ</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ取得、ANSI 除去、色分け、companion ログ</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="33.0" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="50" ht="33.0" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナ内情報の収集と整形</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="82.5" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="51" ht="82.5" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM パラメータ・OpenTelemetry 設定</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">/proc/&lt;pid&gt;/cmdline の走査、JVM オプションの分類、OpenTelemetry 設定の突き合わせ</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="66.0" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中盤</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">対話操作</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bash / HTTP / logs モードと、healthcheck・MySQL・可観測性の各ヘルパ</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="33.0" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Docker 完全クリーンアップ</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">対象の集計、確認フレーズ、削除、検証</t>
         </is>
       </c>
     </row>
     <row r="52" ht="66.0" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">中盤</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">対話操作</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bash / HTTP / logs モードと、healthcheck・MySQL・可観測性の各ヘルパ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="33.0" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docker 完全クリーンアップ</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">対象の集計、確認フレーズ、削除、検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="66.0" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">WAR デプロイ時 Java 例外解析</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">解析ヘルパー (Python 3) の埋め込みと、ログ収集・実行・表示・レポート追記</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポート</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">write_build_report</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">後始末 (cleanup_all)</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">EXIT トラップ本体</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="49.5" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="57" ht="49.5" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">末尾</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">メイン処理</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド → 起動 → 起動確認 → URL 確認 → 対話 → 情報表示</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="58" ht="19.5" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.2 主要な関数グループ》</t>
         </is>
       </c>
-      <c r="B56" s="8"/>
-    </row>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="B58" s="8"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">グループ</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">代表的な関数</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">役割</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="33.0" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="60" ht="33.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ・時刻</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / to_jst_display_time</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">出力整形と UTC→JST 変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="33.0" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">引数処理</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">append_services / need_value / validate_positive_integer</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カンマ区切り分割、値欠落検出、数値検証</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="49.5" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Compose 操作</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose_container_ids / compose_logs / compose_started_services</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">対象サービスの ID・ログ・サービス名取得</t>
         </is>
       </c>
     </row>
     <row r="61" ht="33.0" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認</t>
+          <t xml:space="preserve">引数処理</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
+          <t xml:space="preserve">append_services / need_value / validate_positive_integer</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="33.0" customHeight="1">
+          <t xml:space="preserve">カンマ区切り分割、値欠落検出、数値検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="49.5" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログ表示</t>
+          <t xml:space="preserve">Compose 操作</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
+          <t xml:space="preserve">compose_container_ids / compose_logs / compose_started_services</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">行数制御と重要ログの色分け</t>
+          <t xml:space="preserve">対象サービスの ID・ログ・サービス名取得</t>
         </is>
       </c>
     </row>
     <row r="63" ht="33.0" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL 確認</t>
+          <t xml:space="preserve">起動確認</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">verify_url / show_url_body</t>
+          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl のリトライと応答本文表示</t>
+          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
         </is>
       </c>
     </row>
     <row r="64" ht="33.0" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">情報表示</t>
+          <t xml:space="preserve">ログ表示</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_verified_container_envs / ..._directory_trees / ..._deployment_structures</t>
+          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="66.0" customHeight="1">
+          <t xml:space="preserve">行数制御と重要ログの色分け</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="33.0" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JVM / OTel</t>
+          <t xml:space="preserve">URL 確認</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_verified_container_jvm_parameters / ..._otel_settings / collect_container_java_processes / classify_jvm_option / is_otel_jvm_option</t>
+          <t xml:space="preserve">verify_url / show_url_body</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java プロセスの検出、JVM オプションの分類、OpenTelemetry 設定の集約</t>
+          <t xml:space="preserve">curl のリトライと応答本文表示</t>
         </is>
       </c>
     </row>
     <row r="66" ht="33.0" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作</t>
+          <t xml:space="preserve">情報表示</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
+          <t xml:space="preserve">show_verified_container_envs / ..._directory_trees / ..._deployment_structures</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / HTTP / logs モード</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="33.0" customHeight="1">
+          <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="66.0" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck</t>
+          <t xml:space="preserve">JVM / OTel</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
+          <t xml:space="preserve">show_verified_container_jvm_parameters / ..._otel_settings / collect_container_java_processes / classify_jvm_option / is_otel_jvm_option</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
+          <t xml:space="preserve">Java プロセスの検出、JVM オプションの分類、OpenTelemetry 設定の集約</t>
         </is>
       </c>
     </row>
     <row r="68" ht="33.0" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">可観測性</t>
+          <t xml:space="preserve">対話操作</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+          <t xml:space="preserve">bash / HTTP / logs モード</t>
         </is>
       </c>
     </row>
     <row r="69" ht="33.0" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">healthcheck</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="33.0" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可観測性</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="33.0" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">クリーンアップ</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cleanup_all_docker_data / teardown_container / cleanup_copied_files</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 全体削除と通常後始末</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="66.0" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cwagent 送信検証</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="66.0" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cwagent ロググループ準備</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prepare_cwagent_log_groups / cwagent_ensure_log_groups / cwagent_resolve_delivery_target</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">設定ファイルの log_group_name が実 CloudWatch Logs に無ければ作成</t>
         </is>
       </c>
     </row>
     <row r="72" ht="66.0" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析</t>
+          <t xml:space="preserve">cwagent 送信検証</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyze_war_deploy_exceptions / collect_deploy_exception_logs / resolve_deploy_exception_excel_path / show_war_deploy_exception_analysis / append_deploy_exception_report</t>
+          <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、画面表示と Excel 出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="33.0" customHeight="1">
+          <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="66.0" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">レポート</t>
+          <t xml:space="preserve">cwagent ロググループ準備</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">write_build_report / append_compose_service_logs_report / append_jboss_password_report / append_cwagent_report / append_deploy_exception_report</t>
+          <t xml:space="preserve">prepare_cwagent_log_groups / cwagent_ensure_log_groups / cwagent_resolve_delivery_target</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの生成</t>
+          <t xml:space="preserve">設定ファイルの log_group_name が実 CloudWatch Logs に無ければ作成</t>
         </is>
       </c>
     </row>
     <row r="74" ht="66.0" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Java 例外解析</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analyze_war_deploy_exceptions / collect_deploy_exception_logs / resolve_deploy_exception_excel_path / show_war_deploy_exception_analysis / append_deploy_exception_report</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、画面表示と Excel 出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="33.0" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">レポート</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">write_build_report / append_compose_service_logs_report / append_jboss_password_report / append_cwagent_report / append_deploy_exception_report</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートの生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="66.0" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">パスワード伝搬検証</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">verify_jboss_password_host_stages / verify_jboss_password_build_secret / verify_jboss_password_container_stages / jboss_xml_attributes / jboss_xml_unescape / jboss_wildfly_literal</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">各段の値の取得、XML と WildFly 式のエスケープ解除、原本との突き合わせ</t>
         </is>
       </c>
-    </row>
-    <row r="75" ht="19.5" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
-        </is>
-      </c>
-      <c r="B75" s="8"/>
-    </row>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">処理のどの経路 (成功・失敗・中断) でも、次の順で実行されます。</t>
-        </is>
-      </c>
-      <c r="B76" s="3"/>
     </row>
     <row r="77" ht="19.5" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
@@ -1503,84 +1521,104 @@
       </c>
       <c r="B77" s="8"/>
     </row>
-    <row r="78" ht="148.5" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">処理のどの経路 (成功・失敗・中断) でも、次の順で実行されます。</t>
+        </is>
+      </c>
+      <c r="B78" s="3"/>
+    </row>
+    <row r="79" ht="19.5" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
+        </is>
+      </c>
+      <c r="B79" s="8"/>
+    </row>
+    <row r="80" ht="214.5" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1. analyze_war_deploy_exceptions … デプロイ処理の Java 例外を解析 (削除より前・レポートより前)
                                    成功経路で実行済みなら何もしない
 2. write_build_report        … --report-dir 指定時、全量レポートを保存 (削除より前に実行)
 3. cleanup_all_docker_data   … --cleanup-all-docker-data 指定時、確認フレーズ入力後に全削除
 4. teardown_container        … compose down (--keep-container 指定時は残す)
-5. cleanup_copied_files      … --copy-file でコピーしたファイルを削除
+5. prune_build_cache         … --prune-build-cache / --prune-build-cache-keep 指定時、
+                                   ビルドキャッシュを削除 (コンテナ削除の後)
+6. report_disk_usage_at_exit … --disk-usage-report 指定時、終了時の使用量と増減を表示
+                                   (3 が実際に削除を行った場合は重複するため出さない)
+7. cleanup_copied_files      … --copy-file でコピーしたファイルを削除
                                    (既存ファイルを強制上書きした分は削除せず、
                                     退避しておいた上書き前のファイルを復元)
-6. 一時ファイル削除          … Java 例外解析結果・URL 応答本文・HTTP ボディ・healthcheck 診断</t>
-        </is>
-      </c>
-      <c r="B78" s="6"/>
-    </row>
-    <row r="79" ht="19.5" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
+8. 一時ファイル削除          … Java 例外解析結果・URL 応答本文・HTTP ボディ・healthcheck 診断</t>
+        </is>
+      </c>
+      <c r="B80" s="6"/>
+    </row>
+    <row r="81" ht="19.5" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B79" s="8"/>
-    </row>
-    <row r="80" ht="33.0" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="B81" s="8"/>
+    </row>
+    <row r="82" ht="33.0" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">終了コードは、本処理が既に失敗していれば元の終了コードを優先します。
 成功していた場合は、後始末の結果 (レポート保存失敗やクリーンアップ未承認なら 1) を返します。</t>
         </is>
       </c>
-      <c r="B80" s="3"/>
-    </row>
-    <row r="81" ht="19.5" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="B82" s="3"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B81" s="8"/>
-    </row>
-    <row r="82" ht="19.5" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="B83" s="8"/>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B82" s="3"/>
-    </row>
-    <row r="83" ht="9.0" customHeight="1">
-      <c r="A83" s="0"/>
-    </row>
-    <row r="84" ht="24.0" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" ht="9.0" customHeight="1">
+      <c r="A85" s="0"/>
+    </row>
+    <row r="86" ht="24.0" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">3. 処理の流れ</t>
         </is>
       </c>
-      <c r="B84" s="5"/>
-    </row>
-    <row r="85" ht="19.5" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="B86" s="5"/>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B85" s="8"/>
-    </row>
-    <row r="86" ht="19.5" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="B87" s="8"/>
+    </row>
+    <row r="88" ht="19.5" customHeight="1">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B86" s="8"/>
-    </row>
-    <row r="87" ht="99.0" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="B88" s="8"/>
+    </row>
+    <row r="89" ht="99.0" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時は、EXIT の後始末でレポートのログ本文を集める直前に
 compose stop (SIGTERM) を挟みます (3.6 参照)。
@@ -1590,22 +1628,6 @@
 必ず実行します** (6.7 参照)。</t>
         </is>
       </c>
-      <c r="B87" s="3"/>
-    </row>
-    <row r="88" ht="19.5" customHeight="1">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
-        </is>
-      </c>
-      <c r="B88" s="8"/>
-    </row>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--compose-service の指定数によってビルド戦略が変わります。</t>
-        </is>
-      </c>
       <c r="B89" s="3"/>
     </row>
     <row r="90" ht="19.5" customHeight="1">
@@ -1617,149 +1639,237 @@
       <c r="B90" s="8"/>
     </row>
     <row r="91" ht="19.5" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--compose-service の指定数によってビルド戦略が変わります。</t>
+        </is>
+      </c>
+      <c r="B91" s="3"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B92" s="8"/>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">指定</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">動作</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="19.5" customHeight="1">
-      <c r="A92" s="11" t="inlineStr">
+    <row r="94" ht="19.5" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">未指定</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全サービスを 1 回の compose build でビルド</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="19.5" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1 個</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そのサービスのみビルド</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="33.0" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
+    <row r="96" ht="33.0" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2 個以上</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">第 1 フェーズ: base サービスを単独で先行ビルド → ローカルイメージ確認 → 第 2 フェーズ: base 以外をまとめて並列ビルド</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="19.5" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
+    <row r="97" ht="19.5" customHeight="1">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B95" s="8"/>
-    </row>
-    <row r="96" ht="33.0" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="B97" s="8"/>
+    </row>
+    <row r="98" ht="33.0" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2 段階に分けるのは、ベースイメージを参照するサービスが base の完成前にビルドを始めるのを
 防ぐためです。並列オプションは compose のバージョンによって使い分けます。</t>
         </is>
       </c>
-      <c r="B96" s="3"/>
-    </row>
-    <row r="97" ht="19.5" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="B98" s="3"/>
+    </row>
+    <row r="99" ht="19.5" customHeight="1">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B97" s="8"/>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="B99" s="8"/>
+    </row>
+    <row r="100" ht="19.5" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">compose</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">並列指定</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="19.5" customHeight="1">
-      <c r="A99" s="11" t="inlineStr">
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">v2 (docker compose)</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">グローバルオプション --parallel &lt;サービス数&gt;</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="19.5" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">v1 (docker-compose)</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build --parallel (未対応版は exit 1)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="19.5" customHeight="1">
-      <c r="A101" s="8" t="inlineStr">
+    <row r="103" ht="19.5" customHeight="1">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B101" s="8"/>
-    </row>
-    <row r="102" ht="33.0" customHeight="1">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="B103" s="8"/>
+    </row>
+    <row r="104" ht="33.0" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド後は docker image inspect でローカルイメージを確認し、
 image=... id=... created=... size=... bytes を JST 表記でログに残します。</t>
         </is>
       </c>
-      <c r="B102" s="3"/>
-    </row>
-    <row r="103" ht="19.5" customHeight="1">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="B104" s="3"/>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B105" s="8"/>
+    </row>
+    <row r="106" ht="19.5" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルドの前後では、ディスク使用量を抑えるために次を行います (5.8-2 参照)。</t>
+        </is>
+      </c>
+      <c r="B106" s="3"/>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B107" s="8"/>
+    </row>
+    <row r="108" ht="19.5" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">タイミング</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="19.5" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="19.5" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="19.5" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ローカルイメージ確認の直後</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID が変わっていれば、タグを失った旧世代イメージを削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="19.5" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B103" s="8"/>
-    </row>
-    <row r="104" ht="19.5" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="B112" s="8"/>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B104" s="8"/>
-    </row>
-    <row r="105" ht="99.0" customHeight="1">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="B113" s="8"/>
+    </row>
+    <row r="114" ht="99.0" customHeight="1">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・--startup-service を指定した場合は、サービスごとに個別に起動完了を判定し、
   指定した全サービスの完了をもって成功とします
@@ -1769,35 +1879,35 @@
 ・失敗時は --suppress-startup-logs を指定していてもログを表示します (原因を隠さないため)</t>
         </is>
       </c>
-      <c r="B105" s="3"/>
-    </row>
-    <row r="106" ht="19.5" customHeight="1">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="B114" s="3"/>
+    </row>
+    <row r="115" ht="19.5" customHeight="1">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B106" s="8"/>
-    </row>
-    <row r="107" ht="33.0" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
+      <c r="B115" s="8"/>
+    </row>
+    <row r="116" ht="33.0" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">curl -s -S -m 30 -o &lt;一時ファイル&gt; -w '%{http_code}' -X &lt;URL_METHOD&gt; \
      [-k] [-H "Content-Type: &lt;URL_CONTENT_TYPE&gt;"] [--data &lt;ボディ&gt;] &lt;VERIFY_URL&gt;</t>
         </is>
       </c>
-      <c r="B107" s="6"/>
-    </row>
-    <row r="108" ht="19.5" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="B116" s="6"/>
+    </row>
+    <row r="117" ht="19.5" customHeight="1">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B108" s="8"/>
-    </row>
-    <row r="109" ht="66.0" customHeight="1">
-      <c r="A109" s="3" t="inlineStr">
+      <c r="B117" s="8"/>
+    </row>
+    <row r="118" ht="66.0" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・期待ステータス (--expect-status) と一致するまで --url-interval 秒間隔でリトライ
 ・--url-timeout 秒を超えると失敗 (最後の応答コードを表示)
@@ -1805,103 +1915,121 @@
 ・成功・失敗いずれの場合も、応答本文の先頭 20 行を表示</t>
         </is>
       </c>
-      <c r="B109" s="3"/>
-    </row>
-    <row r="110" ht="19.5" customHeight="1">
-      <c r="A110" s="8" t="inlineStr">
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" ht="19.5" customHeight="1">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B110" s="8"/>
-    </row>
-    <row r="111" ht="33.0" customHeight="1">
-      <c r="A111" s="3" t="inlineStr">
+      <c r="B119" s="8"/>
+    </row>
+    <row r="120" ht="33.0" customHeight="1">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup を付けず --verify-url のみを指定した場合もコンテナは起動します
 (起動完了のログ確認は行わず、URL のリトライで readiness を担保します)。</t>
         </is>
       </c>
-      <c r="B111" s="3"/>
-    </row>
-    <row r="112" ht="19.5" customHeight="1">
-      <c r="A112" s="8" t="inlineStr">
+      <c r="B120" s="3"/>
+    </row>
+    <row r="121" ht="19.5" customHeight="1">
+      <c r="A121" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B112" s="8"/>
-    </row>
-    <row r="113" ht="19.5" customHeight="1">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="B121" s="8"/>
+    </row>
+    <row r="122" ht="19.5" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">状況</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの扱い</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="19.5" customHeight="1">
-      <c r="A114" s="11" t="inlineStr">
+    <row r="123" ht="19.5" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">通常</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down で停止・削除</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="33.0" customHeight="1">
-      <c r="A115" s="11" t="inlineStr">
+    <row r="124" ht="33.0" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--keep-container / --keep-container-mode 指定</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="19.5" customHeight="1">
-      <c r="A116" s="11" t="inlineStr">
+    <row r="125" ht="19.5" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="19.5" customHeight="1">
-      <c r="A117" s="11" t="inlineStr">
+    <row r="126" ht="19.5" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="19.5" customHeight="1">
-      <c r="A118" s="8" t="inlineStr">
+    <row r="127" ht="19.5" customHeight="1">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B127" s="8"/>
+    </row>
+    <row r="128" ht="49.5" customHeight="1">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナの削除後に、--prune-build-cache / --prune-build-cache-keep 指定時はビルド
+キャッシュを削除し、--disk-usage-report 指定時は終了時の使用量と実行前からの増減を
+表示します (5.8-2 参照)。</t>
+        </is>
+      </c>
+      <c r="B128" s="3"/>
+    </row>
+    <row r="129" ht="19.5" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B118" s="8"/>
-    </row>
-    <row r="119" ht="66.0" customHeight="1">
-      <c r="A119" s="3" t="inlineStr">
+      <c r="B129" s="8"/>
+    </row>
+    <row r="130" ht="66.0" customHeight="1">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS はタスク停止時に各コンテナへ SIGTERM を送るため、adot collector のような
 サイドカーは「シグナル受信 → パイプラインの graceful shutdown → 終了」までを
@@ -1909,34 +2037,34 @@
 誰にも取得されないままコンテナごと削除されてしまいます。</t>
         </is>
       </c>
-      <c r="B119" s="3"/>
-    </row>
-    <row r="120" ht="19.5" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" ht="19.5" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B120" s="8"/>
-    </row>
-    <row r="121" ht="19.5" customHeight="1">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="B131" s="8"/>
+    </row>
+    <row r="132" ht="19.5" customHeight="1">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そこでエラー終了時に限り、削除の前に SIGTERM による停止を挟みます。</t>
         </is>
       </c>
-      <c r="B121" s="3"/>
-    </row>
-    <row r="122" ht="19.5" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
+      <c r="B132" s="3"/>
+    </row>
+    <row r="133" ht="19.5" customHeight="1">
+      <c r="A133" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B122" s="8"/>
-    </row>
-    <row r="123" ht="148.5" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
+      <c r="B133" s="8"/>
+    </row>
+    <row r="134" ht="148.5" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">[2] 〜 [6] の収集 (起動中のコンテナが必要)
         ↓
@@ -1949,18 +2077,18 @@
 compose down (削除)</t>
         </is>
       </c>
-      <c r="B123" s="6"/>
-    </row>
-    <row r="124" ht="19.5" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
+      <c r="B134" s="6"/>
+    </row>
+    <row r="135" ht="19.5" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B124" s="8"/>
-    </row>
-    <row r="125" ht="165.0" customHeight="1">
-      <c r="A125" s="3" t="inlineStr">
+      <c r="B135" s="8"/>
+    </row>
+    <row r="136" ht="165.0" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・対象は compose ps --services が返す稼働中の全サービスです
   (起動確認対象だけでなく adot collector などのサイドカーも含みます)
@@ -1974,505 +2102,510 @@
   従来どおり compose down でまとめて削除します</t>
         </is>
       </c>
-      <c r="B125" s="3"/>
-    </row>
-    <row r="126" ht="19.5" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="B136" s="3"/>
+    </row>
+    <row r="137" ht="19.5" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B126" s="8"/>
-    </row>
-    <row r="127" ht="49.5" customHeight="1">
-      <c r="A127" s="3" t="inlineStr">
+      <c r="B137" s="8"/>
+    </row>
+    <row r="138" ht="49.5" customHeight="1">
+      <c r="A138" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">adot collector の healthcheck が失敗し、depends_on の condition: service_healthy
 を満たせずバックエンドが起動しなかった場合、ECS 上でも同じくタスクが停止します。
 その終了処理まで含めてローカルで再現・確認できるようにするのがこの動作の狙いです。</t>
         </is>
       </c>
-      <c r="B127" s="3"/>
-    </row>
-    <row r="128" ht="19.5" customHeight="1">
-      <c r="A128" s="8" t="inlineStr">
+      <c r="B138" s="3"/>
+    </row>
+    <row r="139" ht="19.5" customHeight="1">
+      <c r="A139" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B128" s="8"/>
-    </row>
-    <row r="129" ht="19.5" customHeight="1">
-      <c r="A129" s="3" t="inlineStr">
+      <c r="B139" s="8"/>
+    </row>
+    <row r="140" ht="19.5" customHeight="1">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B129" s="3"/>
-    </row>
-    <row r="130" ht="9.0" customHeight="1">
-      <c r="A130" s="0"/>
-    </row>
-    <row r="131" ht="24.0" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
+      <c r="B140" s="3"/>
+    </row>
+    <row r="141" ht="9.0" customHeight="1">
+      <c r="A141" s="0"/>
+    </row>
+    <row r="142" ht="24.0" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">5. 終了コード</t>
         </is>
       </c>
-      <c r="B131" s="5"/>
-    </row>
-    <row r="132" ht="19.5" customHeight="1">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="B142" s="5"/>
+    </row>
+    <row r="143" ht="19.5" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コード</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">意味</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">主な発生条件</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="33.0" customHeight="1">
-      <c r="A133" s="11" t="inlineStr">
+    <row r="144" ht="33.0" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B144" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">正常終了</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド (と指定した確認) がすべて成功</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="346.5" customHeight="1">
-      <c r="A134" s="11" t="inlineStr">
+    <row r="145" ht="346.5" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B145" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行時エラー</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="379.5" customHeight="1">
-      <c r="A135" s="11" t="inlineStr">
+    <row r="146" ht="379.5" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B146" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数エラー</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="19.5" customHeight="1">
-      <c r="A136" s="3" t="inlineStr">
+    <row r="147" ht="19.5" customHeight="1">
+      <c r="A147" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">本処理が失敗している場合は、後始末の結果にかかわらず元の終了コードが優先されます。</t>
         </is>
       </c>
-      <c r="B136" s="3"/>
-    </row>
-    <row r="137" ht="19.5" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
+      <c r="B147" s="3"/>
+    </row>
+    <row r="148" ht="19.5" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B137" s="3"/>
-    </row>
-    <row r="138" ht="9.0" customHeight="1">
-      <c r="A138" s="0"/>
-    </row>
-    <row r="139" ht="24.0" customHeight="1">
-      <c r="A139" s="5" t="inlineStr">
+      <c r="B148" s="3"/>
+    </row>
+    <row r="149" ht="9.0" customHeight="1">
+      <c r="A149" s="0"/>
+    </row>
+    <row r="150" ht="24.0" customHeight="1">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">6. 環境変数</t>
         </is>
       </c>
-      <c r="B139" s="5"/>
-    </row>
-    <row r="140" ht="19.5" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+      <c r="B150" s="5"/>
+    </row>
+    <row r="151" ht="19.5" customHeight="1">
+      <c r="A151" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.1 入力として参照する環境変数》</t>
         </is>
       </c>
-      <c r="B140" s="8"/>
-    </row>
-    <row r="141" ht="19.5" customHeight="1">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="B151" s="8"/>
+    </row>
+    <row r="152" ht="19.5" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="19.5" customHeight="1">
-      <c r="A142" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="19.5" customHeight="1">
-      <c r="A143" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="19.5" customHeight="1">
-      <c r="A144" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="19.5" customHeight="1">
-      <c r="A145" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO_COLOR</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定義されていれば色分けを無効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="19.5" customHeight="1">
-      <c r="A146" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLICOLOR_FORCE</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="19.5" customHeight="1">
-      <c r="A147" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TERM</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dumb の場合は色分けしない</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="19.5" customHeight="1">
-      <c r="A148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
-        </is>
-      </c>
-      <c r="B148" s="8"/>
-    </row>
-    <row r="149" ht="19.5" customHeight="1">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="19.5" customHeight="1">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TZ</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="19.5" customHeight="1">
-      <c r="A151" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="19.5" customHeight="1">
-      <c r="A152" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
         </is>
       </c>
     </row>
     <row r="153" ht="19.5" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="19.5" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="19.5" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="19.5" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO_COLOR</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定義されていれば色分けを無効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="19.5" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLICOLOR_FORCE</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="19.5" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TERM</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dumb の場合は色分けしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="19.5" customHeight="1">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
+        </is>
+      </c>
+      <c r="B159" s="8"/>
+    </row>
+    <row r="160" ht="19.5" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用途</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="19.5" customHeight="1">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TZ</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="19.5" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="19.5" customHeight="1">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="19.5" customHeight="1">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B164" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="19.5" customHeight="1">
-      <c r="A154" s="8" t="inlineStr">
+    <row r="165" ht="19.5" customHeight="1">
+      <c r="A165" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B154" s="8"/>
-    </row>
-    <row r="155" ht="49.5" customHeight="1">
-      <c r="A155" s="3" t="inlineStr">
+      <c r="B165" s="8"/>
+    </row>
+    <row r="166" ht="49.5" customHeight="1">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 / 7.2 はスクリプト自身が実行ホストで参照・設定する環境変数です。
 これとは別に、起動したコンテナ内の環境変数を収集して一覧表示します
 (スクリプトの動作は変えません)。</t>
         </is>
       </c>
-      <c r="B155" s="3"/>
-    </row>
-    <row r="156" ht="19.5" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
+      <c r="B166" s="3"/>
+    </row>
+    <row r="167" ht="19.5" customHeight="1">
+      <c r="A167" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B156" s="8"/>
-    </row>
-    <row r="157" ht="19.5" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="B167" s="8"/>
+    </row>
+    <row r="168" ht="19.5" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">出力先</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="33.0" customHeight="1">
-      <c r="A158" s="11" t="inlineStr">
+    <row r="169" ht="33.0" customHeight="1">
+      <c r="A169" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM オプションの受け渡し</t>
         </is>
       </c>
-      <c r="B158" s="3" t="inlineStr">
+      <c r="B169" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="C169" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="33.0" customHeight="1">
-      <c r="A159" s="11" t="inlineStr">
+    <row r="170" ht="33.0" customHeight="1">
+      <c r="A170" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 標準設定</t>
         </is>
       </c>
-      <c r="B159" s="3" t="inlineStr">
+      <c r="B170" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="C170" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="33.0" customHeight="1">
-      <c r="A160" s="11" t="inlineStr">
+    <row r="171" ht="33.0" customHeight="1">
+      <c r="A171" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 関連設定</t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr">
+      <c r="B171" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS_XRAY_DAEMON_ADDRESS / AWS_XRAY_CONTEXT_MISSING / AWS_XRAY_TRACING_NAME / AWS_LAMBDA_EXEC_WRAPPER / AOT_CONFIG_CONTENT</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="C171" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="19.5" customHeight="1">
-      <c r="A161" s="11" t="inlineStr">
+    <row r="172" ht="19.5" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリ構造の起点</t>
         </is>
       </c>
-      <c r="B161" s="3" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--deployment-dir-env で指定した名前</t>
         </is>
       </c>
-      <c r="C161" s="3" t="inlineStr">
+      <c r="C172" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="19.5" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
+    <row r="173" ht="19.5" customHeight="1">
+      <c r="A173" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B162" s="8"/>
-    </row>
-    <row r="163" ht="19.5" customHeight="1">
-      <c r="A163" s="3" t="inlineStr">
+      <c r="B173" s="8"/>
+    </row>
+    <row r="174" ht="19.5" customHeight="1">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B163" s="3"/>
+      <c r="B174" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="73">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="A77:B77"/>
     <mergeCell ref="A78:B78"/>
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A83:B83"/>
     <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A85:B85"/>
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="A87:B87"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A92:B92"/>
     <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A99:B99"/>
     <mergeCell ref="A103:B103"/>
     <mergeCell ref="A104:B104"/>
     <mergeCell ref="A105:B105"/>
     <mergeCell ref="A106:B106"/>
     <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="A111:B111"/>
     <mergeCell ref="A112:B112"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A117:B117"/>
     <mergeCell ref="A118:B118"/>
     <mergeCell ref="A119:B119"/>
     <mergeCell ref="A120:B120"/>
     <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A125:B125"/>
-    <mergeCell ref="A126:B126"/>
     <mergeCell ref="A127:B127"/>
     <mergeCell ref="A128:B128"/>
     <mergeCell ref="A129:B129"/>
+    <mergeCell ref="A130:B130"/>
     <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="A135:B135"/>
     <mergeCell ref="A136:B136"/>
     <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A138:B138"/>
     <mergeCell ref="A139:B139"/>
     <mergeCell ref="A140:B140"/>
+    <mergeCell ref="A142:B142"/>
+    <mergeCell ref="A147:B147"/>
     <mergeCell ref="A148:B148"/>
-    <mergeCell ref="A154:B154"/>
-    <mergeCell ref="A155:B155"/>
-    <mergeCell ref="A156:B156"/>
-    <mergeCell ref="A162:B162"/>
-    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="A150:B150"/>
+    <mergeCell ref="A151:B151"/>
+    <mergeCell ref="A159:B159"/>
+    <mergeCell ref="A165:B165"/>
+    <mergeCell ref="A166:B166"/>
+    <mergeCell ref="A167:B167"/>
+    <mergeCell ref="A173:B173"/>
+    <mergeCell ref="A174:B174"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4633,108 +4766,248 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="19.5" customHeight="1">
+    <row r="75" ht="33.0" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E75" s="7"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="76" ht="33.0" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E76" s="7"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="77" ht="33.0" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E77" s="7"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="78" ht="33.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E78" s="7"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="79" ht="33.0" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E79" s="7"/>
       <c r="F79" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="19.5" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.9 その他</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-h, --help</t>
+        </is>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="33.0" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="33.0" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="33.0" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="33.0" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F79"/>
+  <autoFilter ref="A4:F84"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -4856,88 +5129,80 @@
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
     </row>
-    <row r="10" ht="82.5" customHeight="1">
+    <row r="10" ht="33.0" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent (cwagent) の設定ファイルチェックとコンテナ内設定の照合 (送達レポートは --cwagent-delivery-report 指定時のみ)</t>
+          <t xml:space="preserve">世代交代した旧イメージ (dangling) の回収</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(compose.yml に cwagent があれば自動)</t>
+          <t xml:space="preserve">(既定で有効。無効化は --no-reclaim-old-image)</t>
         </is>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
     </row>
-    <row r="11" ht="49.5" customHeight="1">
+    <row r="11" ht="82.5" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外エラー解析 (原因分析・対処提案の Excel / テキスト出力)</t>
+          <t xml:space="preserve">CloudWatch Agent (cwagent) の設定ファイルチェックとコンテナ内設定の照合 (送達レポートは --cwagent-delivery-report 指定時のみ)</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(起動確認時に自動。ファイル出力は --report-dir / --deploy-exception-excel / --deploy-exception-text 指定時)</t>
+          <t xml:space="preserve">(compose.yml に cwagent があれば自動)</t>
         </is>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
     </row>
-    <row r="12" ht="9.0" customHeight="1">
-      <c r="A12" s="0"/>
-    </row>
-    <row r="13" ht="24.0" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="12" ht="49.5" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外エラー解析 (原因分析・対処提案の Excel / テキスト出力)</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(起動確認時に自動。ファイル出力は --report-dir / --deploy-exception-excel / --deploy-exception-text 指定時)</t>
+        </is>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+    </row>
+    <row r="13" ht="9.0" customHeight="1">
+      <c r="A13" s="0"/>
+    </row>
+    <row r="14" ht="24.0" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値が設定されているパラメータ</t>
         </is>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">分類</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">オプション</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">その既定値での動作</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--local-image NAME</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1/base.local</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose build で生成されるローカルイメージ名</t>
         </is>
       </c>
     </row>
@@ -4949,17 +5214,17 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--compose-file FILE</t>
+          <t xml:space="preserve">--local-image NAME</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml</t>
+          <t xml:space="preserve">j1/base.local</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose 定義ファイル</t>
+          <t xml:space="preserve">compose build で生成されるローカルイメージ名</t>
         </is>
       </c>
     </row>
@@ -4971,39 +5236,39 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--compose-file FILE</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose.yml</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose 定義ファイル</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--compose-service NAME</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">(全サービス)</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド・起動対象。複数指定時は base を先行ビルド。base は起動対象にならない</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="33.0" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
         </is>
       </c>
     </row>
@@ -5015,17 +5280,17 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss_master_password</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
         </is>
       </c>
     </row>
@@ -5037,39 +5302,39 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--region REGION</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="21" ht="33.0" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5346,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -5091,7 +5356,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5368,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -5113,7 +5378,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
@@ -5125,39 +5390,39 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="25" ht="33.0" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -5169,17 +5434,17 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -5191,17 +5456,17 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -5213,17 +5478,17 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -5235,17 +5500,17 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -5257,17 +5522,17 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -5279,17 +5544,17 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -5301,39 +5566,39 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="33" ht="33.0" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
@@ -5345,17 +5610,17 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -5367,17 +5632,17 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -5389,17 +5654,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -5411,17 +5676,17 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -5433,17 +5698,17 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -5455,39 +5720,39 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--wait-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="33.0" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -5499,17 +5764,17 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-method METHOD</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GET</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストメソッド</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -5521,17 +5786,17 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動)</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -5543,17 +5808,17 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -5565,39 +5830,39 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="45" ht="19.5" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+          <t xml:space="preserve">リトライ間隔</t>
         </is>
       </c>
     </row>
@@ -5609,61 +5874,61 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="47" ht="19.5" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="33.0" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
@@ -5675,17 +5940,17 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
@@ -5697,84 +5962,100 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="33.0" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">50</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="9.0" customHeight="1">
-      <c r="A51" s="0"/>
-    </row>
-    <row r="52" ht="24.0" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="52" ht="33.0" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="9.0" customHeight="1">
+      <c r="A53" s="0"/>
+    </row>
+    <row r="54" ht="24.0" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
         </is>
       </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-    </row>
-    <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+    </row>
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">記載箇所</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-    </row>
-    <row r="54" ht="33.0" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-    </row>
-    <row r="55" ht="33.0" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
     </row>
     <row r="56" ht="33.0" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
       <c r="C56" s="3"/>
@@ -5783,19 +6064,47 @@
     <row r="57" ht="33.0" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
     </row>
+    <row r="58" ht="33.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+    </row>
+    <row r="59" ht="33.0" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -5806,13 +6115,14 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6299,30 +6609,84 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="33.0" customHeight="1">
+    <row r="29" ht="82.5" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">15-2</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディスクを増やさずに --no-cache の検証を回す
+旧世代イメージの回収は既定で有効。ビルドキャッシュは 10GB まで残して削除し、
+実行前からの増減を表示する</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --no-cache --verify-startup \
+    --disk-usage-report --prune-build-cache-keep 10GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15-3</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">使用量の増減だけを先に測る (削除は行わない)</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --no-cache --disk-usage-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="33.0" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15-4</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代を比較したいので旧イメージを残す (調査用)</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --no-cache --no-reclaim-old-image</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="33.0" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh 経由での呼び出し (同じ処理)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_push.sh --build-only --verify-startup --log-dir ./logs</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="115.5" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="33" ht="115.5" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイ結果ファイルと Java 例外解析 (Excel + テキスト) をまとめて保存
 (reports/build_and_verify_&lt;日時&gt;.txt、
@@ -6330,7 +6694,7 @@
 reports/build_and_verify_&lt;日時&gt;_java_exceptions.txt が出力される)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -6338,18 +6702,18 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="66.0" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="34" ht="66.0" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-2</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析の Excel / テキストを任意のパスへ出力する</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -6358,18 +6722,18 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="33.0" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="35" ht="33.0" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-3</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析を行わない (ログ量を抑えたい場合)</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-deploy-exception-analysis</t>
         </is>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05 06:13:17</t>
+          <t xml:space="preserve">2026-08-05 10:03:50</t>
         </is>
       </c>
     </row>
@@ -1139,29 +1139,29 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルドの停滞検知・進捗表示</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド出力の読み手、監視プロセス、停滞診断、上限時間での中断</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="66.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">WAR デプロイ時 Java 例外解析</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">解析ヘルパー (Python 3) の埋め込みと、ログ収集・実行・表示・レポート追記</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポート</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">write_build_report</t>
         </is>
       </c>
     </row>
@@ -1173,361 +1173,379 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">全量レポート</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">write_build_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="19.5" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">後始末 (cleanup_all)</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">EXIT トラップ本体</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="49.5" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="58" ht="49.5" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">末尾</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">メイン処理</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド → 起動 → 起動確認 → URL 確認 → 対話 → 情報表示</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.2 主要な関数グループ》</t>
         </is>
       </c>
-      <c r="B58" s="8"/>
-    </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="B59" s="8"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">グループ</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">代表的な関数</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">役割</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="33.0" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ログ・時刻</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">log / warn / err / diag / to_jst_display_time</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">出力整形と UTC→JST 変換</t>
         </is>
       </c>
     </row>
     <row r="61" ht="33.0" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">ログ・時刻</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">log / warn / err / diag / to_jst_display_time</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出力整形と UTC→JST 変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="66.0" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">引数処理</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">append_services / need_value / validate_positive_integer</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カンマ区切り分割、値欠落検出、数値検証</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="49.5" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">append_services / need_value / validate_positive_integer / validate_non_negative_integer</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カンマ区切り分割、値欠落検出、数値検証 (ビルド監視の各値は 0 を許す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="49.5" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Compose 操作</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose_container_ids / compose_logs / compose_started_services</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対象サービスの ID・ログ・サービス名取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="33.0" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
         </is>
       </c>
     </row>
     <row r="64" ht="33.0" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログ表示</t>
+          <t xml:space="preserve">起動確認</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
+          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">行数制御と重要ログの色分け</t>
+          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
         </is>
       </c>
     </row>
     <row r="65" ht="33.0" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL 確認</t>
+          <t xml:space="preserve">ログ表示</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">verify_url / show_url_body</t>
+          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl のリトライと応答本文表示</t>
+          <t xml:space="preserve">行数制御と重要ログの色分け</t>
         </is>
       </c>
     </row>
     <row r="66" ht="33.0" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">URL 確認</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verify_url / show_url_body</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curl のリトライと応答本文表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="33.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">情報表示</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">show_verified_container_envs / ..._directory_trees / ..._deployment_structures</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="66.0" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
+    <row r="68" ht="66.0" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM / OTel</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">show_verified_container_jvm_parameters / ..._otel_settings / collect_container_java_processes / classify_jvm_option / is_otel_jvm_option</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Java プロセスの検出、JVM オプションの分類、OpenTelemetry 設定の集約</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="33.0" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">対話操作</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bash / HTTP / logs モード</t>
         </is>
       </c>
     </row>
     <row r="69" ht="33.0" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck</t>
+          <t xml:space="preserve">対話操作</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
+          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
+          <t xml:space="preserve">bash / HTTP / logs モード</t>
         </is>
       </c>
     </row>
     <row r="70" ht="33.0" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">可観測性</t>
+          <t xml:space="preserve">healthcheck</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
         </is>
       </c>
     </row>
     <row r="71" ht="33.0" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">可観測性</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="33.0" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">クリーンアップ</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cleanup_all_docker_data / teardown_container / cleanup_copied_files</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 全体削除と通常後始末</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="66.0" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cwagent 送信検証</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="66.0" customHeight="1">
+    <row r="73" ht="82.5" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent ロググループ準備</t>
+          <t xml:space="preserve">ビルド監視</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepare_cwagent_log_groups / cwagent_ensure_log_groups / cwagent_resolve_delivery_target</t>
+          <t xml:space="preserve">run_build_with_watchdog / build_watchdog_reader / build_watchdog_monitor / diagnose_build_stall / build_phase_from_line / check_build_disk_space</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの log_group_name が実 CloudWatch Logs に無ければ作成</t>
+          <t xml:space="preserve">exporting layers などで出力が途切れたときの進捗表示・停滞診断・上限時間での中断</t>
         </is>
       </c>
     </row>
     <row r="74" ht="66.0" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析</t>
+          <t xml:space="preserve">cwagent 送信検証</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyze_war_deploy_exceptions / collect_deploy_exception_logs / resolve_deploy_exception_excel_path / show_war_deploy_exception_analysis / append_deploy_exception_report</t>
+          <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、画面表示と Excel 出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="33.0" customHeight="1">
+          <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="66.0" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">レポート</t>
+          <t xml:space="preserve">cwagent ロググループ準備</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">write_build_report / append_compose_service_logs_report / append_jboss_password_report / append_cwagent_report / append_deploy_exception_report</t>
+          <t xml:space="preserve">prepare_cwagent_log_groups / cwagent_ensure_log_groups / cwagent_resolve_delivery_target</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの生成</t>
+          <t xml:space="preserve">設定ファイルの log_group_name が実 CloudWatch Logs に無ければ作成</t>
         </is>
       </c>
     </row>
     <row r="76" ht="66.0" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Java 例外解析</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analyze_war_deploy_exceptions / collect_deploy_exception_logs / resolve_deploy_exception_excel_path / show_war_deploy_exception_analysis / append_deploy_exception_report</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、画面表示と Excel 出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="33.0" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">レポート</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">write_build_report / append_compose_service_logs_report / append_jboss_password_report / append_cwagent_report / append_deploy_exception_report</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートの生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="66.0" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">パスワード伝搬検証</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">verify_jboss_password_host_stages / verify_jboss_password_build_secret / verify_jboss_password_container_stages / jboss_xml_attributes / jboss_xml_unescape / jboss_wildfly_literal</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">各段の値の取得、XML と WildFly 式のエスケープ解除、原本との突き合わせ</t>
         </is>
       </c>
-    </row>
-    <row r="77" ht="19.5" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
-        </is>
-      </c>
-      <c r="B77" s="8"/>
-    </row>
-    <row r="78" ht="19.5" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">処理のどの経路 (成功・失敗・中断) でも、次の順で実行されます。</t>
-        </is>
-      </c>
-      <c r="B78" s="3"/>
     </row>
     <row r="79" ht="19.5" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
@@ -1537,8 +1555,24 @@
       </c>
       <c r="B79" s="8"/>
     </row>
-    <row r="80" ht="214.5" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
+    <row r="80" ht="19.5" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">処理のどの経路 (成功・失敗・中断) でも、次の順で実行されます。</t>
+        </is>
+      </c>
+      <c r="B80" s="3"/>
+    </row>
+    <row r="81" ht="19.5" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
+        </is>
+      </c>
+      <c r="B81" s="8"/>
+    </row>
+    <row r="82" ht="214.5" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1. analyze_war_deploy_exceptions … デプロイ処理の Java 例外を解析 (削除より前・レポートより前)
                                    成功経路で実行済みなら何もしない
@@ -1555,70 +1589,70 @@
 8. 一時ファイル削除          … Java 例外解析結果・URL 応答本文・HTTP ボディ・healthcheck 診断</t>
         </is>
       </c>
-      <c r="B80" s="6"/>
-    </row>
-    <row r="81" ht="19.5" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="B82" s="6"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B81" s="8"/>
-    </row>
-    <row r="82" ht="33.0" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="B83" s="8"/>
+    </row>
+    <row r="84" ht="33.0" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">終了コードは、本処理が既に失敗していれば元の終了コードを優先します。
 成功していた場合は、後始末の結果 (レポート保存失敗やクリーンアップ未承認なら 1) を返します。</t>
         </is>
       </c>
-      <c r="B82" s="3"/>
-    </row>
-    <row r="83" ht="19.5" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" ht="19.5" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B83" s="8"/>
-    </row>
-    <row r="84" ht="19.5" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="B85" s="8"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B84" s="3"/>
-    </row>
-    <row r="85" ht="9.0" customHeight="1">
-      <c r="A85" s="0"/>
-    </row>
-    <row r="86" ht="24.0" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="B86" s="3"/>
+    </row>
+    <row r="87" ht="9.0" customHeight="1">
+      <c r="A87" s="0"/>
+    </row>
+    <row r="88" ht="24.0" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">3. 処理の流れ</t>
         </is>
       </c>
-      <c r="B86" s="5"/>
-    </row>
-    <row r="87" ht="19.5" customHeight="1">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="B88" s="5"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B87" s="8"/>
-    </row>
-    <row r="88" ht="19.5" customHeight="1">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="B89" s="8"/>
+    </row>
+    <row r="90" ht="19.5" customHeight="1">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B88" s="8"/>
-    </row>
-    <row r="89" ht="99.0" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="B90" s="8"/>
+    </row>
+    <row r="91" ht="99.0" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時は、EXIT の後始末でレポートのログ本文を集める直前に
 compose stop (SIGTERM) を挟みます (3.6 参照)。
@@ -1628,22 +1662,6 @@
 必ず実行します** (6.7 参照)。</t>
         </is>
       </c>
-      <c r="B89" s="3"/>
-    </row>
-    <row r="90" ht="19.5" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
-        </is>
-      </c>
-      <c r="B90" s="8"/>
-    </row>
-    <row r="91" ht="19.5" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--compose-service の指定数によってビルド戦略が変わります。</t>
-        </is>
-      </c>
       <c r="B91" s="3"/>
     </row>
     <row r="92" ht="19.5" customHeight="1">
@@ -1655,145 +1673,145 @@
       <c r="B92" s="8"/>
     </row>
     <row r="93" ht="19.5" customHeight="1">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--compose-service の指定数によってビルド戦略が変わります。</t>
+        </is>
+      </c>
+      <c r="B93" s="3"/>
+    </row>
+    <row r="94" ht="19.5" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B94" s="8"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">指定</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">動作</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="19.5" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">未指定</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全サービスを 1 回の compose build でビルド</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="19.5" customHeight="1">
-      <c r="A95" s="11" t="inlineStr">
+    <row r="97" ht="19.5" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1 個</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そのサービスのみビルド</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="33.0" customHeight="1">
-      <c r="A96" s="11" t="inlineStr">
+    <row r="98" ht="33.0" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2 個以上</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">第 1 フェーズ: base サービスを単独で先行ビルド → ローカルイメージ確認 → 第 2 フェーズ: base 以外をまとめて並列ビルド</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="19.5" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
+    <row r="99" ht="19.5" customHeight="1">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B97" s="8"/>
-    </row>
-    <row r="98" ht="33.0" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="B99" s="8"/>
+    </row>
+    <row r="100" ht="33.0" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2 段階に分けるのは、ベースイメージを参照するサービスが base の完成前にビルドを始めるのを
 防ぐためです。並列オプションは compose のバージョンによって使い分けます。</t>
         </is>
       </c>
-      <c r="B98" s="3"/>
-    </row>
-    <row r="99" ht="19.5" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="B100" s="3"/>
+    </row>
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B99" s="8"/>
-    </row>
-    <row r="100" ht="19.5" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="B101" s="8"/>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">compose</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">並列指定</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="19.5" customHeight="1">
-      <c r="A101" s="11" t="inlineStr">
+    <row r="103" ht="19.5" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">v2 (docker compose)</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">グローバルオプション --parallel &lt;サービス数&gt;</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="19.5" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
+    <row r="104" ht="19.5" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">v1 (docker-compose)</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build --parallel (未対応版は exit 1)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="19.5" customHeight="1">
-      <c r="A103" s="8" t="inlineStr">
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B103" s="8"/>
-    </row>
-    <row r="104" ht="33.0" customHeight="1">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="B105" s="8"/>
+    </row>
+    <row r="106" ht="33.0" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド後は docker image inspect でローカルイメージを確認し、
 image=... id=... created=... size=... bytes を JST 表記でログに残します。</t>
         </is>
       </c>
-      <c r="B104" s="3"/>
-    </row>
-    <row r="105" ht="19.5" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
-        </is>
-      </c>
-      <c r="B105" s="8"/>
-    </row>
-    <row r="106" ht="19.5" customHeight="1">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルドの前後では、ディスク使用量を抑えるために次を行います (5.8-2 参照)。</t>
-        </is>
-      </c>
       <c r="B106" s="3"/>
     </row>
     <row r="107" ht="19.5" customHeight="1">
@@ -1805,71 +1823,116 @@
       <c r="B107" s="8"/>
     </row>
     <row r="108" ht="19.5" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルドの前後では、ディスク使用量を抑えるために次を行います (5.8-2 参照)。</t>
+        </is>
+      </c>
+      <c r="B108" s="3"/>
+    </row>
+    <row r="109" ht="19.5" customHeight="1">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B109" s="8"/>
+    </row>
+    <row r="110" ht="19.5" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">タイミング</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="19.5" customHeight="1">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="19.5" customHeight="1">
-      <c r="A110" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
         </is>
       </c>
     </row>
     <row r="111" ht="19.5" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="19.5" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data root の空き容量を確認し、5 GiB 未満なら警告する (5.2-2 参照)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="19.5" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">ローカルイメージ確認の直後</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ID が変わっていれば、タグを失った旧世代イメージを削除する</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="19.5" customHeight="1">
-      <c r="A112" s="8" t="inlineStr">
+    <row r="115" ht="19.5" customHeight="1">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B115" s="8"/>
+    </row>
+    <row r="116" ht="33.0" customHeight="1">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド自体は監視プロセス付きで実行し、exporting to image / exporting layers で
+出力が途切れても状況が分かるようにします (5.2-2 参照)。</t>
+        </is>
+      </c>
+      <c r="B116" s="3"/>
+    </row>
+    <row r="117" ht="19.5" customHeight="1">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B112" s="8"/>
-    </row>
-    <row r="113" ht="19.5" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
+      <c r="B117" s="8"/>
+    </row>
+    <row r="118" ht="19.5" customHeight="1">
+      <c r="A118" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B113" s="8"/>
-    </row>
-    <row r="114" ht="99.0" customHeight="1">
-      <c r="A114" s="3" t="inlineStr">
+      <c r="B118" s="8"/>
+    </row>
+    <row r="119" ht="99.0" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・--startup-service を指定した場合は、サービスごとに個別に起動完了を判定し、
   指定した全サービスの完了をもって成功とします
@@ -1879,35 +1942,35 @@
 ・失敗時は --suppress-startup-logs を指定していてもログを表示します (原因を隠さないため)</t>
         </is>
       </c>
-      <c r="B114" s="3"/>
-    </row>
-    <row r="115" ht="19.5" customHeight="1">
-      <c r="A115" s="8" t="inlineStr">
+      <c r="B119" s="3"/>
+    </row>
+    <row r="120" ht="19.5" customHeight="1">
+      <c r="A120" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B115" s="8"/>
-    </row>
-    <row r="116" ht="33.0" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
+      <c r="B120" s="8"/>
+    </row>
+    <row r="121" ht="33.0" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">curl -s -S -m 30 -o &lt;一時ファイル&gt; -w '%{http_code}' -X &lt;URL_METHOD&gt; \
      [-k] [-H "Content-Type: &lt;URL_CONTENT_TYPE&gt;"] [--data &lt;ボディ&gt;] &lt;VERIFY_URL&gt;</t>
         </is>
       </c>
-      <c r="B116" s="6"/>
-    </row>
-    <row r="117" ht="19.5" customHeight="1">
-      <c r="A117" s="8" t="inlineStr">
+      <c r="B121" s="6"/>
+    </row>
+    <row r="122" ht="19.5" customHeight="1">
+      <c r="A122" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B117" s="8"/>
-    </row>
-    <row r="118" ht="66.0" customHeight="1">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="B122" s="8"/>
+    </row>
+    <row r="123" ht="66.0" customHeight="1">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・期待ステータス (--expect-status) と一致するまで --url-interval 秒間隔でリトライ
 ・--url-timeout 秒を超えると失敗 (最後の応答コードを表示)
@@ -1915,121 +1978,121 @@
 ・成功・失敗いずれの場合も、応答本文の先頭 20 行を表示</t>
         </is>
       </c>
-      <c r="B118" s="3"/>
-    </row>
-    <row r="119" ht="19.5" customHeight="1">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="B123" s="3"/>
+    </row>
+    <row r="124" ht="19.5" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B119" s="8"/>
-    </row>
-    <row r="120" ht="33.0" customHeight="1">
-      <c r="A120" s="3" t="inlineStr">
+      <c r="B124" s="8"/>
+    </row>
+    <row r="125" ht="33.0" customHeight="1">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup を付けず --verify-url のみを指定した場合もコンテナは起動します
 (起動完了のログ確認は行わず、URL のリトライで readiness を担保します)。</t>
         </is>
       </c>
-      <c r="B120" s="3"/>
-    </row>
-    <row r="121" ht="19.5" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" ht="19.5" customHeight="1">
+      <c r="A126" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B121" s="8"/>
-    </row>
-    <row r="122" ht="19.5" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="B126" s="8"/>
+    </row>
+    <row r="127" ht="19.5" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">状況</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの扱い</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="19.5" customHeight="1">
-      <c r="A123" s="11" t="inlineStr">
+    <row r="128" ht="19.5" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">通常</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B128" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down で停止・削除</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="33.0" customHeight="1">
-      <c r="A124" s="11" t="inlineStr">
+    <row r="129" ht="33.0" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--keep-container / --keep-container-mode 指定</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="19.5" customHeight="1">
-      <c r="A125" s="11" t="inlineStr">
+    <row r="130" ht="19.5" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="19.5" customHeight="1">
-      <c r="A126" s="11" t="inlineStr">
+    <row r="131" ht="19.5" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="19.5" customHeight="1">
-      <c r="A127" s="8" t="inlineStr">
+    <row r="132" ht="19.5" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B127" s="8"/>
-    </row>
-    <row r="128" ht="49.5" customHeight="1">
-      <c r="A128" s="3" t="inlineStr">
+      <c r="B132" s="8"/>
+    </row>
+    <row r="133" ht="49.5" customHeight="1">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの削除後に、--prune-build-cache / --prune-build-cache-keep 指定時はビルド
 キャッシュを削除し、--disk-usage-report 指定時は終了時の使用量と実行前からの増減を
 表示します (5.8-2 参照)。</t>
         </is>
       </c>
-      <c r="B128" s="3"/>
-    </row>
-    <row r="129" ht="19.5" customHeight="1">
-      <c r="A129" s="8" t="inlineStr">
+      <c r="B133" s="3"/>
+    </row>
+    <row r="134" ht="19.5" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B129" s="8"/>
-    </row>
-    <row r="130" ht="66.0" customHeight="1">
-      <c r="A130" s="3" t="inlineStr">
+      <c r="B134" s="8"/>
+    </row>
+    <row r="135" ht="66.0" customHeight="1">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS はタスク停止時に各コンテナへ SIGTERM を送るため、adot collector のような
 サイドカーは「シグナル受信 → パイプラインの graceful shutdown → 終了」までを
@@ -2037,34 +2100,34 @@
 誰にも取得されないままコンテナごと削除されてしまいます。</t>
         </is>
       </c>
-      <c r="B130" s="3"/>
-    </row>
-    <row r="131" ht="19.5" customHeight="1">
-      <c r="A131" s="8" t="inlineStr">
+      <c r="B135" s="3"/>
+    </row>
+    <row r="136" ht="19.5" customHeight="1">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B131" s="8"/>
-    </row>
-    <row r="132" ht="19.5" customHeight="1">
-      <c r="A132" s="3" t="inlineStr">
+      <c r="B136" s="8"/>
+    </row>
+    <row r="137" ht="19.5" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そこでエラー終了時に限り、削除の前に SIGTERM による停止を挟みます。</t>
         </is>
       </c>
-      <c r="B132" s="3"/>
-    </row>
-    <row r="133" ht="19.5" customHeight="1">
-      <c r="A133" s="8" t="inlineStr">
+      <c r="B137" s="3"/>
+    </row>
+    <row r="138" ht="19.5" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B133" s="8"/>
-    </row>
-    <row r="134" ht="148.5" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
+      <c r="B138" s="8"/>
+    </row>
+    <row r="139" ht="148.5" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">[2] 〜 [6] の収集 (起動中のコンテナが必要)
         ↓
@@ -2077,18 +2140,18 @@
 compose down (削除)</t>
         </is>
       </c>
-      <c r="B134" s="6"/>
-    </row>
-    <row r="135" ht="19.5" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+      <c r="B139" s="6"/>
+    </row>
+    <row r="140" ht="19.5" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B135" s="8"/>
-    </row>
-    <row r="136" ht="165.0" customHeight="1">
-      <c r="A136" s="3" t="inlineStr">
+      <c r="B140" s="8"/>
+    </row>
+    <row r="141" ht="165.0" customHeight="1">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・対象は compose ps --services が返す稼働中の全サービスです
   (起動確認対象だけでなく adot collector などのサイドカーも含みます)
@@ -2102,437 +2165,437 @@
   従来どおり compose down でまとめて削除します</t>
         </is>
       </c>
-      <c r="B136" s="3"/>
-    </row>
-    <row r="137" ht="19.5" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+      <c r="B141" s="3"/>
+    </row>
+    <row r="142" ht="19.5" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B137" s="8"/>
-    </row>
-    <row r="138" ht="49.5" customHeight="1">
-      <c r="A138" s="3" t="inlineStr">
+      <c r="B142" s="8"/>
+    </row>
+    <row r="143" ht="49.5" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">adot collector の healthcheck が失敗し、depends_on の condition: service_healthy
 を満たせずバックエンドが起動しなかった場合、ECS 上でも同じくタスクが停止します。
 その終了処理まで含めてローカルで再現・確認できるようにするのがこの動作の狙いです。</t>
         </is>
       </c>
-      <c r="B138" s="3"/>
-    </row>
-    <row r="139" ht="19.5" customHeight="1">
-      <c r="A139" s="8" t="inlineStr">
+      <c r="B143" s="3"/>
+    </row>
+    <row r="144" ht="19.5" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B139" s="8"/>
-    </row>
-    <row r="140" ht="19.5" customHeight="1">
-      <c r="A140" s="3" t="inlineStr">
+      <c r="B144" s="8"/>
+    </row>
+    <row r="145" ht="19.5" customHeight="1">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B140" s="3"/>
-    </row>
-    <row r="141" ht="9.0" customHeight="1">
-      <c r="A141" s="0"/>
-    </row>
-    <row r="142" ht="24.0" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
+      <c r="B145" s="3"/>
+    </row>
+    <row r="146" ht="9.0" customHeight="1">
+      <c r="A146" s="0"/>
+    </row>
+    <row r="147" ht="24.0" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">5. 終了コード</t>
         </is>
       </c>
-      <c r="B142" s="5"/>
-    </row>
-    <row r="143" ht="19.5" customHeight="1">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="B147" s="5"/>
+    </row>
+    <row r="148" ht="19.5" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コード</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">意味</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">主な発生条件</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="33.0" customHeight="1">
-      <c r="A144" s="11" t="inlineStr">
+    <row r="149" ht="33.0" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B149" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">正常終了</t>
         </is>
       </c>
-      <c r="C144" s="3" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド (と指定した確認) がすべて成功</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="346.5" customHeight="1">
-      <c r="A145" s="11" t="inlineStr">
+    <row r="150" ht="379.5" customHeight="1">
+      <c r="A150" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B145" s="3" t="inlineStr">
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行時エラー</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="379.5" customHeight="1">
-      <c r="A146" s="11" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="409.0" customHeight="1">
+      <c r="A151" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B146" s="3" t="inlineStr">
+      <c r="B151" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数エラー</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="19.5" customHeight="1">
-      <c r="A147" s="3" t="inlineStr">
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="19.5" customHeight="1">
+      <c r="A152" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">本処理が失敗している場合は、後始末の結果にかかわらず元の終了コードが優先されます。</t>
         </is>
       </c>
-      <c r="B147" s="3"/>
-    </row>
-    <row r="148" ht="19.5" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
+      <c r="B152" s="3"/>
+    </row>
+    <row r="153" ht="19.5" customHeight="1">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B148" s="3"/>
-    </row>
-    <row r="149" ht="9.0" customHeight="1">
-      <c r="A149" s="0"/>
-    </row>
-    <row r="150" ht="24.0" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
+      <c r="B153" s="3"/>
+    </row>
+    <row r="154" ht="9.0" customHeight="1">
+      <c r="A154" s="0"/>
+    </row>
+    <row r="155" ht="24.0" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">6. 環境変数</t>
         </is>
       </c>
-      <c r="B150" s="5"/>
-    </row>
-    <row r="151" ht="19.5" customHeight="1">
-      <c r="A151" s="8" t="inlineStr">
+      <c r="B155" s="5"/>
+    </row>
+    <row r="156" ht="19.5" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.1 入力として参照する環境変数》</t>
         </is>
       </c>
-      <c r="B151" s="8"/>
-    </row>
-    <row r="152" ht="19.5" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="B156" s="8"/>
+    </row>
+    <row r="157" ht="19.5" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="19.5" customHeight="1">
-      <c r="A153" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="19.5" customHeight="1">
-      <c r="A154" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="19.5" customHeight="1">
-      <c r="A155" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="19.5" customHeight="1">
-      <c r="A156" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO_COLOR</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定義されていれば色分けを無効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="19.5" customHeight="1">
-      <c r="A157" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLICOLOR_FORCE</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
         </is>
       </c>
     </row>
     <row r="158" ht="19.5" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERM</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dumb の場合は色分けしない</t>
+          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
     </row>
     <row r="159" ht="19.5" customHeight="1">
-      <c r="A159" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
-        </is>
-      </c>
-      <c r="B159" s="8"/>
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="19.5" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用途</t>
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
         </is>
       </c>
     </row>
     <row r="161" ht="19.5" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TZ</t>
+          <t xml:space="preserve">NO_COLOR</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
+          <t xml:space="preserve">定義されていれば色分けを無効化</t>
         </is>
       </c>
     </row>
     <row r="162" ht="19.5" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">CLICOLOR_FORCE</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
         </is>
       </c>
     </row>
     <row r="163" ht="19.5" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">TERM</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dumb の場合は色分けしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="19.5" customHeight="1">
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
+        </is>
+      </c>
+      <c r="B164" s="8"/>
+    </row>
+    <row r="165" ht="19.5" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用途</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="19.5" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TZ</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="19.5" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="19.5" customHeight="1">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
         </is>
       </c>
-      <c r="B163" s="3" t="inlineStr">
+      <c r="B168" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="19.5" customHeight="1">
-      <c r="A164" s="11" t="inlineStr">
+    <row r="169" ht="19.5" customHeight="1">
+      <c r="A169" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B164" s="3" t="inlineStr">
+      <c r="B169" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="19.5" customHeight="1">
-      <c r="A165" s="8" t="inlineStr">
+    <row r="170" ht="19.5" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B165" s="8"/>
-    </row>
-    <row r="166" ht="49.5" customHeight="1">
-      <c r="A166" s="3" t="inlineStr">
+      <c r="B170" s="8"/>
+    </row>
+    <row r="171" ht="49.5" customHeight="1">
+      <c r="A171" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 / 7.2 はスクリプト自身が実行ホストで参照・設定する環境変数です。
 これとは別に、起動したコンテナ内の環境変数を収集して一覧表示します
 (スクリプトの動作は変えません)。</t>
         </is>
       </c>
-      <c r="B166" s="3"/>
-    </row>
-    <row r="167" ht="19.5" customHeight="1">
-      <c r="A167" s="8" t="inlineStr">
+      <c r="B171" s="3"/>
+    </row>
+    <row r="172" ht="19.5" customHeight="1">
+      <c r="A172" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B167" s="8"/>
-    </row>
-    <row r="168" ht="19.5" customHeight="1">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="B172" s="8"/>
+    </row>
+    <row r="173" ht="19.5" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">出力先</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="33.0" customHeight="1">
-      <c r="A169" s="11" t="inlineStr">
+    <row r="174" ht="33.0" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM オプションの受け渡し</t>
         </is>
       </c>
-      <c r="B169" s="3" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
         </is>
       </c>
-      <c r="C169" s="3" t="inlineStr">
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="33.0" customHeight="1">
-      <c r="A170" s="11" t="inlineStr">
+    <row r="175" ht="33.0" customHeight="1">
+      <c r="A175" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 標準設定</t>
         </is>
       </c>
-      <c r="B170" s="3" t="inlineStr">
+      <c r="B175" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
         </is>
       </c>
-      <c r="C170" s="3" t="inlineStr">
+      <c r="C175" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="33.0" customHeight="1">
-      <c r="A171" s="11" t="inlineStr">
+    <row r="176" ht="33.0" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 関連設定</t>
         </is>
       </c>
-      <c r="B171" s="3" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS_XRAY_DAEMON_ADDRESS / AWS_XRAY_CONTEXT_MISSING / AWS_XRAY_TRACING_NAME / AWS_LAMBDA_EXEC_WRAPPER / AOT_CONFIG_CONTENT</t>
         </is>
       </c>
-      <c r="C171" s="3" t="inlineStr">
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="19.5" customHeight="1">
-      <c r="A172" s="11" t="inlineStr">
+    <row r="177" ht="19.5" customHeight="1">
+      <c r="A177" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリ構造の起点</t>
         </is>
       </c>
-      <c r="B172" s="3" t="inlineStr">
+      <c r="B177" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--deployment-dir-env で指定した名前</t>
         </is>
       </c>
-      <c r="C172" s="3" t="inlineStr">
+      <c r="C177" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="19.5" customHeight="1">
-      <c r="A173" s="8" t="inlineStr">
+    <row r="178" ht="19.5" customHeight="1">
+      <c r="A178" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B173" s="8"/>
-    </row>
-    <row r="174" ht="19.5" customHeight="1">
-      <c r="A174" s="3" t="inlineStr">
+      <c r="B178" s="8"/>
+    </row>
+    <row r="179" ht="19.5" customHeight="1">
+      <c r="A179" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B174" s="3"/>
+      <c r="B179" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="75">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
@@ -2547,33 +2610,30 @@
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A83:B83"/>
     <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A85:B85"/>
     <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A87:B87"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="A90:B90"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="A94:B94"/>
     <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A101:B101"/>
     <mergeCell ref="A105:B105"/>
     <mergeCell ref="A106:B106"/>
     <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A112:B112"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A109:B109"/>
     <mergeCell ref="A115:B115"/>
     <mergeCell ref="A116:B116"/>
     <mergeCell ref="A117:B117"/>
@@ -2581,11 +2641,11 @@
     <mergeCell ref="A119:B119"/>
     <mergeCell ref="A120:B120"/>
     <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="A130:B130"/>
-    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A125:B125"/>
+    <mergeCell ref="A126:B126"/>
     <mergeCell ref="A132:B132"/>
     <mergeCell ref="A133:B133"/>
     <mergeCell ref="A134:B134"/>
@@ -2595,17 +2655,22 @@
     <mergeCell ref="A138:B138"/>
     <mergeCell ref="A139:B139"/>
     <mergeCell ref="A140:B140"/>
+    <mergeCell ref="A141:B141"/>
     <mergeCell ref="A142:B142"/>
+    <mergeCell ref="A143:B143"/>
+    <mergeCell ref="A144:B144"/>
+    <mergeCell ref="A145:B145"/>
     <mergeCell ref="A147:B147"/>
-    <mergeCell ref="A148:B148"/>
-    <mergeCell ref="A150:B150"/>
-    <mergeCell ref="A151:B151"/>
-    <mergeCell ref="A159:B159"/>
-    <mergeCell ref="A165:B165"/>
-    <mergeCell ref="A166:B166"/>
-    <mergeCell ref="A167:B167"/>
-    <mergeCell ref="A173:B173"/>
-    <mergeCell ref="A174:B174"/>
+    <mergeCell ref="A152:B152"/>
+    <mergeCell ref="A153:B153"/>
+    <mergeCell ref="A155:B155"/>
+    <mergeCell ref="A156:B156"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="A170:B170"/>
+    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="A172:B172"/>
+    <mergeCell ref="A178:B178"/>
+    <mergeCell ref="A179:B179"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2810,7 +2875,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19.5" customHeight="1">
+    <row r="9" ht="33.0" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
@@ -2818,27 +2883,27 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--dry-run</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド/起動/URL 呼び出し/ファイル操作を行わずプレビュー</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
@@ -2850,171 +2915,187 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="33.0" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--build-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (無制限)</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="33.0" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-build-watchdog</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の監視をすべて行わない。監視が有効な間は BUILDKIT_PROGRESS=tty を plain へ切り替えるため、tty 形式を使いたい場合に指定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--dry-run</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド/起動/URL 呼び出し/ファイル操作を行わずプレビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="33.0" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">可</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド前にコピーし、終了後に自動削除。コピー先に同名ファイルがあれば強制上書きし、終了時に上書き前のファイルへ復元</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--copy-file-no-overwrite</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--copy-file のコピー先に同名ファイルがあれば上書きせず中止 (exit 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="49.5" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-param NAME</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SSM パラメータ名</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パラメータストアから取得。このとき AWS 認証が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="49.5" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password VALUE</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パスワード文字列</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="49.5" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
-        </is>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="49.5" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">シークレット id</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jboss_master_password</t>
-        </is>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
@@ -3026,135 +3107,135 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--region REGION</t>
+          <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS リージョン名</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+          <t xml:space="preserve">SSM パラメータ名</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="33.0" customHeight="1">
+          <t xml:space="preserve">パラメータストアから取得。このとき AWS 認証が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="49.5" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-jboss-password</t>
+          <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
+          <t xml:space="preserve">パスワード文字列</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="33.0" customHeight="1">
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="49.5" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-mask</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="33.0" customHeight="1">
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="49.5" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">シークレット id</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33.0" customHeight="1">
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="49.5" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">AWS リージョン名</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
@@ -3166,23 +3247,23 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--verify-jboss-password</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
         </is>
       </c>
     </row>
@@ -3194,119 +3275,119 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--jboss-password-mask</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="33.0" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33.0" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-verify-cwagent</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証を行わない</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="25" ht="33.0" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3316,13 +3397,13 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -3334,12 +3415,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">列挙</t>
+          <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -3350,7 +3431,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3443,7 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-report</t>
+          <t xml:space="preserve">--no-verify-cwagent</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3372,13 +3453,13 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
+          <t xml:space="preserve">検証を行わない</t>
         </is>
       </c>
     </row>
@@ -3390,23 +3471,23 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-delivery-report</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達レポートを行わない (既定)</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -3418,23 +3499,23 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -3446,23 +3527,23 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">列挙</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -3474,27 +3555,27 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="49.5" customHeight="1">
+          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="33.0" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
@@ -3502,23 +3583,23 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--no-cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">送達レポートを行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -3530,23 +3611,23 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-required</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -3558,23 +3639,23 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -3586,151 +3667,135 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="33.0" customHeight="1">
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="49.5" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-startup</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+        </is>
+      </c>
+      <c r="E37" s="7"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
     <row r="38" ht="33.0" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-required</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(対象全体)</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E38" s="7"/>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
         </is>
       </c>
     </row>
     <row r="39" ht="33.0" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">拡張正規表現</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E39" s="7"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="33.0" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--no-cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E40" s="7"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
         </is>
       </c>
     </row>
@@ -3742,27 +3807,27 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--verify-startup</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
         </is>
       </c>
     </row>
@@ -3774,27 +3839,27 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -3806,27 +3871,27 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-healthy</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">拡張正規表現</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3903,7 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3848,7 +3913,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -3858,7 +3923,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -3870,27 +3935,27 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--allow-service-exit NAME</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -3902,27 +3967,27 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -3934,27 +3999,27 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--wait-healthy</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
         </is>
       </c>
     </row>
@@ -3966,27 +4031,27 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -3998,27 +4063,27 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--allow-service-exit NAME</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
         </is>
       </c>
     </row>
@@ -4030,139 +4095,155 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--suppress-startup-logs</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="33.0" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="33.0" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="33.0" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="33.0" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E51" s="7"/>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E52" s="7"/>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E53" s="7"/>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIME タイプ</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E54" s="7"/>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4255,12 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON 文字列</t>
+          <t xml:space="preserve">URL</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -4190,7 +4271,7 @@
       <c r="E55" s="7"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -4202,23 +4283,23 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -4230,23 +4311,23 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP メソッド</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -4258,23 +4339,23 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">MIME タイプ</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E58" s="7"/>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -4286,40 +4367,40 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">JSON 文字列</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E59" s="7"/>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
     <row r="60" ht="19.5" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
+          <t xml:space="preserve">key=value&amp;...</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -4330,75 +4411,75 @@
       <c r="E60" s="7"/>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="19.5" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="33.0" customHeight="1">
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4414,191 +4495,175 @@
       <c r="E63" s="7"/>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="33.0" customHeight="1">
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="19.5" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E64" s="7"/>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="19.5" customHeight="1">
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="33.0" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">コンテキストルートのパス</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="E65" s="7"/>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="66" ht="33.0" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E66" s="7"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
         </is>
       </c>
     </row>
     <row r="67" ht="33.0" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E67" s="7"/>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="33.0" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="33.0" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir DIR</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
@@ -4606,7 +4671,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel とテキストも同じディレクトリへ追加出力</t>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4683,17 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -4638,7 +4703,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
@@ -4650,17 +4715,17 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -4670,7 +4735,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
         </is>
       </c>
     </row>
@@ -4682,27 +4747,27 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
         </is>
       </c>
     </row>
@@ -4714,17 +4779,17 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--report-dir DIR</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -4734,103 +4799,115 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel とテキストも同じディレクトリへ追加出力</t>
         </is>
       </c>
     </row>
     <row r="74" ht="33.0" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E74" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="75" ht="33.0" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E75" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="19.5" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E76" s="7"/>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
     <row r="77" ht="33.0" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -4843,38 +4920,42 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E77" s="7"/>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="78" ht="33.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -4886,115 +4967,147 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="19.5" customHeight="1">
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E80" s="7"/>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="81" ht="33.0" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E81" s="7"/>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="82" ht="33.0" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="83" ht="33.0" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E83" s="7"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C84" s="3"/>
@@ -5002,12 +5115,92 @@
       <c r="E84" s="7"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="33.0" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="33.0" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="33.0" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="33.0" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F84"/>
+  <autoFilter ref="A4:F88"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -5275,132 +5468,132 @@
     <row r="19" ht="33.0" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
     <row r="20" ht="33.0" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss_master_password</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
     <row r="21" ht="33.0" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--region REGION</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+          <t xml:space="preserve">0 (無制限)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
         </is>
       </c>
     </row>
     <row r="22" ht="33.0" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
         </is>
       </c>
     </row>
     <row r="23" ht="33.0" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33.0" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
@@ -5412,83 +5605,83 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="27" ht="33.0" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="28" ht="33.0" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5693,7 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -5510,7 +5703,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -5522,17 +5715,17 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -5544,17 +5737,17 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -5566,17 +5759,17 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -5588,83 +5781,83 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="33.0" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="33.0" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="36" ht="33.0" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
@@ -5676,17 +5869,17 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -5698,17 +5891,17 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -5720,17 +5913,17 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -5742,83 +5935,83 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--startup-interval SEC</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ポーリング間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="33.0" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="33.0" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--wait-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="33.0" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -5830,17 +6023,17 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -5852,256 +6045,322 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
     <row r="46" ht="19.5" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="47" ht="19.5" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="48" ht="19.5" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--url-interval SEC</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="19.5" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="19.5" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19.5" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="33.0" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="33.0" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="33.0" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
     <row r="52" ht="33.0" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="33.0" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="33.0" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="33.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">有効</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="9.0" customHeight="1">
-      <c r="A53" s="0"/>
-    </row>
-    <row r="54" ht="24.0" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="56" ht="9.0" customHeight="1">
+      <c r="A56" s="0"/>
+    </row>
+    <row r="57" ht="24.0" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
         </is>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-    </row>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" ht="19.5" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">記載箇所</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-    </row>
-    <row r="56" ht="33.0" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-    </row>
-    <row r="57" ht="33.0" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-    </row>
-    <row r="58" ht="33.0" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
-        </is>
-      </c>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
     </row>
     <row r="59" ht="33.0" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
+    </row>
+    <row r="60" ht="33.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+        </is>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+    </row>
+    <row r="61" ht="33.0" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+    </row>
+    <row r="62" ht="33.0" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -6117,12 +6376,12 @@
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6739,6 +6998,41 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="66.0" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
+進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="33.0" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05 10:03:50</t>
+          <t xml:space="preserve">2026-08-11 11:36:52</t>
         </is>
       </c>
     </row>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11 11:36:52</t>
+          <t xml:space="preserve">2026-08-11 15:06:08</t>
         </is>
       </c>
     </row>
@@ -735,416 +735,416 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="24" ht="132.0" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析 (tmpfs / バインドマウントの要否判定と Excel / テキスト出力)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定で自動。無効化は --no-readonly-analysis。ファイル出力は --report-dir / --readonly-analysis-excel / --readonly-analysis-text 指定時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《できること》</t>
         </is>
       </c>
-      <c r="B24" s="8"/>
-    </row>
-    <row r="25" ht="33.0" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="B25" s="8"/>
+    </row>
+    <row r="26" ht="33.0" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup も --verify-url も指定しなければ、純粋にビルドのみを行って終了します
 (従来の build_and_push.sh --build-only 相当)。</t>
         </is>
       </c>
-      <c r="B25" s="3"/>
-    </row>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《行わないこと》</t>
         </is>
       </c>
-      <c r="B26" s="8"/>
-    </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="B27" s="8"/>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECR 権限チェック / ECR ログイン / タグ付け / プッシュ / imagedefinition.json の出力。</t>
         </is>
       </c>
-      <c r="B27" s="3"/>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B28" s="8"/>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="B29" s="8"/>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">前提</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">必須コマンド</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">docker、docker compose または docker-compose</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="33.0" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="32" ht="33.0" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">追加で必要</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">curl (--verify-url / --keep-container-mode http 時)、aws (--jboss-password-param 時)、Python 3 (送達診断の JSON 整形時)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS 認証</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--jboss-password-param を使う場合のみ必要 (aws login --remote 済み)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B33" s="8"/>
-    </row>
-    <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="B34" s="8"/>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B34" s="3"/>
-    </row>
-    <row r="35" ht="9.0" customHeight="1">
-      <c r="A35" s="0"/>
-    </row>
-    <row r="36" ht="24.0" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" ht="9.0" customHeight="1">
+      <c r="A36" s="0"/>
+    </row>
+    <row r="37" ht="24.0" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2. 全体構成</t>
         </is>
       </c>
-      <c r="B36" s="5"/>
-    </row>
-    <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.1 ファイル内のセクション構成》</t>
         </is>
       </c>
-      <c r="B37" s="8"/>
-    </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="B38" s="8"/>
+    </row>
+    <row r="39" ht="19.5" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">位置</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">セクション</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="33.0" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冒頭</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ヘッダーコメント</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">目的・機能一覧・使い方</t>
         </is>
       </c>
     </row>
     <row r="40" ht="33.0" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">冒頭</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘッダーコメント</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目的・機能一覧・使い方</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="33.0" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示タイムゾーン設定</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示・保存する時刻をすべて JST に固定</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="82.5" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="42" ht="82.5" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="49.5" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="43" ht="49.5" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ用ヘルパ</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / run / JST 変換ヘルパ</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="44" ht="19.5" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">usage()</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--help の本文</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="66.0" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="45" ht="66.0" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数パース</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">append_services によるカンマ区切り分割、need_value による値欠落検出</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="49.5" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="46" ht="49.5" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">入力値の検証</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">数値・モード・排他関係・サービス指定の整合性</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">依存コマンド / AWS 認証 / compose 判定</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行環境の確認</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="49.5" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="48" ht="49.5" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">シークレット準備・一時ファイルコピー</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">prepare_jboss_password / prepare_copy_files</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="82.5" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="49" ht="82.5" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">マスターパスワードの伝搬検証</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">危険文字の分析、段ごとの比較、compose.yml と standalone.xml の解析、CredentialStore の開封確認</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="49.5" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="50" ht="49.5" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">起動確認・ログ表示ヘルパ</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ取得、ANSI 除去、色分け、companion ログ</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="33.0" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="51" ht="33.0" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナ内情報の収集と整形</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="82.5" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="52" ht="82.5" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM パラメータ・OpenTelemetry 設定</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">/proc/&lt;pid&gt;/cmdline の走査、JVM オプションの分類、OpenTelemetry 設定の突き合わせ</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="66.0" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="53" ht="66.0" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対話操作</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">bash / HTTP / logs モードと、healthcheck・MySQL・可観測性の各ヘルパ</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="33.0" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="54" ht="33.0" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 完全クリーンアップ</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対象の集計、確認フレーズ、削除、検証</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="66.0" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルドの停滞検知・進捗表示</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド出力の読み手、監視プロセス、停滞診断、上限時間での中断</t>
         </is>
       </c>
     </row>
@@ -1156,503 +1156,557 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルドの停滞検知・進捗表示</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド出力の読み手、監視プロセス、停滞診断、上限時間での中断</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="66.0" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">WAR デプロイ時 Java 例外解析</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">解析ヘルパー (Python 3) の埋め込みと、ログ収集・実行・表示・レポート追記</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="57" ht="82.5" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分析ヘルパー (Python 3) の埋め込みと、compose.yml / 実行状況の収集・実行・表示・レポート追記</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="19.5" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポート</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">write_build_report</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">後始末 (cleanup_all)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">EXIT トラップ本体</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="49.5" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="60" ht="49.5" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">末尾</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">メイン処理</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド → 起動 → 起動確認 → URL 確認 → 対話 → 情報表示</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.2 主要な関数グループ》</t>
         </is>
       </c>
-      <c r="B59" s="8"/>
-    </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="B61" s="8"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">グループ</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">代表的な関数</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">役割</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="33.0" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
+    <row r="63" ht="33.0" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ・時刻</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / to_jst_display_time</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">出力整形と UTC→JST 変換</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="66.0" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+    <row r="64" ht="66.0" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">引数処理</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">append_services / need_value / validate_positive_integer / validate_non_negative_integer</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">カンマ区切り分割、値欠落検出、数値検証 (ビルド監視の各値は 0 を許す)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="49.5" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
+    <row r="65" ht="49.5" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Compose 操作</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose_container_ids / compose_logs / compose_started_services</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対象サービスの ID・ログ・サービス名取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="33.0" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="33.0" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ログ表示</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">行数制御と重要ログの色分け</t>
         </is>
       </c>
     </row>
     <row r="66" ht="33.0" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL 確認</t>
+          <t xml:space="preserve">起動確認</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">verify_url / show_url_body</t>
+          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl のリトライと応答本文表示</t>
+          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
         </is>
       </c>
     </row>
     <row r="67" ht="33.0" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">情報表示</t>
+          <t xml:space="preserve">ログ表示</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_verified_container_envs / ..._directory_trees / ..._deployment_structures</t>
+          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="66.0" customHeight="1">
+          <t xml:space="preserve">行数制御と重要ログの色分け</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="33.0" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JVM / OTel</t>
+          <t xml:space="preserve">URL 確認</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_verified_container_jvm_parameters / ..._otel_settings / collect_container_java_processes / classify_jvm_option / is_otel_jvm_option</t>
+          <t xml:space="preserve">verify_url / show_url_body</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java プロセスの検出、JVM オプションの分類、OpenTelemetry 設定の集約</t>
+          <t xml:space="preserve">curl のリトライと応答本文表示</t>
         </is>
       </c>
     </row>
     <row r="69" ht="33.0" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作</t>
+          <t xml:space="preserve">情報表示</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
+          <t xml:space="preserve">show_verified_container_envs / ..._directory_trees / ..._deployment_structures</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / HTTP / logs モード</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="33.0" customHeight="1">
+          <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="66.0" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck</t>
+          <t xml:space="preserve">JVM / OTel</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
+          <t xml:space="preserve">show_verified_container_jvm_parameters / ..._otel_settings / collect_container_java_processes / classify_jvm_option / is_otel_jvm_option</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
+          <t xml:space="preserve">Java プロセスの検出、JVM オプションの分類、OpenTelemetry 設定の集約</t>
         </is>
       </c>
     </row>
     <row r="71" ht="33.0" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">可観測性</t>
+          <t xml:space="preserve">対話操作</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+          <t xml:space="preserve">bash / HTTP / logs モード</t>
         </is>
       </c>
     </row>
     <row r="72" ht="33.0" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">healthcheck</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="33.0" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可観測性</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="33.0" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">クリーンアップ</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cleanup_all_docker_data / teardown_container / cleanup_copied_files</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 全体削除と通常後始末</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="82.5" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
+    <row r="75" ht="82.5" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド監視</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">run_build_with_watchdog / build_watchdog_reader / build_watchdog_monitor / diagnose_build_stall / build_phase_from_line / check_build_disk_space</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exporting layers などで出力が途切れたときの進捗表示・停滞診断・上限時間での中断</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="66.0" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cwagent 送信検証</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="66.0" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cwagent ロググループ準備</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prepare_cwagent_log_groups / cwagent_ensure_log_groups / cwagent_resolve_delivery_target</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">設定ファイルの log_group_name が実 CloudWatch Logs に無ければ作成</t>
         </is>
       </c>
     </row>
     <row r="76" ht="66.0" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析</t>
+          <t xml:space="preserve">cwagent 送信検証</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyze_war_deploy_exceptions / collect_deploy_exception_logs / resolve_deploy_exception_excel_path / show_war_deploy_exception_analysis / append_deploy_exception_report</t>
+          <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、画面表示と Excel 出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="33.0" customHeight="1">
+          <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="66.0" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">レポート</t>
+          <t xml:space="preserve">cwagent ロググループ準備</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">write_build_report / append_compose_service_logs_report / append_jboss_password_report / append_cwagent_report / append_deploy_exception_report</t>
+          <t xml:space="preserve">prepare_cwagent_log_groups / cwagent_ensure_log_groups / cwagent_resolve_delivery_target</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの生成</t>
+          <t xml:space="preserve">設定ファイルの log_group_name が実 CloudWatch Logs に無ければ作成</t>
         </is>
       </c>
     </row>
     <row r="78" ht="66.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Java 例外解析</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analyze_war_deploy_exceptions / collect_deploy_exception_logs / resolve_analysis_output_path / show_war_deploy_exception_analysis / append_deploy_exception_report</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、画面表示と Excel 出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="115.5" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用 FS 分析</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analyze_readonly_filesystem / readonly_collect_compose_facts / readonly_collect_runtime_facts / readonly_container_probe / show_readonly_filesystem_analysis / append_readonly_analysis_report</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose.yml の read_only / tmpfs / volumes の解析、コンテナの書き込み状況の収集、判定結果の表示と Excel / テキスト出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">レポート</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">write_build_report / append_compose_service_logs_report / append_jboss_password_report / append_cwagent_report / append_deploy_exception_report / append_readonly_analysis_report</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートの生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="66.0" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">パスワード伝搬検証</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">verify_jboss_password_host_stages / verify_jboss_password_build_secret / verify_jboss_password_container_stages / jboss_xml_attributes / jboss_xml_unescape / jboss_wildfly_literal</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">各段の値の取得、XML と WildFly 式のエスケープ解除、原本との突き合わせ</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="19.5" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B79" s="8"/>
-    </row>
-    <row r="80" ht="19.5" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="B82" s="8"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">処理のどの経路 (成功・失敗・中断) でも、次の順で実行されます。</t>
         </is>
       </c>
-      <c r="B80" s="3"/>
-    </row>
-    <row r="81" ht="19.5" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="B83" s="3"/>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B81" s="8"/>
-    </row>
-    <row r="82" ht="214.5" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="B84" s="8"/>
+    </row>
+    <row r="85" ht="264.0" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1. analyze_war_deploy_exceptions … デプロイ処理の Java 例外を解析 (削除より前・レポートより前)
                                    成功経路で実行済みなら何もしない
-2. write_build_report        … --report-dir 指定時、全量レポートを保存 (削除より前に実行)
-3. cleanup_all_docker_data   … --cleanup-all-docker-data 指定時、確認フレーズ入力後に全削除
-4. teardown_container        … compose down (--keep-container 指定時は残す)
-5. prune_build_cache         … --prune-build-cache / --prune-build-cache-keep 指定時、
+2. analyze_readonly_filesystem … read_only の書き込み先を分析 (削除より前・レポートより前)
+                                   成功経路で実行済みなら何もしない
+3. write_build_report        … --report-dir 指定時、全量レポートを保存 (削除より前に実行)
+4. cleanup_all_docker_data   … --cleanup-all-docker-data 指定時、確認フレーズ入力後に全削除
+5. teardown_container        … compose down (--keep-container 指定時は残す)
+6. prune_build_cache         … --prune-build-cache / --prune-build-cache-keep 指定時、
                                    ビルドキャッシュを削除 (コンテナ削除の後)
-6. report_disk_usage_at_exit … --disk-usage-report 指定時、終了時の使用量と増減を表示
-                                   (3 が実際に削除を行った場合は重複するため出さない)
-7. cleanup_copied_files      … --copy-file でコピーしたファイルを削除
+7. report_disk_usage_at_exit … --disk-usage-report 指定時、終了時の使用量と増減を表示
+                                   (4 が実際に削除を行った場合は重複するため出さない)
+8. cleanup_copied_files      … --copy-file でコピーしたファイルを削除
                                    (既存ファイルを強制上書きした分は削除せず、
                                     退避しておいた上書き前のファイルを復元)
-8. 一時ファイル削除          … Java 例外解析結果・URL 応答本文・HTTP ボディ・healthcheck 診断</t>
-        </is>
-      </c>
-      <c r="B82" s="6"/>
-    </row>
-    <row r="83" ht="19.5" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
+9. 一時ファイル削除          … Java 例外解析結果・読み取り専用 FS 分析結果・
+                                   URL 応答本文・HTTP ボディ・healthcheck 診断</t>
+        </is>
+      </c>
+      <c r="B85" s="6"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B83" s="8"/>
-    </row>
-    <row r="84" ht="33.0" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="B86" s="8"/>
+    </row>
+    <row r="87" ht="33.0" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">終了コードは、本処理が既に失敗していれば元の終了コードを優先します。
 成功していた場合は、後始末の結果 (レポート保存失敗やクリーンアップ未承認なら 1) を返します。</t>
         </is>
       </c>
-      <c r="B84" s="3"/>
-    </row>
-    <row r="85" ht="19.5" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="B87" s="3"/>
+    </row>
+    <row r="88" ht="19.5" customHeight="1">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B85" s="8"/>
-    </row>
-    <row r="86" ht="19.5" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="B88" s="8"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B86" s="3"/>
-    </row>
-    <row r="87" ht="9.0" customHeight="1">
-      <c r="A87" s="0"/>
-    </row>
-    <row r="88" ht="24.0" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="B89" s="3"/>
+    </row>
+    <row r="90" ht="9.0" customHeight="1">
+      <c r="A90" s="0"/>
+    </row>
+    <row r="91" ht="24.0" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">3. 処理の流れ</t>
         </is>
       </c>
-      <c r="B88" s="5"/>
-    </row>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="B91" s="5"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B89" s="8"/>
-    </row>
-    <row r="90" ht="19.5" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="B92" s="8"/>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B90" s="8"/>
-    </row>
-    <row r="91" ht="99.0" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="B93" s="8"/>
+    </row>
+    <row r="94" ht="99.0" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時は、EXIT の後始末でレポートのログ本文を集める直前に
 compose stop (SIGTERM) を挟みます (3.6 参照)。
@@ -1662,79 +1716,42 @@
 必ず実行します** (6.7 参照)。</t>
         </is>
       </c>
-      <c r="B91" s="3"/>
-    </row>
-    <row r="92" ht="19.5" customHeight="1">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="B94" s="3"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.1 全体フロー》</t>
+        </is>
+      </c>
+      <c r="B95" s="8"/>
+    </row>
+    <row r="96" ht="66.0" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析も同じタイミングで実行します。
+こちらは compose.yml の定義だけでも判定できるため、**コンテナを起動しない実行
+(ビルドのみ / ビルド失敗) でも必ず実行**し、実行状況からの根拠が無いことを
+結果へ明記します (6.8 参照)。</t>
+        </is>
+      </c>
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" ht="19.5" customHeight="1">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B92" s="8"/>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="B97" s="8"/>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--compose-service の指定数によってビルド戦略が変わります。</t>
         </is>
       </c>
-      <c r="B93" s="3"/>
-    </row>
-    <row r="94" ht="19.5" customHeight="1">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
-        </is>
-      </c>
-      <c r="B94" s="8"/>
-    </row>
-    <row r="95" ht="19.5" customHeight="1">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">指定</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">動作</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">未指定</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全サービスを 1 回の compose build でビルド</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="19.5" customHeight="1">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 個</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">そのサービスのみビルド</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="33.0" customHeight="1">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 個以上</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">第 1 フェーズ: base サービスを単独で先行ビルド → ローカルイメージ確認 → 第 2 フェーズ: base 以外をまとめて並列ビルド</t>
-        </is>
-      </c>
+      <c r="B98" s="3"/>
     </row>
     <row r="99" ht="19.5" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
@@ -1744,195 +1761,251 @@
       </c>
       <c r="B99" s="8"/>
     </row>
-    <row r="100" ht="33.0" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
+    <row r="100" ht="19.5" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">動作</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未指定</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全サービスを 1 回の compose build でビルド</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 個</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">そのサービスのみビルド</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="33.0" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 個以上</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">第 1 フェーズ: base サービスを単独で先行ビルド → ローカルイメージ確認 → 第 2 フェーズ: base 以外をまとめて並列ビルド</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="19.5" customHeight="1">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B104" s="8"/>
+    </row>
+    <row r="105" ht="33.0" customHeight="1">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2 段階に分けるのは、ベースイメージを参照するサービスが base の完成前にビルドを始めるのを
 防ぐためです。並列オプションは compose のバージョンによって使い分けます。</t>
         </is>
       </c>
-      <c r="B100" s="3"/>
-    </row>
-    <row r="101" ht="19.5" customHeight="1">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="B105" s="3"/>
+    </row>
+    <row r="106" ht="19.5" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B101" s="8"/>
-    </row>
-    <row r="102" ht="19.5" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="B106" s="8"/>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">compose</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">並列指定</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="19.5" customHeight="1">
-      <c r="A103" s="11" t="inlineStr">
+    <row r="108" ht="19.5" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">v2 (docker compose)</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">グローバルオプション --parallel &lt;サービス数&gt;</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="19.5" customHeight="1">
-      <c r="A104" s="11" t="inlineStr">
+    <row r="109" ht="19.5" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">v1 (docker-compose)</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build --parallel (未対応版は exit 1)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="19.5" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
+    <row r="110" ht="19.5" customHeight="1">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B105" s="8"/>
-    </row>
-    <row r="106" ht="33.0" customHeight="1">
-      <c r="A106" s="3" t="inlineStr">
+      <c r="B110" s="8"/>
+    </row>
+    <row r="111" ht="33.0" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド後は docker image inspect でローカルイメージを確認し、
 image=... id=... created=... size=... bytes を JST 表記でログに残します。</t>
         </is>
       </c>
-      <c r="B106" s="3"/>
-    </row>
-    <row r="107" ht="19.5" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="B111" s="3"/>
+    </row>
+    <row r="112" ht="19.5" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B107" s="8"/>
-    </row>
-    <row r="108" ht="19.5" customHeight="1">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="B112" s="8"/>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドの前後では、ディスク使用量を抑えるために次を行います (5.8-2 参照)。</t>
         </is>
       </c>
-      <c r="B108" s="3"/>
-    </row>
-    <row r="109" ht="19.5" customHeight="1">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="B113" s="3"/>
+    </row>
+    <row r="114" ht="19.5" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B109" s="8"/>
-    </row>
-    <row r="110" ht="19.5" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="B114" s="8"/>
+    </row>
+    <row r="115" ht="19.5" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">タイミング</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">処理</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="19.5" customHeight="1">
-      <c r="A111" s="11" t="inlineStr">
+    <row r="116" ht="19.5" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド前</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="19.5" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
+    <row r="117" ht="19.5" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド前</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">data root の空き容量を確認し、5 GiB 未満なら警告する (5.2-2 参照)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="19.5" customHeight="1">
-      <c r="A113" s="11" t="inlineStr">
+    <row r="118" ht="19.5" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド前</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="19.5" customHeight="1">
-      <c r="A114" s="11" t="inlineStr">
+    <row r="119" ht="19.5" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ローカルイメージ確認の直後</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ID が変わっていれば、タグを失った旧世代イメージを削除する</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="19.5" customHeight="1">
-      <c r="A115" s="8" t="inlineStr">
+    <row r="120" ht="19.5" customHeight="1">
+      <c r="A120" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B115" s="8"/>
-    </row>
-    <row r="116" ht="33.0" customHeight="1">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="B120" s="8"/>
+    </row>
+    <row r="121" ht="33.0" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド自体は監視プロセス付きで実行し、exporting to image / exporting layers で
 出力が途切れても状況が分かるようにします (5.2-2 参照)。</t>
         </is>
       </c>
-      <c r="B116" s="3"/>
-    </row>
-    <row r="117" ht="19.5" customHeight="1">
-      <c r="A117" s="8" t="inlineStr">
+      <c r="B121" s="3"/>
+    </row>
+    <row r="122" ht="19.5" customHeight="1">
+      <c r="A122" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B117" s="8"/>
-    </row>
-    <row r="118" ht="19.5" customHeight="1">
-      <c r="A118" s="8" t="inlineStr">
+      <c r="B122" s="8"/>
+    </row>
+    <row r="123" ht="19.5" customHeight="1">
+      <c r="A123" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B118" s="8"/>
-    </row>
-    <row r="119" ht="99.0" customHeight="1">
-      <c r="A119" s="3" t="inlineStr">
+      <c r="B123" s="8"/>
+    </row>
+    <row r="124" ht="99.0" customHeight="1">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・--startup-service を指定した場合は、サービスごとに個別に起動完了を判定し、
   指定した全サービスの完了をもって成功とします
@@ -1942,35 +2015,35 @@
 ・失敗時は --suppress-startup-logs を指定していてもログを表示します (原因を隠さないため)</t>
         </is>
       </c>
-      <c r="B119" s="3"/>
-    </row>
-    <row r="120" ht="19.5" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" ht="19.5" customHeight="1">
+      <c r="A125" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B120" s="8"/>
-    </row>
-    <row r="121" ht="33.0" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
+      <c r="B125" s="8"/>
+    </row>
+    <row r="126" ht="33.0" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">curl -s -S -m 30 -o &lt;一時ファイル&gt; -w '%{http_code}' -X &lt;URL_METHOD&gt; \
      [-k] [-H "Content-Type: &lt;URL_CONTENT_TYPE&gt;"] [--data &lt;ボディ&gt;] &lt;VERIFY_URL&gt;</t>
         </is>
       </c>
-      <c r="B121" s="6"/>
-    </row>
-    <row r="122" ht="19.5" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
+      <c r="B126" s="6"/>
+    </row>
+    <row r="127" ht="19.5" customHeight="1">
+      <c r="A127" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B122" s="8"/>
-    </row>
-    <row r="123" ht="66.0" customHeight="1">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="B127" s="8"/>
+    </row>
+    <row r="128" ht="66.0" customHeight="1">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・期待ステータス (--expect-status) と一致するまで --url-interval 秒間隔でリトライ
 ・--url-timeout 秒を超えると失敗 (最後の応答コードを表示)
@@ -1978,121 +2051,121 @@
 ・成功・失敗いずれの場合も、応答本文の先頭 20 行を表示</t>
         </is>
       </c>
-      <c r="B123" s="3"/>
-    </row>
-    <row r="124" ht="19.5" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
+      <c r="B128" s="3"/>
+    </row>
+    <row r="129" ht="19.5" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B124" s="8"/>
-    </row>
-    <row r="125" ht="33.0" customHeight="1">
-      <c r="A125" s="3" t="inlineStr">
+      <c r="B129" s="8"/>
+    </row>
+    <row r="130" ht="33.0" customHeight="1">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup を付けず --verify-url のみを指定した場合もコンテナは起動します
 (起動完了のログ確認は行わず、URL のリトライで readiness を担保します)。</t>
         </is>
       </c>
-      <c r="B125" s="3"/>
-    </row>
-    <row r="126" ht="19.5" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" ht="19.5" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B126" s="8"/>
-    </row>
-    <row r="127" ht="19.5" customHeight="1">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="B131" s="8"/>
+    </row>
+    <row r="132" ht="19.5" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">状況</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの扱い</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="19.5" customHeight="1">
-      <c r="A128" s="11" t="inlineStr">
+    <row r="133" ht="19.5" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">通常</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down で停止・削除</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="33.0" customHeight="1">
-      <c r="A129" s="11" t="inlineStr">
+    <row r="134" ht="33.0" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--keep-container / --keep-container-mode 指定</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="19.5" customHeight="1">
-      <c r="A130" s="11" t="inlineStr">
+    <row r="135" ht="19.5" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="19.5" customHeight="1">
-      <c r="A131" s="11" t="inlineStr">
+    <row r="136" ht="19.5" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="19.5" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
+    <row r="137" ht="19.5" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B132" s="8"/>
-    </row>
-    <row r="133" ht="49.5" customHeight="1">
-      <c r="A133" s="3" t="inlineStr">
+      <c r="B137" s="8"/>
+    </row>
+    <row r="138" ht="49.5" customHeight="1">
+      <c r="A138" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの削除後に、--prune-build-cache / --prune-build-cache-keep 指定時はビルド
 キャッシュを削除し、--disk-usage-report 指定時は終了時の使用量と実行前からの増減を
 表示します (5.8-2 参照)。</t>
         </is>
       </c>
-      <c r="B133" s="3"/>
-    </row>
-    <row r="134" ht="19.5" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+      <c r="B138" s="3"/>
+    </row>
+    <row r="139" ht="19.5" customHeight="1">
+      <c r="A139" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B134" s="8"/>
-    </row>
-    <row r="135" ht="66.0" customHeight="1">
-      <c r="A135" s="3" t="inlineStr">
+      <c r="B139" s="8"/>
+    </row>
+    <row r="140" ht="66.0" customHeight="1">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS はタスク停止時に各コンテナへ SIGTERM を送るため、adot collector のような
 サイドカーは「シグナル受信 → パイプラインの graceful shutdown → 終了」までを
@@ -2100,34 +2173,34 @@
 誰にも取得されないままコンテナごと削除されてしまいます。</t>
         </is>
       </c>
-      <c r="B135" s="3"/>
-    </row>
-    <row r="136" ht="19.5" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
+      <c r="B140" s="3"/>
+    </row>
+    <row r="141" ht="19.5" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B136" s="8"/>
-    </row>
-    <row r="137" ht="19.5" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
+      <c r="B141" s="8"/>
+    </row>
+    <row r="142" ht="19.5" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そこでエラー終了時に限り、削除の前に SIGTERM による停止を挟みます。</t>
         </is>
       </c>
-      <c r="B137" s="3"/>
-    </row>
-    <row r="138" ht="19.5" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
+      <c r="B142" s="3"/>
+    </row>
+    <row r="143" ht="19.5" customHeight="1">
+      <c r="A143" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B138" s="8"/>
-    </row>
-    <row r="139" ht="148.5" customHeight="1">
-      <c r="A139" s="6" t="inlineStr">
+      <c r="B143" s="8"/>
+    </row>
+    <row r="144" ht="148.5" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">[2] 〜 [6] の収集 (起動中のコンテナが必要)
         ↓
@@ -2140,18 +2213,18 @@
 compose down (削除)</t>
         </is>
       </c>
-      <c r="B139" s="6"/>
-    </row>
-    <row r="140" ht="19.5" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+      <c r="B144" s="6"/>
+    </row>
+    <row r="145" ht="19.5" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B140" s="8"/>
-    </row>
-    <row r="141" ht="165.0" customHeight="1">
-      <c r="A141" s="3" t="inlineStr">
+      <c r="B145" s="8"/>
+    </row>
+    <row r="146" ht="165.0" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・対象は compose ps --services が返す稼働中の全サービスです
   (起動確認対象だけでなく adot collector などのサイドカーも含みます)
@@ -2165,480 +2238,477 @@
   従来どおり compose down でまとめて削除します</t>
         </is>
       </c>
-      <c r="B141" s="3"/>
-    </row>
-    <row r="142" ht="19.5" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
+      <c r="B146" s="3"/>
+    </row>
+    <row r="147" ht="19.5" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B142" s="8"/>
-    </row>
-    <row r="143" ht="49.5" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
+      <c r="B147" s="8"/>
+    </row>
+    <row r="148" ht="49.5" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">adot collector の healthcheck が失敗し、depends_on の condition: service_healthy
 を満たせずバックエンドが起動しなかった場合、ECS 上でも同じくタスクが停止します。
 その終了処理まで含めてローカルで再現・確認できるようにするのがこの動作の狙いです。</t>
         </is>
       </c>
-      <c r="B143" s="3"/>
-    </row>
-    <row r="144" ht="19.5" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
+      <c r="B148" s="3"/>
+    </row>
+    <row r="149" ht="19.5" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B144" s="8"/>
-    </row>
-    <row r="145" ht="19.5" customHeight="1">
-      <c r="A145" s="3" t="inlineStr">
+      <c r="B149" s="8"/>
+    </row>
+    <row r="150" ht="19.5" customHeight="1">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B145" s="3"/>
-    </row>
-    <row r="146" ht="9.0" customHeight="1">
-      <c r="A146" s="0"/>
-    </row>
-    <row r="147" ht="24.0" customHeight="1">
-      <c r="A147" s="5" t="inlineStr">
+      <c r="B150" s="3"/>
+    </row>
+    <row r="151" ht="9.0" customHeight="1">
+      <c r="A151" s="0"/>
+    </row>
+    <row r="152" ht="24.0" customHeight="1">
+      <c r="A152" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">5. 終了コード</t>
         </is>
       </c>
-      <c r="B147" s="5"/>
-    </row>
-    <row r="148" ht="19.5" customHeight="1">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="B152" s="5"/>
+    </row>
+    <row r="153" ht="19.5" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コード</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">意味</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">主な発生条件</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="33.0" customHeight="1">
-      <c r="A149" s="11" t="inlineStr">
+    <row r="154" ht="33.0" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="B154" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">正常終了</t>
         </is>
       </c>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="C154" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド (と指定した確認) がすべて成功</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="379.5" customHeight="1">
-      <c r="A150" s="11" t="inlineStr">
+    <row r="155" ht="379.5" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B155" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行時エラー</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="409.0" customHeight="1">
-      <c r="A151" s="11" t="inlineStr">
+    <row r="156" ht="409.0" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B151" s="3" t="inlineStr">
+      <c r="B156" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数エラー</t>
         </is>
       </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="19.5" customHeight="1">
-      <c r="A152" s="3" t="inlineStr">
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="19.5" customHeight="1">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">本処理が失敗している場合は、後始末の結果にかかわらず元の終了コードが優先されます。</t>
         </is>
       </c>
-      <c r="B152" s="3"/>
-    </row>
-    <row r="153" ht="19.5" customHeight="1">
-      <c r="A153" s="3" t="inlineStr">
+      <c r="B157" s="3"/>
+    </row>
+    <row r="158" ht="19.5" customHeight="1">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B153" s="3"/>
-    </row>
-    <row r="154" ht="9.0" customHeight="1">
-      <c r="A154" s="0"/>
-    </row>
-    <row r="155" ht="24.0" customHeight="1">
-      <c r="A155" s="5" t="inlineStr">
+      <c r="B158" s="3"/>
+    </row>
+    <row r="159" ht="9.0" customHeight="1">
+      <c r="A159" s="0"/>
+    </row>
+    <row r="160" ht="24.0" customHeight="1">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">6. 環境変数</t>
         </is>
       </c>
-      <c r="B155" s="5"/>
-    </row>
-    <row r="156" ht="19.5" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
+      <c r="B160" s="5"/>
+    </row>
+    <row r="161" ht="19.5" customHeight="1">
+      <c r="A161" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.1 入力として参照する環境変数》</t>
         </is>
       </c>
-      <c r="B156" s="8"/>
-    </row>
-    <row r="157" ht="19.5" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="B161" s="8"/>
+    </row>
+    <row r="162" ht="19.5" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="19.5" customHeight="1">
-      <c r="A158" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="19.5" customHeight="1">
-      <c r="A159" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="19.5" customHeight="1">
-      <c r="A160" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="19.5" customHeight="1">
-      <c r="A161" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO_COLOR</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定義されていれば色分けを無効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="19.5" customHeight="1">
-      <c r="A162" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLICOLOR_FORCE</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
         </is>
       </c>
     </row>
     <row r="163" ht="19.5" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERM</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dumb の場合は色分けしない</t>
+          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
     </row>
     <row r="164" ht="19.5" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
-        </is>
-      </c>
-      <c r="B164" s="8"/>
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="19.5" customHeight="1">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用途</t>
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
         </is>
       </c>
     </row>
     <row r="166" ht="19.5" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TZ</t>
+          <t xml:space="preserve">NO_COLOR</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
+          <t xml:space="preserve">定義されていれば色分けを無効化</t>
         </is>
       </c>
     </row>
     <row r="167" ht="19.5" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">CLICOLOR_FORCE</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
         </is>
       </c>
     </row>
     <row r="168" ht="19.5" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">TERM</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dumb の場合は色分けしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="19.5" customHeight="1">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
+        </is>
+      </c>
+      <c r="B169" s="8"/>
+    </row>
+    <row r="170" ht="19.5" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用途</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="19.5" customHeight="1">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TZ</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="19.5" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="19.5" customHeight="1">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B173" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="19.5" customHeight="1">
-      <c r="A169" s="11" t="inlineStr">
+    <row r="174" ht="19.5" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B169" s="3" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="19.5" customHeight="1">
-      <c r="A170" s="8" t="inlineStr">
+    <row r="175" ht="19.5" customHeight="1">
+      <c r="A175" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B170" s="8"/>
-    </row>
-    <row r="171" ht="49.5" customHeight="1">
-      <c r="A171" s="3" t="inlineStr">
+      <c r="B175" s="8"/>
+    </row>
+    <row r="176" ht="49.5" customHeight="1">
+      <c r="A176" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 / 7.2 はスクリプト自身が実行ホストで参照・設定する環境変数です。
 これとは別に、起動したコンテナ内の環境変数を収集して一覧表示します
 (スクリプトの動作は変えません)。</t>
         </is>
       </c>
-      <c r="B171" s="3"/>
-    </row>
-    <row r="172" ht="19.5" customHeight="1">
-      <c r="A172" s="8" t="inlineStr">
+      <c r="B176" s="3"/>
+    </row>
+    <row r="177" ht="19.5" customHeight="1">
+      <c r="A177" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B172" s="8"/>
-    </row>
-    <row r="173" ht="19.5" customHeight="1">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="B177" s="8"/>
+    </row>
+    <row r="178" ht="19.5" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">出力先</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="33.0" customHeight="1">
-      <c r="A174" s="11" t="inlineStr">
+    <row r="179" ht="33.0" customHeight="1">
+      <c r="A179" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM オプションの受け渡し</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr">
+      <c r="B179" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
         </is>
       </c>
-      <c r="C174" s="3" t="inlineStr">
+      <c r="C179" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="33.0" customHeight="1">
-      <c r="A175" s="11" t="inlineStr">
+    <row r="180" ht="33.0" customHeight="1">
+      <c r="A180" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 標準設定</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B180" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
         </is>
       </c>
-      <c r="C175" s="3" t="inlineStr">
+      <c r="C180" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="33.0" customHeight="1">
-      <c r="A176" s="11" t="inlineStr">
+    <row r="181" ht="33.0" customHeight="1">
+      <c r="A181" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 関連設定</t>
         </is>
       </c>
-      <c r="B176" s="3" t="inlineStr">
+      <c r="B181" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS_XRAY_DAEMON_ADDRESS / AWS_XRAY_CONTEXT_MISSING / AWS_XRAY_TRACING_NAME / AWS_LAMBDA_EXEC_WRAPPER / AOT_CONFIG_CONTENT</t>
         </is>
       </c>
-      <c r="C176" s="3" t="inlineStr">
+      <c r="C181" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="19.5" customHeight="1">
-      <c r="A177" s="11" t="inlineStr">
+    <row r="182" ht="19.5" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリ構造の起点</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--deployment-dir-env で指定した名前</t>
         </is>
       </c>
-      <c r="C177" s="3" t="inlineStr">
+      <c r="C182" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="19.5" customHeight="1">
-      <c r="A178" s="8" t="inlineStr">
+    <row r="183" ht="19.5" customHeight="1">
+      <c r="A183" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B178" s="8"/>
-    </row>
-    <row r="179" ht="19.5" customHeight="1">
-      <c r="A179" s="3" t="inlineStr">
+      <c r="B183" s="8"/>
+    </row>
+    <row r="184" ht="19.5" customHeight="1">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B179" s="3"/>
+      <c r="B184" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="75">
+  <mergeCells count="77">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A83:B83"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A87:B87"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A90:B90"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A93:B93"/>
     <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A98:B98"/>
     <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A104:B104"/>
     <mergeCell ref="A105:B105"/>
     <mergeCell ref="A106:B106"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A118:B118"/>
-    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="A114:B114"/>
     <mergeCell ref="A120:B120"/>
     <mergeCell ref="A121:B121"/>
     <mergeCell ref="A122:B122"/>
@@ -2646,11 +2716,11 @@
     <mergeCell ref="A124:B124"/>
     <mergeCell ref="A125:B125"/>
     <mergeCell ref="A126:B126"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A134:B134"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="A127:B127"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="A130:B130"/>
+    <mergeCell ref="A131:B131"/>
     <mergeCell ref="A137:B137"/>
     <mergeCell ref="A138:B138"/>
     <mergeCell ref="A139:B139"/>
@@ -2660,17 +2730,22 @@
     <mergeCell ref="A143:B143"/>
     <mergeCell ref="A144:B144"/>
     <mergeCell ref="A145:B145"/>
+    <mergeCell ref="A146:B146"/>
     <mergeCell ref="A147:B147"/>
+    <mergeCell ref="A148:B148"/>
+    <mergeCell ref="A149:B149"/>
+    <mergeCell ref="A150:B150"/>
     <mergeCell ref="A152:B152"/>
-    <mergeCell ref="A153:B153"/>
-    <mergeCell ref="A155:B155"/>
-    <mergeCell ref="A156:B156"/>
-    <mergeCell ref="A164:B164"/>
-    <mergeCell ref="A170:B170"/>
-    <mergeCell ref="A171:B171"/>
-    <mergeCell ref="A172:B172"/>
-    <mergeCell ref="A178:B178"/>
-    <mergeCell ref="A179:B179"/>
+    <mergeCell ref="A157:B157"/>
+    <mergeCell ref="A158:B158"/>
+    <mergeCell ref="A160:B160"/>
+    <mergeCell ref="A161:B161"/>
+    <mergeCell ref="A169:B169"/>
+    <mergeCell ref="A175:B175"/>
+    <mergeCell ref="A176:B176"/>
+    <mergeCell ref="A177:B177"/>
+    <mergeCell ref="A183:B183"/>
+    <mergeCell ref="A184:B184"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4799,7 +4874,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel とテキストも同じディレクトリへ追加出力</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
         </is>
       </c>
     </row>
@@ -4934,68 +5009,76 @@
     <row r="78" ht="33.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E78" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="79" ht="33.0" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E79" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="19.5" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -5008,22 +5091,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E80" s="7"/>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="81" ht="33.0" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -5039,7 +5126,7 @@
       <c r="E81" s="7"/>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -5051,23 +5138,23 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5166,7 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -5095,79 +5182,103 @@
       <c r="E83" s="7"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="19.5" customHeight="1">
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="33.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E84" s="7"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="85" ht="33.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E85" s="7"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="86" ht="33.0" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E86" s="7"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C87" s="3"/>
@@ -5175,7 +5286,7 @@
       <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5298,7 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C88" s="3"/>
@@ -5195,12 +5306,72 @@
       <c r="E88" s="7"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="33.0" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="33.0" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="33.0" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F88"/>
+  <autoFilter ref="A4:F91"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -5364,60 +5535,52 @@
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
     </row>
-    <row r="13" ht="9.0" customHeight="1">
-      <c r="A13" s="0"/>
-    </row>
-    <row r="14" ht="24.0" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="13" ht="82.5" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析 (tmpfs / バインドマウントの要否判定と Excel / テキスト出力)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定で自動。無効化は --no-readonly-analysis。ファイル出力は --report-dir / --readonly-analysis-excel / --readonly-analysis-text 指定時)</t>
+        </is>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+    </row>
+    <row r="14" ht="9.0" customHeight="1">
+      <c r="A14" s="0"/>
+    </row>
+    <row r="15" ht="24.0" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値が設定されているパラメータ</t>
         </is>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">分類</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">オプション</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">その既定値での動作</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--local-image NAME</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1/base.local</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose build で生成されるローカルイメージ名</t>
         </is>
       </c>
     </row>
@@ -5429,17 +5592,17 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--compose-file FILE</t>
+          <t xml:space="preserve">--local-image NAME</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml</t>
+          <t xml:space="preserve">j1/base.local</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose 定義ファイル</t>
+          <t xml:space="preserve">compose build で生成されるローカルイメージ名</t>
         </is>
       </c>
     </row>
@@ -5451,39 +5614,39 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--compose-file FILE</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose.yml</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose 定義ファイル</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--compose-service NAME</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">(全サービス)</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド・起動対象。複数指定時は base を先行ビルド。base は起動対象にならない</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="33.0" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--build-progress-interval SEC</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
@@ -5495,17 +5658,17 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-stall-timeout SEC</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">300</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
@@ -5517,39 +5680,39 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-timeout SEC</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (無制限)</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
     <row r="22" ht="33.0" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">0 (無制限)</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
         </is>
       </c>
     </row>
@@ -5561,17 +5724,17 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss_master_password</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
         </is>
       </c>
     </row>
@@ -5583,39 +5746,39 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--region REGION</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="25" ht="33.0" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5790,7 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -5637,7 +5800,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5812,7 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -5659,7 +5822,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
@@ -5671,39 +5834,39 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="29" ht="33.0" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -5715,17 +5878,17 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -5737,17 +5900,17 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -5759,17 +5922,17 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -5781,17 +5944,17 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -5803,17 +5966,17 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -5825,17 +5988,17 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -5847,39 +6010,39 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="37" ht="33.0" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
@@ -5891,17 +6054,17 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -5913,17 +6076,17 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -5935,17 +6098,17 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -5957,17 +6120,17 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -5979,17 +6142,17 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -6001,39 +6164,39 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--wait-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="33.0" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -6045,17 +6208,17 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-method METHOD</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GET</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストメソッド</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -6067,17 +6230,17 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動)</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -6089,17 +6252,17 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -6111,39 +6274,39 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="49" ht="19.5" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+          <t xml:space="preserve">リトライ間隔</t>
         </is>
       </c>
     </row>
@@ -6155,61 +6318,61 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="51" ht="19.5" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="19.5" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="33.0" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
@@ -6221,17 +6384,17 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
@@ -6243,92 +6406,100 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
         </is>
       </c>
     </row>
     <row r="55" ht="33.0" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="33.0" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">有効</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="9.0" customHeight="1">
-      <c r="A56" s="0"/>
-    </row>
-    <row r="57" ht="24.0" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="57" ht="9.0" customHeight="1">
+      <c r="A57" s="0"/>
+    </row>
+    <row r="58" ht="24.0" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
         </is>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-    </row>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">記載箇所</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-    </row>
-    <row r="59" ht="33.0" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
     </row>
     <row r="60" ht="33.0" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
       <c r="C60" s="3"/>
@@ -6342,7 +6513,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
       <c r="C61" s="3"/>
@@ -6351,19 +6522,33 @@
     <row r="62" ht="33.0" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
     </row>
+    <row r="63" ht="33.0" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -6375,13 +6560,14 @@
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A58:D58"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="B60:D60"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6998,36 +7184,94 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="66.0" customHeight="1">
+    <row r="36" ht="82.5" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">17-4</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
+既定で毎回実行される。--report-dir があれば
+reports/build_and_verify_&lt;日時&gt;_readonly_filesystem.xlsx / .txt も出力される</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --report-dir ./reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="66.0" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-5</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel / テキストを任意のパスへ出力する</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --readonly-analysis-excel ./reports/readonly.xlsx \
+    --readonly-analysis-text ./reports/readonly.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="33.0" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-6</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステムの分析を行わない</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-readonly-analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="66.0" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
 進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="33.0" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="40" ht="33.0" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
         </is>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11 15:06:08</t>
+          <t xml:space="preserve">2026-08-12 04:52:00</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析 (tmpfs / バインドマウントの要否判定と Excel / テキスト出力)</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析 (Dockerfile のビルド時と entrypoint.sh などの実行時を分けた、tmpfs / バインドマウントの要否判定と Excel / テキスト出力)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="82.5" customHeight="1">
+    <row r="57" ht="132.0" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">分析ヘルパー (Python 3) の埋め込みと、compose.yml / 実行状況の収集・実行・表示・レポート追記</t>
+          <t xml:space="preserve">分析ヘルパー (Python 3) の埋め込みと、compose.yml / Dockerfile (ビルド時) / 起動スクリプト・実行状況 (実行時) の収集・実行・表示・レポート追記</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="115.5" customHeight="1">
+    <row r="79" ht="181.5" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用 FS 分析</t>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyze_readonly_filesystem / readonly_collect_compose_facts / readonly_collect_runtime_facts / readonly_container_probe / show_readonly_filesystem_analysis / append_readonly_analysis_report</t>
+          <t xml:space="preserve">analyze_readonly_filesystem / readonly_collect_compose_facts / readonly_collect_dockerfile_facts / readonly_parse_dockerfile / readonly_shell_write_targets / readonly_scan_context_script / readonly_collect_runtime_facts / readonly_container_probe / readonly_collect_container_scripts / show_readonly_filesystem_analysis / append_readonly_analysis_report</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml の read_only / tmpfs / volumes の解析、コンテナの書き込み状況の収集、判定結果の表示と Excel / テキスト出力</t>
+          <t xml:space="preserve">compose.yml の read_only / tmpfs / volumes の解析、Dockerfile からのビルド時の書き込み先の収集、起動スクリプトからの実行時の書き込み先の収集、コンテナの書き込み状況の収集、判定結果の表示と Excel / テキスト出力</t>
         </is>
       </c>
     </row>
@@ -1730,9 +1730,9 @@
       <c r="A96" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析も同じタイミングで実行します。
-こちらは compose.yml の定義だけでも判定できるため、**コンテナを起動しない実行
-(ビルドのみ / ビルド失敗) でも必ず実行**し、実行状況からの根拠が無いことを
-結果へ明記します (6.8 参照)。</t>
+こちらは compose.yml と Dockerfile の定義だけでも判定できるため、
+コンテナを起動しない実行 (ビルドのみ / ビルド失敗) でも必ず実行し、
+実行状況からの根拠が無いことを結果へ明記します (6.8 参照)。</t>
         </is>
       </c>
       <c r="B96" s="3"/>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--no-pull-images</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
         </is>
       </c>
     </row>
@@ -4202,17 +4202,17 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">0 以上の整数</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4234,27 +4234,27 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -4266,27 +4266,27 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4298,195 +4298,219 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-up-retry</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="33.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="33.0" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-startup-logs</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="33.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="33.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="33.0" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="33.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E55" s="7"/>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E56" s="7"/>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E57" s="7"/>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B58" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIME タイプ</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E58" s="7"/>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E59" s="7"/>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E60" s="7"/>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
         </is>
       </c>
     </row>
@@ -4498,23 +4522,23 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">URL</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -4526,23 +4550,23 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -4554,327 +4578,303 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">HTTP メソッド</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E63" s="7"/>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
     <row r="64" ht="19.5" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">MIME タイプ</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="33.0" customHeight="1">
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="19.5" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">JSON 文字列</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E65" s="7"/>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="19.5" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">key=value&amp;...</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="19.5" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="33.0" customHeight="1">
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E68" s="7"/>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">リトライ間隔</t>
         </is>
       </c>
     </row>
     <row r="69" ht="19.5" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E69" s="7"/>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="19.5" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="33.0" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="E70" s="7"/>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="71" ht="33.0" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="E71" s="7"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="33.0" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E72" s="7"/>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
         </is>
       </c>
     </row>
     <row r="73" ht="33.0" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E73" s="7"/>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
         </is>
       </c>
     </row>
@@ -4886,91 +4886,91 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="19.5" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="33.0" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="33.0" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
@@ -4982,17 +4982,17 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -5002,11 +5002,11 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="33.0" customHeight="1">
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="19.5" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
         </is>
       </c>
     </row>
@@ -5046,12 +5046,12 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--report-dir DIR</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -5066,11 +5066,11 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="19.5" customHeight="1">
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5078,17 +5078,17 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -5098,75 +5098,83 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="81" ht="33.0" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E81" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="19.5" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E82" s="7"/>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
     <row r="83" ht="33.0" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -5179,55 +5187,63 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E83" s="7"/>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="84" ht="33.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E84" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="85" ht="33.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -5235,22 +5251,26 @@
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E85" s="7"/>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -5263,115 +5283,287 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E86" s="7"/>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="19.5" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="33.0" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
     <row r="88" ht="33.0" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E88" s="7"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="89" ht="33.0" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E89" s="7"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="90" ht="33.0" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E90" s="7"/>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="91" ht="33.0" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E91" s="7"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="33.0" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E92" s="7"/>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.9 その他</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-h, --help</t>
+        </is>
+      </c>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="33.0" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="33.0" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="33.0" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="33.0" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F91"/>
+  <autoFilter ref="A4:F97"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -5535,10 +5727,10 @@
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
     </row>
-    <row r="13" ht="82.5" customHeight="1">
+    <row r="13" ht="115.5" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析 (tmpfs / バインドマウントの要否判定と Excel / テキスト出力)</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析 (Dockerfile のビルド時と entrypoint.sh などの実行時を分けた、tmpfs / バインドマウントの要否判定と Excel / テキスト出力)</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -6186,105 +6378,105 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--pull-retry N</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="33.0" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="33.0" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--up-retry N</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="33.0" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="33.0" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
@@ -6296,256 +6488,344 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
     <row r="50" ht="19.5" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
     <row r="51" ht="19.5" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="52" ht="19.5" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--url-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="19.5" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--url-interval SEC</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="19.5" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="33.0" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="57" ht="33.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="33.0" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="58" ht="33.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="33.0" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="59" ht="33.0" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">50</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
-    </row>
-    <row r="56" ht="33.0" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(オプション不要)</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="9.0" customHeight="1">
-      <c r="A57" s="0"/>
-    </row>
-    <row r="58" ht="24.0" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
-        </is>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-    </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">記載箇所</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
     </row>
     <row r="60" ht="33.0" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="9.0" customHeight="1">
+      <c r="A61" s="0"/>
+    </row>
+    <row r="62" ht="24.0" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
+        </is>
+      </c>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">記載箇所</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内容</t>
+        </is>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+    </row>
+    <row r="64" ht="33.0" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-    </row>
-    <row r="61" ht="33.0" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+    </row>
+    <row r="65" ht="33.0" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-    </row>
-    <row r="62" ht="33.0" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+    </row>
+    <row r="66" ht="33.0" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-    </row>
-    <row r="63" ht="33.0" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+    </row>
+    <row r="67" ht="33.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
         </is>
       </c>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -6562,12 +6842,12 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B67:D67"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7184,7 +7464,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="82.5" customHeight="1">
+    <row r="36" ht="148.5" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-4</t>
@@ -7194,7 +7474,9 @@
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
 既定で毎回実行される。--report-dir があれば
-reports/build_and_verify_&lt;日時&gt;_readonly_filesystem.xlsx / .txt も出力される</t>
+reports/build_and_verify_&lt;日時&gt;_readonly_filesystem.xlsx / .txt も出力される
+Dockerfile のビルド時に書くだけのディレクトリは「ビルド時のみ」として
+対象から外し、entrypoint.sh などが起動のたびに書く場所を「要対応」に挙げる</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12 04:52:00</t>
+          <t xml:space="preserve">2026-08-12 13:21:33</t>
         </is>
       </c>
     </row>
@@ -2427,245 +2427,269 @@
     <row r="165" ht="19.5" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
+          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
         </is>
       </c>
     </row>
     <row r="166" ht="19.5" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_COLOR</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">定義されていれば色分けを無効化</t>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
         </is>
       </c>
     </row>
     <row r="167" ht="19.5" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLICOLOR_FORCE</t>
+          <t xml:space="preserve">NO_COLOR</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+          <t xml:space="preserve">定義されていれば色分けを無効化</t>
         </is>
       </c>
     </row>
     <row r="168" ht="19.5" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">CLICOLOR_FORCE</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="19.5" customHeight="1">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">TERM</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B169" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">dumb の場合は色分けしない</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="19.5" customHeight="1">
-      <c r="A169" s="8" t="inlineStr">
+    <row r="170" ht="19.5" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
         </is>
       </c>
-      <c r="B169" s="8"/>
-    </row>
-    <row r="170" ht="19.5" customHeight="1">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="B170" s="8"/>
+    </row>
+    <row r="171" ht="19.5" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="19.5" customHeight="1">
-      <c r="A171" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TZ</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
         </is>
       </c>
     </row>
     <row r="172" ht="19.5" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">TZ</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
         </is>
       </c>
     </row>
     <row r="173" ht="19.5" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="19.5" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="19.5" customHeight="1">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr">
+      <c r="B175" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="19.5" customHeight="1">
-      <c r="A175" s="8" t="inlineStr">
+    <row r="176" ht="33.0" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;--cacert-bundle-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CA 証明書をまとめた tar のパス。compose の file 型シークレットへ渡す。--cacert-dir 未指定時は「空の tar」のパスが入り、従来どおり証明書なしでビルドされる</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="19.5" customHeight="1">
+      <c r="A177" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B175" s="8"/>
-    </row>
-    <row r="176" ht="49.5" customHeight="1">
-      <c r="A176" s="3" t="inlineStr">
+      <c r="B177" s="8"/>
+    </row>
+    <row r="178" ht="49.5" customHeight="1">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 / 7.2 はスクリプト自身が実行ホストで参照・設定する環境変数です。
 これとは別に、起動したコンテナ内の環境変数を収集して一覧表示します
 (スクリプトの動作は変えません)。</t>
         </is>
       </c>
-      <c r="B176" s="3"/>
-    </row>
-    <row r="177" ht="19.5" customHeight="1">
-      <c r="A177" s="8" t="inlineStr">
+      <c r="B178" s="3"/>
+    </row>
+    <row r="179" ht="19.5" customHeight="1">
+      <c r="A179" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B177" s="8"/>
-    </row>
-    <row r="178" ht="19.5" customHeight="1">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="B179" s="8"/>
+    </row>
+    <row r="180" ht="19.5" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">出力先</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="33.0" customHeight="1">
-      <c r="A179" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JVM オプションの受け渡し</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="33.0" customHeight="1">
-      <c r="A180" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OpenTelemetry 標準設定</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
     <row r="181" ht="33.0" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">JVM オプションの受け渡し</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="33.0" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenTelemetry 標準設定</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="33.0" customHeight="1">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">OpenTelemetry 関連設定</t>
         </is>
       </c>
-      <c r="B181" s="3" t="inlineStr">
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS_XRAY_DAEMON_ADDRESS / AWS_XRAY_CONTEXT_MISSING / AWS_XRAY_TRACING_NAME / AWS_LAMBDA_EXEC_WRAPPER / AOT_CONFIG_CONTENT</t>
         </is>
       </c>
-      <c r="C181" s="3" t="inlineStr">
+      <c r="C183" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="19.5" customHeight="1">
-      <c r="A182" s="11" t="inlineStr">
+    <row r="184" ht="19.5" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリ構造の起点</t>
         </is>
       </c>
-      <c r="B182" s="3" t="inlineStr">
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--deployment-dir-env で指定した名前</t>
         </is>
       </c>
-      <c r="C182" s="3" t="inlineStr">
+      <c r="C184" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="19.5" customHeight="1">
-      <c r="A183" s="8" t="inlineStr">
+    <row r="185" ht="19.5" customHeight="1">
+      <c r="A185" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B183" s="8"/>
-    </row>
-    <row r="184" ht="19.5" customHeight="1">
-      <c r="A184" s="3" t="inlineStr">
+      <c r="B185" s="8"/>
+    </row>
+    <row r="186" ht="19.5" customHeight="1">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B184" s="3"/>
+      <c r="B186" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="77">
@@ -2740,12 +2764,12 @@
     <mergeCell ref="A158:B158"/>
     <mergeCell ref="A160:B160"/>
     <mergeCell ref="A161:B161"/>
-    <mergeCell ref="A169:B169"/>
-    <mergeCell ref="A175:B175"/>
-    <mergeCell ref="A176:B176"/>
+    <mergeCell ref="A170:B170"/>
     <mergeCell ref="A177:B177"/>
-    <mergeCell ref="A183:B183"/>
-    <mergeCell ref="A184:B184"/>
+    <mergeCell ref="A178:B178"/>
+    <mergeCell ref="A179:B179"/>
+    <mergeCell ref="A185:B185"/>
+    <mergeCell ref="A186:B186"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3317,140 +3341,148 @@
     <row r="21" ht="33.0" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-jboss-password</t>
+          <t xml:space="preserve">--cacert-dir DIR</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
+          <t xml:space="preserve">ディレクトリのパス</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E21" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
         </is>
       </c>
     </row>
     <row r="22" ht="33.0" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-mask</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">英数字と . _ -</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="23" ht="33.0" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">tar のパス</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33.0" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="25" ht="33.0" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">glob パターン</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
-        </is>
-      </c>
-      <c r="E25" s="7"/>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
@@ -3462,35 +3494,35 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--verify-jboss-password</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="33.0" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-password-mask</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -3498,83 +3530,83 @@
           <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto</t>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="33.0" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-verify-cwagent</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証を行わない</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="29" ht="33.0" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="30" ht="33.0" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3584,41 +3616,41 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="31" ht="33.0" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">列挙</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3662,7 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-report</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3638,15 +3670,15 @@
           <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3690,7 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-delivery-report</t>
+          <t xml:space="preserve">--no-verify-cwagent</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -3674,7 +3706,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達レポートを行わない (既定)</t>
+          <t xml:space="preserve">検証を行わない</t>
         </is>
       </c>
     </row>
@@ -3686,23 +3718,23 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -3714,23 +3746,23 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -3742,27 +3774,27 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">列挙</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="49.5" customHeight="1">
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="33.0" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
@@ -3770,23 +3802,23 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3830,7 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-required</t>
+          <t xml:space="preserve">--no-cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3808,13 +3840,13 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
+          <t xml:space="preserve">送達レポートを行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -3826,23 +3858,23 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -3854,183 +3886,163 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="33.0" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-startup</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
+        </is>
+      </c>
+      <c r="E41" s="7"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="33.0" customHeight="1">
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="49.5" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+        </is>
+      </c>
+      <c r="E42" s="7"/>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
     <row r="43" ht="33.0" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-required</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">拡張正規表現</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E43" s="7"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
         </is>
       </c>
     </row>
     <row r="44" ht="33.0" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E44" s="7"/>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="33.0" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--no-cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E45" s="7"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
         </is>
       </c>
     </row>
@@ -4042,27 +4054,27 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--verify-startup</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
         </is>
       </c>
     </row>
@@ -4074,27 +4086,27 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-healthy</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4106,17 +4118,17 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">拡張正規表現</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -4126,7 +4138,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -4138,27 +4150,27 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--allow-service-exit NAME</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -4170,27 +4182,27 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-pull-images</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -4202,17 +4214,17 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -4222,7 +4234,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -4234,27 +4246,27 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--wait-healthy</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
         </is>
       </c>
     </row>
@@ -4266,17 +4278,17 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -4286,7 +4298,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4298,27 +4310,27 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-up-retry</t>
+          <t xml:space="preserve">--allow-service-exit NAME</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
+          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
         </is>
       </c>
     </row>
@@ -4330,27 +4342,27 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--no-pull-images</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
         </is>
       </c>
     </row>
@@ -4362,27 +4374,27 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4394,17 +4406,17 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">0 以上の整数</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
@@ -4414,7 +4426,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -4426,27 +4438,27 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4470,7 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--no-up-retry</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4478,7 +4490,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
         </is>
       </c>
     </row>
@@ -4490,167 +4502,187 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="33.0" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-startup-logs</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="33.0" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="33.0" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="33.0" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="33.0" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E61" s="7"/>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E62" s="7"/>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E63" s="7"/>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="19.5" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIME タイプ</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E64" s="7"/>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E65" s="7"/>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
@@ -4662,12 +4694,12 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
+          <t xml:space="preserve">URL</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -4678,7 +4710,7 @@
       <c r="E66" s="7"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -4690,23 +4722,23 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -4718,23 +4750,23 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP メソッド</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -4746,40 +4778,40 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">MIME タイプ</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E69" s="7"/>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="70" ht="19.5" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
+          <t xml:space="preserve">JSON 文字列</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -4790,140 +4822,136 @@
       <c r="E70" s="7"/>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="19.5" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">key=value&amp;...</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="19.5" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="33.0" customHeight="1">
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="19.5" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E74" s="7"/>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
         </is>
       </c>
     </row>
     <row r="75" ht="19.5" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">bash / http / logs</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -4931,110 +4959,94 @@
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="E75" s="7"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="76" ht="33.0" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="E76" s="7"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="77" ht="33.0" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E77" s="7"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="33.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E78" s="7"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
         </is>
       </c>
     </row>
@@ -5046,59 +5058,59 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="19.5" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="33.0" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
         </is>
       </c>
     </row>
@@ -5110,91 +5122,91 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="33.0" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="19.5" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B82" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="33.0" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
         </is>
       </c>
     </row>
@@ -5206,12 +5218,12 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--report-dir DIR</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -5226,7 +5238,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
         </is>
       </c>
     </row>
@@ -5238,211 +5250,231 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="33.0" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="19.5" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="33.0" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
     <row r="88" ht="33.0" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E88" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="89" ht="33.0" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E89" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="90" ht="33.0" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="19.5" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-readonly-analysis</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E90" s="7"/>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="33.0" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E91" s="7"/>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="92" ht="33.0" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -5458,112 +5490,252 @@
       <c r="E92" s="7"/>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="33.0" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E93" s="7"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="94" ht="33.0" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E94" s="7"/>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="95" ht="33.0" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E95" s="7"/>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="96" ht="33.0" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E96" s="7"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="97" ht="33.0" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E97" s="7"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.9 その他</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-h, --help</t>
+        </is>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="33.0" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="33.0" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="33.0" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="33.0" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F97"/>
+  <autoFilter ref="A4:F102"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -5977,176 +6149,176 @@
     <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="27" ht="33.0" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
     <row r="28" ht="33.0" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="29" ht="33.0" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">*.crt と *.pem</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
     <row r="30" ht="33.0" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="31" ht="33.0" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="32" ht="33.0" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="33" ht="33.0" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -6158,17 +6330,17 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -6180,17 +6352,17 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -6202,17 +6374,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -6224,105 +6396,105 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
     <row r="38" ht="33.0" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="33.0" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="33.0" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="41" ht="33.0" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
@@ -6334,17 +6506,17 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -6356,17 +6528,17 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -6378,17 +6550,17 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -6400,17 +6572,17 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -6422,17 +6594,17 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6616,17 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -6466,105 +6638,105 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--pull-retry N</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="33.0" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="33.0" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--up-retry N</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="33.0" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="33.0" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="19.5" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
@@ -6576,259 +6748,361 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
     <row r="54" ht="19.5" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
     <row r="55" ht="19.5" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="56" ht="19.5" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--url-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="19.5" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--url-interval SEC</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="19.5" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="33.0" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="61" ht="33.0" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="33.0" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="62" ht="33.0" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="33.0" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="63" ht="33.0" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">50</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
-    </row>
-    <row r="60" ht="33.0" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(オプション不要)</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="9.0" customHeight="1">
-      <c r="A61" s="0"/>
-    </row>
-    <row r="62" ht="24.0" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
-        </is>
-      </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">記載箇所</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
     </row>
     <row r="64" ht="33.0" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="9.0" customHeight="1">
+      <c r="A65" s="0"/>
+    </row>
+    <row r="66" ht="24.0" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
+        </is>
+      </c>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+    </row>
+    <row r="67" ht="19.5" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">記載箇所</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内容</t>
+        </is>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68" ht="33.0" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-    </row>
-    <row r="65" ht="33.0" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+    </row>
+    <row r="69" ht="33.0" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-    </row>
-    <row r="66" ht="33.0" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+    </row>
+    <row r="70" ht="33.0" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-    </row>
-    <row r="67" ht="33.0" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+    </row>
+    <row r="71" ht="33.0" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+    </row>
+    <row r="72" ht="33.0" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
         </is>
       </c>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -6842,12 +7116,13 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="A66:D66"/>
     <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B72:D72"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12 13:21:33</t>
+          <t xml:space="preserve">2026-08-13 05:54:26</t>
         </is>
       </c>
     </row>
@@ -752,416 +752,416 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="25" ht="115.5" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss EAP Undertow バーチャルホスト (default-host) の分析 (Host ヘッダーごとの振り分け判定、default-host の利用状況、Host ヘッダーを差し替えた実リクエストによる確認)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(起動確認時に既定で自動。無効化は --no-undertow-analysis。テキスト出力は --report-dir / --undertow-analysis-text 指定時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19.5" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《できること》</t>
         </is>
       </c>
-      <c r="B25" s="8"/>
-    </row>
-    <row r="26" ht="33.0" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="B26" s="8"/>
+    </row>
+    <row r="27" ht="33.0" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup も --verify-url も指定しなければ、純粋にビルドのみを行って終了します
 (従来の build_and_push.sh --build-only 相当)。</t>
         </is>
       </c>
-      <c r="B26" s="3"/>
-    </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="B27" s="3"/>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《行わないこと》</t>
         </is>
       </c>
-      <c r="B27" s="8"/>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="B28" s="8"/>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECR 権限チェック / ECR ログイン / タグ付け / プッシュ / imagedefinition.json の出力。</t>
         </is>
       </c>
-      <c r="B28" s="3"/>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B29" s="8"/>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="B30" s="8"/>
+    </row>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">前提</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">必須コマンド</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">docker、docker compose または docker-compose</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="33.0" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33" ht="33.0" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">追加で必要</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">curl (--verify-url / --keep-container-mode http 時)、aws (--jboss-password-param 時)、Python 3 (送達診断の JSON 整形時)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS 認証</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--jboss-password-param を使う場合のみ必要 (aws login --remote 済み)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B34" s="8"/>
-    </row>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="B35" s="8"/>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B35" s="3"/>
-    </row>
-    <row r="36" ht="9.0" customHeight="1">
-      <c r="A36" s="0"/>
-    </row>
-    <row r="37" ht="24.0" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="B36" s="3"/>
+    </row>
+    <row r="37" ht="9.0" customHeight="1">
+      <c r="A37" s="0"/>
+    </row>
+    <row r="38" ht="24.0" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2. 全体構成</t>
         </is>
       </c>
-      <c r="B37" s="5"/>
-    </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" ht="19.5" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.1 ファイル内のセクション構成》</t>
         </is>
       </c>
-      <c r="B38" s="8"/>
-    </row>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="B39" s="8"/>
+    </row>
+    <row r="40" ht="19.5" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">位置</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">セクション</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="33.0" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冒頭</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ヘッダーコメント</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">目的・機能一覧・使い方</t>
         </is>
       </c>
     </row>
     <row r="41" ht="33.0" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">冒頭</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘッダーコメント</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目的・機能一覧・使い方</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="33.0" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示タイムゾーン設定</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示・保存する時刻をすべて JST に固定</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="82.5" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="43" ht="82.5" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="49.5" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="44" ht="49.5" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ用ヘルパ</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / run / JST 変換ヘルパ</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">usage()</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--help の本文</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="66.0" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="46" ht="66.0" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数パース</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">append_services によるカンマ区切り分割、need_value による値欠落検出</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="49.5" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="47" ht="49.5" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">入力値の検証</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">数値・モード・排他関係・サービス指定の整合性</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">依存コマンド / AWS 認証 / compose 判定</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行環境の確認</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="49.5" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="49" ht="49.5" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">シークレット準備・一時ファイルコピー</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">prepare_jboss_password / prepare_copy_files</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="82.5" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="50" ht="82.5" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">マスターパスワードの伝搬検証</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">危険文字の分析、段ごとの比較、compose.yml と standalone.xml の解析、CredentialStore の開封確認</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="49.5" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="51" ht="49.5" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">起動確認・ログ表示ヘルパ</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ取得、ANSI 除去、色分け、companion ログ</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="33.0" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="52" ht="33.0" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナ内情報の収集と整形</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="82.5" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="53" ht="82.5" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM パラメータ・OpenTelemetry 設定</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">/proc/&lt;pid&gt;/cmdline の走査、JVM オプションの分類、OpenTelemetry 設定の突き合わせ</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="66.0" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="54" ht="66.0" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対話操作</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">bash / HTTP / logs モードと、healthcheck・MySQL・可観測性の各ヘルパ</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="33.0" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="55" ht="33.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 完全クリーンアップ</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対象の集計、確認フレーズ、削除、検証</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="66.0" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルドの停滞検知・進捗表示</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド出力の読み手、監視プロセス、停滞診断、上限時間での中断</t>
         </is>
       </c>
     </row>
@@ -1173,46 +1173,46 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルドの停滞検知・進捗表示</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド出力の読み手、監視プロセス、停滞診断、上限時間での中断</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="66.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">WAR デプロイ時 Java 例外解析</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">解析ヘルパー (Python 3) の埋め込みと、ログ収集・実行・表示・レポート追記</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="132.0" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="58" ht="132.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">分析ヘルパー (Python 3) の埋め込みと、compose.yml / Dockerfile (ビルド時) / 起動スクリプト・実行状況 (実行時) の収集・実行・表示・レポート追記</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポート</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">write_build_report</t>
         </is>
       </c>
     </row>
@@ -1224,406 +1224,423 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">全量レポート</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">write_build_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">後始末 (cleanup_all)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">EXIT トラップ本体</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="49.5" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="61" ht="49.5" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">末尾</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">メイン処理</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド → 起動 → 起動確認 → URL 確認 → 対話 → 情報表示</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.2 主要な関数グループ》</t>
         </is>
       </c>
-      <c r="B61" s="8"/>
-    </row>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B62" s="8"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">グループ</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">代表的な関数</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">役割</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="33.0" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
+    <row r="64" ht="33.0" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ・時刻</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / to_jst_display_time</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">出力整形と UTC→JST 変換</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="66.0" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="65" ht="66.0" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">引数処理</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">append_services / need_value / validate_positive_integer / validate_non_negative_integer</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">カンマ区切り分割、値欠落検出、数値検証 (ビルド監視の各値は 0 を許す)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="49.5" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
+    <row r="66" ht="49.5" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Compose 操作</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose_container_ids / compose_logs / compose_started_services</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対象サービスの ID・ログ・サービス名取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="33.0" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
         </is>
       </c>
     </row>
     <row r="67" ht="33.0" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログ表示</t>
+          <t xml:space="preserve">起動確認</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
+          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">行数制御と重要ログの色分け</t>
+          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
         </is>
       </c>
     </row>
     <row r="68" ht="33.0" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL 確認</t>
+          <t xml:space="preserve">ログ表示</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">verify_url / show_url_body</t>
+          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl のリトライと応答本文表示</t>
+          <t xml:space="preserve">行数制御と重要ログの色分け</t>
         </is>
       </c>
     </row>
     <row r="69" ht="33.0" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">URL 確認</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verify_url / show_url_body</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curl のリトライと応答本文表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="33.0" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">情報表示</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">show_verified_container_envs / ..._directory_trees / ..._deployment_structures</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="66.0" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
+    <row r="71" ht="66.0" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM / OTel</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">show_verified_container_jvm_parameters / ..._otel_settings / collect_container_java_processes / classify_jvm_option / is_otel_jvm_option</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Java プロセスの検出、JVM オプションの分類、OpenTelemetry 設定の集約</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="33.0" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">対話操作</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bash / HTTP / logs モード</t>
         </is>
       </c>
     </row>
     <row r="72" ht="33.0" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck</t>
+          <t xml:space="preserve">対話操作</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
+          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
+          <t xml:space="preserve">bash / HTTP / logs モード</t>
         </is>
       </c>
     </row>
     <row r="73" ht="33.0" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">可観測性</t>
+          <t xml:space="preserve">healthcheck</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
         </is>
       </c>
     </row>
     <row r="74" ht="33.0" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">可観測性</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="33.0" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">クリーンアップ</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cleanup_all_docker_data / teardown_container / cleanup_copied_files</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 全体削除と通常後始末</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="82.5" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="76" ht="82.5" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド監視</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">run_build_with_watchdog / build_watchdog_reader / build_watchdog_monitor / diagnose_build_stall / build_phase_from_line / check_build_disk_space</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exporting layers などで出力が途切れたときの進捗表示・停滞診断・上限時間での中断</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="66.0" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cwagent 送信検証</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
         </is>
       </c>
     </row>
     <row r="77" ht="66.0" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent ロググループ準備</t>
+          <t xml:space="preserve">cwagent 送信検証</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepare_cwagent_log_groups / cwagent_ensure_log_groups / cwagent_resolve_delivery_target</t>
+          <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの log_group_name が実 CloudWatch Logs に無ければ作成</t>
+          <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
         </is>
       </c>
     </row>
     <row r="78" ht="66.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">cwagent ロググループ準備</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prepare_cwagent_log_groups / cwagent_ensure_log_groups / cwagent_resolve_delivery_target</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">設定ファイルの log_group_name が実 CloudWatch Logs に無ければ作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="66.0" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Java 例外解析</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">analyze_war_deploy_exceptions / collect_deploy_exception_logs / resolve_analysis_output_path / show_war_deploy_exception_analysis / append_deploy_exception_report</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、画面表示と Excel 出力</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="181.5" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
+    <row r="80" ht="181.5" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用 FS 分析</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">analyze_readonly_filesystem / readonly_collect_compose_facts / readonly_collect_dockerfile_facts / readonly_parse_dockerfile / readonly_shell_write_targets / readonly_scan_context_script / readonly_collect_runtime_facts / readonly_container_probe / readonly_collect_container_scripts / show_readonly_filesystem_analysis / append_readonly_analysis_report</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose.yml の read_only / tmpfs / volumes の解析、Dockerfile からのビルド時の書き込み先の収集、起動スクリプトからの実行時の書き込み先の収集、コンテナの書き込み状況の収集、判定結果の表示と Excel / テキスト出力</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="33.0" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
+    <row r="81" ht="33.0" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">レポート</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">write_build_report / append_compose_service_logs_report / append_jboss_password_report / append_cwagent_report / append_deploy_exception_report / append_readonly_analysis_report</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートの生成</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="66.0" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
+    <row r="82" ht="66.0" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">パスワード伝搬検証</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">verify_jboss_password_host_stages / verify_jboss_password_build_secret / verify_jboss_password_container_stages / jboss_xml_attributes / jboss_xml_unescape / jboss_wildfly_literal</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">各段の値の取得、XML と WildFly 式のエスケープ解除、原本との突き合わせ</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="19.5" customHeight="1">
-      <c r="A82" s="8" t="inlineStr">
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B82" s="8"/>
-    </row>
-    <row r="83" ht="19.5" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="B83" s="8"/>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">処理のどの経路 (成功・失敗・中断) でも、次の順で実行されます。</t>
         </is>
       </c>
-      <c r="B83" s="3"/>
-    </row>
-    <row r="84" ht="19.5" customHeight="1">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" ht="19.5" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B84" s="8"/>
-    </row>
-    <row r="85" ht="264.0" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="B85" s="8"/>
+    </row>
+    <row r="86" ht="264.0" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1. analyze_war_deploy_exceptions … デプロイ処理の Java 例外を解析 (削除より前・レポートより前)
                                    成功経路で実行済みなら何もしない
@@ -1643,59 +1660,51 @@
                                    URL 応答本文・HTTP ボディ・healthcheck 診断</t>
         </is>
       </c>
-      <c r="B85" s="6"/>
-    </row>
-    <row r="86" ht="19.5" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="B86" s="6"/>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B86" s="8"/>
-    </row>
-    <row r="87" ht="33.0" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="B87" s="8"/>
+    </row>
+    <row r="88" ht="33.0" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">終了コードは、本処理が既に失敗していれば元の終了コードを優先します。
 成功していた場合は、後始末の結果 (レポート保存失敗やクリーンアップ未承認なら 1) を返します。</t>
         </is>
       </c>
-      <c r="B87" s="3"/>
-    </row>
-    <row r="88" ht="19.5" customHeight="1">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="B88" s="3"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B88" s="8"/>
-    </row>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="B89" s="8"/>
+    </row>
+    <row r="90" ht="19.5" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B89" s="3"/>
-    </row>
-    <row r="90" ht="9.0" customHeight="1">
-      <c r="A90" s="0"/>
-    </row>
-    <row r="91" ht="24.0" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="B90" s="3"/>
+    </row>
+    <row r="91" ht="9.0" customHeight="1">
+      <c r="A91" s="0"/>
+    </row>
+    <row r="92" ht="24.0" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">3. 処理の流れ</t>
         </is>
       </c>
-      <c r="B91" s="5"/>
-    </row>
-    <row r="92" ht="19.5" customHeight="1">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.1 全体フロー》</t>
-        </is>
-      </c>
-      <c r="B92" s="8"/>
+      <c r="B92" s="5"/>
     </row>
     <row r="93" ht="19.5" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
@@ -1705,8 +1714,16 @@
       </c>
       <c r="B93" s="8"/>
     </row>
-    <row r="94" ht="99.0" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="94" ht="19.5" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.1 全体フロー》</t>
+        </is>
+      </c>
+      <c r="B94" s="8"/>
+    </row>
+    <row r="95" ht="99.0" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時は、EXIT の後始末でレポートのログ本文を集める直前に
 compose stop (SIGTERM) を挟みます (3.6 参照)。
@@ -1716,18 +1733,18 @@
 必ず実行します** (6.7 参照)。</t>
         </is>
       </c>
-      <c r="B94" s="3"/>
-    </row>
-    <row r="95" ht="19.5" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="B95" s="3"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B95" s="8"/>
-    </row>
-    <row r="96" ht="66.0" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="B96" s="8"/>
+    </row>
+    <row r="97" ht="66.0" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析も同じタイミングで実行します。
 こちらは compose.yml と Dockerfile の定義だけでも判定できるため、
@@ -1735,203 +1752,191 @@
 実行状況からの根拠が無いことを結果へ明記します (6.8 参照)。</t>
         </is>
       </c>
-      <c r="B96" s="3"/>
-    </row>
-    <row r="97" ht="19.5" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B97" s="8"/>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="B98" s="8"/>
+    </row>
+    <row r="99" ht="19.5" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--compose-service の指定数によってビルド戦略が変わります。</t>
         </is>
       </c>
-      <c r="B98" s="3"/>
-    </row>
-    <row r="99" ht="19.5" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="B99" s="3"/>
+    </row>
+    <row r="100" ht="19.5" customHeight="1">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B99" s="8"/>
-    </row>
-    <row r="100" ht="19.5" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="B100" s="8"/>
+    </row>
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">指定</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">動作</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="19.5" customHeight="1">
-      <c r="A101" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">未指定</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全サービスを 1 回の compose build でビルド</t>
         </is>
       </c>
     </row>
     <row r="102" ht="19.5" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">未指定</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全サービスを 1 回の compose build でビルド</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="19.5" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">1 個</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そのサービスのみビルド</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="33.0" customHeight="1">
-      <c r="A103" s="11" t="inlineStr">
+    <row r="104" ht="33.0" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2 個以上</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">第 1 フェーズ: base サービスを単独で先行ビルド → ローカルイメージ確認 → 第 2 フェーズ: base 以外をまとめて並列ビルド</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="19.5" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B104" s="8"/>
-    </row>
-    <row r="105" ht="33.0" customHeight="1">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="B105" s="8"/>
+    </row>
+    <row r="106" ht="33.0" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2 段階に分けるのは、ベースイメージを参照するサービスが base の完成前にビルドを始めるのを
 防ぐためです。並列オプションは compose のバージョンによって使い分けます。</t>
         </is>
       </c>
-      <c r="B105" s="3"/>
-    </row>
-    <row r="106" ht="19.5" customHeight="1">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="B106" s="3"/>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B106" s="8"/>
-    </row>
-    <row r="107" ht="19.5" customHeight="1">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="B107" s="8"/>
+    </row>
+    <row r="108" ht="19.5" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">compose</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">並列指定</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="19.5" customHeight="1">
-      <c r="A108" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v2 (docker compose)</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">グローバルオプション --parallel &lt;サービス数&gt;</t>
         </is>
       </c>
     </row>
     <row r="109" ht="19.5" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">v2 (docker compose)</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">グローバルオプション --parallel &lt;サービス数&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="19.5" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">v1 (docker-compose)</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build --parallel (未対応版は exit 1)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="19.5" customHeight="1">
-      <c r="A110" s="8" t="inlineStr">
+    <row r="111" ht="19.5" customHeight="1">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B110" s="8"/>
-    </row>
-    <row r="111" ht="33.0" customHeight="1">
-      <c r="A111" s="3" t="inlineStr">
+      <c r="B111" s="8"/>
+    </row>
+    <row r="112" ht="33.0" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド後は docker image inspect でローカルイメージを確認し、
 image=... id=... created=... size=... bytes を JST 表記でログに残します。</t>
         </is>
       </c>
-      <c r="B111" s="3"/>
-    </row>
-    <row r="112" ht="19.5" customHeight="1">
-      <c r="A112" s="8" t="inlineStr">
+      <c r="B112" s="3"/>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B112" s="8"/>
-    </row>
-    <row r="113" ht="19.5" customHeight="1">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="B113" s="8"/>
+    </row>
+    <row r="114" ht="19.5" customHeight="1">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドの前後では、ディスク使用量を抑えるために次を行います (5.8-2 参照)。</t>
         </is>
       </c>
-      <c r="B113" s="3"/>
-    </row>
-    <row r="114" ht="19.5" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
+      <c r="B114" s="3"/>
+    </row>
+    <row r="115" ht="19.5" customHeight="1">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B114" s="8"/>
-    </row>
-    <row r="115" ht="19.5" customHeight="1">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="B115" s="8"/>
+    </row>
+    <row r="116" ht="19.5" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">タイミング</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="19.5" customHeight="1">
-      <c r="A116" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1948,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">data root の空き容量を確認し、5 GiB 未満なら警告する (5.2-2 参照)</t>
+          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
         </is>
       </c>
     </row>
@@ -1955,46 +1960,50 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
+          <t xml:space="preserve">data root の空き容量を確認し、5 GiB 未満なら警告する (5.2-2 参照)</t>
         </is>
       </c>
     </row>
     <row r="119" ht="19.5" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="19.5" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">ローカルイメージ確認の直後</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ID が変わっていれば、タグを失った旧世代イメージを削除する</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="19.5" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
+    <row r="121" ht="19.5" customHeight="1">
+      <c r="A121" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B120" s="8"/>
-    </row>
-    <row r="121" ht="33.0" customHeight="1">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="B121" s="8"/>
+    </row>
+    <row r="122" ht="33.0" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド自体は監視プロセス付きで実行し、exporting to image / exporting layers で
 出力が途切れても状況が分かるようにします (5.2-2 参照)。</t>
         </is>
       </c>
-      <c r="B121" s="3"/>
-    </row>
-    <row r="122" ht="19.5" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
-        </is>
-      </c>
-      <c r="B122" s="8"/>
+      <c r="B122" s="3"/>
     </row>
     <row r="123" ht="19.5" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
@@ -2004,8 +2013,16 @@
       </c>
       <c r="B123" s="8"/>
     </row>
-    <row r="124" ht="99.0" customHeight="1">
-      <c r="A124" s="3" t="inlineStr">
+    <row r="124" ht="19.5" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B124" s="8"/>
+    </row>
+    <row r="125" ht="99.0" customHeight="1">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・--startup-service を指定した場合は、サービスごとに個別に起動完了を判定し、
   指定した全サービスの完了をもって成功とします
@@ -2015,35 +2032,35 @@
 ・失敗時は --suppress-startup-logs を指定していてもログを表示します (原因を隠さないため)</t>
         </is>
       </c>
-      <c r="B124" s="3"/>
-    </row>
-    <row r="125" ht="19.5" customHeight="1">
-      <c r="A125" s="8" t="inlineStr">
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" ht="19.5" customHeight="1">
+      <c r="A126" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B125" s="8"/>
-    </row>
-    <row r="126" ht="33.0" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
+      <c r="B126" s="8"/>
+    </row>
+    <row r="127" ht="33.0" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">curl -s -S -m 30 -o &lt;一時ファイル&gt; -w '%{http_code}' -X &lt;URL_METHOD&gt; \
      [-k] [-H "Content-Type: &lt;URL_CONTENT_TYPE&gt;"] [--data &lt;ボディ&gt;] &lt;VERIFY_URL&gt;</t>
         </is>
       </c>
-      <c r="B126" s="6"/>
-    </row>
-    <row r="127" ht="19.5" customHeight="1">
-      <c r="A127" s="8" t="inlineStr">
+      <c r="B127" s="6"/>
+    </row>
+    <row r="128" ht="19.5" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B127" s="8"/>
-    </row>
-    <row r="128" ht="66.0" customHeight="1">
-      <c r="A128" s="3" t="inlineStr">
+      <c r="B128" s="8"/>
+    </row>
+    <row r="129" ht="66.0" customHeight="1">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・期待ステータス (--expect-status) と一致するまで --url-interval 秒間隔でリトライ
 ・--url-timeout 秒を超えると失敗 (最後の応答コードを表示)
@@ -2051,121 +2068,121 @@
 ・成功・失敗いずれの場合も、応答本文の先頭 20 行を表示</t>
         </is>
       </c>
-      <c r="B128" s="3"/>
-    </row>
-    <row r="129" ht="19.5" customHeight="1">
-      <c r="A129" s="8" t="inlineStr">
+      <c r="B129" s="3"/>
+    </row>
+    <row r="130" ht="19.5" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B129" s="8"/>
-    </row>
-    <row r="130" ht="33.0" customHeight="1">
-      <c r="A130" s="3" t="inlineStr">
+      <c r="B130" s="8"/>
+    </row>
+    <row r="131" ht="33.0" customHeight="1">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup を付けず --verify-url のみを指定した場合もコンテナは起動します
 (起動完了のログ確認は行わず、URL のリトライで readiness を担保します)。</t>
         </is>
       </c>
-      <c r="B130" s="3"/>
-    </row>
-    <row r="131" ht="19.5" customHeight="1">
-      <c r="A131" s="8" t="inlineStr">
+      <c r="B131" s="3"/>
+    </row>
+    <row r="132" ht="19.5" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B131" s="8"/>
-    </row>
-    <row r="132" ht="19.5" customHeight="1">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="B132" s="8"/>
+    </row>
+    <row r="133" ht="19.5" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">状況</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの扱い</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="19.5" customHeight="1">
-      <c r="A133" s="11" t="inlineStr">
+    <row r="134" ht="19.5" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">通常</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down で停止・削除</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="33.0" customHeight="1">
-      <c r="A134" s="11" t="inlineStr">
+    <row r="135" ht="33.0" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--keep-container / --keep-container-mode 指定</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="19.5" customHeight="1">
-      <c r="A135" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
         </is>
       </c>
     </row>
     <row r="136" ht="19.5" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="19.5" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="19.5" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+    <row r="138" ht="19.5" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B137" s="8"/>
-    </row>
-    <row r="138" ht="49.5" customHeight="1">
-      <c r="A138" s="3" t="inlineStr">
+      <c r="B138" s="8"/>
+    </row>
+    <row r="139" ht="49.5" customHeight="1">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの削除後に、--prune-build-cache / --prune-build-cache-keep 指定時はビルド
 キャッシュを削除し、--disk-usage-report 指定時は終了時の使用量と実行前からの増減を
 表示します (5.8-2 参照)。</t>
         </is>
       </c>
-      <c r="B138" s="3"/>
-    </row>
-    <row r="139" ht="19.5" customHeight="1">
-      <c r="A139" s="8" t="inlineStr">
+      <c r="B139" s="3"/>
+    </row>
+    <row r="140" ht="19.5" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B139" s="8"/>
-    </row>
-    <row r="140" ht="66.0" customHeight="1">
-      <c r="A140" s="3" t="inlineStr">
+      <c r="B140" s="8"/>
+    </row>
+    <row r="141" ht="66.0" customHeight="1">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS はタスク停止時に各コンテナへ SIGTERM を送るため、adot collector のような
 サイドカーは「シグナル受信 → パイプラインの graceful shutdown → 終了」までを
@@ -2173,34 +2190,34 @@
 誰にも取得されないままコンテナごと削除されてしまいます。</t>
         </is>
       </c>
-      <c r="B140" s="3"/>
-    </row>
-    <row r="141" ht="19.5" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+      <c r="B141" s="3"/>
+    </row>
+    <row r="142" ht="19.5" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B141" s="8"/>
-    </row>
-    <row r="142" ht="19.5" customHeight="1">
-      <c r="A142" s="3" t="inlineStr">
+      <c r="B142" s="8"/>
+    </row>
+    <row r="143" ht="19.5" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そこでエラー終了時に限り、削除の前に SIGTERM による停止を挟みます。</t>
         </is>
       </c>
-      <c r="B142" s="3"/>
-    </row>
-    <row r="143" ht="19.5" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+      <c r="B143" s="3"/>
+    </row>
+    <row r="144" ht="19.5" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B143" s="8"/>
-    </row>
-    <row r="144" ht="148.5" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
+      <c r="B144" s="8"/>
+    </row>
+    <row r="145" ht="148.5" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">[2] 〜 [6] の収集 (起動中のコンテナが必要)
         ↓
@@ -2213,18 +2230,18 @@
 compose down (削除)</t>
         </is>
       </c>
-      <c r="B144" s="6"/>
-    </row>
-    <row r="145" ht="19.5" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+      <c r="B145" s="6"/>
+    </row>
+    <row r="146" ht="19.5" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B145" s="8"/>
-    </row>
-    <row r="146" ht="165.0" customHeight="1">
-      <c r="A146" s="3" t="inlineStr">
+      <c r="B146" s="8"/>
+    </row>
+    <row r="147" ht="165.0" customHeight="1">
+      <c r="A147" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・対象は compose ps --services が返す稼働中の全サービスです
   (起動確認対象だけでなく adot collector などのサイドカーも含みます)
@@ -2238,458 +2255,458 @@
   従来どおり compose down でまとめて削除します</t>
         </is>
       </c>
-      <c r="B146" s="3"/>
-    </row>
-    <row r="147" ht="19.5" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
+      <c r="B147" s="3"/>
+    </row>
+    <row r="148" ht="19.5" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B147" s="8"/>
-    </row>
-    <row r="148" ht="49.5" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
+      <c r="B148" s="8"/>
+    </row>
+    <row r="149" ht="49.5" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">adot collector の healthcheck が失敗し、depends_on の condition: service_healthy
 を満たせずバックエンドが起動しなかった場合、ECS 上でも同じくタスクが停止します。
 その終了処理まで含めてローカルで再現・確認できるようにするのがこの動作の狙いです。</t>
         </is>
       </c>
-      <c r="B148" s="3"/>
-    </row>
-    <row r="149" ht="19.5" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
+      <c r="B149" s="3"/>
+    </row>
+    <row r="150" ht="19.5" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B149" s="8"/>
-    </row>
-    <row r="150" ht="19.5" customHeight="1">
-      <c r="A150" s="3" t="inlineStr">
+      <c r="B150" s="8"/>
+    </row>
+    <row r="151" ht="19.5" customHeight="1">
+      <c r="A151" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B150" s="3"/>
-    </row>
-    <row r="151" ht="9.0" customHeight="1">
-      <c r="A151" s="0"/>
-    </row>
-    <row r="152" ht="24.0" customHeight="1">
-      <c r="A152" s="5" t="inlineStr">
+      <c r="B151" s="3"/>
+    </row>
+    <row r="152" ht="9.0" customHeight="1">
+      <c r="A152" s="0"/>
+    </row>
+    <row r="153" ht="24.0" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">5. 終了コード</t>
         </is>
       </c>
-      <c r="B152" s="5"/>
-    </row>
-    <row r="153" ht="19.5" customHeight="1">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="B153" s="5"/>
+    </row>
+    <row r="154" ht="19.5" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コード</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">意味</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">主な発生条件</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="33.0" customHeight="1">
-      <c r="A154" s="11" t="inlineStr">
+    <row r="155" ht="33.0" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr">
+      <c r="B155" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">正常終了</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド (と指定した確認) がすべて成功</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="379.5" customHeight="1">
-      <c r="A155" s="11" t="inlineStr">
+    <row r="156" ht="379.5" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B155" s="3" t="inlineStr">
+      <c r="B156" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行時エラー</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="C156" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="409.0" customHeight="1">
-      <c r="A156" s="11" t="inlineStr">
+    <row r="157" ht="409.0" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="B157" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数エラー</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
         </is>
       </c>
-    </row>
-    <row r="157" ht="19.5" customHeight="1">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">本処理が失敗している場合は、後始末の結果にかかわらず元の終了コードが優先されます。</t>
-        </is>
-      </c>
-      <c r="B157" s="3"/>
     </row>
     <row r="158" ht="19.5" customHeight="1">
       <c r="A158" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">本処理が失敗している場合は、後始末の結果にかかわらず元の終了コードが優先されます。</t>
+        </is>
+      </c>
+      <c r="B158" s="3"/>
+    </row>
+    <row r="159" ht="19.5" customHeight="1">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B158" s="3"/>
-    </row>
-    <row r="159" ht="9.0" customHeight="1">
-      <c r="A159" s="0"/>
-    </row>
-    <row r="160" ht="24.0" customHeight="1">
-      <c r="A160" s="5" t="inlineStr">
+      <c r="B159" s="3"/>
+    </row>
+    <row r="160" ht="9.0" customHeight="1">
+      <c r="A160" s="0"/>
+    </row>
+    <row r="161" ht="24.0" customHeight="1">
+      <c r="A161" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">6. 環境変数</t>
         </is>
       </c>
-      <c r="B160" s="5"/>
-    </row>
-    <row r="161" ht="19.5" customHeight="1">
-      <c r="A161" s="8" t="inlineStr">
+      <c r="B161" s="5"/>
+    </row>
+    <row r="162" ht="19.5" customHeight="1">
+      <c r="A162" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.1 入力として参照する環境変数》</t>
         </is>
       </c>
-      <c r="B161" s="8"/>
-    </row>
-    <row r="162" ht="19.5" customHeight="1">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="B162" s="8"/>
+    </row>
+    <row r="163" ht="19.5" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="19.5" customHeight="1">
-      <c r="A163" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
     </row>
     <row r="164" ht="19.5" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
     </row>
     <row r="165" ht="19.5" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
     </row>
     <row r="166" ht="19.5" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
+          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
         </is>
       </c>
     </row>
     <row r="167" ht="19.5" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_COLOR</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">定義されていれば色分けを無効化</t>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
         </is>
       </c>
     </row>
     <row r="168" ht="19.5" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLICOLOR_FORCE</t>
+          <t xml:space="preserve">NO_COLOR</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+          <t xml:space="preserve">定義されていれば色分けを無効化</t>
         </is>
       </c>
     </row>
     <row r="169" ht="19.5" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">CLICOLOR_FORCE</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="19.5" customHeight="1">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">TERM</t>
         </is>
       </c>
-      <c r="B169" s="3" t="inlineStr">
+      <c r="B170" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">dumb の場合は色分けしない</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="19.5" customHeight="1">
-      <c r="A170" s="8" t="inlineStr">
+    <row r="171" ht="19.5" customHeight="1">
+      <c r="A171" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
         </is>
       </c>
-      <c r="B170" s="8"/>
-    </row>
-    <row r="171" ht="19.5" customHeight="1">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="B171" s="8"/>
+    </row>
+    <row r="172" ht="19.5" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="19.5" customHeight="1">
-      <c r="A172" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TZ</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
         </is>
       </c>
     </row>
     <row r="173" ht="19.5" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">TZ</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
         </is>
       </c>
     </row>
     <row r="174" ht="19.5" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="19.5" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="19.5" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="33.0" customHeight="1">
-      <c r="A176" s="11" t="inlineStr">
+    <row r="177" ht="33.0" customHeight="1">
+      <c r="A177" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;--cacert-bundle-env の値&gt;</t>
         </is>
       </c>
-      <c r="B176" s="3" t="inlineStr">
+      <c r="B177" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CA 証明書をまとめた tar のパス。compose の file 型シークレットへ渡す。--cacert-dir 未指定時は「空の tar」のパスが入り、従来どおり証明書なしでビルドされる</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="19.5" customHeight="1">
-      <c r="A177" s="8" t="inlineStr">
+    <row r="178" ht="19.5" customHeight="1">
+      <c r="A178" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B177" s="8"/>
-    </row>
-    <row r="178" ht="49.5" customHeight="1">
-      <c r="A178" s="3" t="inlineStr">
+      <c r="B178" s="8"/>
+    </row>
+    <row r="179" ht="49.5" customHeight="1">
+      <c r="A179" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 / 7.2 はスクリプト自身が実行ホストで参照・設定する環境変数です。
 これとは別に、起動したコンテナ内の環境変数を収集して一覧表示します
 (スクリプトの動作は変えません)。</t>
         </is>
       </c>
-      <c r="B178" s="3"/>
-    </row>
-    <row r="179" ht="19.5" customHeight="1">
-      <c r="A179" s="8" t="inlineStr">
+      <c r="B179" s="3"/>
+    </row>
+    <row r="180" ht="19.5" customHeight="1">
+      <c r="A180" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B179" s="8"/>
-    </row>
-    <row r="180" ht="19.5" customHeight="1">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="B180" s="8"/>
+    </row>
+    <row r="181" ht="19.5" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">出力先</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="33.0" customHeight="1">
-      <c r="A181" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JVM オプションの受け渡し</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
         </is>
       </c>
     </row>
     <row r="182" ht="33.0" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenTelemetry 標準設定</t>
+          <t xml:space="preserve">JVM オプションの受け渡し</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
+          <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
+          <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
         </is>
       </c>
     </row>
     <row r="183" ht="33.0" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">OpenTelemetry 標準設定</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="33.0" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">OpenTelemetry 関連設定</t>
         </is>
       </c>
-      <c r="B183" s="3" t="inlineStr">
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS_XRAY_DAEMON_ADDRESS / AWS_XRAY_CONTEXT_MISSING / AWS_XRAY_TRACING_NAME / AWS_LAMBDA_EXEC_WRAPPER / AOT_CONFIG_CONTENT</t>
         </is>
       </c>
-      <c r="C183" s="3" t="inlineStr">
+      <c r="C184" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="19.5" customHeight="1">
-      <c r="A184" s="11" t="inlineStr">
+    <row r="185" ht="19.5" customHeight="1">
+      <c r="A185" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリ構造の起点</t>
         </is>
       </c>
-      <c r="B184" s="3" t="inlineStr">
+      <c r="B185" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--deployment-dir-env で指定した名前</t>
         </is>
       </c>
-      <c r="C184" s="3" t="inlineStr">
+      <c r="C185" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="19.5" customHeight="1">
-      <c r="A185" s="8" t="inlineStr">
+    <row r="186" ht="19.5" customHeight="1">
+      <c r="A186" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B185" s="8"/>
-    </row>
-    <row r="186" ht="19.5" customHeight="1">
-      <c r="A186" s="3" t="inlineStr">
+      <c r="B186" s="8"/>
+    </row>
+    <row r="187" ht="19.5" customHeight="1">
+      <c r="A187" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B186" s="3"/>
+      <c r="B187" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="77">
@@ -2698,17 +2715,16 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A62:B62"/>
     <mergeCell ref="A83:B83"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="A85:B85"/>
@@ -2716,7 +2732,7 @@
     <mergeCell ref="A87:B87"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A90:B90"/>
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A93:B93"/>
     <mergeCell ref="A94:B94"/>
@@ -2725,15 +2741,15 @@
     <mergeCell ref="A97:B97"/>
     <mergeCell ref="A98:B98"/>
     <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="A100:B100"/>
     <mergeCell ref="A105:B105"/>
     <mergeCell ref="A106:B106"/>
-    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="A107:B107"/>
     <mergeCell ref="A111:B111"/>
     <mergeCell ref="A112:B112"/>
     <mergeCell ref="A113:B113"/>
     <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="A115:B115"/>
     <mergeCell ref="A121:B121"/>
     <mergeCell ref="A122:B122"/>
     <mergeCell ref="A123:B123"/>
@@ -2745,7 +2761,7 @@
     <mergeCell ref="A129:B129"/>
     <mergeCell ref="A130:B130"/>
     <mergeCell ref="A131:B131"/>
-    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A132:B132"/>
     <mergeCell ref="A138:B138"/>
     <mergeCell ref="A139:B139"/>
     <mergeCell ref="A140:B140"/>
@@ -2759,17 +2775,18 @@
     <mergeCell ref="A148:B148"/>
     <mergeCell ref="A149:B149"/>
     <mergeCell ref="A150:B150"/>
-    <mergeCell ref="A152:B152"/>
-    <mergeCell ref="A157:B157"/>
+    <mergeCell ref="A151:B151"/>
+    <mergeCell ref="A153:B153"/>
     <mergeCell ref="A158:B158"/>
-    <mergeCell ref="A160:B160"/>
+    <mergeCell ref="A159:B159"/>
     <mergeCell ref="A161:B161"/>
-    <mergeCell ref="A170:B170"/>
-    <mergeCell ref="A177:B177"/>
+    <mergeCell ref="A162:B162"/>
+    <mergeCell ref="A171:B171"/>
     <mergeCell ref="A178:B178"/>
     <mergeCell ref="A179:B179"/>
-    <mergeCell ref="A185:B185"/>
+    <mergeCell ref="A180:B180"/>
     <mergeCell ref="A186:B186"/>
+    <mergeCell ref="A187:B187"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5466,71 +5483,79 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="33.0" customHeight="1">
+    <row r="92" ht="49.5" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E92" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="93" ht="33.0" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">/ で始まるパス</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E93" s="7"/>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="33.0" customHeight="1">
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="19.5" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-undertow-probe</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5543,78 +5568,90 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E94" s="7"/>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
     <row r="95" ht="33.0" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E95" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="96" ht="33.0" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E96" s="7"/>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="33.0" customHeight="1">
+          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="19.5" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -5627,115 +5664,319 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E97" s="7"/>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
         </is>
       </c>
     </row>
     <row r="98" ht="19.5" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="7"/>
+          <t xml:space="preserve">--no-undertow-analysis</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="99" ht="33.0" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E99" s="7"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
     <row r="100" ht="33.0" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E100" s="7"/>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="101" ht="33.0" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E101" s="7"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="102" ht="33.0" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E102" s="7"/>
       <c r="F102" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="33.0" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E103" s="7"/>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="33.0" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E104" s="7"/>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.9 その他</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-h, --help</t>
+        </is>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="33.0" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="33.0" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="33.0" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="33.0" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F102"/>
+  <autoFilter ref="A4:F109"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -5913,60 +6154,52 @@
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
     </row>
-    <row r="14" ht="9.0" customHeight="1">
-      <c r="A14" s="0"/>
-    </row>
-    <row r="15" ht="24.0" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="14" ht="99.0" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss EAP Undertow バーチャルホスト (default-host) の分析 (Host ヘッダーごとの振り分け判定、default-host の利用状況、Host ヘッダーを差し替えた実リクエストによる確認)</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(起動確認時に既定で自動。無効化は --no-undertow-analysis。テキスト出力は --report-dir / --undertow-analysis-text 指定時)</t>
+        </is>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+    </row>
+    <row r="15" ht="9.0" customHeight="1">
+      <c r="A15" s="0"/>
+    </row>
+    <row r="16" ht="24.0" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値が設定されているパラメータ</t>
         </is>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" ht="19.5" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">分類</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">オプション</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">その既定値での動作</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--local-image NAME</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1/base.local</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose build で生成されるローカルイメージ名</t>
         </is>
       </c>
     </row>
@@ -5978,17 +6211,17 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--compose-file FILE</t>
+          <t xml:space="preserve">--local-image NAME</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml</t>
+          <t xml:space="preserve">j1/base.local</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose 定義ファイル</t>
+          <t xml:space="preserve">compose build で生成されるローカルイメージ名</t>
         </is>
       </c>
     </row>
@@ -6000,39 +6233,39 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--compose-file FILE</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose.yml</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose 定義ファイル</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--compose-service NAME</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">(全サービス)</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド・起動対象。複数指定時は base を先行ビルド。base は起動対象にならない</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33.0" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--build-progress-interval SEC</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
@@ -6044,17 +6277,17 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-stall-timeout SEC</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">300</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
@@ -6066,39 +6299,39 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-timeout SEC</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (無制限)</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
     <row r="23" ht="33.0" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">0 (無制限)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
         </is>
       </c>
     </row>
@@ -6110,17 +6343,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss_master_password</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
         </is>
       </c>
     </row>
@@ -6132,39 +6365,39 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--region REGION</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-secret-id ID</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cacerts</t>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
@@ -6176,17 +6409,17 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle PATH</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">一時ファイル</t>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
@@ -6198,17 +6431,17 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
@@ -6220,39 +6453,39 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-glob PATTERN</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">*.crt と *.pem</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="30" ht="33.0" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">*.crt と *.pem</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6497,7 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -6274,7 +6507,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6519,7 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -6296,7 +6529,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
@@ -6308,39 +6541,39 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="34" ht="33.0" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6585,17 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -6374,17 +6607,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -6396,17 +6629,17 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -6418,17 +6651,17 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -6440,17 +6673,17 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -6462,17 +6695,17 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -6484,39 +6717,39 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="42" ht="33.0" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
@@ -6528,17 +6761,17 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -6550,17 +6783,17 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -6572,17 +6805,17 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -6594,17 +6827,17 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -6616,17 +6849,17 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -6638,17 +6871,17 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -6660,17 +6893,17 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -6682,17 +6915,17 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -6704,17 +6937,17 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -6726,39 +6959,39 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="33.0" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -6770,17 +7003,17 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-method METHOD</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GET</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストメソッド</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -6792,17 +7025,17 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動)</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -6814,17 +7047,17 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -6836,39 +7069,39 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="58" ht="19.5" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+          <t xml:space="preserve">リトライ間隔</t>
         </is>
       </c>
     </row>
@@ -6880,61 +7113,61 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="60" ht="19.5" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="33.0" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
@@ -6946,17 +7179,17 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
@@ -6968,106 +7201,122 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
         </is>
       </c>
     </row>
     <row r="64" ht="33.0" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="33.0" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="33.0" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">有効</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="9.0" customHeight="1">
-      <c r="A65" s="0"/>
-    </row>
-    <row r="66" ht="24.0" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="67" ht="9.0" customHeight="1">
+      <c r="A67" s="0"/>
+    </row>
+    <row r="68" ht="24.0" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
         </is>
       </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-    </row>
-    <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">記載箇所</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-    </row>
-    <row r="68" ht="33.0" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-    </row>
-    <row r="69" ht="33.0" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
     </row>
     <row r="70" ht="33.0" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
       <c r="C70" s="3"/>
@@ -7076,12 +7325,12 @@
     <row r="71" ht="33.0" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C71" s="3"/>
@@ -7090,19 +7339,61 @@
     <row r="72" ht="33.0" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
     </row>
+    <row r="73" ht="33.0" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+    </row>
+    <row r="74" ht="33.0" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+    </row>
+    <row r="75" ht="33.0" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -7115,14 +7406,16 @@
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A68:D68"/>
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="B70:D70"/>
     <mergeCell ref="B71:D71"/>
     <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B75:D75"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-13 05:54:26</t>
+          <t xml:space="preserve">2026-08-13 16:17:49</t>
         </is>
       </c>
     </row>
@@ -5710,68 +5710,76 @@
     <row r="99" ht="33.0" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="19.5" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E99" s="7"/>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="33.0" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(オプション不要)</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E100" s="7"/>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="101" ht="33.0" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5787,7 +5795,7 @@
       <c r="E101" s="7"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -5799,23 +5807,23 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -5827,23 +5835,23 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5863,7 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--prune-build-cache</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -5871,59 +5879,75 @@
       <c r="E104" s="7"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="19.5" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="33.0" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E105" s="7"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="106" ht="33.0" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E106" s="7"/>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C107" s="3"/>
@@ -5931,7 +5955,7 @@
       <c r="E107" s="7"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5967,7 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C108" s="3"/>
@@ -5951,7 +5975,7 @@
       <c r="E108" s="7"/>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5987,7 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">--directory-file-limit N</t>
         </is>
       </c>
       <c r="C109" s="3"/>
@@ -5971,12 +5995,52 @@
       <c r="E109" s="7"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="33.0" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="33.0" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F109"/>
+  <autoFilter ref="A4:F111"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-13 16:17:49</t>
+          <t xml:space="preserve">2026-08-14 18:25:17</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--recreate-containers</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
         </is>
       </c>
     </row>
@@ -4583,27 +4583,27 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--no-recreate-containers</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--suppress-startup-logs</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
         </is>
       </c>
     </row>
@@ -4647,27 +4647,27 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
         </is>
       </c>
     </row>
@@ -4679,83 +4679,91 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="33.0" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="33.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E66" s="7"/>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E67" s="7"/>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -4767,23 +4775,23 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-method METHOD</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
+          <t xml:space="preserve">URL</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストメソッド</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -4795,23 +4803,23 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIME タイプ</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動)</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E69" s="7"/>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -4823,23 +4831,23 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">HTTP メソッド</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -4851,23 +4859,23 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">MIME タイプ</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -4879,23 +4887,23 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">JSON 文字列</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
@@ -4907,23 +4915,23 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">key=value&amp;...</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
         </is>
       </c>
     </row>
@@ -4935,83 +4943,83 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="75" ht="19.5" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="19.5" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="33.0" customHeight="1">
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="19.5" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5019,23 +5027,23 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E77" s="7"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -5047,87 +5055,79 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="79" ht="33.0" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E79" s="7"/>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E80" s="7"/>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
         </is>
       </c>
     </row>
@@ -5139,91 +5139,91 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="33.0" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="33.0" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B82" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="19.5" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
         </is>
       </c>
     </row>
@@ -5235,59 +5235,59 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="19.5" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="33.0" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--report-dir DIR</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -5319,11 +5319,11 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="19.5" customHeight="1">
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="33.0" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5331,17 +5331,17 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5363,17 +5363,17 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -5383,11 +5383,11 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5395,17 +5395,17 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -5427,155 +5427,155 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="33.0" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="33.0" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="19.5" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="49.5" customHeight="1">
-      <c r="A92" s="11" t="inlineStr">
+    <row r="94" ht="49.5" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">可</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="33.0" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="19.5" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
@@ -5587,155 +5587,155 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="33.0" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="33.0" customHeight="1">
-      <c r="A96" s="11" t="inlineStr">
+    <row r="98" ht="33.0" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="19.5" customHeight="1">
-      <c r="A97" s="11" t="inlineStr">
+    <row r="99" ht="19.5" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="33.0" customHeight="1">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B99" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -5767,75 +5767,83 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="101" ht="33.0" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E101" s="7"/>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="33.0" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(オプション不要)</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E102" s="7"/>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="103" ht="33.0" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -5851,7 +5859,7 @@
       <c r="E103" s="7"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -5863,23 +5871,23 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E104" s="7"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -5891,23 +5899,23 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5927,7 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--prune-build-cache</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -5935,59 +5943,75 @@
       <c r="E106" s="7"/>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="19.5" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="33.0" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E107" s="7"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="108" ht="33.0" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E108" s="7"/>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="19.5" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C109" s="3"/>
@@ -5995,7 +6019,7 @@
       <c r="E109" s="7"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6031,7 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C110" s="3"/>
@@ -6015,7 +6039,7 @@
       <c r="E110" s="7"/>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6051,7 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">--directory-file-limit N</t>
         </is>
       </c>
       <c r="C111" s="3"/>
@@ -6035,12 +6059,52 @@
       <c r="E111" s="7"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="33.0" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="33.0" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F111"/>
+  <autoFilter ref="A4:F113"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-14 18:25:17</t>
+          <t xml:space="preserve">2026-08-14 20:41:49</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="33.0" customHeight="1">
+    <row r="12" ht="115.5" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
@@ -544,11 +544,11 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth ほか</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="49.5" customHeight="1">
+          <t xml:space="preserve">--directory-tree (既定は非表示。--directory-tree-depth / --directory-file-limit / --deployment-dir-env 指定時も自動で有効)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="115.5" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -561,7 +561,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env / --env-list-limit</t>
+          <t xml:space="preserve">デプロイ構造は --directory-tree (表示対象の追加は --deployment-dir-env) / 環境変数一覧は起動確認時に自動 (件数は --env-list-limit)</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="33.0" customHeight="1">
+    <row r="83" ht="19.5" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5203,17 +5203,17 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -5223,11 +5223,11 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5235,17 +5235,17 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -5267,31 +5267,31 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="33.0" customHeight="1">
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5299,17 +5299,17 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
@@ -5331,17 +5331,17 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -5363,91 +5363,91 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="33.0" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="49.5" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="33.0" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -5523,59 +5523,59 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="33.0" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="49.5" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
         </is>
       </c>
     </row>
@@ -5587,155 +5587,155 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="33.0" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="19.5" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-readonly-analysis</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="49.5" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="33.0" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--undertow-probe-path PATH</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">/ で始まるパス</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">(WFLYUT0021 から検出)</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B96" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="33.0" customHeight="1">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="33.0" customHeight="1">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="19.5" customHeight="1">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B99" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
+          <t xml:space="preserve">--no-undertow-probe</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5799,11 +5799,11 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="19.5" customHeight="1">
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="33.0" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5831,19 +5831,19 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="33.0" customHeight="1">
+          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="19.5" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -5856,122 +5856,138 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E103" s="7"/>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="33.0" customHeight="1">
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="19.5" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E104" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="105" ht="33.0" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="19.5" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E105" s="7"/>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="33.0" customHeight="1">
-      <c r="A106" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B106" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--prune-build-cache</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E106" s="7"/>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="107" ht="33.0" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -5983,115 +5999,147 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E108" s="7"/>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="19.5" customHeight="1">
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="33.0" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E109" s="7"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="110" ht="33.0" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E110" s="7"/>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="111" ht="33.0" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E111" s="7"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="112" ht="33.0" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E112" s="7"/>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C113" s="3"/>
@@ -6099,12 +6147,212 @@
       <c r="E113" s="7"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリのみ表示</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="33.0" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="33.0" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="33.0" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree</t>
+        </is>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="7"/>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="33.0" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="33.0" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="7"/>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="33.0" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="33.0" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="33.0" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="33.0" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="33.0" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F113"/>
+  <autoFilter ref="A4:F123"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -6201,12 +6449,12 @@
     <row r="8" ht="33.0" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java の JVM パラメータ一覧表示</t>
+          <t xml:space="preserve">コンテナ内ディレクトリツリー表示</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(起動確認時に自動)</t>
+          <t xml:space="preserve">--directory-tree (既定は非表示。--directory-tree-depth / --directory-file-limit / --deployment-dir-env 指定時も自動で有効)</t>
         </is>
       </c>
       <c r="C8" s="10"/>
@@ -6215,12 +6463,12 @@
     <row r="9" ht="33.0" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenTelemetry 環境変数・JVM パラメータ一覧表示</t>
+          <t xml:space="preserve">JBoss デプロイ構造・環境変数一覧の表示</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(起動確認時に自動)</t>
+          <t xml:space="preserve">デプロイ構造は --directory-tree (表示対象の追加は --deployment-dir-env) / 環境変数一覧は起動確認時に自動 (件数は --env-list-limit)</t>
         </is>
       </c>
       <c r="C9" s="10"/>
@@ -6229,149 +6477,133 @@
     <row r="10" ht="33.0" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">世代交代した旧イメージ (dangling) の回収</t>
+          <t xml:space="preserve">Java の JVM パラメータ一覧表示</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定で有効。無効化は --no-reclaim-old-image)</t>
+          <t xml:space="preserve">(起動確認時に自動)</t>
         </is>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
     </row>
-    <row r="11" ht="82.5" customHeight="1">
+    <row r="11" ht="33.0" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent (cwagent) の設定ファイルチェックとコンテナ内設定の照合 (送達レポートは --cwagent-delivery-report 指定時のみ)</t>
+          <t xml:space="preserve">OpenTelemetry 環境変数・JVM パラメータ一覧表示</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(compose.yml に cwagent があれば自動)</t>
+          <t xml:space="preserve">(起動確認時に自動)</t>
         </is>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
     </row>
-    <row r="12" ht="49.5" customHeight="1">
+    <row r="12" ht="33.0" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外エラー解析 (原因分析・対処提案の Excel / テキスト出力)</t>
+          <t xml:space="preserve">世代交代した旧イメージ (dangling) の回収</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(起動確認時に自動。ファイル出力は --report-dir / --deploy-exception-excel / --deploy-exception-text 指定時)</t>
+          <t xml:space="preserve">(既定で有効。無効化は --no-reclaim-old-image)</t>
         </is>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
     </row>
-    <row r="13" ht="115.5" customHeight="1">
+    <row r="13" ht="82.5" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析 (Dockerfile のビルド時と entrypoint.sh などの実行時を分けた、tmpfs / バインドマウントの要否判定と Excel / テキスト出力)</t>
+          <t xml:space="preserve">CloudWatch Agent (cwagent) の設定ファイルチェックとコンテナ内設定の照合 (送達レポートは --cwagent-delivery-report 指定時のみ)</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定で自動。無効化は --no-readonly-analysis。ファイル出力は --report-dir / --readonly-analysis-excel / --readonly-analysis-text 指定時)</t>
+          <t xml:space="preserve">(compose.yml に cwagent があれば自動)</t>
         </is>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
     </row>
-    <row r="14" ht="99.0" customHeight="1">
+    <row r="14" ht="49.5" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss EAP Undertow バーチャルホスト (default-host) の分析 (Host ヘッダーごとの振り分け判定、default-host の利用状況、Host ヘッダーを差し替えた実リクエストによる確認)</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外エラー解析 (原因分析・対処提案の Excel / テキスト出力)</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(起動確認時に既定で自動。無効化は --no-undertow-analysis。テキスト出力は --report-dir / --undertow-analysis-text 指定時)</t>
+          <t xml:space="preserve">(起動確認時に自動。ファイル出力は --report-dir / --deploy-exception-excel / --deploy-exception-text 指定時)</t>
         </is>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
     </row>
-    <row r="15" ht="9.0" customHeight="1">
-      <c r="A15" s="0"/>
-    </row>
-    <row r="16" ht="24.0" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="15" ht="115.5" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析 (Dockerfile のビルド時と entrypoint.sh などの実行時を分けた、tmpfs / バインドマウントの要否判定と Excel / テキスト出力)</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定で自動。無効化は --no-readonly-analysis。ファイル出力は --report-dir / --readonly-analysis-excel / --readonly-analysis-text 指定時)</t>
+        </is>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+    </row>
+    <row r="16" ht="99.0" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss EAP Undertow バーチャルホスト (default-host) の分析 (Host ヘッダーごとの振り分け判定、default-host の利用状況、Host ヘッダーを差し替えた実リクエストによる確認)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(起動確認時に既定で自動。無効化は --no-undertow-analysis。テキスト出力は --report-dir / --undertow-analysis-text 指定時)</t>
+        </is>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+    </row>
+    <row r="17" ht="9.0" customHeight="1">
+      <c r="A17" s="0"/>
+    </row>
+    <row r="18" ht="24.0" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値が設定されているパラメータ</t>
         </is>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">分類</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">オプション</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">その既定値での動作</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--local-image NAME</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1/base.local</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose build で生成されるローカルイメージ名</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--compose-file FILE</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose 定義ファイル</t>
         </is>
       </c>
     </row>
@@ -6383,61 +6615,61 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--local-image NAME</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1/base.local</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose build で生成されるローカルイメージ名</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--compose-file FILE</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose.yml</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose 定義ファイル</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--compose-service NAME</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">(全サービス)</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド・起動対象。複数指定時は base を先行ビルド。base は起動対象にならない</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="33.0" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--build-progress-interval SEC</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="33.0" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--build-stall-timeout SEC</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
@@ -6449,61 +6681,61 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-timeout SEC</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (無制限)</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33.0" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
     <row r="25" ht="33.0" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss_master_password</t>
+          <t xml:space="preserve">0 (無制限)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
         </is>
       </c>
     </row>
@@ -6515,61 +6747,61 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--region REGION</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
         </is>
       </c>
     </row>
     <row r="27" ht="33.0" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-secret-id ID</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cacerts</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="28" ht="33.0" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle PATH</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">一時ファイル</t>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
@@ -6581,17 +6813,17 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
@@ -6603,61 +6835,61 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-glob PATTERN</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">*.crt と *.pem</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
     <row r="31" ht="33.0" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="32" ht="33.0" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">*.crt と *.pem</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6901,7 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -6679,7 +6911,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
@@ -6691,61 +6923,61 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="35" ht="33.0" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="36" ht="33.0" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -6757,17 +6989,17 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -6779,17 +7011,17 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -6801,17 +7033,17 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -6823,17 +7055,17 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -6845,17 +7077,17 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -6867,61 +7099,61 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="33.0" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="44" ht="33.0" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
@@ -6933,17 +7165,17 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -6955,17 +7187,17 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -6977,17 +7209,17 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -6999,17 +7231,17 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -7021,17 +7253,17 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -7043,17 +7275,17 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -7065,17 +7297,17 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -7087,17 +7319,17 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -7109,61 +7341,61 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--up-retry N</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="33.0" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="33.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -7175,17 +7407,17 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動)</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -7197,17 +7429,17 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -7219,309 +7451,433 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="59" ht="19.5" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="60" ht="19.5" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">リトライ間隔</t>
         </is>
       </c>
     </row>
     <row r="61" ht="19.5" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="33.0" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+    <row r="64" ht="19.5" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="33.0" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="33.0" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="33.0" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
         </is>
       </c>
     </row>
     <row r="66" ht="33.0" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="9.0" customHeight="1">
-      <c r="A67" s="0"/>
-    </row>
-    <row r="68" ht="24.0" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
-        </is>
-      </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">記載箇所</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="33.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="33.0" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="33.0" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="33.0" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="33.0" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
-        </is>
-      </c>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-    </row>
-    <row r="72" ht="33.0" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-    </row>
-    <row r="73" ht="33.0" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
-        </is>
-      </c>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-    </row>
-    <row r="74" ht="33.0" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
-        </is>
-      </c>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="9.0" customHeight="1">
+      <c r="A72" s="0"/>
+    </row>
+    <row r="73" ht="24.0" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
+        </is>
+      </c>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">記載箇所</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内容</t>
+        </is>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
     </row>
     <row r="75" ht="33.0" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
     </row>
+    <row r="76" ht="33.0" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
+        </is>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+    </row>
+    <row r="77" ht="33.0" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+        </is>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+    </row>
+    <row r="78" ht="33.0" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+        </is>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+    </row>
+    <row r="79" ht="33.0" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+    </row>
+    <row r="81" ht="33.0" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="25">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -7535,15 +7891,18 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A73:D73"/>
     <mergeCell ref="B74:D74"/>
     <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B81:D81"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7807,7 +8166,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="49.5" customHeight="1">
+    <row r="17" ht="66.0" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
@@ -7815,118 +8174,155 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートとコンテナ内ツリーを保存
-(JVM パラメータと OpenTelemetry 設定も同じレポートへ保存される)</t>
+          <t xml:space="preserve">全量レポートを保存 (ツリーは画面・レポートとも既定では出さない)
+(JVM パラメータと OpenTelemetry 設定は指定不要で同じレポートへ保存される)</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup --report-dir ./reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="49.5" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11-2</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面にもレポートにもコンテナ内ツリーを出す
+--directory-tree-depth / --directory-file-limit を付けると画面表示は自動で有効になる</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
-    --report-dir ./reports --directory-tree-depth 3 --directory-file-limit 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="33.0" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    --report-dir ./reports --directory-tree-report \
+    --directory-tree-depth 3 --directory-file-limit 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33.0" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11-3</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面には出さず、全量レポートにだけツリーを残す</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --report-dir ./reports --directory-tree-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="33.0" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">デプロイ構造を環境変数から特定して表示</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">デプロイ構造を環境変数から特定して表示 (指定すると画面表示が有効になる)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --deployment-dir-env JBOSS_HOME,APP_DEPLOY_DIR</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="49.5" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="21" ht="49.5" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">認証情報を一時配置してビルド
 (コピー先に .npmrc があっても強制上書きし、終了時に元のファイルへ戻す)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --copy-file .npmrc:./app</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="33.0" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="22" ht="33.0" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">13-2</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">コピー先の既存ファイルには一切触れず、あれば中止する</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --copy-file-no-overwrite --copy-file .npmrc:./app</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="33.0" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="23" ht="33.0" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアのマスターパスワードを使ってビルド</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --jboss-password-param /j1/jboss/master-password</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="66.0" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="24" ht="66.0" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-2</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">マスターパスワードが実行時の値まで一致しているかを検証
 (standalone.xml と CredentialStore まで見るので起動確認と併用する)</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">export JBOSS_MASTER_PASSWORD='pa$w#o"r`d&amp;x'
 ./build_and_verify.sh --verify-startup --verify-jboss-password</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="49.5" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="25" ht="49.5" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-3</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアから取得した値で検証し、平文は伏せる</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --jboss-password-param /j1/jboss/master-password \
@@ -7934,18 +8330,18 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="49.5" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="26" ht="49.5" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-4</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">既定以外のパスに設定ファイル・CredentialStore がある場合</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --verify-jboss-password \
     --jboss-config-file /opt/eap/standalone/configuration/standalone-full.xml \
@@ -7953,37 +8349,37 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="66.0" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="27" ht="66.0" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-5</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">cwagent の設定ファイルチェックとコンテナ内設定の照合を行う
 (compose.yml に cwagent があれば自動。送達レポートは既定では行わない)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent,cloudwatch-logs-mock --startup-service app</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="66.0" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="28" ht="66.0" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-6</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">送達レポートまで行い、送達待ちを 3 分へ延ばして届かなければビルド失敗とする</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent,cloudwatch-logs-mock --startup-service app \
@@ -7992,19 +8388,19 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="66.0" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="29" ht="66.0" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-7</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">実 CloudWatch Logs のロググループへ届いたかを aws logs で確認する
 (ロググループが無ければ設定ファイルの名前で作成してから確認する)</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent --startup-service app \
@@ -8013,101 +8409,101 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="33.0" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="30" ht="33.0" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">検証後に Docker を完全クリーンアップ (確認フレーズ入力が必要)</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --cleanup-all-docker-data</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="82.5" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="31" ht="82.5" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15-2</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ディスクを増やさずに --no-cache の検証を回す
 旧世代イメージの回収は既定で有効。ビルドキャッシュは 10GB まで残して削除し、
 実行前からの増減を表示する</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --no-cache --verify-startup \
     --disk-usage-report --prune-build-cache-keep 10GB</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15-3</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">使用量の増減だけを先に測る (削除は行わない)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --no-cache --disk-usage-report</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="33.0" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="33" ht="33.0" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15-4</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">世代を比較したいので旧イメージを残す (調査用)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --no-cache --no-reclaim-old-image</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="33.0" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="34" ht="33.0" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh 経由での呼び出し (同じ処理)</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_push.sh --build-only --verify-startup --log-dir ./logs</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="115.5" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="35" ht="115.5" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイ結果ファイルと Java 例外解析 (Excel + テキスト) をまとめて保存
 (reports/build_and_verify_&lt;日時&gt;.txt、
@@ -8115,7 +8511,7 @@
 reports/build_and_verify_&lt;日時&gt;_java_exceptions.txt が出力される)</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -8123,18 +8519,18 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="66.0" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="36" ht="66.0" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-2</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析の Excel / テキストを任意のパスへ出力する</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -8143,30 +8539,30 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="33.0" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="37" ht="33.0" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-3</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析を行わない (ログ量を抑えたい場合)</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-deploy-exception-analysis</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="148.5" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="38" ht="148.5" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-4</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
 既定で毎回実行される。--report-dir があれば
@@ -8175,7 +8571,7 @@
 対象から外し、entrypoint.sh などが起動のたびに書く場所を「要対応」に挙げる</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -8183,18 +8579,18 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="66.0" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="39" ht="66.0" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-5</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel / テキストを任意のパスへ出力する</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -8203,53 +8599,53 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="33.0" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="40" ht="33.0" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-6</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの分析を行わない</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-readonly-analysis</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="66.0" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="41" ht="66.0" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
 進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="33.0" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="42" ht="33.0" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
         </is>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-14 20:41:49</t>
+          <t xml:space="preserve">2026-08-21 03:45:20</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="99.0" customHeight="1">
+    <row r="23" ht="148.5" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
@@ -731,7 +731,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(起動確認時に自動。ファイル出力は --report-dir / --deploy-exception-excel / --deploy-exception-text 指定時)</t>
+          <t xml:space="preserve">(起動確認時に自動。結果は全量レポート [10] と Excel へ。画面表示は --deploy-exception-display 指定時のみ、テキスト出力は --deploy-exception-text 指定時のみ)</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="66.0" customHeight="1">
+    <row r="79" ht="115.5" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析</t>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyze_war_deploy_exceptions / collect_deploy_exception_logs / resolve_analysis_output_path / show_war_deploy_exception_analysis / append_deploy_exception_report</t>
+          <t xml:space="preserve">analyze_war_deploy_exceptions / deploy_exception_output_requested / collect_deploy_exception_logs / resolve_analysis_output_path / show_war_deploy_exception_analysis / show_war_deploy_exception_outputs / append_deploy_exception_report</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、画面表示と Excel 出力</t>
+          <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、出力先の要否判定、画面表示 (--deploy-exception-display 指定時) と Excel / テキスト出力</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B85" s="8"/>
     </row>
-    <row r="86" ht="264.0" customHeight="1">
+    <row r="86" ht="379.5" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1. analyze_war_deploy_exceptions … デプロイ処理の Java 例外を解析 (削除より前・レポートより前)
@@ -1649,15 +1649,22 @@
 3. write_build_report        … --report-dir 指定時、全量レポートを保存 (削除より前に実行)
 4. cleanup_all_docker_data   … --cleanup-all-docker-data 指定時、確認フレーズ入力後に全削除
 5. teardown_container        … compose down (--keep-container 指定時は残す)
-6. prune_build_cache         … --prune-build-cache / --prune-build-cache-keep 指定時、
+                                   対話操作を最後まで終えた実行では、--keep-container が
+                                   暗黙有効でもここで削除する (6 の対象にするため)
+6. run_post_interaction_cleanup … 対話操作を最後まで終えた実行 (かつ終了コード 0) のとき、
+                                   docker-usage-check.sh --clean all --force で
+                                   未使用リソースを完全クリア (→ 5.4-2)
+7. prune_build_cache         … --prune-build-cache / --prune-build-cache-keep 指定時、
                                    ビルドキャッシュを削除 (コンテナ削除の後)
-7. report_disk_usage_at_exit … --disk-usage-report 指定時、終了時の使用量と増減を表示
+8. report_disk_usage_at_exit … --disk-usage-report 指定時、終了時の使用量と増減を表示
                                    (4 が実際に削除を行った場合は重複するため出さない)
-8. cleanup_copied_files      … --copy-file でコピーしたファイルを削除
+9. cleanup_copied_files      … --copy-file でコピーしたファイルを削除
                                    (既存ファイルを強制上書きした分は削除せず、
                                     退避しておいた上書き前のファイルを復元)
-9. 一時ファイル削除          … Java 例外解析結果・読み取り専用 FS 分析結果・
-                                   URL 応答本文・HTTP ボディ・healthcheck 診断</t>
+10. 一時ファイル削除         … Java 例外解析結果・読み取り専用 FS 分析結果・
+                                   URL 応答本文・HTTP ボディ・healthcheck 診断
+11. show_post_interaction_disk_free … 6 を試行した実行のみ、各ディレクトリの
+                                   ディスク空き容量を一覧表示して終える</t>
         </is>
       </c>
       <c r="B86" s="6"/>
@@ -2119,70 +2126,94 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="33.0" customHeight="1">
+    <row r="135" ht="49.5" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container / --keep-container-mode 指定</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作をすべて終了し、終了コードが 0</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">compose down で削除したうえで、未使用リソースまで完全クリア (→ 5.4-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="33.0" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container / --keep-container-mode 指定 (上記以外)</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="19.5" customHeight="1">
-      <c r="A136" s="11" t="inlineStr">
+    <row r="137" ht="33.0" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container-after-interaction 指定</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">対話操作を終えても残す (従来の動作)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="19.5" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="19.5" customHeight="1">
-      <c r="A137" s="11" t="inlineStr">
+    <row r="139" ht="19.5" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="19.5" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
+    <row r="140" ht="19.5" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B138" s="8"/>
-    </row>
-    <row r="139" ht="49.5" customHeight="1">
-      <c r="A139" s="3" t="inlineStr">
+      <c r="B140" s="8"/>
+    </row>
+    <row r="141" ht="49.5" customHeight="1">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの削除後に、--prune-build-cache / --prune-build-cache-keep 指定時はビルド
 キャッシュを削除し、--disk-usage-report 指定時は終了時の使用量と実行前からの増減を
 表示します (5.8-2 参照)。</t>
         </is>
       </c>
-      <c r="B139" s="3"/>
-    </row>
-    <row r="140" ht="19.5" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+      <c r="B141" s="3"/>
+    </row>
+    <row r="142" ht="19.5" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B140" s="8"/>
-    </row>
-    <row r="141" ht="66.0" customHeight="1">
-      <c r="A141" s="3" t="inlineStr">
+      <c r="B142" s="8"/>
+    </row>
+    <row r="143" ht="66.0" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS はタスク停止時に各コンテナへ SIGTERM を送るため、adot collector のような
 サイドカーは「シグナル受信 → パイプラインの graceful shutdown → 終了」までを
@@ -2190,22 +2221,6 @@
 誰にも取得されないままコンテナごと削除されてしまいます。</t>
         </is>
       </c>
-      <c r="B141" s="3"/>
-    </row>
-    <row r="142" ht="19.5" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
-        </is>
-      </c>
-      <c r="B142" s="8"/>
-    </row>
-    <row r="143" ht="19.5" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">そこでエラー終了時に限り、削除の前に SIGTERM による停止を挟みます。</t>
-        </is>
-      </c>
       <c r="B143" s="3"/>
     </row>
     <row r="144" ht="19.5" customHeight="1">
@@ -2216,8 +2231,24 @@
       </c>
       <c r="B144" s="8"/>
     </row>
-    <row r="145" ht="148.5" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
+    <row r="145" ht="19.5" customHeight="1">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">そこでエラー終了時に限り、削除の前に SIGTERM による停止を挟みます。</t>
+        </is>
+      </c>
+      <c r="B145" s="3"/>
+    </row>
+    <row r="146" ht="19.5" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
+        </is>
+      </c>
+      <c r="B146" s="8"/>
+    </row>
+    <row r="147" ht="148.5" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">[2] 〜 [6] の収集 (起動中のコンテナが必要)
         ↓
@@ -2230,18 +2261,18 @@
 compose down (削除)</t>
         </is>
       </c>
-      <c r="B145" s="6"/>
-    </row>
-    <row r="146" ht="19.5" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="B147" s="6"/>
+    </row>
+    <row r="148" ht="19.5" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B146" s="8"/>
-    </row>
-    <row r="147" ht="165.0" customHeight="1">
-      <c r="A147" s="3" t="inlineStr">
+      <c r="B148" s="8"/>
+    </row>
+    <row r="149" ht="165.0" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・対象は compose ps --services が返す稼働中の全サービスです
   (起動確認対象だけでなく adot collector などのサイドカーも含みます)
@@ -2255,458 +2286,458 @@
   従来どおり compose down でまとめて削除します</t>
         </is>
       </c>
-      <c r="B147" s="3"/>
-    </row>
-    <row r="148" ht="19.5" customHeight="1">
-      <c r="A148" s="8" t="inlineStr">
+      <c r="B149" s="3"/>
+    </row>
+    <row r="150" ht="19.5" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B148" s="8"/>
-    </row>
-    <row r="149" ht="49.5" customHeight="1">
-      <c r="A149" s="3" t="inlineStr">
+      <c r="B150" s="8"/>
+    </row>
+    <row r="151" ht="49.5" customHeight="1">
+      <c r="A151" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">adot collector の healthcheck が失敗し、depends_on の condition: service_healthy
 を満たせずバックエンドが起動しなかった場合、ECS 上でも同じくタスクが停止します。
 その終了処理まで含めてローカルで再現・確認できるようにするのがこの動作の狙いです。</t>
         </is>
       </c>
-      <c r="B149" s="3"/>
-    </row>
-    <row r="150" ht="19.5" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
+      <c r="B151" s="3"/>
+    </row>
+    <row r="152" ht="19.5" customHeight="1">
+      <c r="A152" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B150" s="8"/>
-    </row>
-    <row r="151" ht="19.5" customHeight="1">
-      <c r="A151" s="3" t="inlineStr">
+      <c r="B152" s="8"/>
+    </row>
+    <row r="153" ht="19.5" customHeight="1">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B151" s="3"/>
-    </row>
-    <row r="152" ht="9.0" customHeight="1">
-      <c r="A152" s="0"/>
-    </row>
-    <row r="153" ht="24.0" customHeight="1">
-      <c r="A153" s="5" t="inlineStr">
+      <c r="B153" s="3"/>
+    </row>
+    <row r="154" ht="9.0" customHeight="1">
+      <c r="A154" s="0"/>
+    </row>
+    <row r="155" ht="24.0" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">5. 終了コード</t>
         </is>
       </c>
-      <c r="B153" s="5"/>
-    </row>
-    <row r="154" ht="19.5" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="B155" s="5"/>
+    </row>
+    <row r="156" ht="19.5" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コード</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">意味</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">主な発生条件</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="33.0" customHeight="1">
-      <c r="A155" s="11" t="inlineStr">
+    <row r="157" ht="33.0" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="B155" s="3" t="inlineStr">
+      <c r="B157" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">正常終了</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド (と指定した確認) がすべて成功</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="379.5" customHeight="1">
-      <c r="A156" s="11" t="inlineStr">
+    <row r="158" ht="409.0" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="B158" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行時エラー</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="409.0" customHeight="1">
-      <c r="A157" s="11" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、対話操作の終了後の完全クリーンアップ失敗 (docker-usage-check.sh が見つからない・失敗した)、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="409.0" customHeight="1">
+      <c r="A159" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B157" s="3" t="inlineStr">
+      <c r="B159" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数エラー</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="19.5" customHeight="1">
-      <c r="A158" s="3" t="inlineStr">
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="19.5" customHeight="1">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">本処理が失敗している場合は、後始末の結果にかかわらず元の終了コードが優先されます。</t>
         </is>
       </c>
-      <c r="B158" s="3"/>
-    </row>
-    <row r="159" ht="19.5" customHeight="1">
-      <c r="A159" s="3" t="inlineStr">
+      <c r="B160" s="3"/>
+    </row>
+    <row r="161" ht="19.5" customHeight="1">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B159" s="3"/>
-    </row>
-    <row r="160" ht="9.0" customHeight="1">
-      <c r="A160" s="0"/>
-    </row>
-    <row r="161" ht="24.0" customHeight="1">
-      <c r="A161" s="5" t="inlineStr">
+      <c r="B161" s="3"/>
+    </row>
+    <row r="162" ht="9.0" customHeight="1">
+      <c r="A162" s="0"/>
+    </row>
+    <row r="163" ht="24.0" customHeight="1">
+      <c r="A163" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">6. 環境変数</t>
         </is>
       </c>
-      <c r="B161" s="5"/>
-    </row>
-    <row r="162" ht="19.5" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
+      <c r="B163" s="5"/>
+    </row>
+    <row r="164" ht="19.5" customHeight="1">
+      <c r="A164" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.1 入力として参照する環境変数》</t>
         </is>
       </c>
-      <c r="B162" s="8"/>
-    </row>
-    <row r="163" ht="19.5" customHeight="1">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="B164" s="8"/>
+    </row>
+    <row r="165" ht="19.5" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="19.5" customHeight="1">
-      <c r="A164" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="19.5" customHeight="1">
-      <c r="A165" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
     </row>
     <row r="166" ht="19.5" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
     </row>
     <row r="167" ht="19.5" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
+          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
     </row>
     <row r="168" ht="19.5" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_COLOR</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">定義されていれば色分けを無効化</t>
+          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
         </is>
       </c>
     </row>
     <row r="169" ht="19.5" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLICOLOR_FORCE</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
         </is>
       </c>
     </row>
     <row r="170" ht="19.5" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">NO_COLOR</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定義されていれば色分けを無効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="19.5" customHeight="1">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLICOLOR_FORCE</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="19.5" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">TERM</t>
         </is>
       </c>
-      <c r="B170" s="3" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">dumb の場合は色分けしない</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="19.5" customHeight="1">
-      <c r="A171" s="8" t="inlineStr">
+    <row r="173" ht="19.5" customHeight="1">
+      <c r="A173" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
         </is>
       </c>
-      <c r="B171" s="8"/>
-    </row>
-    <row r="172" ht="19.5" customHeight="1">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="B173" s="8"/>
+    </row>
+    <row r="174" ht="19.5" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="19.5" customHeight="1">
-      <c r="A173" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TZ</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="19.5" customHeight="1">
-      <c r="A174" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="19.5" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+          <t xml:space="preserve">TZ</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
         </is>
       </c>
     </row>
     <row r="176" ht="19.5" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="19.5" customHeight="1">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="19.5" customHeight="1">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B176" s="3" t="inlineStr">
+      <c r="B178" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="33.0" customHeight="1">
-      <c r="A177" s="11" t="inlineStr">
+    <row r="179" ht="33.0" customHeight="1">
+      <c r="A179" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;--cacert-bundle-env の値&gt;</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B179" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CA 証明書をまとめた tar のパス。compose の file 型シークレットへ渡す。--cacert-dir 未指定時は「空の tar」のパスが入り、従来どおり証明書なしでビルドされる</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="19.5" customHeight="1">
-      <c r="A178" s="8" t="inlineStr">
+    <row r="180" ht="19.5" customHeight="1">
+      <c r="A180" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B178" s="8"/>
-    </row>
-    <row r="179" ht="49.5" customHeight="1">
-      <c r="A179" s="3" t="inlineStr">
+      <c r="B180" s="8"/>
+    </row>
+    <row r="181" ht="49.5" customHeight="1">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 / 7.2 はスクリプト自身が実行ホストで参照・設定する環境変数です。
 これとは別に、起動したコンテナ内の環境変数を収集して一覧表示します
 (スクリプトの動作は変えません)。</t>
         </is>
       </c>
-      <c r="B179" s="3"/>
-    </row>
-    <row r="180" ht="19.5" customHeight="1">
-      <c r="A180" s="8" t="inlineStr">
+      <c r="B181" s="3"/>
+    </row>
+    <row r="182" ht="19.5" customHeight="1">
+      <c r="A182" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B180" s="8"/>
-    </row>
-    <row r="181" ht="19.5" customHeight="1">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="B182" s="8"/>
+    </row>
+    <row r="183" ht="19.5" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">出力先</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="33.0" customHeight="1">
-      <c r="A182" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JVM オプションの受け渡し</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="33.0" customHeight="1">
-      <c r="A183" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OpenTelemetry 標準設定</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
     <row r="184" ht="33.0" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">JVM オプションの受け渡し</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="33.0" customHeight="1">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenTelemetry 標準設定</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="33.0" customHeight="1">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">OpenTelemetry 関連設定</t>
         </is>
       </c>
-      <c r="B184" s="3" t="inlineStr">
+      <c r="B186" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS_XRAY_DAEMON_ADDRESS / AWS_XRAY_CONTEXT_MISSING / AWS_XRAY_TRACING_NAME / AWS_LAMBDA_EXEC_WRAPPER / AOT_CONFIG_CONTENT</t>
         </is>
       </c>
-      <c r="C184" s="3" t="inlineStr">
+      <c r="C186" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="19.5" customHeight="1">
-      <c r="A185" s="11" t="inlineStr">
+    <row r="187" ht="19.5" customHeight="1">
+      <c r="A187" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリ構造の起点</t>
         </is>
       </c>
-      <c r="B185" s="3" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--deployment-dir-env で指定した名前</t>
         </is>
       </c>
-      <c r="C185" s="3" t="inlineStr">
+      <c r="C187" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="19.5" customHeight="1">
-      <c r="A186" s="8" t="inlineStr">
+    <row r="188" ht="19.5" customHeight="1">
+      <c r="A188" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B186" s="8"/>
-    </row>
-    <row r="187" ht="19.5" customHeight="1">
-      <c r="A187" s="3" t="inlineStr">
+      <c r="B188" s="8"/>
+    </row>
+    <row r="189" ht="19.5" customHeight="1">
+      <c r="A189" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B187" s="3"/>
+      <c r="B189" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="77">
@@ -2762,8 +2793,6 @@
     <mergeCell ref="A130:B130"/>
     <mergeCell ref="A131:B131"/>
     <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A138:B138"/>
-    <mergeCell ref="A139:B139"/>
     <mergeCell ref="A140:B140"/>
     <mergeCell ref="A141:B141"/>
     <mergeCell ref="A142:B142"/>
@@ -2776,17 +2805,19 @@
     <mergeCell ref="A149:B149"/>
     <mergeCell ref="A150:B150"/>
     <mergeCell ref="A151:B151"/>
+    <mergeCell ref="A152:B152"/>
     <mergeCell ref="A153:B153"/>
-    <mergeCell ref="A158:B158"/>
-    <mergeCell ref="A159:B159"/>
+    <mergeCell ref="A155:B155"/>
+    <mergeCell ref="A160:B160"/>
     <mergeCell ref="A161:B161"/>
-    <mergeCell ref="A162:B162"/>
-    <mergeCell ref="A171:B171"/>
-    <mergeCell ref="A178:B178"/>
-    <mergeCell ref="A179:B179"/>
+    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="A173:B173"/>
     <mergeCell ref="A180:B180"/>
-    <mergeCell ref="A186:B186"/>
-    <mergeCell ref="A187:B187"/>
+    <mergeCell ref="A181:B181"/>
+    <mergeCell ref="A182:B182"/>
+    <mergeCell ref="A188:B188"/>
+    <mergeCell ref="A189:B189"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5134,44 +5165,40 @@
     <row r="81" ht="33.0" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--keep-container-after-interaction</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E81" s="7"/>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
         </is>
       </c>
     </row>
     <row r="82" ht="19.5" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -5179,83 +5206,75 @@
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
         </is>
       </c>
     </row>
     <row r="83" ht="19.5" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-free-path DIR</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="E83" s="7"/>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="33.0" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="19.5" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B84" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
         </is>
       </c>
     </row>
@@ -5267,17 +5286,17 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--env-list-file FILE</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -5287,7 +5306,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
         </is>
       </c>
     </row>
@@ -5299,155 +5318,155 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="19.5" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="33.0" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
+    <row r="90" ht="33.0" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B87" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="33.0" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B88" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="33.0" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="49.5" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir DIR</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -5459,17 +5478,17 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -5479,7 +5498,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -5491,12 +5510,12 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -5506,44 +5525,44 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="66.0" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5574,7 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--deploy-exception-display</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5563,9 +5582,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -5575,11 +5594,11 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="33.0" customHeight="1">
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5587,17 +5606,17 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -5607,7 +5626,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -5619,91 +5638,91 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--report-dir 指定時は未指定でも自動出力。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="33.0" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="19.5" customHeight="1">
-      <c r="A97" s="11" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="49.5" customHeight="1">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -5715,17 +5734,17 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
@@ -5735,11 +5754,11 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="19.5" customHeight="1">
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="33.0" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5747,17 +5766,17 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -5767,7 +5786,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5779,199 +5798,199 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-readonly-analysis</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="49.5" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="33.0" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="33.0" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="33.0" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="19.5" customHeight="1">
-      <c r="A103" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B103" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="19.5" customHeight="1">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B104" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="33.0" customHeight="1">
-      <c r="A105" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B105" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="19.5" customHeight="1">
-      <c r="A106" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B106" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="107" ht="33.0" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -5984,50 +6003,58 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E107" s="7"/>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="33.0" customHeight="1">
+          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="19.5" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E108" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="33.0" customHeight="1">
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="19.5" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -6040,78 +6067,90 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E109" s="7"/>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="110" ht="33.0" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="19.5" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E110" s="7"/>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="33.0" customHeight="1">
-      <c r="A111" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E111" s="7"/>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="112" ht="33.0" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -6127,119 +6166,159 @@
       <c r="E112" s="7"/>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="19.5" customHeight="1">
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="33.0" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E113" s="7"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="114" ht="33.0" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E114" s="7"/>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="115" ht="33.0" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E115" s="7"/>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="116" ht="33.0" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E116" s="7"/>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="117" ht="33.0" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E117" s="7"/>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="19.5" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C118" s="3"/>
@@ -6247,7 +6326,7 @@
       <c r="E118" s="7"/>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6338,7 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C119" s="3"/>
@@ -6267,7 +6346,7 @@
       <c r="E119" s="7"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6358,7 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C120" s="3"/>
@@ -6287,7 +6366,7 @@
       <c r="E120" s="7"/>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6378,7 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C121" s="3"/>
@@ -6307,7 +6386,7 @@
       <c r="E121" s="7"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6398,7 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C122" s="3"/>
@@ -6327,7 +6406,7 @@
       <c r="E122" s="7"/>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6418,7 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C123" s="3"/>
@@ -6347,12 +6426,112 @@
       <c r="E123" s="7"/>
       <c r="F123" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="33.0" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="33.0" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="33.0" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="33.0" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="7"/>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="33.0" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="7"/>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F123"/>
+  <autoFilter ref="A4:F128"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -6538,7 +6717,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(起動確認時に自動。ファイル出力は --report-dir / --deploy-exception-excel / --deploy-exception-text 指定時)</t>
+          <t xml:space="preserve">(起動確認時に自動。結果は全量レポート [10] と Excel へ。画面表示は --deploy-exception-display 指定時のみ、テキスト出力は --deploy-exception-text 指定時のみ)</t>
         </is>
       </c>
       <c r="C14" s="10"/>
@@ -7556,44 +7735,44 @@
     <row r="63" ht="19.5" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">(自動解決)</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
         </is>
       </c>
     </row>
     <row r="64" ht="19.5" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--disk-free-path DIR</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">(既定の 7 か所)</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
         </is>
       </c>
     </row>
@@ -7605,61 +7784,61 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="19.5" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="33.0" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="33.0" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -7671,17 +7850,17 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
@@ -7693,17 +7872,17 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -7715,120 +7894,144 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
     <row r="71" ht="33.0" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="33.0" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="33.0" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="33.0" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">有効</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="9.0" customHeight="1">
-      <c r="A72" s="0"/>
-    </row>
-    <row r="73" ht="24.0" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
+    <row r="75" ht="9.0" customHeight="1">
+      <c r="A75" s="0"/>
+    </row>
+    <row r="76" ht="24.0" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
         </is>
       </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-    </row>
-    <row r="74" ht="19.5" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">記載箇所</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-    </row>
-    <row r="75" ht="33.0" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-    </row>
-    <row r="76" ht="33.0" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
-        </is>
-      </c>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-    </row>
-    <row r="77" ht="33.0" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
-        </is>
-      </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
     </row>
     <row r="78" ht="33.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
       <c r="C78" s="3"/>
@@ -7837,26 +8040,26 @@
     <row r="79" ht="33.0" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
     </row>
-    <row r="80" ht="33.0" customHeight="1">
+    <row r="80" ht="49.5" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">5.4-2 デプロイエラー時の調査モード (既定) / --exit-on-deploy-error</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">対話の前 / 失敗した起動ログを表示し、WAR デプロイ時 Java 例外解析を先に済ませる (画面へ出すのは --deploy-exception-display 指定時。既定では全量レポート [10] と Excel へ残すだけ)</t>
         </is>
       </c>
       <c r="C80" s="3"/>
@@ -7865,19 +8068,75 @@
     <row r="81" ht="33.0" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
     </row>
+    <row r="82" ht="33.0" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+        </is>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+    </row>
+    <row r="83" ht="33.0" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+    </row>
+    <row r="84" ht="33.0" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+    </row>
+    <row r="85" ht="33.0" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -7894,15 +8153,16 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="A76:D76"/>
     <mergeCell ref="B77:D77"/>
     <mergeCell ref="B78:D78"/>
     <mergeCell ref="B79:D79"/>
     <mergeCell ref="B80:D80"/>
     <mergeCell ref="B81:D81"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B85:D85"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8505,10 +8765,10 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイ結果ファイルと Java 例外解析 (Excel + テキスト) をまとめて保存
-(reports/build_and_verify_&lt;日時&gt;.txt、
-reports/build_and_verify_&lt;日時&gt;_java_exceptions.xlsx、
-reports/build_and_verify_&lt;日時&gt;_java_exceptions.txt が出力される)</t>
+          <t xml:space="preserve">デプロイ結果ファイルと Java 例外解析の Excel をまとめて保存
+(reports/build_and_verify_&lt;日時&gt;.txt … [10] に例外解析の全文、
+reports/build_and_verify_&lt;日時&gt;_java_exceptions.xlsx が出力される。
+画面には解析結果を出さない ← 既定)</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -8527,10 +8787,31 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析の Excel / テキストを任意のパスへ出力する</t>
+          <t xml:space="preserve">解析結果を画面でも読む (既定は非表示)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --report-dir ./reports \
+    --deploy-exception-display</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="66.0" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-3</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Java 例外解析の Excel / テキストを任意のパスへ出力する
+(テキストは --deploy-exception-text を指定したときだけ出力される)</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -8539,30 +8820,30 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="33.0" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-3</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Java 例外解析を行わない (ログ量を抑えたい場合)</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-4</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Java 例外解析を行わない (解析処理ごと省く)</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-deploy-exception-analysis</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="148.5" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-4</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
+    <row r="39" ht="148.5" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-5</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
 既定で毎回実行される。--report-dir があれば
@@ -8571,7 +8852,7 @@
 対象から外し、entrypoint.sh などが起動のたびに書く場所を「要対応」に挙げる</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -8579,18 +8860,18 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="66.0" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-5</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
+    <row r="40" ht="66.0" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-6</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel / テキストを任意のパスへ出力する</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -8599,53 +8880,53 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="33.0" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-6</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
+    <row r="41" ht="33.0" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-7</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの分析を行わない</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-readonly-analysis</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="66.0" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="42" ht="66.0" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
 進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="33.0" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="43" ht="33.0" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
         </is>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-21 03:45:20</t>
+          <t xml:space="preserve">2026-08-22 04:58:59</t>
         </is>
       </c>
     </row>
@@ -769,280 +769,280 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="26" ht="115.5" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コピーしたファイル (WAR など) の取り込み検証 (差し替えたファイルが本当にコンテナへ届いているかを SHA-256 で照合し、届いていなければエラー終了)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(--copy-file 指定時は既定で自動。無効化は --no-verify-copy-artifact。未検出もエラーにするのは --copy-artifact-required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="99.0" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後始末でのボリューム削除 (デプロイ先を覆っているボリュームを残さない)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(対話操作をすべて終えた実行では既定で compose down -v。常に削除は --remove-volumes、残すのは --keep-volumes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《できること》</t>
         </is>
       </c>
-      <c r="B26" s="8"/>
-    </row>
-    <row r="27" ht="33.0" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="B28" s="8"/>
+    </row>
+    <row r="29" ht="33.0" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup も --verify-url も指定しなければ、純粋にビルドのみを行って終了します
 (従来の build_and_push.sh --build-only 相当)。</t>
         </is>
       </c>
-      <c r="B27" s="3"/>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《行わないこと》</t>
-        </is>
-      </c>
-      <c r="B28" s="8"/>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ECR 権限チェック / ECR ログイン / タグ付け / プッシュ / imagedefinition.json の出力。</t>
-        </is>
-      </c>
       <c r="B29" s="3"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">《行わないこと》</t>
+        </is>
+      </c>
+      <c r="B30" s="8"/>
+    </row>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECR 権限チェック / ECR ログイン / タグ付け / プッシュ / imagedefinition.json の出力。</t>
+        </is>
+      </c>
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B30" s="8"/>
-    </row>
-    <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="B32" s="8"/>
+    </row>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">前提</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">必須コマンド</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">docker、docker compose または docker-compose</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="33.0" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">追加で必要</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">curl (--verify-url / --keep-container-mode http 時)、aws (--jboss-password-param 時)、Python 3 (送達診断の JSON 整形時)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">必須コマンド</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker、docker compose または docker-compose</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="33.0" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">追加で必要</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curl (--verify-url / --keep-container-mode http 時)、aws (--jboss-password-param 時)、Python 3 (送達診断の JSON 整形時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">AWS 認証</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--jboss-password-param を使う場合のみ必要 (aws login --remote 済み)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B35" s="8"/>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="B37" s="8"/>
+    </row>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B36" s="3"/>
-    </row>
-    <row r="37" ht="9.0" customHeight="1">
-      <c r="A37" s="0"/>
-    </row>
-    <row r="38" ht="24.0" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="B38" s="3"/>
+    </row>
+    <row r="39" ht="9.0" customHeight="1">
+      <c r="A39" s="0"/>
+    </row>
+    <row r="40" ht="24.0" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2. 全体構成</t>
         </is>
       </c>
-      <c r="B38" s="5"/>
-    </row>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="B40" s="5"/>
+    </row>
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.1 ファイル内のセクション構成》</t>
         </is>
       </c>
-      <c r="B39" s="8"/>
-    </row>
-    <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="B41" s="8"/>
+    </row>
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">位置</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">セクション</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="33.0" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="43" ht="33.0" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">冒頭</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ヘッダーコメント</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">目的・機能一覧・使い方</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="33.0" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="44" ht="33.0" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示タイムゾーン設定</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示・保存する時刻をすべて JST に固定</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="82.5" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="45" ht="82.5" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="49.5" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="46" ht="49.5" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ用ヘルパ</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / run / JST 変換ヘルパ</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">usage()</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--help の本文</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="66.0" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="48" ht="66.0" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数パース</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">append_services によるカンマ区切り分割、need_value による値欠落検出</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="49.5" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中盤</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力値の検証</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">数値・モード・排他関係・サービス指定の整合性</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中盤</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">依存コマンド / AWS 認証 / compose 判定</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実行環境の確認</t>
         </is>
       </c>
     </row>
@@ -1054,16 +1054,16 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット準備・一時ファイルコピー</t>
+          <t xml:space="preserve">入力値の検証</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepare_jboss_password / prepare_copy_files</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="82.5" customHeight="1">
+          <t xml:space="preserve">数値・モード・排他関係・サービス指定の整合性</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="19.5" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">依存コマンド / AWS 認証 / compose 判定</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">危険文字の分析、段ごとの比較、compose.yml と standalone.xml の解析、CredentialStore の開封確認</t>
+          <t xml:space="preserve">実行環境の確認</t>
         </is>
       </c>
     </row>
@@ -1088,548 +1088,566 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">シークレット準備・一時ファイルコピー</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prepare_jboss_password / prepare_copy_files</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="82.5" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中盤</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">マスターパスワードの伝搬検証</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">危険文字の分析、段ごとの比較、compose.yml と standalone.xml の解析、CredentialStore の開封確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="49.5" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中盤</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">起動確認・ログ表示ヘルパ</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ取得、ANSI 除去、色分け、companion ログ</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="33.0" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="54" ht="33.0" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナ内情報の収集と整形</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="82.5" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="55" ht="82.5" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM パラメータ・OpenTelemetry 設定</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">/proc/&lt;pid&gt;/cmdline の走査、JVM オプションの分類、OpenTelemetry 設定の突き合わせ</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="66.0" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中盤</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">対話操作</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bash / HTTP / logs モードと、healthcheck・MySQL・可観測性の各ヘルパ</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="33.0" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Docker 完全クリーンアップ</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">対象の集計、確認フレーズ、削除、検証</t>
         </is>
       </c>
     </row>
     <row r="56" ht="66.0" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">中盤</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">対話操作</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bash / HTTP / logs モードと、healthcheck・MySQL・可観測性の各ヘルパ</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="33.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docker 完全クリーンアップ</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">対象の集計、確認フレーズ、削除、検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="66.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドの停滞検知・進捗表示</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド出力の読み手、監視プロセス、停滞診断、上限時間での中断</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="66.0" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="59" ht="66.0" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">WAR デプロイ時 Java 例外解析</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">解析ヘルパー (Python 3) の埋め込みと、ログ収集・実行・表示・レポート追記</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="132.0" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="60" ht="132.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">分析ヘルパー (Python 3) の埋め込みと、compose.yml / Dockerfile (ビルド時) / 起動スクリプト・実行状況 (実行時) の収集・実行・表示・レポート追記</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポート</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">write_build_report</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">後始末 (cleanup_all)</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">EXIT トラップ本体</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="49.5" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
+    <row r="63" ht="49.5" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">末尾</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">メイン処理</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド → 起動 → 起動確認 → URL 確認 → 対話 → 情報表示</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+    <row r="64" ht="19.5" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.2 主要な関数グループ》</t>
         </is>
       </c>
-      <c r="B62" s="8"/>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="B64" s="8"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">グループ</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">代表的な関数</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">役割</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="33.0" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="66" ht="33.0" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ・時刻</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / to_jst_display_time</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">出力整形と UTC→JST 変換</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="66.0" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
+    <row r="67" ht="66.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">引数処理</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">append_services / need_value / validate_positive_integer / validate_non_negative_integer</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">カンマ区切り分割、値欠落検出、数値検証 (ビルド監視の各値は 0 を許す)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="49.5" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="68" ht="49.5" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Compose 操作</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose_container_ids / compose_logs / compose_started_services</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対象サービスの ID・ログ・サービス名取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="33.0" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="33.0" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ログ表示</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">行数制御と重要ログの色分け</t>
         </is>
       </c>
     </row>
     <row r="69" ht="33.0" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL 確認</t>
+          <t xml:space="preserve">起動確認</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">verify_url / show_url_body</t>
+          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl のリトライと応答本文表示</t>
+          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
         </is>
       </c>
     </row>
     <row r="70" ht="33.0" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">情報表示</t>
+          <t xml:space="preserve">ログ表示</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_verified_container_envs / ..._directory_trees / ..._deployment_structures</t>
+          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="66.0" customHeight="1">
+          <t xml:space="preserve">行数制御と重要ログの色分け</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="33.0" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JVM / OTel</t>
+          <t xml:space="preserve">URL 確認</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_verified_container_jvm_parameters / ..._otel_settings / collect_container_java_processes / classify_jvm_option / is_otel_jvm_option</t>
+          <t xml:space="preserve">verify_url / show_url_body</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java プロセスの検出、JVM オプションの分類、OpenTelemetry 設定の集約</t>
+          <t xml:space="preserve">curl のリトライと応答本文表示</t>
         </is>
       </c>
     </row>
     <row r="72" ht="33.0" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作</t>
+          <t xml:space="preserve">情報表示</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
+          <t xml:space="preserve">show_verified_container_envs / ..._directory_trees / ..._deployment_structures</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / HTTP / logs モード</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="33.0" customHeight="1">
+          <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="66.0" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck</t>
+          <t xml:space="preserve">JVM / OTel</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
+          <t xml:space="preserve">show_verified_container_jvm_parameters / ..._otel_settings / collect_container_java_processes / classify_jvm_option / is_otel_jvm_option</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
+          <t xml:space="preserve">Java プロセスの検出、JVM オプションの分類、OpenTelemetry 設定の集約</t>
         </is>
       </c>
     </row>
     <row r="74" ht="33.0" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">可観測性</t>
+          <t xml:space="preserve">対話操作</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+          <t xml:space="preserve">bash / HTTP / logs モード</t>
         </is>
       </c>
     </row>
     <row r="75" ht="33.0" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">healthcheck</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="33.0" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可観測性</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="33.0" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">クリーンアップ</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cleanup_all_docker_data / teardown_container / cleanup_copied_files</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 全体削除と通常後始末</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="82.5" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
+    <row r="78" ht="82.5" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド監視</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">run_build_with_watchdog / build_watchdog_reader / build_watchdog_monitor / diagnose_build_stall / build_phase_from_line / check_build_disk_space</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exporting layers などで出力が途切れたときの進捗表示・停滞診断・上限時間での中断</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="66.0" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
+    <row r="79" ht="66.0" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">cwagent 送信検証</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="66.0" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
+    <row r="80" ht="66.0" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">cwagent ロググループ準備</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">prepare_cwagent_log_groups / cwagent_ensure_log_groups / cwagent_resolve_delivery_target</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">設定ファイルの log_group_name が実 CloudWatch Logs に無ければ作成</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="115.5" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
+    <row r="81" ht="115.5" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">analyze_war_deploy_exceptions / deploy_exception_output_requested / collect_deploy_exception_logs / resolve_analysis_output_path / show_war_deploy_exception_analysis / show_war_deploy_exception_outputs / append_deploy_exception_report</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、出力先の要否判定、画面表示 (--deploy-exception-display 指定時) と Excel / テキスト出力</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="181.5" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
+    <row r="82" ht="181.5" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用 FS 分析</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">analyze_readonly_filesystem / readonly_collect_compose_facts / readonly_collect_dockerfile_facts / readonly_parse_dockerfile / readonly_shell_write_targets / readonly_scan_context_script / readonly_collect_runtime_facts / readonly_container_probe / readonly_collect_container_scripts / show_readonly_filesystem_analysis / append_readonly_analysis_report</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose.yml の read_only / tmpfs / volumes の解析、Dockerfile からのビルド時の書き込み先の収集、起動スクリプトからの実行時の書き込み先の収集、コンテナの書き込み状況の収集、判定結果の表示と Excel / テキスト出力</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="33.0" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
+    <row r="83" ht="33.0" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">レポート</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">write_build_report / append_compose_service_logs_report / append_jboss_password_report / append_cwagent_report / append_deploy_exception_report / append_readonly_analysis_report</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートの生成</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="66.0" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
+    <row r="84" ht="66.0" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">パスワード伝搬検証</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">verify_jboss_password_host_stages / verify_jboss_password_build_secret / verify_jboss_password_container_stages / jboss_xml_attributes / jboss_xml_unescape / jboss_wildfly_literal</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">各段の値の取得、XML と WildFly 式のエスケープ解除、原本との突き合わせ</t>
         </is>
       </c>
-    </row>
-    <row r="83" ht="19.5" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
-        </is>
-      </c>
-      <c r="B83" s="8"/>
-    </row>
-    <row r="84" ht="19.5" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">処理のどの経路 (成功・失敗・中断) でも、次の順で実行されます。</t>
-        </is>
-      </c>
-      <c r="B84" s="3"/>
     </row>
     <row r="85" ht="19.5" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
@@ -1639,8 +1657,24 @@
       </c>
       <c r="B85" s="8"/>
     </row>
-    <row r="86" ht="379.5" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">処理のどの経路 (成功・失敗・中断) でも、次の順で実行されます。</t>
+        </is>
+      </c>
+      <c r="B86" s="3"/>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
+        </is>
+      </c>
+      <c r="B87" s="8"/>
+    </row>
+    <row r="88" ht="409.0" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1. analyze_war_deploy_exceptions … デプロイ処理の Java 例外を解析 (削除より前・レポートより前)
                                    成功経路で実行済みなら何もしない
@@ -1651,6 +1685,10 @@
 5. teardown_container        … compose down (--keep-container 指定時は残す)
                                    対話操作を最後まで終えた実行では、--keep-container が
                                    暗黙有効でもここで削除する (6 の対象にするため)
+                                   そのとき、および取り込み検証で古い成果物を抱えた
+                                   ボリュームを検出したときは --volumes を付けて
+                                   ボリュームごと削除する (--keep-volumes で抑止、
+                                   --remove-volumes で常に付与) → 5.13
 6. run_post_interaction_cleanup … 対話操作を最後まで終えた実行 (かつ終了コード 0) のとき、
                                    docker-usage-check.sh --clean all --force で
                                    未使用リソースを完全クリア (→ 5.4-2)
@@ -1667,70 +1705,70 @@
                                    ディスク空き容量を一覧表示して終える</t>
         </is>
       </c>
-      <c r="B86" s="6"/>
-    </row>
-    <row r="87" ht="19.5" customHeight="1">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="B88" s="6"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B87" s="8"/>
-    </row>
-    <row r="88" ht="33.0" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="B89" s="8"/>
+    </row>
+    <row r="90" ht="33.0" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">終了コードは、本処理が既に失敗していれば元の終了コードを優先します。
 成功していた場合は、後始末の結果 (レポート保存失敗やクリーンアップ未承認なら 1) を返します。</t>
         </is>
       </c>
-      <c r="B88" s="3"/>
-    </row>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="B90" s="3"/>
+    </row>
+    <row r="91" ht="19.5" customHeight="1">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B89" s="8"/>
-    </row>
-    <row r="90" ht="19.5" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="B91" s="8"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B90" s="3"/>
-    </row>
-    <row r="91" ht="9.0" customHeight="1">
-      <c r="A91" s="0"/>
-    </row>
-    <row r="92" ht="24.0" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="B92" s="3"/>
+    </row>
+    <row r="93" ht="9.0" customHeight="1">
+      <c r="A93" s="0"/>
+    </row>
+    <row r="94" ht="24.0" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">3. 処理の流れ</t>
         </is>
       </c>
-      <c r="B92" s="5"/>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="B94" s="5"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B93" s="8"/>
-    </row>
-    <row r="94" ht="19.5" customHeight="1">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="B95" s="8"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B94" s="8"/>
-    </row>
-    <row r="95" ht="99.0" customHeight="1">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="B96" s="8"/>
+    </row>
+    <row r="97" ht="99.0" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時は、EXIT の後始末でレポートのログ本文を集める直前に
 compose stop (SIGTERM) を挟みます (3.6 参照)。
@@ -1740,18 +1778,18 @@
 必ず実行します** (6.7 参照)。</t>
         </is>
       </c>
-      <c r="B95" s="3"/>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B96" s="8"/>
-    </row>
-    <row r="97" ht="66.0" customHeight="1">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="B98" s="8"/>
+    </row>
+    <row r="99" ht="66.0" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析も同じタイミングで実行します。
 こちらは compose.yml と Dockerfile の定義だけでも判定できるため、
@@ -1759,22 +1797,6 @@
 実行状況からの根拠が無いことを結果へ明記します (6.8 参照)。</t>
         </is>
       </c>
-      <c r="B97" s="3"/>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
-        </is>
-      </c>
-      <c r="B98" s="8"/>
-    </row>
-    <row r="99" ht="19.5" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--compose-service の指定数によってビルド戦略が変わります。</t>
-        </is>
-      </c>
       <c r="B99" s="3"/>
     </row>
     <row r="100" ht="19.5" customHeight="1">
@@ -1786,145 +1808,145 @@
       <c r="B100" s="8"/>
     </row>
     <row r="101" ht="19.5" customHeight="1">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--compose-service の指定数によってビルド戦略が変わります。</t>
+        </is>
+      </c>
+      <c r="B101" s="3"/>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B102" s="8"/>
+    </row>
+    <row r="103" ht="19.5" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">指定</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">動作</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="19.5" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
+    <row r="104" ht="19.5" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">未指定</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全サービスを 1 回の compose build でビルド</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="19.5" customHeight="1">
-      <c r="A103" s="11" t="inlineStr">
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1 個</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そのサービスのみビルド</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="33.0" customHeight="1">
-      <c r="A104" s="11" t="inlineStr">
+    <row r="106" ht="33.0" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2 個以上</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">第 1 フェーズ: base サービスを単独で先行ビルド → ローカルイメージ確認 → 第 2 フェーズ: base 以外をまとめて並列ビルド</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="19.5" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
+    <row r="107" ht="19.5" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B105" s="8"/>
-    </row>
-    <row r="106" ht="33.0" customHeight="1">
-      <c r="A106" s="3" t="inlineStr">
+      <c r="B107" s="8"/>
+    </row>
+    <row r="108" ht="33.0" customHeight="1">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2 段階に分けるのは、ベースイメージを参照するサービスが base の完成前にビルドを始めるのを
 防ぐためです。並列オプションは compose のバージョンによって使い分けます。</t>
         </is>
       </c>
-      <c r="B106" s="3"/>
-    </row>
-    <row r="107" ht="19.5" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="B108" s="3"/>
+    </row>
+    <row r="109" ht="19.5" customHeight="1">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B107" s="8"/>
-    </row>
-    <row r="108" ht="19.5" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="B109" s="8"/>
+    </row>
+    <row r="110" ht="19.5" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">compose</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">並列指定</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="19.5" customHeight="1">
-      <c r="A109" s="11" t="inlineStr">
+    <row r="111" ht="19.5" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">v2 (docker compose)</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">グローバルオプション --parallel &lt;サービス数&gt;</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="19.5" customHeight="1">
-      <c r="A110" s="11" t="inlineStr">
+    <row r="112" ht="19.5" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">v1 (docker-compose)</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build --parallel (未対応版は exit 1)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="19.5" customHeight="1">
-      <c r="A111" s="8" t="inlineStr">
+    <row r="113" ht="19.5" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B111" s="8"/>
-    </row>
-    <row r="112" ht="33.0" customHeight="1">
-      <c r="A112" s="3" t="inlineStr">
+      <c r="B113" s="8"/>
+    </row>
+    <row r="114" ht="33.0" customHeight="1">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド後は docker image inspect でローカルイメージを確認し、
 image=... id=... created=... size=... bytes を JST 表記でログに残します。</t>
         </is>
       </c>
-      <c r="B112" s="3"/>
-    </row>
-    <row r="113" ht="19.5" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
-        </is>
-      </c>
-      <c r="B113" s="8"/>
-    </row>
-    <row r="114" ht="19.5" customHeight="1">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルドの前後では、ディスク使用量を抑えるために次を行います (5.8-2 参照)。</t>
-        </is>
-      </c>
       <c r="B114" s="3"/>
     </row>
     <row r="115" ht="19.5" customHeight="1">
@@ -1936,38 +1958,30 @@
       <c r="B115" s="8"/>
     </row>
     <row r="116" ht="19.5" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルドの前後では、ディスク使用量を抑えるために次を行います (5.8-2 参照)。</t>
+        </is>
+      </c>
+      <c r="B116" s="3"/>
+    </row>
+    <row r="117" ht="19.5" customHeight="1">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
+        </is>
+      </c>
+      <c r="B117" s="8"/>
+    </row>
+    <row r="118" ht="19.5" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">タイミング</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="19.5" customHeight="1">
-      <c r="A117" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="19.5" customHeight="1">
-      <c r="A118" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">data root の空き容量を確認し、5 GiB 未満なら警告する (5.2-2 参照)</t>
         </is>
       </c>
     </row>
@@ -1979,57 +1993,81 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
+          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
         </is>
       </c>
     </row>
     <row r="120" ht="19.5" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data root の空き容量を確認し、5 GiB 未満なら警告する (5.2-2 参照)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="19.5" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="19.5" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">ローカルイメージ確認の直後</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ID が変わっていれば、タグを失った旧世代イメージを削除する</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="19.5" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
+    <row r="123" ht="19.5" customHeight="1">
+      <c r="A123" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B121" s="8"/>
-    </row>
-    <row r="122" ht="33.0" customHeight="1">
-      <c r="A122" s="3" t="inlineStr">
+      <c r="B123" s="8"/>
+    </row>
+    <row r="124" ht="33.0" customHeight="1">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド自体は監視プロセス付きで実行し、exporting to image / exporting layers で
 出力が途切れても状況が分かるようにします (5.2-2 参照)。</t>
         </is>
       </c>
-      <c r="B122" s="3"/>
-    </row>
-    <row r="123" ht="19.5" customHeight="1">
-      <c r="A123" s="8" t="inlineStr">
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" ht="19.5" customHeight="1">
+      <c r="A125" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B123" s="8"/>
-    </row>
-    <row r="124" ht="19.5" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
+      <c r="B125" s="8"/>
+    </row>
+    <row r="126" ht="19.5" customHeight="1">
+      <c r="A126" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B124" s="8"/>
-    </row>
-    <row r="125" ht="99.0" customHeight="1">
-      <c r="A125" s="3" t="inlineStr">
+      <c r="B126" s="8"/>
+    </row>
+    <row r="127" ht="99.0" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・--startup-service を指定した場合は、サービスごとに個別に起動完了を判定し、
   指定した全サービスの完了をもって成功とします
@@ -2039,35 +2077,35 @@
 ・失敗時は --suppress-startup-logs を指定していてもログを表示します (原因を隠さないため)</t>
         </is>
       </c>
-      <c r="B125" s="3"/>
-    </row>
-    <row r="126" ht="19.5" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="B127" s="3"/>
+    </row>
+    <row r="128" ht="19.5" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B126" s="8"/>
-    </row>
-    <row r="127" ht="33.0" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
+      <c r="B128" s="8"/>
+    </row>
+    <row r="129" ht="33.0" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">curl -s -S -m 30 -o &lt;一時ファイル&gt; -w '%{http_code}' -X &lt;URL_METHOD&gt; \
      [-k] [-H "Content-Type: &lt;URL_CONTENT_TYPE&gt;"] [--data &lt;ボディ&gt;] &lt;VERIFY_URL&gt;</t>
         </is>
       </c>
-      <c r="B127" s="6"/>
-    </row>
-    <row r="128" ht="19.5" customHeight="1">
-      <c r="A128" s="8" t="inlineStr">
+      <c r="B129" s="6"/>
+    </row>
+    <row r="130" ht="19.5" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B128" s="8"/>
-    </row>
-    <row r="129" ht="66.0" customHeight="1">
-      <c r="A129" s="3" t="inlineStr">
+      <c r="B130" s="8"/>
+    </row>
+    <row r="131" ht="66.0" customHeight="1">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・期待ステータス (--expect-status) と一致するまで --url-interval 秒間隔でリトライ
 ・--url-timeout 秒を超えると失敗 (最後の応答コードを表示)
@@ -2075,145 +2113,181 @@
 ・成功・失敗いずれの場合も、応答本文の先頭 20 行を表示</t>
         </is>
       </c>
-      <c r="B129" s="3"/>
-    </row>
-    <row r="130" ht="19.5" customHeight="1">
-      <c r="A130" s="8" t="inlineStr">
+      <c r="B131" s="3"/>
+    </row>
+    <row r="132" ht="19.5" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B130" s="8"/>
-    </row>
-    <row r="131" ht="33.0" customHeight="1">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="B132" s="8"/>
+    </row>
+    <row r="133" ht="33.0" customHeight="1">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup を付けず --verify-url のみを指定した場合もコンテナは起動します
 (起動完了のログ確認は行わず、URL のリトライで readiness を担保します)。</t>
         </is>
       </c>
-      <c r="B131" s="3"/>
-    </row>
-    <row r="132" ht="19.5" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
+      <c r="B133" s="3"/>
+    </row>
+    <row r="134" ht="19.5" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B132" s="8"/>
-    </row>
-    <row r="133" ht="19.5" customHeight="1">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="B134" s="8"/>
+    </row>
+    <row r="135" ht="19.5" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">状況</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの扱い</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="19.5" customHeight="1">
-      <c r="A134" s="11" t="inlineStr">
+    <row r="136" ht="19.5" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">通常</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose down で停止・削除</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="49.5" customHeight="1">
-      <c r="A135" s="11" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down で停止・削除 (ボリュームは残す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="49.5" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--keep-container-mode logs の対話操作をすべて終了し、終了コードが 0</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose down で削除したうえで、未使用リソースまで完全クリア (→ 5.4-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="33.0" customHeight="1">
-      <c r="A136" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--keep-container / --keep-container-mode 指定 (上記以外)</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="33.0" customHeight="1">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--keep-container-after-interaction 指定</t>
-        </is>
-      </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作を終えても残す (従来の動作)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="19.5" customHeight="1">
+          <t xml:space="preserve">compose down --volumes でボリュームごと削除したうえで、未使用リソースまで完全クリア (→ 5.4-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="33.0" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
+          <t xml:space="preserve">取り込み検証で「古い成果物を抱えたボリューム」を検出</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
+          <t xml:space="preserve">compose down --volumes でボリュームごと削除し、次回の実行で作り直させる (→ 5.13)</t>
         </is>
       </c>
     </row>
     <row r="139" ht="19.5" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--remove-volumes 指定</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">この実行が行うすべての compose down へ --volumes を付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="19.5" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-volumes 指定</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記いずれの場合もボリュームを残す (従来の動作)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="33.0" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container / --keep-container-mode 指定 (上記以外)</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="33.0" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container-after-interaction 指定</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">対話操作を終えても残す (従来の動作)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="19.5" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="19.5" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B144" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="19.5" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+    <row r="145" ht="19.5" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B140" s="8"/>
-    </row>
-    <row r="141" ht="49.5" customHeight="1">
-      <c r="A141" s="3" t="inlineStr">
+      <c r="B145" s="8"/>
+    </row>
+    <row r="146" ht="49.5" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの削除後に、--prune-build-cache / --prune-build-cache-keep 指定時はビルド
 キャッシュを削除し、--disk-usage-report 指定時は終了時の使用量と実行前からの増減を
 表示します (5.8-2 参照)。</t>
         </is>
       </c>
-      <c r="B141" s="3"/>
-    </row>
-    <row r="142" ht="19.5" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
+      <c r="B146" s="3"/>
+    </row>
+    <row r="147" ht="19.5" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B142" s="8"/>
-    </row>
-    <row r="143" ht="66.0" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
+      <c r="B147" s="8"/>
+    </row>
+    <row r="148" ht="66.0" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS はタスク停止時に各コンテナへ SIGTERM を送るため、adot collector のような
 サイドカーは「シグナル受信 → パイプラインの graceful shutdown → 終了」までを
@@ -2221,34 +2295,34 @@
 誰にも取得されないままコンテナごと削除されてしまいます。</t>
         </is>
       </c>
-      <c r="B143" s="3"/>
-    </row>
-    <row r="144" ht="19.5" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
+      <c r="B148" s="3"/>
+    </row>
+    <row r="149" ht="19.5" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B144" s="8"/>
-    </row>
-    <row r="145" ht="19.5" customHeight="1">
-      <c r="A145" s="3" t="inlineStr">
+      <c r="B149" s="8"/>
+    </row>
+    <row r="150" ht="19.5" customHeight="1">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そこでエラー終了時に限り、削除の前に SIGTERM による停止を挟みます。</t>
         </is>
       </c>
-      <c r="B145" s="3"/>
-    </row>
-    <row r="146" ht="19.5" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="B150" s="3"/>
+    </row>
+    <row r="151" ht="19.5" customHeight="1">
+      <c r="A151" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B146" s="8"/>
-    </row>
-    <row r="147" ht="148.5" customHeight="1">
-      <c r="A147" s="6" t="inlineStr">
+      <c r="B151" s="8"/>
+    </row>
+    <row r="152" ht="148.5" customHeight="1">
+      <c r="A152" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">[2] 〜 [6] の収集 (起動中のコンテナが必要)
         ↓
@@ -2261,18 +2335,18 @@
 compose down (削除)</t>
         </is>
       </c>
-      <c r="B147" s="6"/>
-    </row>
-    <row r="148" ht="19.5" customHeight="1">
-      <c r="A148" s="8" t="inlineStr">
+      <c r="B152" s="6"/>
+    </row>
+    <row r="153" ht="19.5" customHeight="1">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B148" s="8"/>
-    </row>
-    <row r="149" ht="165.0" customHeight="1">
-      <c r="A149" s="3" t="inlineStr">
+      <c r="B153" s="8"/>
+    </row>
+    <row r="154" ht="165.0" customHeight="1">
+      <c r="A154" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・対象は compose ps --services が返す稼働中の全サービスです
   (起動確認対象だけでなく adot collector などのサイドカーも含みます)
@@ -2286,458 +2360,458 @@
   従来どおり compose down でまとめて削除します</t>
         </is>
       </c>
-      <c r="B149" s="3"/>
-    </row>
-    <row r="150" ht="19.5" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
+      <c r="B154" s="3"/>
+    </row>
+    <row r="155" ht="19.5" customHeight="1">
+      <c r="A155" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B150" s="8"/>
-    </row>
-    <row r="151" ht="49.5" customHeight="1">
-      <c r="A151" s="3" t="inlineStr">
+      <c r="B155" s="8"/>
+    </row>
+    <row r="156" ht="49.5" customHeight="1">
+      <c r="A156" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">adot collector の healthcheck が失敗し、depends_on の condition: service_healthy
 を満たせずバックエンドが起動しなかった場合、ECS 上でも同じくタスクが停止します。
 その終了処理まで含めてローカルで再現・確認できるようにするのがこの動作の狙いです。</t>
         </is>
       </c>
-      <c r="B151" s="3"/>
-    </row>
-    <row r="152" ht="19.5" customHeight="1">
-      <c r="A152" s="8" t="inlineStr">
+      <c r="B156" s="3"/>
+    </row>
+    <row r="157" ht="19.5" customHeight="1">
+      <c r="A157" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B152" s="8"/>
-    </row>
-    <row r="153" ht="19.5" customHeight="1">
-      <c r="A153" s="3" t="inlineStr">
+      <c r="B157" s="8"/>
+    </row>
+    <row r="158" ht="19.5" customHeight="1">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B153" s="3"/>
-    </row>
-    <row r="154" ht="9.0" customHeight="1">
-      <c r="A154" s="0"/>
-    </row>
-    <row r="155" ht="24.0" customHeight="1">
-      <c r="A155" s="5" t="inlineStr">
+      <c r="B158" s="3"/>
+    </row>
+    <row r="159" ht="9.0" customHeight="1">
+      <c r="A159" s="0"/>
+    </row>
+    <row r="160" ht="24.0" customHeight="1">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">5. 終了コード</t>
         </is>
       </c>
-      <c r="B155" s="5"/>
-    </row>
-    <row r="156" ht="19.5" customHeight="1">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="B160" s="5"/>
+    </row>
+    <row r="161" ht="19.5" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コード</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">意味</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">主な発生条件</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="33.0" customHeight="1">
-      <c r="A157" s="11" t="inlineStr">
+    <row r="162" ht="33.0" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="B157" s="3" t="inlineStr">
+      <c r="B162" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">正常終了</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="C162" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド (と指定した確認) がすべて成功</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="409.0" customHeight="1">
-      <c r="A158" s="11" t="inlineStr">
+    <row r="163" ht="409.0" customHeight="1">
+      <c r="A163" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B158" s="3" t="inlineStr">
+      <c r="B163" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行時エラー</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、対話操作の終了後の完全クリーンアップ失敗 (docker-usage-check.sh が見つからない・失敗した)、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="409.0" customHeight="1">
-      <c r="A159" s="11" t="inlineStr">
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、対話操作の終了後の完全クリーンアップ失敗 (docker-usage-check.sh が見つからない・失敗した)、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG、コピーしたファイルの取り込み検証 NG (コンテナ内の中身がコピー元と一致しない / --copy-artifact-required 指定時に未検出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="409.0" customHeight="1">
+      <c r="A164" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B159" s="3" t="inlineStr">
+      <c r="B164" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数エラー</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="19.5" customHeight="1">
-      <c r="A160" s="3" t="inlineStr">
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正、--copy-artifact-path / --copy-artifact-search-dir が絶対パスでない、--remove-volumes と --keep-volumes の同時指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="19.5" customHeight="1">
+      <c r="A165" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">本処理が失敗している場合は、後始末の結果にかかわらず元の終了コードが優先されます。</t>
         </is>
       </c>
-      <c r="B160" s="3"/>
-    </row>
-    <row r="161" ht="19.5" customHeight="1">
-      <c r="A161" s="3" t="inlineStr">
+      <c r="B165" s="3"/>
+    </row>
+    <row r="166" ht="19.5" customHeight="1">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B161" s="3"/>
-    </row>
-    <row r="162" ht="9.0" customHeight="1">
-      <c r="A162" s="0"/>
-    </row>
-    <row r="163" ht="24.0" customHeight="1">
-      <c r="A163" s="5" t="inlineStr">
+      <c r="B166" s="3"/>
+    </row>
+    <row r="167" ht="9.0" customHeight="1">
+      <c r="A167" s="0"/>
+    </row>
+    <row r="168" ht="24.0" customHeight="1">
+      <c r="A168" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">6. 環境変数</t>
         </is>
       </c>
-      <c r="B163" s="5"/>
-    </row>
-    <row r="164" ht="19.5" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
+      <c r="B168" s="5"/>
+    </row>
+    <row r="169" ht="19.5" customHeight="1">
+      <c r="A169" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.1 入力として参照する環境変数》</t>
         </is>
       </c>
-      <c r="B164" s="8"/>
-    </row>
-    <row r="165" ht="19.5" customHeight="1">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="B169" s="8"/>
+    </row>
+    <row r="170" ht="19.5" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="19.5" customHeight="1">
-      <c r="A166" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="19.5" customHeight="1">
-      <c r="A167" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="19.5" customHeight="1">
-      <c r="A168" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="19.5" customHeight="1">
-      <c r="A169" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="19.5" customHeight="1">
-      <c r="A170" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO_COLOR</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定義されていれば色分けを無効化</t>
         </is>
       </c>
     </row>
     <row r="171" ht="19.5" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLICOLOR_FORCE</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
     </row>
     <row r="172" ht="19.5" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERM</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dumb の場合は色分けしない</t>
+          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
     </row>
     <row r="173" ht="19.5" customHeight="1">
-      <c r="A173" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
-        </is>
-      </c>
-      <c r="B173" s="8"/>
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="19.5" customHeight="1">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用途</t>
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
         </is>
       </c>
     </row>
     <row r="175" ht="19.5" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TZ</t>
+          <t xml:space="preserve">NO_COLOR</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
+          <t xml:space="preserve">定義されていれば色分けを無効化</t>
         </is>
       </c>
     </row>
     <row r="176" ht="19.5" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">CLICOLOR_FORCE</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
         </is>
       </c>
     </row>
     <row r="177" ht="19.5" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">TERM</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dumb の場合は色分けしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="19.5" customHeight="1">
+      <c r="A178" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
+        </is>
+      </c>
+      <c r="B178" s="8"/>
+    </row>
+    <row r="179" ht="19.5" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用途</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="19.5" customHeight="1">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TZ</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="19.5" customHeight="1">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="19.5" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="19.5" customHeight="1">
-      <c r="A178" s="11" t="inlineStr">
+    <row r="183" ht="19.5" customHeight="1">
+      <c r="A183" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B178" s="3" t="inlineStr">
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="33.0" customHeight="1">
-      <c r="A179" s="11" t="inlineStr">
+    <row r="184" ht="33.0" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;--cacert-bundle-env の値&gt;</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CA 証明書をまとめた tar のパス。compose の file 型シークレットへ渡す。--cacert-dir 未指定時は「空の tar」のパスが入り、従来どおり証明書なしでビルドされる</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="19.5" customHeight="1">
-      <c r="A180" s="8" t="inlineStr">
+    <row r="185" ht="19.5" customHeight="1">
+      <c r="A185" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B180" s="8"/>
-    </row>
-    <row r="181" ht="49.5" customHeight="1">
-      <c r="A181" s="3" t="inlineStr">
+      <c r="B185" s="8"/>
+    </row>
+    <row r="186" ht="49.5" customHeight="1">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 / 7.2 はスクリプト自身が実行ホストで参照・設定する環境変数です。
 これとは別に、起動したコンテナ内の環境変数を収集して一覧表示します
 (スクリプトの動作は変えません)。</t>
         </is>
       </c>
-      <c r="B181" s="3"/>
-    </row>
-    <row r="182" ht="19.5" customHeight="1">
-      <c r="A182" s="8" t="inlineStr">
+      <c r="B186" s="3"/>
+    </row>
+    <row r="187" ht="19.5" customHeight="1">
+      <c r="A187" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B182" s="8"/>
-    </row>
-    <row r="183" ht="19.5" customHeight="1">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="B187" s="8"/>
+    </row>
+    <row r="188" ht="19.5" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">出力先</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="33.0" customHeight="1">
-      <c r="A184" s="11" t="inlineStr">
+    <row r="189" ht="33.0" customHeight="1">
+      <c r="A189" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM オプションの受け渡し</t>
         </is>
       </c>
-      <c r="B184" s="3" t="inlineStr">
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
         </is>
       </c>
-      <c r="C184" s="3" t="inlineStr">
+      <c r="C189" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="33.0" customHeight="1">
-      <c r="A185" s="11" t="inlineStr">
+    <row r="190" ht="33.0" customHeight="1">
+      <c r="A190" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 標準設定</t>
         </is>
       </c>
-      <c r="B185" s="3" t="inlineStr">
+      <c r="B190" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
         </is>
       </c>
-      <c r="C185" s="3" t="inlineStr">
+      <c r="C190" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="33.0" customHeight="1">
-      <c r="A186" s="11" t="inlineStr">
+    <row r="191" ht="33.0" customHeight="1">
+      <c r="A191" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 関連設定</t>
         </is>
       </c>
-      <c r="B186" s="3" t="inlineStr">
+      <c r="B191" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS_XRAY_DAEMON_ADDRESS / AWS_XRAY_CONTEXT_MISSING / AWS_XRAY_TRACING_NAME / AWS_LAMBDA_EXEC_WRAPPER / AOT_CONFIG_CONTENT</t>
         </is>
       </c>
-      <c r="C186" s="3" t="inlineStr">
+      <c r="C191" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="19.5" customHeight="1">
-      <c r="A187" s="11" t="inlineStr">
+    <row r="192" ht="19.5" customHeight="1">
+      <c r="A192" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリ構造の起点</t>
         </is>
       </c>
-      <c r="B187" s="3" t="inlineStr">
+      <c r="B192" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--deployment-dir-env で指定した名前</t>
         </is>
       </c>
-      <c r="C187" s="3" t="inlineStr">
+      <c r="C192" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="19.5" customHeight="1">
-      <c r="A188" s="8" t="inlineStr">
+    <row r="193" ht="19.5" customHeight="1">
+      <c r="A193" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B188" s="8"/>
-    </row>
-    <row r="189" ht="19.5" customHeight="1">
-      <c r="A189" s="3" t="inlineStr">
+      <c r="B193" s="8"/>
+    </row>
+    <row r="194" ht="19.5" customHeight="1">
+      <c r="A194" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B189" s="3"/>
+      <c r="B194" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="77">
@@ -2746,26 +2820,24 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="A87:B87"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A91:B91"/>
     <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A93:B93"/>
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="A95:B95"/>
     <mergeCell ref="A96:B96"/>
@@ -2773,16 +2845,16 @@
     <mergeCell ref="A98:B98"/>
     <mergeCell ref="A99:B99"/>
     <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A102:B102"/>
     <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A109:B109"/>
     <mergeCell ref="A113:B113"/>
     <mergeCell ref="A114:B114"/>
     <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A117:B117"/>
     <mergeCell ref="A123:B123"/>
     <mergeCell ref="A124:B124"/>
     <mergeCell ref="A125:B125"/>
@@ -2793,11 +2865,8 @@
     <mergeCell ref="A130:B130"/>
     <mergeCell ref="A131:B131"/>
     <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A140:B140"/>
-    <mergeCell ref="A141:B141"/>
-    <mergeCell ref="A142:B142"/>
-    <mergeCell ref="A143:B143"/>
-    <mergeCell ref="A144:B144"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A134:B134"/>
     <mergeCell ref="A145:B145"/>
     <mergeCell ref="A146:B146"/>
     <mergeCell ref="A147:B147"/>
@@ -2807,17 +2876,22 @@
     <mergeCell ref="A151:B151"/>
     <mergeCell ref="A152:B152"/>
     <mergeCell ref="A153:B153"/>
+    <mergeCell ref="A154:B154"/>
     <mergeCell ref="A155:B155"/>
+    <mergeCell ref="A156:B156"/>
+    <mergeCell ref="A157:B157"/>
+    <mergeCell ref="A158:B158"/>
     <mergeCell ref="A160:B160"/>
-    <mergeCell ref="A161:B161"/>
-    <mergeCell ref="A163:B163"/>
-    <mergeCell ref="A164:B164"/>
-    <mergeCell ref="A173:B173"/>
-    <mergeCell ref="A180:B180"/>
-    <mergeCell ref="A181:B181"/>
-    <mergeCell ref="A182:B182"/>
-    <mergeCell ref="A188:B188"/>
-    <mergeCell ref="A189:B189"/>
+    <mergeCell ref="A165:B165"/>
+    <mergeCell ref="A166:B166"/>
+    <mergeCell ref="A168:B168"/>
+    <mergeCell ref="A169:B169"/>
+    <mergeCell ref="A178:B178"/>
+    <mergeCell ref="A185:B185"/>
+    <mergeCell ref="A186:B186"/>
+    <mergeCell ref="A187:B187"/>
+    <mergeCell ref="A193:B193"/>
+    <mergeCell ref="A194:B194"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3246,431 +3320,451 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="49.5" customHeight="1">
+    <row r="16" ht="33.0" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--verify-copy-artifact</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auto (--copy-file 指定時のみ有効)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-file を指定していない実行でも取り込み検証を行う (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="33.0" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-verify-copy-artifact</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">取り込み検証を行わない。--copy-artifact-path / --copy-artifact-search-dir / --copy-artifact-required とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33.0" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-artifact-path PATH</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33.0" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-artifact-search-dir DIR</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="33.0" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-artifact-required</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コピーしたファイルがコンテナ内に見つからない場合もエラーとする (既定は警告のみ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="49.5" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">SSM パラメータ名</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E21" s="7"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアから取得。このとき AWS 認証が必要</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="49.5" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="22" ht="49.5" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パスワード文字列</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="49.5" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
-        </is>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="49.5" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">シークレット id</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jboss_master_password</t>
-        </is>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="49.5" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region REGION</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS リージョン名</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
-        </is>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="33.0" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cacert-dir DIR</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリのパス</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="33.0" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cacert-secret-id ID</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">英数字と . _ -</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="33.0" customHeight="1">
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="49.5" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle PATH</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">一時ファイル</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="33.0" customHeight="1">
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="49.5" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">シークレット id</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="33.0" customHeight="1">
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="49.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-glob PATTERN</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">glob パターン</t>
+          <t xml:space="preserve">AWS リージョン名</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">*.crt と *.pem</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+        </is>
+      </c>
+      <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
     <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-jboss-password</t>
+          <t xml:space="preserve">--cacert-dir DIR</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
+          <t xml:space="preserve">ディレクトリのパス</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E26" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
         </is>
       </c>
     </row>
     <row r="27" ht="33.0" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-mask</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">英数字と . _ -</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="28" ht="33.0" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">tar のパス</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
     <row r="29" ht="33.0" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="30" ht="33.0" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">glob パターン</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
-        </is>
-      </c>
-      <c r="E30" s="7"/>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
@@ -3682,35 +3776,35 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--verify-jboss-password</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="33.0" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-password-mask</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3718,83 +3812,83 @@
           <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto</t>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="33.0" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-verify-cwagent</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証を行わない</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="34" ht="33.0" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="35" ht="33.0" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3804,41 +3898,41 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="36" ht="33.0" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">列挙</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3944,7 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-report</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3858,15 +3952,15 @@
           <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3972,7 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-delivery-report</t>
+          <t xml:space="preserve">--no-verify-cwagent</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3894,7 +3988,7 @@
       <c r="E38" s="7"/>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達レポートを行わない (既定)</t>
+          <t xml:space="preserve">検証を行わない</t>
         </is>
       </c>
     </row>
@@ -3906,23 +4000,23 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -3934,23 +4028,23 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -3962,27 +4056,27 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">列挙</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="49.5" customHeight="1">
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="33.0" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
@@ -3990,23 +4084,23 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4112,7 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-required</t>
+          <t xml:space="preserve">--no-cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -4028,13 +4122,13 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
+          <t xml:space="preserve">送達レポートを行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -4046,23 +4140,23 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -4074,183 +4168,163 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="33.0" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-startup</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
+        </is>
+      </c>
+      <c r="E46" s="7"/>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="33.0" customHeight="1">
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="49.5" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+        </is>
+      </c>
+      <c r="E47" s="7"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
     <row r="48" ht="33.0" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-required</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">拡張正規表現</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E48" s="7"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
         </is>
       </c>
     </row>
     <row r="49" ht="33.0" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E49" s="7"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="33.0" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--no-cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E50" s="7"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
         </is>
       </c>
     </row>
@@ -4262,27 +4336,27 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--verify-startup</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
         </is>
       </c>
     </row>
@@ -4294,27 +4368,27 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-healthy</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4326,17 +4400,17 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">拡張正規表現</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -4346,7 +4420,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -4358,27 +4432,27 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--allow-service-exit NAME</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -4390,27 +4464,27 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-pull-images</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -4422,17 +4496,17 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -4442,7 +4516,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -4454,27 +4528,27 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--wait-healthy</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
         </is>
       </c>
     </row>
@@ -4486,17 +4560,17 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -4506,7 +4580,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4518,27 +4592,27 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-up-retry</t>
+          <t xml:space="preserve">--allow-service-exit NAME</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
+          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
         </is>
       </c>
     </row>
@@ -4550,27 +4624,27 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--no-pull-images</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
         </is>
       </c>
     </row>
@@ -4582,27 +4656,27 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--recreate-containers</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4614,27 +4688,27 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-recreate-containers</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -4646,27 +4720,27 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4678,27 +4752,27 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--no-up-retry</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
         </is>
       </c>
     </row>
@@ -4710,27 +4784,27 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">compose up の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4816,7 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--recreate-containers</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -4762,7 +4836,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
         </is>
       </c>
     </row>
@@ -4774,167 +4848,187 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-recreate-containers</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="33.0" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-startup-logs</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="33.0" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="33.0" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="33.0" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="33.0" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E68" s="7"/>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E69" s="7"/>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="19.5" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E70" s="7"/>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="19.5" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIME タイプ</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E71" s="7"/>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="19.5" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E72" s="7"/>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
@@ -4946,12 +5040,12 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
+          <t xml:space="preserve">URL</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -4962,7 +5056,7 @@
       <c r="E73" s="7"/>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -4974,23 +5068,23 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -5002,23 +5096,23 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP メソッド</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -5030,40 +5124,40 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">MIME タイプ</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="77" ht="19.5" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
+          <t xml:space="preserve">JSON 文字列</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -5074,103 +5168,103 @@
       <c r="E77" s="7"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="19.5" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">key=value&amp;...</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="19.5" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="33.0" customHeight="1">
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="19.5" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="19.5" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-after-interaction</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -5186,7 +5280,7 @@
       <c r="E81" s="7"/>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
         </is>
       </c>
     </row>
@@ -5198,27 +5292,27 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--usage-check-script PATH</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動解決)</t>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="19.5" customHeight="1">
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="33.0" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5226,99 +5320,91 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-free-path DIR</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定の 7 か所)</t>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="E83" s="7"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="84" ht="33.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E84" s="7"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="33.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E85" s="7"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="19.5" customHeight="1">
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="33.0" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--keep-container-after-interaction</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -5326,31 +5412,27 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E86" s="7"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
         </is>
       </c>
     </row>
     <row r="87" ht="19.5" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--remove-volumes</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -5363,26 +5445,22 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="19.5" customHeight="1">
+          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="33.0" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--keep-volumes</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -5390,83 +5468,71 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E88" s="7"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
         </is>
       </c>
     </row>
     <row r="89" ht="19.5" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="E89" s="7"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="33.0" customHeight="1">
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="19.5" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--disk-free-path DIR</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">ディレクトリ</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="E90" s="7"/>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5544,7 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -5488,7 +5554,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -5498,11 +5564,11 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="33.0" customHeight="1">
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5510,12 +5576,12 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--env-list-file FILE</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -5525,16 +5591,16 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="66.0" customHeight="1">
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5542,17 +5608,17 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -5562,11 +5628,11 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="19.5" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5574,7 +5640,7 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5582,9 +5648,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -5594,7 +5660,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5672,7 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5614,9 +5680,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -5626,11 +5692,11 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="33.0" customHeight="1">
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5638,17 +5704,17 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -5658,7 +5724,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--report-dir 指定時は未指定でも自動出力。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
@@ -5670,17 +5736,17 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -5690,11 +5756,11 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="33.0" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5702,17 +5768,17 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
@@ -5722,7 +5788,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -5734,59 +5800,59 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="66.0" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="33.0" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -5798,17 +5864,17 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-display</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5818,7 +5884,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5896,7 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5840,7 +5906,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -5850,11 +5916,11 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="49.5" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="33.0" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5862,12 +5928,12 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -5877,12 +5943,12 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--report-dir 指定時は未指定でも自動出力。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5894,17 +5960,17 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -5914,7 +5980,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -5926,17 +5992,17 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
@@ -5946,7 +6012,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -5958,17 +6024,17 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -5978,7 +6044,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
         </is>
       </c>
     </row>
@@ -5990,17 +6056,17 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
@@ -6010,11 +6076,11 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="19.5" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="33.0" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6022,17 +6088,17 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
@@ -6042,7 +6108,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6120,7 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -6074,11 +6140,11 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="33.0" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="49.5" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6086,12 +6152,12 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -6101,112 +6167,120 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="33.0" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="19.5" customHeight="1">
-      <c r="A111" s="11" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="19.5" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E111" s="7" t="inlineStr">
+      <c r="E112" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="33.0" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
-        </is>
-      </c>
-      <c r="B112" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E112" s="7"/>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
     <row r="113" ht="33.0" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E113" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="114" ht="33.0" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -6219,22 +6293,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E114" s="7"/>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="33.0" customHeight="1">
+          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="19.5" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -6247,218 +6325,290 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E115" s="7"/>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="33.0" customHeight="1">
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="19.5" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E116" s="7"/>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="117" ht="33.0" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E117" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="118" ht="19.5" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="7"/>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="119" ht="33.0" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E119" s="7"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
     <row r="120" ht="33.0" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E120" s="7"/>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="121" ht="33.0" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C121" s="3"/>
-      <c r="D121" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E121" s="7"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="122" ht="33.0" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E122" s="7"/>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="123" ht="33.0" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E123" s="7"/>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="124" ht="33.0" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C124" s="3"/>
-      <c r="D124" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E124" s="7"/>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="19.5" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C125" s="3"/>
@@ -6466,7 +6616,7 @@
       <c r="E125" s="7"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6628,7 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C126" s="3"/>
@@ -6486,7 +6636,7 @@
       <c r="E126" s="7"/>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6648,7 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C127" s="3"/>
@@ -6506,7 +6656,7 @@
       <c r="E127" s="7"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6668,7 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C128" s="3"/>
@@ -6526,12 +6676,152 @@
       <c r="E128" s="7"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="33.0" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="33.0" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="7"/>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="33.0" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="33.0" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="7"/>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="33.0" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="33.0" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="33.0" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F128"/>
+  <autoFilter ref="A4:F135"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -6751,82 +7041,66 @@
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
     </row>
-    <row r="17" ht="9.0" customHeight="1">
-      <c r="A17" s="0"/>
-    </row>
-    <row r="18" ht="24.0" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="17" ht="82.5" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コピーしたファイル (WAR など) の取り込み検証 (差し替えたファイルが本当にコンテナへ届いているかを SHA-256 で照合し、届いていなければエラー終了)</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(--copy-file 指定時は既定で自動。無効化は --no-verify-copy-artifact。未検出もエラーにするのは --copy-artifact-required)</t>
+        </is>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+    </row>
+    <row r="18" ht="49.5" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後始末でのボリューム削除 (デプロイ先を覆っているボリュームを残さない)</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(対話操作をすべて終えた実行では既定で compose down -v。常に削除は --remove-volumes、残すのは --keep-volumes)</t>
+        </is>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+    </row>
+    <row r="19" ht="9.0" customHeight="1">
+      <c r="A19" s="0"/>
+    </row>
+    <row r="20" ht="24.0" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値が設定されているパラメータ</t>
         </is>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">分類</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">オプション</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">その既定値での動作</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--local-image NAME</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1/base.local</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose build で生成されるローカルイメージ名</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--compose-file FILE</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose 定義ファイル</t>
         </is>
       </c>
     </row>
@@ -6838,61 +7112,61 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--local-image NAME</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1/base.local</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose build で生成されるローカルイメージ名</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--compose-file FILE</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose.yml</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose 定義ファイル</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--compose-service NAME</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">(全サービス)</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド・起動対象。複数指定時は base を先行ビルド。base は起動対象にならない</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="33.0" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--build-progress-interval SEC</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="33.0" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--build-stall-timeout SEC</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
@@ -6904,369 +7178,369 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-timeout SEC</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (無制限)</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
     <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
     <row r="27" ht="33.0" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss_master_password</t>
+          <t xml:space="preserve">0 (無制限)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
         </is>
       </c>
     </row>
     <row r="28" ht="33.0" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--region REGION</t>
+          <t xml:space="preserve">--verify-copy-artifact</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+          <t xml:space="preserve">auto (--copy-file 指定時のみ有効)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
+          <t xml:space="preserve">--copy-file を指定していない実行でも取り込み検証を行う (→ 5.13)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="33.0" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-secret-id ID</t>
+          <t xml:space="preserve">--copy-artifact-path PATH</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cacerts</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する</t>
         </is>
       </c>
     </row>
     <row r="30" ht="33.0" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle PATH</t>
+          <t xml:space="preserve">--copy-artifact-search-dir DIR</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">一時ファイル</t>
+          <t xml:space="preserve">/</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="33.0" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
         </is>
       </c>
     </row>
     <row r="32" ht="33.0" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-glob PATTERN</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">*.crt と *.pem</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="33" ht="33.0" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
     <row r="34" ht="33.0" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="35" ht="33.0" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
     <row r="36" ht="33.0" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="37" ht="33.0" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">*.crt と *.pem</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
     <row r="38" ht="33.0" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="39" ht="33.0" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="40" ht="33.0" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="41" ht="33.0" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -7278,17 +7552,17 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -7300,17 +7574,17 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -7322,127 +7596,127 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
     <row r="45" ht="33.0" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
     <row r="46" ht="33.0" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="33.0" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="33.0" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="49" ht="33.0" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
@@ -7454,17 +7728,17 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -7476,17 +7750,17 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -7498,17 +7772,17 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -7520,17 +7794,17 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -7542,17 +7816,17 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -7564,391 +7838,391 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--wait-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="33.0" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--pull-retry N</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="33.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="33.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--up-retry N</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="33.0" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="33.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B58" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-interval SEC</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リトライ間隔</t>
         </is>
       </c>
     </row>
     <row r="61" ht="19.5" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
     <row r="62" ht="19.5" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
     <row r="63" ht="19.5" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--usage-check-script PATH</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動解決)</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="64" ht="19.5" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-free-path DIR</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定の 7 か所)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="65" ht="19.5" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">リトライ間隔</t>
         </is>
       </c>
     </row>
     <row r="66" ht="19.5" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="67" ht="19.5" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--usage-check-script PATH</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-free-path DIR</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="19.5" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="19.5" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="33.0" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="33.0" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="33.0" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="33.0" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="33.0" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -7960,148 +8234,188 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
     <row r="74" ht="33.0" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="9.0" customHeight="1">
-      <c r="A75" s="0"/>
-    </row>
-    <row r="76" ht="24.0" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
-        </is>
-      </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-    </row>
-    <row r="77" ht="19.5" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">記載箇所</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="33.0" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="33.0" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="33.0" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="33.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="33.0" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
-        </is>
-      </c>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-    </row>
-    <row r="80" ht="49.5" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.4-2 デプロイエラー時の調査モード (既定) / --exit-on-deploy-error</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">対話の前 / 失敗した起動ログを表示し、WAR デプロイ時 Java 例外解析を先に済ませる (画面へ出すのは --deploy-exception-display 指定時。既定では全量レポート [10] と Excel へ残すだけ)</t>
-        </is>
-      </c>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-    </row>
-    <row r="81" ht="33.0" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
-        </is>
-      </c>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-    </row>
-    <row r="82" ht="33.0" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="9.0" customHeight="1">
+      <c r="A80" s="0"/>
+    </row>
+    <row r="81" ht="24.0" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
+        </is>
+      </c>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+    </row>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">記載箇所</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内容</t>
+        </is>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
     </row>
     <row r="83" ht="33.0" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
       <c r="C83" s="3"/>
@@ -8110,33 +8424,145 @@
     <row r="84" ht="33.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
     </row>
-    <row r="85" ht="33.0" customHeight="1">
+    <row r="85" ht="49.5" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">5.4-2 デプロイエラー時の調査モード (既定) / --exit-on-deploy-error</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">対話の前 / 失敗した起動ログを表示し、WAR デプロイ時 Java 例外解析を先に済ませる (画面へ出すのは --deploy-exception-display 指定時。既定では全量レポート [10] と Excel へ残すだけ)</t>
         </is>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
     </row>
+    <row r="86" ht="33.0" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+        </is>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+    </row>
+    <row r="87" ht="49.5" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原因</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+        </is>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+    </row>
+    <row r="88" ht="19.5" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+        </is>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+    </row>
+    <row r="89" ht="33.0" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2 出力ファイル</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+        </is>
+      </c>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+    </row>
+    <row r="90" ht="33.0" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+        </is>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+    </row>
+    <row r="91" ht="33.0" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+    </row>
+    <row r="92" ht="33.0" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+    </row>
+    <row r="93" ht="33.0" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="31">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -8152,17 +8578,22 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A81:D81"/>
     <mergeCell ref="B82:D82"/>
     <mergeCell ref="B83:D83"/>
     <mergeCell ref="B84:D84"/>
     <mergeCell ref="B85:D85"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B93:D93"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-22 04:58:59</t>
+          <t xml:space="preserve">2026-08-23 02:15:29</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="148.5" customHeight="1">
+    <row r="23" ht="181.5" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
@@ -731,7 +731,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(起動確認時に自動。結果は全量レポート [10] と Excel へ。画面表示は --deploy-exception-display 指定時のみ、テキスト出力は --deploy-exception-text 指定時のみ)</t>
+          <t xml:space="preserve">(起動確認時に自動。結果は全量レポート [10] へ。画面表示は --deploy-exception-display 指定時のみ、Excel 出力は --deploy-exception-excel 指定時のみ、テキスト出力は --deploy-exception-text 指定時のみ)</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="115.5" customHeight="1">
+    <row r="26" ht="148.5" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -782,7 +782,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(--copy-file 指定時は既定で自動。無効化は --no-verify-copy-artifact。未検出もエラーにするのは --copy-artifact-required)</t>
+          <t xml:space="preserve">(既定では行わない。--verify-copy-artifact で有効化。--copy-artifact-path / --copy-artifact-search-dir / --copy-artifact-required を指定した場合も有効になる)</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto (--copy-file 指定時のみ有効)</t>
+          <t xml:space="preserve">false (既定では照合しない)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-file を指定していない実行でも取り込み検証を行う (→ 5.13)</t>
+          <t xml:space="preserve">取り込み検証を行う (→ 5.13)</t>
         </is>
       </c>
     </row>
@@ -3368,9 +3368,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定と同じ)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する</t>
+          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)</t>
+          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コピーしたファイルがコンテナ内に見つからない場合もエラーとする (既定は警告のみ)</t>
+          <t xml:space="preserve">コピーしたファイルがコンテナ内に見つからない場合もエラーとする (既定は警告のみ)。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--report-dir 指定時は未指定でも自動出力。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6623,102 +6623,82 @@
     <row r="126" ht="33.0" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="7"/>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
+      <c r="F126" s="3"/>
     </row>
     <row r="127" ht="33.0" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="7"/>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
-        </is>
-      </c>
+      <c r="F127" s="3"/>
     </row>
     <row r="128" ht="33.0" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="7"/>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
-        </is>
-      </c>
+      <c r="F128" s="3"/>
     </row>
     <row r="129" ht="33.0" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="7"/>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
-        </is>
-      </c>
+      <c r="F129" s="3"/>
     </row>
     <row r="130" ht="33.0" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="7"/>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
-        </is>
-      </c>
+      <c r="F130" s="3"/>
     </row>
     <row r="131" ht="33.0" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
@@ -6728,7 +6708,7 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C131" s="3"/>
@@ -6736,7 +6716,7 @@
       <c r="E131" s="7"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6728,7 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C132" s="3"/>
@@ -6756,7 +6736,7 @@
       <c r="E132" s="7"/>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6748,7 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C133" s="3"/>
@@ -6776,7 +6756,7 @@
       <c r="E133" s="7"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6768,7 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C134" s="3"/>
@@ -6796,7 +6776,7 @@
       <c r="E134" s="7"/>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6788,7 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C135" s="3"/>
@@ -6816,12 +6796,112 @@
       <c r="E135" s="7"/>
       <c r="F135" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="33.0" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="33.0" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="33.0" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="33.0" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="7"/>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="33.0" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="7"/>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F135"/>
+  <autoFilter ref="A4:F140"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -7007,7 +7087,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(起動確認時に自動。結果は全量レポート [10] と Excel へ。画面表示は --deploy-exception-display 指定時のみ、テキスト出力は --deploy-exception-text 指定時のみ)</t>
+          <t xml:space="preserve">(起動確認時に自動。結果は全量レポート [10] へ。画面表示は --deploy-exception-display 指定時のみ、Excel 出力は --deploy-exception-excel 指定時のみ、テキスト出力は --deploy-exception-text 指定時のみ)</t>
         </is>
       </c>
       <c r="C14" s="10"/>
@@ -7049,7 +7129,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(--copy-file 指定時は既定で自動。無効化は --no-verify-copy-artifact。未検出もエラーにするのは --copy-artifact-required)</t>
+          <t xml:space="preserve">(既定では行わない。--verify-copy-artifact で有効化。--copy-artifact-path / --copy-artifact-search-dir / --copy-artifact-required を指定した場合も有効になる)</t>
         </is>
       </c>
       <c r="C17" s="10"/>
@@ -7249,12 +7329,12 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto (--copy-file 指定時のみ有効)</t>
+          <t xml:space="preserve">false (既定では照合しない)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-file を指定していない実行でも取り込み検証を行う (→ 5.13)</t>
+          <t xml:space="preserve">取り込み検証を行う (→ 5.13)</t>
         </is>
       </c>
     </row>
@@ -7266,17 +7346,17 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-artifact-path PATH</t>
+          <t xml:space="preserve">--no-verify-copy-artifact</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">(既定と同じ)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する</t>
+          <t xml:space="preserve">取り込み検証を行わない。--copy-artifact-path / --copy-artifact-search-dir / --copy-artifact-required とは排他</t>
         </is>
       </c>
     </row>
@@ -7288,39 +7368,39 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-artifact-search-dir DIR</t>
+          <t xml:space="preserve">--copy-artifact-path PATH</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)</t>
+          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
     <row r="31" ht="33.0" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">--copy-artifact-search-dir DIR</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">/</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
@@ -7332,17 +7412,17 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss_master_password</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
         </is>
       </c>
     </row>
@@ -7354,39 +7434,39 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--region REGION</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="34" ht="33.0" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-secret-id ID</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cacerts</t>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
@@ -7398,17 +7478,17 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle PATH</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">一時ファイル</t>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
@@ -7420,17 +7500,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
@@ -7442,39 +7522,39 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-glob PATTERN</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">*.crt と *.pem</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="38" ht="33.0" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">*.crt と *.pem</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7566,7 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -7496,7 +7576,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7588,7 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -7518,7 +7598,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
@@ -7530,39 +7610,39 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="42" ht="33.0" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -7574,17 +7654,17 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -7596,17 +7676,17 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -7618,17 +7698,17 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -7640,17 +7720,17 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -7662,17 +7742,17 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -7684,17 +7764,17 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -7706,39 +7786,39 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="50" ht="33.0" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
@@ -7750,17 +7830,17 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -7772,17 +7852,17 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -7794,17 +7874,17 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -7816,17 +7896,17 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -7838,17 +7918,17 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -7860,17 +7940,17 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -7882,17 +7962,17 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -7904,17 +7984,17 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -7926,17 +8006,17 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -7948,39 +8028,39 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="33.0" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -7992,17 +8072,17 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-method METHOD</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GET</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストメソッド</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -8014,17 +8094,17 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動)</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -8036,17 +8116,17 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -8058,39 +8138,39 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="66" ht="19.5" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+          <t xml:space="preserve">リトライ間隔</t>
         </is>
       </c>
     </row>
@@ -8102,17 +8182,17 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
@@ -8124,17 +8204,17 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--usage-check-script PATH</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動解決)</t>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
         </is>
       </c>
     </row>
@@ -8146,39 +8226,39 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-free-path DIR</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定の 7 か所)</t>
+          <t xml:space="preserve">(自動解決)</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
         </is>
       </c>
     </row>
     <row r="70" ht="19.5" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--disk-free-path DIR</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">(既定の 7 か所)</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
         </is>
       </c>
     </row>
@@ -8190,17 +8270,17 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
         </is>
       </c>
     </row>
@@ -8212,39 +8292,39 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="19.5" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="33.0" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
@@ -8256,17 +8336,17 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
@@ -8278,17 +8358,17 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -8300,17 +8380,17 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -8322,17 +8402,17 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--deploy-exception-display</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -8344,162 +8424,170 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
     <row r="79" ht="33.0" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">有効</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="9.0" customHeight="1">
-      <c r="A80" s="0"/>
-    </row>
-    <row r="81" ht="24.0" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+    <row r="81" ht="9.0" customHeight="1">
+      <c r="A81" s="0"/>
+    </row>
+    <row r="82" ht="24.0" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
         </is>
       </c>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-    </row>
-    <row r="82" ht="19.5" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">記載箇所</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-    </row>
-    <row r="83" ht="33.0" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
     </row>
     <row r="84" ht="33.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
+          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
     </row>
-    <row r="85" ht="49.5" customHeight="1">
+    <row r="85" ht="33.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-2 デプロイエラー時の調査モード (既定) / --exit-on-deploy-error</t>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話の前 / 失敗した起動ログを表示し、WAR デプロイ時 Java 例外解析を先に済ませる (画面へ出すのは --deploy-exception-display 指定時。既定では全量レポート [10] と Excel へ残すだけ)</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
     </row>
-    <row r="86" ht="33.0" customHeight="1">
+    <row r="86" ht="49.5" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">5.4-2 デプロイエラー時の調査モード (既定) / --exit-on-deploy-error</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+          <t xml:space="preserve">対話の前 / 失敗した起動ログを表示し、WAR デプロイ時 Java 例外解析を先に済ませる (画面へ出すのは --deploy-exception-display 指定時。既定では全量レポート [10] へ残すだけ)</t>
         </is>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
     </row>
-    <row r="87" ht="49.5" customHeight="1">
+    <row r="87" ht="33.0" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">原因</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
     </row>
-    <row r="88" ht="19.5" customHeight="1">
+    <row r="88" ht="49.5" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">後始末でのボリューム削除</t>
+          <t xml:space="preserve">原因</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
         </is>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
     </row>
-    <row r="89" ht="33.0" customHeight="1">
+    <row r="89" ht="19.5" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
         </is>
       </c>
       <c r="C89" s="3"/>
@@ -8508,12 +8596,12 @@
     <row r="90" ht="33.0" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">6.2 出力ファイル</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
         </is>
       </c>
       <c r="C90" s="3"/>
@@ -8527,7 +8615,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
       <c r="C91" s="3"/>
@@ -8541,7 +8629,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
       <c r="C92" s="3"/>
@@ -8550,16 +8638,30 @@
     <row r="93" ht="33.0" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
         </is>
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
+    </row>
+    <row r="94" ht="33.0" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -8581,8 +8683,7 @@
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="A82:D82"/>
     <mergeCell ref="B83:D83"/>
     <mergeCell ref="B84:D84"/>
     <mergeCell ref="B85:D85"/>
@@ -8594,6 +8695,7 @@
     <mergeCell ref="B91:D91"/>
     <mergeCell ref="B92:D92"/>
     <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B94:D94"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9188,7 +9290,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="115.5" customHeight="1">
+    <row r="35" ht="82.5" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -9196,10 +9298,9 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイ結果ファイルと Java 例外解析の Excel をまとめて保存
-(reports/build_and_verify_&lt;日時&gt;.txt … [10] に例外解析の全文、
-reports/build_and_verify_&lt;日時&gt;_java_exceptions.xlsx が出力される。
-画面には解析結果を出さない ← 既定)</t>
+          <t xml:space="preserve">デプロイ結果ファイルへ Java 例外解析を残す
+(reports/build_and_verify_&lt;日時&gt;.txt … [10] に例外解析の全文。
+画面表示も Excel / テキストの出力も行わない ← 既定)</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-23 02:15:29</t>
+          <t xml:space="preserve">2026-08-23 09:52:44</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="49.5" customHeight="1">
+    <row r="51" ht="66.0" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
@@ -1088,131 +1088,131 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">build コンテキスト / Dockerfile の上書き</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose_build_scan / compose_build_rewrite / apply_compose_build_overrides</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="49.5" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中盤</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">シークレット準備・一時ファイルコピー</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">prepare_jboss_password / prepare_copy_files</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="82.5" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="53" ht="82.5" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">マスターパスワードの伝搬検証</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">危険文字の分析、段ごとの比較、compose.yml と standalone.xml の解析、CredentialStore の開封確認</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="49.5" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="54" ht="49.5" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">起動確認・ログ表示ヘルパ</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ取得、ANSI 除去、色分け、companion ログ</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="33.0" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="55" ht="33.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナ内情報の収集と整形</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="82.5" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="56" ht="82.5" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM パラメータ・OpenTelemetry 設定</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">/proc/&lt;pid&gt;/cmdline の走査、JVM オプションの分類、OpenTelemetry 設定の突き合わせ</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="66.0" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="57" ht="66.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対話操作</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">bash / HTTP / logs モードと、healthcheck・MySQL・可観測性の各ヘルパ</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="33.0" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="58" ht="33.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 完全クリーンアップ</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対象の集計、確認フレーズ、削除、検証</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="66.0" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルドの停滞検知・進捗表示</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド出力の読み手、監視プロセス、停滞診断、上限時間での中断</t>
         </is>
       </c>
     </row>
@@ -1224,46 +1224,46 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルドの停滞検知・進捗表示</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド出力の読み手、監視プロセス、停滞診断、上限時間での中断</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="66.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">WAR デプロイ時 Java 例外解析</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">解析ヘルパー (Python 3) の埋め込みと、ログ収集・実行・表示・レポート追記</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="132.0" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="61" ht="132.0" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">後半</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">分析ヘルパー (Python 3) の埋め込みと、compose.yml / Dockerfile (ビルド時) / 起動スクリプト・実行状況 (実行時) の収集・実行・表示・レポート追記</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポート</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">write_build_report</t>
         </is>
       </c>
     </row>
@@ -1275,406 +1275,457 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">全量レポート</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">write_build_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">後始末 (cleanup_all)</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">EXIT トラップ本体</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="49.5" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
+    <row r="64" ht="49.5" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">末尾</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">メイン処理</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド → 起動 → 起動確認 → URL 確認 → 対話 → 情報表示</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="19.5" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.2 主要な関数グループ》</t>
         </is>
       </c>
-      <c r="B64" s="8"/>
-    </row>
-    <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="B65" s="8"/>
+    </row>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">グループ</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">代表的な関数</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">役割</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="33.0" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="67" ht="33.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ・時刻</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / to_jst_display_time</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">出力整形と UTC→JST 変換</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="66.0" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
+    <row r="68" ht="66.0" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">引数処理</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">append_services / need_value / validate_positive_integer / validate_non_negative_integer</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">カンマ区切り分割、値欠落検出、数値検証 (ビルド監視の各値は 0 を許す)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="49.5" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
+    <row r="69" ht="49.5" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Compose 操作</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose_container_ids / compose_logs / compose_started_services</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対象サービスの ID・ログ・サービス名取得</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="33.0" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="33.0" customHeight="1">
+    <row r="70" ht="82.5" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログ表示</t>
+          <t xml:space="preserve">build 設定の上書き</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
+          <t xml:space="preserve">apply_compose_build_overrides / compose_build_scan / compose_build_rewrite / cleanup_generated_compose_file / compose_file_display</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">行数制御と重要ログの色分け</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="33.0" customHeight="1">
+          <t xml:space="preserve">--base-context などの指定を反映した実効 compose ファイルの生成・検証・後始末 (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="66.0" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL 確認</t>
+          <t xml:space="preserve">サービスの保護</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">verify_url / show_url_body</t>
+          <t xml:space="preserve">validate_keep_services / resolve_keep_service_targets / service_is_kept / run_compose_build / remove_project_volumes_except_kept / remove_all_images_except_kept / remove_all_volumes_except_kept</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl のリトライと応答本文表示</t>
+          <t xml:space="preserve">--keep-service の no-cache 除外と、イメージ・ボリュームの保護 (→ 5.1-3)</t>
         </is>
       </c>
     </row>
     <row r="72" ht="33.0" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">情報表示</t>
+          <t xml:space="preserve">起動確認</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_verified_container_envs / ..._directory_trees / ..._deployment_structures</t>
+          <t xml:space="preserve">start_container / wait_for_startup / containers_all_running / target_services_all_running</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="66.0" customHeight="1">
+          <t xml:space="preserve">起動、ログポーリング、途中停止の検知</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="33.0" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JVM / OTel</t>
+          <t xml:space="preserve">ログ表示</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">show_verified_container_jvm_parameters / ..._otel_settings / collect_container_java_processes / classify_jvm_option / is_otel_jvm_option</t>
+          <t xml:space="preserve">show_startup_logs / print_startup_logs_with_highlights / show_companion_service_logs</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java プロセスの検出、JVM オプションの分類、OpenTelemetry 設定の集約</t>
+          <t xml:space="preserve">行数制御と重要ログの色分け</t>
         </is>
       </c>
     </row>
     <row r="74" ht="33.0" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作</t>
+          <t xml:space="preserve">URL 確認</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
+          <t xml:space="preserve">verify_url / show_url_body</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / HTTP / logs モード</t>
+          <t xml:space="preserve">curl のリトライと応答本文表示</t>
         </is>
       </c>
     </row>
     <row r="75" ht="33.0" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck</t>
+          <t xml:space="preserve">情報表示</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
+          <t xml:space="preserve">show_verified_container_envs / ..._directory_trees / ..._deployment_structures</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="33.0" customHeight="1">
+          <t xml:space="preserve">環境変数・ツリー・デプロイ構造</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="66.0" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">可観測性</t>
+          <t xml:space="preserve">JVM / OTel</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+          <t xml:space="preserve">show_verified_container_jvm_parameters / ..._otel_settings / collect_container_java_processes / classify_jvm_option / is_otel_jvm_option</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+          <t xml:space="preserve">Java プロセスの検出、JVM オプションの分類、OpenTelemetry 設定の集約</t>
         </is>
       </c>
     </row>
     <row r="77" ht="33.0" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">対話操作</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">run_keep_container_interaction / run_interactive_compose_service_menu ほか</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bash / HTTP / logs モード</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="33.0" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">healthcheck</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">run_interactive_compose_healthcheck / run_healthcheck_http_probe</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">healthcheck の設定・履歴・通信確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="33.0" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可観測性</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">render_cloudwatch_delivery_report / run_otel_jaeger_trace_helper</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cwagent / OTel のローカル送達診断</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">クリーンアップ</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cleanup_all_docker_data / teardown_container / cleanup_copied_files</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 全体削除と通常後始末</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="82.5" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
+    <row r="81" ht="82.5" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド監視</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">run_build_with_watchdog / build_watchdog_reader / build_watchdog_monitor / diagnose_build_stall / build_phase_from_line / check_build_disk_space</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exporting layers などで出力が途切れたときの進捗表示・停滞診断・上限時間での中断</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="66.0" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
+    <row r="82" ht="66.0" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">cwagent 送信検証</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">verify_cwagent_config_definition / verify_cwagent_log_delivery / cwagent_config_facts / cwagent_verify_endpoint_override / cwagent_verify_log_source_mounts</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose.yml と設定 JSON の静的照合、起動後のロググループへの送達確認</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="66.0" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
+    <row r="83" ht="66.0" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">cwagent ロググループ準備</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">prepare_cwagent_log_groups / cwagent_ensure_log_groups / cwagent_resolve_delivery_target</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">設定ファイルの log_group_name が実 CloudWatch Logs に無ければ作成</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="115.5" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
+    <row r="84" ht="115.5" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">analyze_war_deploy_exceptions / deploy_exception_output_requested / collect_deploy_exception_logs / resolve_analysis_output_path / show_war_deploy_exception_analysis / show_war_deploy_exception_outputs / append_deploy_exception_report</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、出力先の要否判定、画面表示 (--deploy-exception-display 指定時) と Excel / テキスト出力</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="181.5" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
+    <row r="85" ht="181.5" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用 FS 分析</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">analyze_readonly_filesystem / readonly_collect_compose_facts / readonly_collect_dockerfile_facts / readonly_parse_dockerfile / readonly_shell_write_targets / readonly_scan_context_script / readonly_collect_runtime_facts / readonly_container_probe / readonly_collect_container_scripts / show_readonly_filesystem_analysis / append_readonly_analysis_report</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose.yml の read_only / tmpfs / volumes の解析、Dockerfile からのビルド時の書き込み先の収集、起動スクリプトからの実行時の書き込み先の収集、コンテナの書き込み状況の収集、判定結果の表示と Excel / テキスト出力</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="33.0" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="86" ht="33.0" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">レポート</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">write_build_report / append_compose_service_logs_report / append_jboss_password_report / append_cwagent_report / append_deploy_exception_report / append_readonly_analysis_report</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートの生成</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="66.0" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
+    <row r="87" ht="66.0" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">パスワード伝搬検証</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">verify_jboss_password_host_stages / verify_jboss_password_build_secret / verify_jboss_password_container_stages / jboss_xml_attributes / jboss_xml_unescape / jboss_wildfly_literal</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">各段の値の取得、XML と WildFly 式のエスケープ解除、原本との突き合わせ</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="19.5" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
+    <row r="88" ht="19.5" customHeight="1">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B85" s="8"/>
-    </row>
-    <row r="86" ht="19.5" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="B88" s="8"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">処理のどの経路 (成功・失敗・中断) でも、次の順で実行されます。</t>
         </is>
       </c>
-      <c r="B86" s="3"/>
-    </row>
-    <row r="87" ht="19.5" customHeight="1">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="B89" s="3"/>
+    </row>
+    <row r="90" ht="19.5" customHeight="1">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B87" s="8"/>
-    </row>
-    <row r="88" ht="409.0" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
+      <c r="B90" s="8"/>
+    </row>
+    <row r="91" ht="409.0" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1. analyze_war_deploy_exceptions … デプロイ処理の Java 例外を解析 (削除より前・レポートより前)
                                    成功経路で実行済みなら何もしない
@@ -1683,6 +1734,8 @@
 3. write_build_report        … --report-dir 指定時、全量レポートを保存 (削除より前に実行)
 4. cleanup_all_docker_data   … --cleanup-all-docker-data 指定時、確認フレーズ入力後に全削除
 5. teardown_container        … compose down (--keep-container 指定時は残す)
+                                   --keep-service を指定した実行では --volumes を付けず、
+                                   保護対象以外のボリュームだけを個別に削除する (→ 5.1-3)
                                    対話操作を最後まで終えた実行では、--keep-container が
                                    暗黙有効でもここで削除する (6 の対象にするため)
                                    そのとき、および取り込み検証で古い成果物を抱えた
@@ -1701,74 +1754,76 @@
                                     退避しておいた上書き前のファイルを復元)
 10. 一時ファイル削除         … Java 例外解析結果・読み取り専用 FS 分析結果・
                                    URL 応答本文・HTTP ボディ・healthcheck 診断
+                                   および build 設定の上書きで生成した実効 compose ファイル
+                                   (元の compose ファイルには触れない)
 11. show_post_interaction_disk_free … 6 を試行した実行のみ、各ディレクトリの
                                    ディスク空き容量を一覧表示して終える</t>
         </is>
       </c>
-      <c r="B88" s="6"/>
-    </row>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="B91" s="6"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B89" s="8"/>
-    </row>
-    <row r="90" ht="33.0" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="B92" s="8"/>
+    </row>
+    <row r="93" ht="33.0" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">終了コードは、本処理が既に失敗していれば元の終了コードを優先します。
 成功していた場合は、後始末の結果 (レポート保存失敗やクリーンアップ未承認なら 1) を返します。</t>
         </is>
       </c>
-      <c r="B90" s="3"/>
-    </row>
-    <row r="91" ht="19.5" customHeight="1">
-      <c r="A91" s="8" t="inlineStr">
+      <c r="B93" s="3"/>
+    </row>
+    <row r="94" ht="19.5" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ (cleanup_all)》</t>
         </is>
       </c>
-      <c r="B91" s="8"/>
-    </row>
-    <row r="92" ht="19.5" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="B94" s="8"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B92" s="3"/>
-    </row>
-    <row r="93" ht="9.0" customHeight="1">
-      <c r="A93" s="0"/>
-    </row>
-    <row r="94" ht="24.0" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="B95" s="3"/>
+    </row>
+    <row r="96" ht="9.0" customHeight="1">
+      <c r="A96" s="0"/>
+    </row>
+    <row r="97" ht="24.0" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">3. 処理の流れ</t>
         </is>
       </c>
-      <c r="B94" s="5"/>
-    </row>
-    <row r="95" ht="19.5" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="B97" s="5"/>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B95" s="8"/>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="B98" s="8"/>
+    </row>
+    <row r="99" ht="19.5" customHeight="1">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B96" s="8"/>
-    </row>
-    <row r="97" ht="99.0" customHeight="1">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="B99" s="8"/>
+    </row>
+    <row r="100" ht="99.0" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時は、EXIT の後始末でレポートのログ本文を集める直前に
 compose stop (SIGTERM) を挟みます (3.6 参照)。
@@ -1778,18 +1833,18 @@
 必ず実行します** (6.7 参照)。</t>
         </is>
       </c>
-      <c r="B97" s="3"/>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="B100" s="3"/>
+    </row>
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.1 全体フロー》</t>
         </is>
       </c>
-      <c r="B98" s="8"/>
-    </row>
-    <row r="99" ht="66.0" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="B101" s="8"/>
+    </row>
+    <row r="102" ht="66.0" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析も同じタイミングで実行します。
 こちらは compose.yml と Dockerfile の定義だけでも判定できるため、
@@ -1797,277 +1852,277 @@
 実行状況からの根拠が無いことを結果へ明記します (6.8 参照)。</t>
         </is>
       </c>
-      <c r="B99" s="3"/>
-    </row>
-    <row r="100" ht="19.5" customHeight="1">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="B102" s="3"/>
+    </row>
+    <row r="103" ht="19.5" customHeight="1">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B100" s="8"/>
-    </row>
-    <row r="101" ht="19.5" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="B103" s="8"/>
+    </row>
+    <row r="104" ht="19.5" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--compose-service の指定数によってビルド戦略が変わります。</t>
         </is>
       </c>
-      <c r="B101" s="3"/>
-    </row>
-    <row r="102" ht="19.5" customHeight="1">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="B104" s="3"/>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B102" s="8"/>
-    </row>
-    <row r="103" ht="19.5" customHeight="1">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="B105" s="8"/>
+    </row>
+    <row r="106" ht="19.5" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">指定</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">動作</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="19.5" customHeight="1">
-      <c r="A104" s="11" t="inlineStr">
+    <row r="107" ht="19.5" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">未指定</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全サービスを 1 回の compose build でビルド</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="19.5" customHeight="1">
-      <c r="A105" s="11" t="inlineStr">
+    <row r="108" ht="19.5" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1 個</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そのサービスのみビルド</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="33.0" customHeight="1">
-      <c r="A106" s="11" t="inlineStr">
+    <row r="109" ht="33.0" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2 個以上</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">第 1 フェーズ: base サービスを単独で先行ビルド → ローカルイメージ確認 → 第 2 フェーズ: base 以外をまとめて並列ビルド</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="19.5" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+    <row r="110" ht="19.5" customHeight="1">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B107" s="8"/>
-    </row>
-    <row r="108" ht="33.0" customHeight="1">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="B110" s="8"/>
+    </row>
+    <row r="111" ht="33.0" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2 段階に分けるのは、ベースイメージを参照するサービスが base の完成前にビルドを始めるのを
 防ぐためです。並列オプションは compose のバージョンによって使い分けます。</t>
         </is>
       </c>
-      <c r="B108" s="3"/>
-    </row>
-    <row r="109" ht="19.5" customHeight="1">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="B111" s="3"/>
+    </row>
+    <row r="112" ht="19.5" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B109" s="8"/>
-    </row>
-    <row r="110" ht="19.5" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="B112" s="8"/>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">compose</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">並列指定</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="19.5" customHeight="1">
-      <c r="A111" s="11" t="inlineStr">
+    <row r="114" ht="19.5" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">v2 (docker compose)</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">グローバルオプション --parallel &lt;サービス数&gt;</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="19.5" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
+    <row r="115" ht="19.5" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">v1 (docker-compose)</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build --parallel (未対応版は exit 1)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="19.5" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
+    <row r="116" ht="19.5" customHeight="1">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B113" s="8"/>
-    </row>
-    <row r="114" ht="33.0" customHeight="1">
-      <c r="A114" s="3" t="inlineStr">
+      <c r="B116" s="8"/>
+    </row>
+    <row r="117" ht="33.0" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド後は docker image inspect でローカルイメージを確認し、
 image=... id=... created=... size=... bytes を JST 表記でログに残します。</t>
         </is>
       </c>
-      <c r="B114" s="3"/>
-    </row>
-    <row r="115" ht="19.5" customHeight="1">
-      <c r="A115" s="8" t="inlineStr">
+      <c r="B117" s="3"/>
+    </row>
+    <row r="118" ht="19.5" customHeight="1">
+      <c r="A118" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B115" s="8"/>
-    </row>
-    <row r="116" ht="19.5" customHeight="1">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="B118" s="8"/>
+    </row>
+    <row r="119" ht="19.5" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドの前後では、ディスク使用量を抑えるために次を行います (5.8-2 参照)。</t>
         </is>
       </c>
-      <c r="B116" s="3"/>
-    </row>
-    <row r="117" ht="19.5" customHeight="1">
-      <c r="A117" s="8" t="inlineStr">
+      <c r="B119" s="3"/>
+    </row>
+    <row r="120" ht="19.5" customHeight="1">
+      <c r="A120" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B117" s="8"/>
-    </row>
-    <row r="118" ht="19.5" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="B120" s="8"/>
+    </row>
+    <row r="121" ht="19.5" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">タイミング</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="19.5" customHeight="1">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="19.5" customHeight="1">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">data root の空き容量を確認し、5 GiB 未満なら警告する (5.2-2 参照)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="19.5" customHeight="1">
-      <c r="A121" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
         </is>
       </c>
     </row>
     <row r="122" ht="19.5" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="19.5" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data root の空き容量を確認し、5 GiB 未満なら警告する (5.2-2 参照)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="19.5" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="19.5" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">ローカルイメージ確認の直後</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ID が変わっていれば、タグを失った旧世代イメージを削除する</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="19.5" customHeight="1">
-      <c r="A123" s="8" t="inlineStr">
+    <row r="126" ht="19.5" customHeight="1">
+      <c r="A126" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.2 ビルドフェーズの詳細》</t>
         </is>
       </c>
-      <c r="B123" s="8"/>
-    </row>
-    <row r="124" ht="33.0" customHeight="1">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="B126" s="8"/>
+    </row>
+    <row r="127" ht="33.0" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド自体は監視プロセス付きで実行し、exporting to image / exporting layers で
 出力が途切れても状況が分かるようにします (5.2-2 参照)。</t>
         </is>
       </c>
-      <c r="B124" s="3"/>
-    </row>
-    <row r="125" ht="19.5" customHeight="1">
-      <c r="A125" s="8" t="inlineStr">
+      <c r="B127" s="3"/>
+    </row>
+    <row r="128" ht="19.5" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B125" s="8"/>
-    </row>
-    <row r="126" ht="19.5" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="B128" s="8"/>
+    </row>
+    <row r="129" ht="19.5" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.3 起動確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B126" s="8"/>
-    </row>
-    <row r="127" ht="99.0" customHeight="1">
-      <c r="A127" s="3" t="inlineStr">
+      <c r="B129" s="8"/>
+    </row>
+    <row r="130" ht="99.0" customHeight="1">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・--startup-service を指定した場合は、サービスごとに個別に起動完了を判定し、
   指定した全サービスの完了をもって成功とします
@@ -2077,35 +2132,35 @@
 ・失敗時は --suppress-startup-logs を指定していてもログを表示します (原因を隠さないため)</t>
         </is>
       </c>
-      <c r="B127" s="3"/>
-    </row>
-    <row r="128" ht="19.5" customHeight="1">
-      <c r="A128" s="8" t="inlineStr">
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" ht="19.5" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B128" s="8"/>
-    </row>
-    <row r="129" ht="33.0" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
+      <c r="B131" s="8"/>
+    </row>
+    <row r="132" ht="33.0" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">curl -s -S -m 30 -o &lt;一時ファイル&gt; -w '%{http_code}' -X &lt;URL_METHOD&gt; \
      [-k] [-H "Content-Type: &lt;URL_CONTENT_TYPE&gt;"] [--data &lt;ボディ&gt;] &lt;VERIFY_URL&gt;</t>
         </is>
       </c>
-      <c r="B129" s="6"/>
-    </row>
-    <row r="130" ht="19.5" customHeight="1">
-      <c r="A130" s="8" t="inlineStr">
+      <c r="B132" s="6"/>
+    </row>
+    <row r="133" ht="19.5" customHeight="1">
+      <c r="A133" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B130" s="8"/>
-    </row>
-    <row r="131" ht="66.0" customHeight="1">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="B133" s="8"/>
+    </row>
+    <row r="134" ht="66.0" customHeight="1">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・期待ステータス (--expect-status) と一致するまで --url-interval 秒間隔でリトライ
 ・--url-timeout 秒を超えると失敗 (最後の応答コードを表示)
@@ -2113,181 +2168,181 @@
 ・成功・失敗いずれの場合も、応答本文の先頭 20 行を表示</t>
         </is>
       </c>
-      <c r="B131" s="3"/>
-    </row>
-    <row r="132" ht="19.5" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
+      <c r="B134" s="3"/>
+    </row>
+    <row r="135" ht="19.5" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 URL 応答確認フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B132" s="8"/>
-    </row>
-    <row r="133" ht="33.0" customHeight="1">
-      <c r="A133" s="3" t="inlineStr">
+      <c r="B135" s="8"/>
+    </row>
+    <row r="136" ht="33.0" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--verify-startup を付けず --verify-url のみを指定した場合もコンテナは起動します
 (起動完了のログ確認は行わず、URL のリトライで readiness を担保します)。</t>
         </is>
       </c>
-      <c r="B133" s="3"/>
-    </row>
-    <row r="134" ht="19.5" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+      <c r="B136" s="3"/>
+    </row>
+    <row r="137" ht="19.5" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B134" s="8"/>
-    </row>
-    <row r="135" ht="19.5" customHeight="1">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="B137" s="8"/>
+    </row>
+    <row r="138" ht="19.5" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">状況</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの扱い</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="19.5" customHeight="1">
-      <c r="A136" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose down で停止・削除 (ボリュームは残す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="49.5" customHeight="1">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作をすべて終了し、終了コードが 0</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose down --volumes でボリュームごと削除したうえで、未使用リソースまで完全クリア (→ 5.4-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="33.0" customHeight="1">
-      <c r="A138" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">取り込み検証で「古い成果物を抱えたボリューム」を検出</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose down --volumes でボリュームごと削除し、次回の実行で作り直させる (→ 5.13)</t>
         </is>
       </c>
     </row>
     <row r="139" ht="19.5" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--remove-volumes 指定</t>
+          <t xml:space="preserve">通常</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">この実行が行うすべての compose down へ --volumes を付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="19.5" customHeight="1">
+          <t xml:space="preserve">compose down で停止・削除 (ボリュームは残す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="49.5" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-volumes 指定</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作をすべて終了し、終了コードが 0</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記いずれの場合もボリュームを残す (従来の動作)</t>
+          <t xml:space="preserve">compose down --volumes でボリュームごと削除したうえで、未使用リソースまで完全クリア (→ 5.4-2)</t>
         </is>
       </c>
     </row>
     <row r="141" ht="33.0" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container / --keep-container-mode 指定 (上記以外)</t>
+          <t xml:space="preserve">取り込み検証で「古い成果物を抱えたボリューム」を検出</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="33.0" customHeight="1">
+          <t xml:space="preserve">compose down --volumes でボリュームごと削除し、次回の実行で作り直させる (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="19.5" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-after-interaction 指定</t>
+          <t xml:space="preserve">--remove-volumes 指定</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作を終えても残す (従来の動作)</t>
+          <t xml:space="preserve">この実行が行うすべての compose down へ --volumes を付ける</t>
         </is>
       </c>
     </row>
     <row r="143" ht="19.5" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--keep-volumes 指定</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記いずれの場合もボリュームを残す (従来の動作)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="33.0" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container / --keep-container-mode 指定 (上記以外)</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="33.0" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container-after-interaction 指定</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">対話操作を終えても残す (従来の動作)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="19.5" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
         </is>
       </c>
-      <c r="B143" s="3" t="inlineStr">
+      <c r="B146" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="19.5" customHeight="1">
-      <c r="A144" s="11" t="inlineStr">
+    <row r="147" ht="19.5" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B147" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="19.5" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+    <row r="148" ht="19.5" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B145" s="8"/>
-    </row>
-    <row r="146" ht="49.5" customHeight="1">
-      <c r="A146" s="3" t="inlineStr">
+      <c r="B148" s="8"/>
+    </row>
+    <row r="149" ht="49.5" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの削除後に、--prune-build-cache / --prune-build-cache-keep 指定時はビルド
 キャッシュを削除し、--disk-usage-report 指定時は終了時の使用量と実行前からの増減を
 表示します (5.8-2 参照)。</t>
         </is>
       </c>
-      <c r="B146" s="3"/>
-    </row>
-    <row r="147" ht="19.5" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
+      <c r="B149" s="3"/>
+    </row>
+    <row r="150" ht="19.5" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B147" s="8"/>
-    </row>
-    <row r="148" ht="66.0" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
+      <c r="B150" s="8"/>
+    </row>
+    <row r="151" ht="66.0" customHeight="1">
+      <c r="A151" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS はタスク停止時に各コンテナへ SIGTERM を送るため、adot collector のような
 サイドカーは「シグナル受信 → パイプラインの graceful shutdown → 終了」までを
@@ -2295,34 +2350,34 @@
 誰にも取得されないままコンテナごと削除されてしまいます。</t>
         </is>
       </c>
-      <c r="B148" s="3"/>
-    </row>
-    <row r="149" ht="19.5" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
+      <c r="B151" s="3"/>
+    </row>
+    <row r="152" ht="19.5" customHeight="1">
+      <c r="A152" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B149" s="8"/>
-    </row>
-    <row r="150" ht="19.5" customHeight="1">
-      <c r="A150" s="3" t="inlineStr">
+      <c r="B152" s="8"/>
+    </row>
+    <row r="153" ht="19.5" customHeight="1">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">そこでエラー終了時に限り、削除の前に SIGTERM による停止を挟みます。</t>
         </is>
       </c>
-      <c r="B150" s="3"/>
-    </row>
-    <row r="151" ht="19.5" customHeight="1">
-      <c r="A151" s="8" t="inlineStr">
+      <c r="B153" s="3"/>
+    </row>
+    <row r="154" ht="19.5" customHeight="1">
+      <c r="A154" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B151" s="8"/>
-    </row>
-    <row r="152" ht="148.5" customHeight="1">
-      <c r="A152" s="6" t="inlineStr">
+      <c r="B154" s="8"/>
+    </row>
+    <row r="155" ht="148.5" customHeight="1">
+      <c r="A155" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">[2] 〜 [6] の収集 (起動中のコンテナが必要)
         ↓
@@ -2335,18 +2390,18 @@
 compose down (削除)</t>
         </is>
       </c>
-      <c r="B152" s="6"/>
-    </row>
-    <row r="153" ht="19.5" customHeight="1">
-      <c r="A153" s="8" t="inlineStr">
+      <c r="B155" s="6"/>
+    </row>
+    <row r="156" ht="19.5" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B153" s="8"/>
-    </row>
-    <row r="154" ht="165.0" customHeight="1">
-      <c r="A154" s="3" t="inlineStr">
+      <c r="B156" s="8"/>
+    </row>
+    <row r="157" ht="165.0" customHeight="1">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・対象は compose ps --services が返す稼働中の全サービスです
   (起動確認対象だけでなく adot collector などのサイドカーも含みます)
@@ -2360,458 +2415,458 @@
   従来どおり compose down でまとめて削除します</t>
         </is>
       </c>
-      <c r="B154" s="3"/>
-    </row>
-    <row r="155" ht="19.5" customHeight="1">
-      <c r="A155" s="8" t="inlineStr">
+      <c r="B157" s="3"/>
+    </row>
+    <row r="158" ht="19.5" customHeight="1">
+      <c r="A158" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B155" s="8"/>
-    </row>
-    <row r="156" ht="49.5" customHeight="1">
-      <c r="A156" s="3" t="inlineStr">
+      <c r="B158" s="8"/>
+    </row>
+    <row r="159" ht="49.5" customHeight="1">
+      <c r="A159" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">adot collector の healthcheck が失敗し、depends_on の condition: service_healthy
 を満たせずバックエンドが起動しなかった場合、ECS 上でも同じくタスクが停止します。
 その終了処理まで含めてローカルで再現・確認できるようにするのがこの動作の狙いです。</t>
         </is>
       </c>
-      <c r="B156" s="3"/>
-    </row>
-    <row r="157" ht="19.5" customHeight="1">
-      <c r="A157" s="8" t="inlineStr">
+      <c r="B159" s="3"/>
+    </row>
+    <row r="160" ht="19.5" customHeight="1">
+      <c r="A160" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.6 エラー終了時の終了 (SIGTERM) ログ》</t>
         </is>
       </c>
-      <c r="B157" s="8"/>
-    </row>
-    <row r="158" ht="19.5" customHeight="1">
-      <c r="A158" s="3" t="inlineStr">
+      <c r="B160" s="8"/>
+    </row>
+    <row r="161" ht="19.5" customHeight="1">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B158" s="3"/>
-    </row>
-    <row r="159" ht="9.0" customHeight="1">
-      <c r="A159" s="0"/>
-    </row>
-    <row r="160" ht="24.0" customHeight="1">
-      <c r="A160" s="5" t="inlineStr">
+      <c r="B161" s="3"/>
+    </row>
+    <row r="162" ht="9.0" customHeight="1">
+      <c r="A162" s="0"/>
+    </row>
+    <row r="163" ht="24.0" customHeight="1">
+      <c r="A163" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">5. 終了コード</t>
         </is>
       </c>
-      <c r="B160" s="5"/>
-    </row>
-    <row r="161" ht="19.5" customHeight="1">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="B163" s="5"/>
+    </row>
+    <row r="164" ht="19.5" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コード</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">意味</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">主な発生条件</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="33.0" customHeight="1">
-      <c r="A162" s="11" t="inlineStr">
+    <row r="165" ht="33.0" customHeight="1">
+      <c r="A165" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="B162" s="3" t="inlineStr">
+      <c r="B165" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">正常終了</t>
         </is>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="C165" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド (と指定した確認) がすべて成功</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="409.0" customHeight="1">
-      <c r="A163" s="11" t="inlineStr">
+    <row r="166" ht="409.0" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B163" s="3" t="inlineStr">
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行時エラー</t>
         </is>
       </c>
-      <c r="C163" s="3" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、対話操作の終了後の完全クリーンアップ失敗 (docker-usage-check.sh が見つからない・失敗した)、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG、コピーしたファイルの取り込み検証 NG (コンテナ内の中身がコピー元と一致しない / --copy-artifact-required 指定時に未検出)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="409.0" customHeight="1">
-      <c r="A164" s="11" t="inlineStr">
+    <row r="167" ht="409.0" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B164" s="3" t="inlineStr">
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数エラー</t>
         </is>
       </c>
-      <c r="C164" s="3" t="inlineStr">
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正、--copy-artifact-path / --copy-artifact-search-dir が絶対パスでない、--remove-volumes と --keep-volumes の同時指定</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="19.5" customHeight="1">
-      <c r="A165" s="3" t="inlineStr">
+    <row r="168" ht="19.5" customHeight="1">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">本処理が失敗している場合は、後始末の結果にかかわらず元の終了コードが優先されます。</t>
         </is>
       </c>
-      <c r="B165" s="3"/>
-    </row>
-    <row r="166" ht="19.5" customHeight="1">
-      <c r="A166" s="3" t="inlineStr">
+      <c r="B168" s="3"/>
+    </row>
+    <row r="169" ht="19.5" customHeight="1">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B166" s="3"/>
-    </row>
-    <row r="167" ht="9.0" customHeight="1">
-      <c r="A167" s="0"/>
-    </row>
-    <row r="168" ht="24.0" customHeight="1">
-      <c r="A168" s="5" t="inlineStr">
+      <c r="B169" s="3"/>
+    </row>
+    <row r="170" ht="9.0" customHeight="1">
+      <c r="A170" s="0"/>
+    </row>
+    <row r="171" ht="24.0" customHeight="1">
+      <c r="A171" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">6. 環境変数</t>
         </is>
       </c>
-      <c r="B168" s="5"/>
-    </row>
-    <row r="169" ht="19.5" customHeight="1">
-      <c r="A169" s="8" t="inlineStr">
+      <c r="B171" s="5"/>
+    </row>
+    <row r="172" ht="19.5" customHeight="1">
+      <c r="A172" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.1 入力として参照する環境変数》</t>
         </is>
       </c>
-      <c r="B169" s="8"/>
-    </row>
-    <row r="170" ht="19.5" customHeight="1">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="B172" s="8"/>
+    </row>
+    <row r="173" ht="19.5" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="19.5" customHeight="1">
-      <c r="A171" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="19.5" customHeight="1">
-      <c r="A172" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="19.5" customHeight="1">
-      <c r="A173" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
         </is>
       </c>
     </row>
     <row r="174" ht="19.5" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
+          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
     </row>
     <row r="175" ht="19.5" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_COLOR</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">定義されていれば色分けを無効化</t>
+          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
     </row>
     <row r="176" ht="19.5" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLICOLOR_FORCE</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
         </is>
       </c>
     </row>
     <row r="177" ht="19.5" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERM</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dumb の場合は色分けしない</t>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
         </is>
       </c>
     </row>
     <row r="178" ht="19.5" customHeight="1">
-      <c r="A178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
-        </is>
-      </c>
-      <c r="B178" s="8"/>
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO_COLOR</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定義されていれば色分けを無効化</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="19.5" customHeight="1">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用途</t>
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLICOLOR_FORCE</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
         </is>
       </c>
     </row>
     <row r="180" ht="19.5" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TZ</t>
+          <t xml:space="preserve">TERM</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
+          <t xml:space="preserve">dumb の場合は色分けしない</t>
         </is>
       </c>
     </row>
     <row r="181" ht="19.5" customHeight="1">
-      <c r="A181" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
-        </is>
-      </c>
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">《7.2 スクリプトが設定する環境変数》</t>
+        </is>
+      </c>
+      <c r="B181" s="8"/>
     </row>
     <row r="182" ht="19.5" customHeight="1">
-      <c r="A182" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用途</t>
         </is>
       </c>
     </row>
     <row r="183" ht="19.5" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">TZ</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia/Tokyo または JST-9。表示・保存時刻を JST に統一</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="19.5" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="19.5" customHeight="1">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="19.5" customHeight="1">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B183" s="3" t="inlineStr">
+      <c r="B186" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="33.0" customHeight="1">
-      <c r="A184" s="11" t="inlineStr">
+    <row r="187" ht="33.0" customHeight="1">
+      <c r="A187" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;--cacert-bundle-env の値&gt;</t>
         </is>
       </c>
-      <c r="B184" s="3" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CA 証明書をまとめた tar のパス。compose の file 型シークレットへ渡す。--cacert-dir 未指定時は「空の tar」のパスが入り、従来どおり証明書なしでビルドされる</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="19.5" customHeight="1">
-      <c r="A185" s="8" t="inlineStr">
+    <row r="188" ht="19.5" customHeight="1">
+      <c r="A188" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B185" s="8"/>
-    </row>
-    <row r="186" ht="49.5" customHeight="1">
-      <c r="A186" s="3" t="inlineStr">
+      <c r="B188" s="8"/>
+    </row>
+    <row r="189" ht="49.5" customHeight="1">
+      <c r="A189" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 / 7.2 はスクリプト自身が実行ホストで参照・設定する環境変数です。
 これとは別に、起動したコンテナ内の環境変数を収集して一覧表示します
 (スクリプトの動作は変えません)。</t>
         </is>
       </c>
-      <c r="B186" s="3"/>
-    </row>
-    <row r="187" ht="19.5" customHeight="1">
-      <c r="A187" s="8" t="inlineStr">
+      <c r="B189" s="3"/>
+    </row>
+    <row r="190" ht="19.5" customHeight="1">
+      <c r="A190" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B187" s="8"/>
-    </row>
-    <row r="188" ht="19.5" customHeight="1">
-      <c r="A188" s="2" t="inlineStr">
+      <c r="B190" s="8"/>
+    </row>
+    <row r="191" ht="19.5" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">出力先</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="33.0" customHeight="1">
-      <c r="A189" s="11" t="inlineStr">
+    <row r="192" ht="33.0" customHeight="1">
+      <c r="A192" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM オプションの受け渡し</t>
         </is>
       </c>
-      <c r="B189" s="3" t="inlineStr">
+      <c r="B192" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
         </is>
       </c>
-      <c r="C189" s="3" t="inlineStr">
+      <c r="C192" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JVM パラメータ一覧 (6.3)</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="33.0" customHeight="1">
-      <c r="A190" s="11" t="inlineStr">
+    <row r="193" ht="33.0" customHeight="1">
+      <c r="A193" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 標準設定</t>
         </is>
       </c>
-      <c r="B190" s="3" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OTEL_ で始まる環境変数すべて</t>
         </is>
       </c>
-      <c r="C190" s="3" t="inlineStr">
+      <c r="C193" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="33.0" customHeight="1">
-      <c r="A191" s="11" t="inlineStr">
+    <row r="194" ht="33.0" customHeight="1">
+      <c r="A194" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 関連設定</t>
         </is>
       </c>
-      <c r="B191" s="3" t="inlineStr">
+      <c r="B194" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS_XRAY_DAEMON_ADDRESS / AWS_XRAY_CONTEXT_MISSING / AWS_XRAY_TRACING_NAME / AWS_LAMBDA_EXEC_WRAPPER / AOT_CONFIG_CONTENT</t>
         </is>
       </c>
-      <c r="C191" s="3" t="inlineStr">
+      <c r="C194" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenTelemetry 一覧 (6.4)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="19.5" customHeight="1">
-      <c r="A192" s="11" t="inlineStr">
+    <row r="195" ht="19.5" customHeight="1">
+      <c r="A195" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリ構造の起点</t>
         </is>
       </c>
-      <c r="B192" s="3" t="inlineStr">
+      <c r="B195" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--deployment-dir-env で指定した名前</t>
         </is>
       </c>
-      <c r="C192" s="3" t="inlineStr">
+      <c r="C195" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss デプロイ構造</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="19.5" customHeight="1">
-      <c r="A193" s="8" t="inlineStr">
+    <row r="196" ht="19.5" customHeight="1">
+      <c r="A196" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《7.3 コンテナ側で検出する環境変数》</t>
         </is>
       </c>
-      <c r="B193" s="8"/>
-    </row>
-    <row r="194" ht="19.5" customHeight="1">
-      <c r="A194" s="3" t="inlineStr">
+      <c r="B196" s="8"/>
+    </row>
+    <row r="197" ht="19.5" customHeight="1">
+      <c r="A197" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B194" s="3"/>
+      <c r="B197" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="77">
@@ -2829,35 +2884,32 @@
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A65:B65"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="A90:B90"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A93:B93"/>
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="A95:B95"/>
-    <mergeCell ref="A96:B96"/>
     <mergeCell ref="A97:B97"/>
     <mergeCell ref="A98:B98"/>
     <mergeCell ref="A99:B99"/>
     <mergeCell ref="A100:B100"/>
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A102:B102"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A112:B112"/>
     <mergeCell ref="A116:B116"/>
     <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A125:B125"/>
+    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="A120:B120"/>
     <mergeCell ref="A126:B126"/>
     <mergeCell ref="A127:B127"/>
     <mergeCell ref="A128:B128"/>
@@ -2867,9 +2919,9 @@
     <mergeCell ref="A132:B132"/>
     <mergeCell ref="A133:B133"/>
     <mergeCell ref="A134:B134"/>
-    <mergeCell ref="A145:B145"/>
-    <mergeCell ref="A146:B146"/>
-    <mergeCell ref="A147:B147"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="A137:B137"/>
     <mergeCell ref="A148:B148"/>
     <mergeCell ref="A149:B149"/>
     <mergeCell ref="A150:B150"/>
@@ -2881,17 +2933,20 @@
     <mergeCell ref="A156:B156"/>
     <mergeCell ref="A157:B157"/>
     <mergeCell ref="A158:B158"/>
+    <mergeCell ref="A159:B159"/>
     <mergeCell ref="A160:B160"/>
-    <mergeCell ref="A165:B165"/>
-    <mergeCell ref="A166:B166"/>
+    <mergeCell ref="A161:B161"/>
+    <mergeCell ref="A163:B163"/>
     <mergeCell ref="A168:B168"/>
     <mergeCell ref="A169:B169"/>
-    <mergeCell ref="A178:B178"/>
-    <mergeCell ref="A185:B185"/>
-    <mergeCell ref="A186:B186"/>
-    <mergeCell ref="A187:B187"/>
-    <mergeCell ref="A193:B193"/>
-    <mergeCell ref="A194:B194"/>
+    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="A172:B172"/>
+    <mergeCell ref="A181:B181"/>
+    <mergeCell ref="A188:B188"/>
+    <mergeCell ref="A189:B189"/>
+    <mergeCell ref="A190:B190"/>
+    <mergeCell ref="A196:B196"/>
+    <mergeCell ref="A197:B197"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3072,27 +3127,27 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cache</t>
+          <t xml:space="preserve">--base-context DIR</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">キャッシュを破棄してビルド</t>
+          <t xml:space="preserve">サービス名に base を含むサービスの build.context を上書き (→ 5.1-2)</t>
         </is>
       </c>
     </row>
@@ -3104,17 +3159,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-progress-interval SEC</t>
+          <t xml:space="preserve">--base-dockerfile FILE</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数 (秒)</t>
+          <t xml:space="preserve">Dockerfile 名 / 相対パス</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3124,11 +3179,11 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ対象サービスの build.dockerfile を上書き。build.context からの相対パスとして解釈される (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
@@ -3136,17 +3191,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-stall-timeout SEC</t>
+          <t xml:space="preserve">--frontend-context DIR</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数 (秒)</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">300</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3156,7 +3211,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+          <t xml:space="preserve">サービス名に frontend を含むサービスの build.context を上書き (→ 5.1-2)</t>
         </is>
       </c>
     </row>
@@ -3168,17 +3223,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-timeout SEC</t>
+          <t xml:space="preserve">--frontend-dockerfile FILE</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数 (秒)</t>
+          <t xml:space="preserve">Dockerfile 名 / 相対パス</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (無制限)</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3188,11 +3243,11 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ対象サービスの build.dockerfile を上書き (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
@@ -3200,123 +3255,123 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-build-watchdog</t>
+          <t xml:space="preserve">--backend-context DIR</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(compose の値)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サービス名に backend を含むサービスの build.context を上書き (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="33.0" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--backend-dockerfile FILE</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dockerfile 名 / 相対パス</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(compose の値)</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ対象サービスの build.dockerfile を上書き (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cache</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上記の監視をすべて行わない。監視が有効な間は BUILDKIT_PROGRESS=tty を plain へ切り替えるため、tty 形式を使いたい場合に指定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">キャッシュを破棄してビルド</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66.0" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--dry-run</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド/起動/URL 呼び出し/ファイル操作を行わずプレビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="33.0" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-service NAME</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前にコピーし、終了後に自動削除。コピー先に同名ファイルがあれば強制上書きし、終了時に上書き前のファイルへ復元</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--copy-file-no-overwrite</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可 (繰り返し / カンマ区切り)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-file のコピー先に同名ファイルがあれば上書きせず中止 (exit 1)</t>
+          <t xml:space="preserve">指定したサービスを --no-cache の対象から外し、後始末でイメージと名前付きボリュームを残す (→ 5.1-3)</t>
         </is>
       </c>
     </row>
@@ -3328,27 +3383,27 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-copy-artifact</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (既定では照合しない)</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取り込み検証を行う (→ 5.13)</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
@@ -3360,27 +3415,27 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-verify-copy-artifact</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定と同じ)</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取り込み検証を行わない。--copy-artifact-path / --copy-artifact-search-dir / --copy-artifact-required とは排他</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
@@ -3392,27 +3447,27 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-artifact-path PATH</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">0 (無制限)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する。指定すると取り込み検証を有効にする</t>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
         </is>
       </c>
     </row>
@@ -3424,221 +3479,241 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-artifact-search-dir DIR</t>
+          <t xml:space="preserve">--no-build-watchdog</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の監視をすべて行わない。監視が有効な間は BUILDKIT_PROGRESS=tty を plain へ切り替えるため、tty 形式を使いたい場合に指定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--dry-run</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド/起動/URL 呼び出し/ファイル操作を行わずプレビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33.0" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前にコピーし、終了後に自動削除。コピー先に同名ファイルがあれば強制上書きし、終了時に上書き前のファイルへ復元</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-file-no-overwrite</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-file のコピー先に同名ファイルがあれば上書きせず中止 (exit 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="33.0" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--verify-copy-artifact</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (既定では照合しない)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">取り込み検証を行う (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="33.0" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-verify-copy-artifact</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定と同じ)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">取り込み検証を行わない。--copy-artifact-path / --copy-artifact-search-dir / --copy-artifact-required とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="33.0" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-artifact-path PATH</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">可</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)。指定すると取り込み検証を有効にする</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33.0" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--copy-artifact-required</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コピーしたファイルがコンテナ内に見つからない場合もエラーとする (既定は警告のみ)。指定すると取り込み検証を有効にする</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="49.5" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-param NAME</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SSM パラメータ名</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パラメータストアから取得。このとき AWS 認証が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="49.5" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password VALUE</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パスワード文字列</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="49.5" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
-        </is>
-      </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="49.5" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">シークレット id</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jboss_master_password</t>
-        </is>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="49.5" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region REGION</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS リージョン名</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
-        </is>
-      </c>
-      <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
+          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
     <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-dir DIR</t>
+          <t xml:space="preserve">--copy-artifact-search-dir DIR</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリのパス</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -3648,331 +3723,339 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
+          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
     <row r="27" ht="33.0" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-secret-id ID</t>
+          <t xml:space="preserve">--copy-artifact-required</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">英数字と . _ -</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cacerts</t>
-        </is>
-      </c>
-      <c r="E27" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コピーしたファイルがコンテナ内に見つからない場合もエラーとする (既定は警告のみ)。指定すると取り込み検証を有効にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="49.5" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle PATH</t>
+          <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパス</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一時ファイル</t>
+          <t xml:space="preserve">SSM パラメータ名</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="33.0" customHeight="1">
+          <t xml:space="preserve">パラメータストアから取得。このとき AWS 認証が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="49.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+          <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+          <t xml:space="preserve">パスワード文字列</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="33.0" customHeight="1">
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="49.5" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-glob PATTERN</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">glob パターン</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">*.crt と *.pem</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+        </is>
+      </c>
+      <c r="E30" s="7"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="33.0" customHeight="1">
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="49.5" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-jboss-password</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">シークレット id</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="33.0" customHeight="1">
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="49.5" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-mask</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">AWS リージョン名</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
     <row r="33" ht="33.0" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--cacert-dir DIR</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動探索)</t>
-        </is>
-      </c>
-      <c r="E33" s="7"/>
+          <t xml:space="preserve">ディレクトリのパス</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
         </is>
       </c>
     </row>
     <row r="34" ht="33.0" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">英数字と . _ -</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="35" ht="33.0" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">tar のパス</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
     <row r="36" ht="33.0" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="37" ht="33.0" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
+          <t xml:space="preserve">glob パターン</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
-        </is>
-      </c>
-      <c r="E37" s="7"/>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
     <row r="38" ht="33.0" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-verify-cwagent</t>
+          <t xml:space="preserve">--verify-jboss-password</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3982,53 +4065,53 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証を行わない</t>
+          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="33.0" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-password-mask</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="33.0" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -4038,97 +4121,97 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="41" ht="33.0" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">列挙</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="42" ht="33.0" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-report</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="43" ht="33.0" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-delivery-report</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達レポートを行わない (既定)</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -4140,23 +4223,23 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -4168,23 +4251,23 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--no-verify-cwagent</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">検証を行わない</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4279,7 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -4206,17 +4289,17 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="49.5" customHeight="1">
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="33.0" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
@@ -4224,23 +4307,23 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="E47" s="7"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -4252,23 +4335,23 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-required</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">列挙</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4363,7 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4296,7 +4379,7 @@
       <c r="E49" s="7"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
+          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4391,7 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-create-log-group</t>
+          <t xml:space="preserve">--no-cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4324,231 +4407,203 @@
       <c r="E50" s="7"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
+          <t xml:space="preserve">送達レポートを行わない (既定)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="33.0" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-startup</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c r="E51" s="7"/>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="33.0" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="E52" s="7"/>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="53" ht="33.0" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">拡張正規表現</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
+        </is>
+      </c>
+      <c r="E53" s="7"/>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="33.0" customHeight="1">
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="49.5" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+        </is>
+      </c>
+      <c r="E54" s="7"/>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
     <row r="55" ht="33.0" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--cwagent-required</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E55" s="7"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
         </is>
       </c>
     </row>
     <row r="56" ht="33.0" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E56" s="7"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="33.0" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-healthy</t>
+          <t xml:space="preserve">--no-cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="E57" s="7"/>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
+          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
         </is>
       </c>
     </row>
@@ -4560,27 +4615,27 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--verify-startup</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4647,7 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--allow-service-exit NAME</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4600,9 +4655,9 @@
           <t xml:space="preserve">サービス名</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
@@ -4612,7 +4667,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4624,27 +4679,27 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-pull-images</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">拡張正規表現</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -4656,17 +4711,17 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
@@ -4676,7 +4731,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -4688,17 +4743,17 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -4708,7 +4763,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -4720,17 +4775,17 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
@@ -4740,7 +4795,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4807,7 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-up-retry</t>
+          <t xml:space="preserve">--wait-healthy</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -4772,7 +4827,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
+          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
         </is>
       </c>
     </row>
@@ -4784,17 +4839,17 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -4804,7 +4859,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4816,27 +4871,27 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--recreate-containers</t>
+          <t xml:space="preserve">--allow-service-exit NAME</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
+          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4903,7 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-recreate-containers</t>
+          <t xml:space="preserve">--no-pull-images</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -4868,7 +4923,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
+          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
         </is>
       </c>
     </row>
@@ -4880,27 +4935,27 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4912,17 +4967,17 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">0 以上の整数</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -4932,7 +4987,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -4944,27 +4999,27 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4976,7 +5031,7 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--no-up-retry</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4996,7 +5051,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
         </is>
       </c>
     </row>
@@ -5008,223 +5063,251 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="33.0" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--recreate-containers</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="33.0" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-recreate-containers</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="33.0" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-startup-logs</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="33.0" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="33.0" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="33.0" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="33.0" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="19.5" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E73" s="7"/>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="19.5" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B74" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E74" s="7"/>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="19.5" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E75" s="7"/>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIME タイプ</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E76" s="7"/>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="19.5" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E77" s="7"/>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="19.5" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E78" s="7"/>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="19.5" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
-        </is>
-      </c>
-      <c r="E79" s="7"/>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
@@ -5236,23 +5319,23 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">URL</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -5264,203 +5347,203 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
     <row r="82" ht="19.5" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">HTTP メソッド</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストメソッド</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
+          <t xml:space="preserve">MIME タイプ</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E83" s="7"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="33.0" customHeight="1">
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">JSON 文字列</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="19.5" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">key=value&amp;...</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-after-interaction</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E86" s="7"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="87" ht="19.5" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--remove-volumes</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="19.5" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-volumes</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -5476,7 +5559,7 @@
       <c r="E88" s="7"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
         </is>
       </c>
     </row>
@@ -5488,27 +5571,27 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--usage-check-script PATH</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動解決)</t>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="19.5" customHeight="1">
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="33.0" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5516,99 +5599,91 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-free-path DIR</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定の 7 か所)</t>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="E90" s="7"/>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="91" ht="33.0" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E91" s="7"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="33.0" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E92" s="7"/>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="33.0" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--keep-container-after-interaction</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -5616,31 +5691,27 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E93" s="7"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
         </is>
       </c>
     </row>
     <row r="94" ht="19.5" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--remove-volumes</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5653,26 +5724,22 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="E94" s="7"/>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="19.5" customHeight="1">
+          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="33.0" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--keep-volumes</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5680,83 +5747,71 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E95" s="7"/>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
         </is>
       </c>
     </row>
     <row r="96" ht="19.5" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="E96" s="7"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="33.0" customHeight="1">
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="19.5" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--disk-free-path DIR</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">ディレクトリ</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="E97" s="7"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5823,7 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -5778,7 +5833,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
@@ -5788,11 +5843,11 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="33.0" customHeight="1">
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="19.5" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5800,12 +5855,12 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--env-list-file FILE</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -5815,16 +5870,16 @@
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="66.0" customHeight="1">
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="19.5" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5832,17 +5887,17 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -5852,11 +5907,11 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="19.5" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5864,7 +5919,7 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5872,9 +5927,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5884,7 +5939,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5951,7 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5904,9 +5959,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -5916,11 +5971,11 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="33.0" customHeight="1">
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="19.5" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5928,17 +5983,17 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -5948,7 +6003,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
@@ -5960,17 +6015,17 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -5980,11 +6035,11 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="19.5" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="33.0" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5992,17 +6047,17 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
@@ -6012,7 +6067,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -6024,59 +6079,59 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="66.0" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="33.0" customHeight="1">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B107" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -6088,17 +6143,17 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-display</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
@@ -6108,7 +6163,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6175,7 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -6130,7 +6185,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -6140,11 +6195,11 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="49.5" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="33.0" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6152,12 +6207,12 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -6167,12 +6222,12 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6184,17 +6239,17 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -6204,7 +6259,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -6216,17 +6271,17 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
@@ -6236,7 +6291,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -6248,17 +6303,17 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -6268,7 +6323,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6280,17 +6335,17 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
@@ -6300,11 +6355,11 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="19.5" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="33.0" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6312,17 +6367,17 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -6332,7 +6387,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6399,7 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -6364,11 +6419,11 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="33.0" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="49.5" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6376,12 +6431,12 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -6391,112 +6446,120 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="33.0" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="19.5" customHeight="1">
-      <c r="A118" s="11" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="19.5" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E118" s="7" t="inlineStr">
+      <c r="E119" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="33.0" customHeight="1">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E119" s="7"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
     <row r="120" ht="33.0" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E120" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="121" ht="33.0" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -6509,22 +6572,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E121" s="7"/>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="33.0" customHeight="1">
+          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="19.5" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -6537,198 +6604,290 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E122" s="7"/>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="33.0" customHeight="1">
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="19.5" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E123" s="7"/>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="124" ht="33.0" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E124" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="125" ht="19.5" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C125" s="3"/>
-      <c r="D125" s="3"/>
-      <c r="E125" s="7"/>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="126" ht="33.0" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C126" s="3"/>
-      <c r="D126" s="3"/>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E126" s="7"/>
-      <c r="F126" s="3"/>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="33.0" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
-        </is>
-      </c>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E127" s="7"/>
-      <c r="F127" s="3"/>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="33.0" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
-        </is>
-      </c>
-      <c r="C128" s="3"/>
-      <c r="D128" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E128" s="7"/>
-      <c r="F128" s="3"/>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="33.0" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
-        </is>
-      </c>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E129" s="7"/>
-      <c r="F129" s="3"/>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="33.0" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
-        </is>
-      </c>
-      <c r="C130" s="3"/>
-      <c r="D130" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E130" s="7"/>
-      <c r="F130" s="3"/>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="33.0" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C131" s="3"/>
-      <c r="D131" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E131" s="7"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="19.5" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C132" s="3"/>
@@ -6736,109 +6895,89 @@
       <c r="E132" s="7"/>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
     <row r="133" ht="33.0" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="7"/>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
-        </is>
-      </c>
+      <c r="F133" s="3"/>
     </row>
     <row r="134" ht="33.0" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="7"/>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
-        </is>
-      </c>
+      <c r="F134" s="3"/>
     </row>
     <row r="135" ht="33.0" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="7"/>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
-        </is>
-      </c>
+      <c r="F135" s="3"/>
     </row>
     <row r="136" ht="33.0" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="7"/>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F136" s="3"/>
     </row>
     <row r="137" ht="33.0" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="7"/>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F137" s="3"/>
     </row>
     <row r="138" ht="33.0" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
@@ -6848,7 +6987,7 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C138" s="3"/>
@@ -6856,7 +6995,7 @@
       <c r="E138" s="7"/>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -6868,7 +7007,7 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C139" s="3"/>
@@ -6876,7 +7015,7 @@
       <c r="E139" s="7"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -6888,7 +7027,7 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C140" s="3"/>
@@ -6896,12 +7035,152 @@
       <c r="E140" s="7"/>
       <c r="F140" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="33.0" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="33.0" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="33.0" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="7"/>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="33.0" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="7"/>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="33.0" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="33.0" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="33.0" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="7"/>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F140"/>
+  <autoFilter ref="A4:F147"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -7250,7 +7529,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="33.0" customHeight="1">
+    <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
@@ -7258,17 +7537,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-progress-interval SEC</t>
+          <t xml:space="preserve">--base-context DIR</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
+          <t xml:space="preserve">サービス名に base を含むサービスの build.context を上書き (→ 5.1-2)</t>
         </is>
       </c>
     </row>
@@ -7280,21 +7559,21 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-stall-timeout SEC</t>
+          <t xml:space="preserve">--base-dockerfile FILE</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">300</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ対象サービスの build.dockerfile を上書き。build.context からの相対パスとして解釈される (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
@@ -7302,17 +7581,17 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-timeout SEC</t>
+          <t xml:space="preserve">--frontend-context DIR</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (無制限)</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+          <t xml:space="preserve">サービス名に frontend を含むサービスの build.context を上書き (→ 5.1-2)</t>
         </is>
       </c>
     </row>
@@ -7324,21 +7603,21 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-copy-artifact</t>
+          <t xml:space="preserve">--frontend-dockerfile FILE</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (既定では照合しない)</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取り込み検証を行う (→ 5.13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ対象サービスの build.dockerfile を上書き (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
@@ -7346,21 +7625,21 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-verify-copy-artifact</t>
+          <t xml:space="preserve">--backend-context DIR</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定と同じ)</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取り込み検証を行わない。--copy-artifact-path / --copy-artifact-search-dir / --copy-artifact-required とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="33.0" customHeight="1">
+          <t xml:space="preserve">サービス名に backend を含むサービスの build.context を上書き (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
@@ -7368,17 +7647,17 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-artifact-path PATH</t>
+          <t xml:space="preserve">--backend-dockerfile FILE</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する。指定すると取り込み検証を有効にする</t>
+          <t xml:space="preserve">同じ対象サービスの build.dockerfile を上書き (→ 5.1-2)</t>
         </is>
       </c>
     </row>
@@ -7390,391 +7669,391 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-artifact-search-dir DIR</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)。指定すると取り込み検証を有効にする</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
     <row r="32" ht="33.0" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
     <row r="33" ht="33.0" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss_master_password</t>
+          <t xml:space="preserve">0 (無制限)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
         </is>
       </c>
     </row>
     <row r="34" ht="33.0" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--region REGION</t>
+          <t xml:space="preserve">--verify-copy-artifact</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+          <t xml:space="preserve">false (既定では照合しない)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
+          <t xml:space="preserve">取り込み検証を行う (→ 5.13)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="33.0" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-secret-id ID</t>
+          <t xml:space="preserve">--no-verify-copy-artifact</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cacerts</t>
+          <t xml:space="preserve">(既定と同じ)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">取り込み検証を行わない。--copy-artifact-path / --copy-artifact-search-dir / --copy-artifact-required とは排他</t>
         </is>
       </c>
     </row>
     <row r="36" ht="33.0" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle PATH</t>
+          <t xml:space="preserve">--copy-artifact-path PATH</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">一時ファイル</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
     <row r="37" ht="33.0" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+          <t xml:space="preserve">--copy-artifact-search-dir DIR</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+          <t xml:space="preserve">/</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
     <row r="38" ht="33.0" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-glob PATTERN</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">*.crt と *.pem</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
         </is>
       </c>
     </row>
     <row r="39" ht="33.0" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="40" ht="33.0" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
     <row r="41" ht="33.0" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="42" ht="33.0" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
     <row r="43" ht="33.0" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="44" ht="33.0" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">*.crt と *.pem</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
     <row r="45" ht="33.0" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="46" ht="33.0" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="47" ht="33.0" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="48" ht="33.0" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -7786,17 +8065,17 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -7808,149 +8087,149 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="51" ht="33.0" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
     <row r="52" ht="33.0" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
     <row r="53" ht="33.0" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="54" ht="33.0" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="55" ht="33.0" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="56" ht="33.0" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
@@ -7962,17 +8241,17 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -7984,17 +8263,17 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -8006,17 +8285,17 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -8028,17 +8307,17 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -8050,572 +8329,620 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="33.0" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--wait-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="33.0" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--pull-retry N</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="33.0" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="33.0" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--up-retry N</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="33.0" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="33.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="19.5" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-interval SEC</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リトライ間隔</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出)</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="68" ht="19.5" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
     <row r="69" ht="19.5" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--usage-check-script PATH</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動解決)</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
     <row r="70" ht="19.5" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-free-path DIR</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定の 7 か所)</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="71" ht="19.5" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="72" ht="19.5" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">リトライ間隔</t>
         </is>
       </c>
     </row>
     <row r="73" ht="19.5" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="19.5" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--usage-check-script PATH</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="19.5" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-free-path DIR</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="19.5" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="19.5" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="33.0" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B74" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="33.0" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="33.0" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="33.0" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="33.0" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="33.0" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="80" ht="33.0" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="9.0" customHeight="1">
-      <c r="A81" s="0"/>
-    </row>
-    <row r="82" ht="24.0" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
-        </is>
-      </c>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-    </row>
-    <row r="83" ht="19.5" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">記載箇所</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="33.0" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="33.0" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="33.0" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="33.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="33.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
-        </is>
-      </c>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-    </row>
-    <row r="86" ht="49.5" customHeight="1">
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="33.0" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-2 デプロイエラー時の調査モード (既定) / --exit-on-deploy-error</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">対話の前 / 失敗した起動ログを表示し、WAR デプロイ時 Java 例外解析を先に済ませる (画面へ出すのは --deploy-exception-display 指定時。既定では全量レポート [10] へ残すだけ)</t>
-        </is>
-      </c>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-    </row>
-    <row r="87" ht="33.0" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
-        </is>
-      </c>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-    </row>
-    <row r="88" ht="49.5" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">原因</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
-        </is>
-      </c>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="9.0" customHeight="1">
+      <c r="A87" s="0"/>
+    </row>
+    <row r="88" ht="24.0" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
+        </is>
+      </c>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
     </row>
     <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後始末でのボリューム削除</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
-        </is>
-      </c>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">記載箇所</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内容</t>
+        </is>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
     </row>
     <row r="90" ht="33.0" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
     </row>
-    <row r="91" ht="33.0" customHeight="1">
+    <row r="91" ht="19.5" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">保護の対象</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">イメージ / compose の image: 指定。無ければ Compose の既定名 &lt;プロジェクト&gt;-&lt;サービス&gt; / &lt;プロジェクト&gt;_&lt;サービス&gt;</t>
         </is>
       </c>
       <c r="C91" s="3"/>
@@ -8624,26 +8951,26 @@
     <row r="92" ht="33.0" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
     </row>
-    <row r="93" ht="33.0" customHeight="1">
+    <row r="93" ht="49.5" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">5.4-2 デプロイエラー時の調査モード (既定) / --exit-on-deploy-error</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">対話の前 / 失敗した起動ログを表示し、WAR デプロイ時 Java 例外解析を先に済ませる (画面へ出すのは --deploy-exception-display 指定時。既定では全量レポート [10] へ残すだけ)</t>
         </is>
       </c>
       <c r="C93" s="3"/>
@@ -8652,19 +8979,117 @@
     <row r="94" ht="33.0" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
     </row>
+    <row r="95" ht="49.5" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原因</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+        </is>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+        </is>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+    </row>
+    <row r="97" ht="33.0" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2 出力ファイル</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+        </is>
+      </c>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+    </row>
+    <row r="98" ht="33.0" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+        </is>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+    </row>
+    <row r="99" ht="33.0" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+    </row>
+    <row r="100" ht="33.0" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+    </row>
+    <row r="101" ht="33.0" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -8683,19 +9108,20 @@
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A82:D82"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="A88:D88"/>
     <mergeCell ref="B89:D89"/>
     <mergeCell ref="B90:D90"/>
     <mergeCell ref="B91:D91"/>
     <mergeCell ref="B92:D92"/>
     <mergeCell ref="B93:D93"/>
     <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B101:D101"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-23 09:52:44</t>
+          <t xml:space="preserve">2026-08-24 03:37:59</t>
         </is>
       </c>
     </row>
@@ -8951,26 +8951,26 @@
     <row r="92" ht="33.0" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
+          <t xml:space="preserve">設定の取得 / --config (file: / env: / yaml: の URI 形式も解釈) → 設定注入用の環境変数 (AOT_CONFIG_CONTENT 等) → 既定パス の順に探し、docker cp で取り出す (distroless でシェルが無くても読める)。取り出せない場合は bind mount 元のホストファイルを読む</t>
         </is>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
     </row>
-    <row r="93" ht="49.5" customHeight="1">
+    <row r="93" ht="33.0" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-2 デプロイエラー時の調査モード (既定) / --exit-on-deploy-error</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話の前 / 失敗した起動ログを表示し、WAR デプロイ時 Java 例外解析を先に済ませる (画面へ出すのは --deploy-exception-display 指定時。既定では全量レポート [10] へ残すだけ)</t>
+          <t xml:space="preserve">実行時の裏取り / Collector の内部テレメトリ (既定 8888/tcp) の otelcol_exporter_sent_spans / otelcol_exporter_send_failed_spans と、Collector ログの送信失敗・AWS 認証エラー</t>
         </is>
       </c>
       <c r="C93" s="3"/>
@@ -8979,26 +8979,26 @@
     <row r="94" ht="33.0" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+          <t xml:space="preserve">主な WARN 判定 / 未参照の定義、memory_limiter が processors の先頭にない、receiver の endpoint 未指定 (v0.104 以降は既定が localhost)、ecs 検出器が有効なのに ECS_CONTAINER_METADATA_URI_V4 が無い、indexed_attributes が空 (X-Ray で注釈検索ができない)</t>
         </is>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
     </row>
-    <row r="95" ht="49.5" customHeight="1">
+    <row r="95" ht="33.0" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">原因</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+          <t xml:space="preserve">出力形式 / --trace-report-format single (既定) は .htm 1 ファイルへ HTML・CSS・JS・データを埋め込む。files は index.html / trace-report.css / trace-report.js / trace-data.js をディレクトリへ出力する (相対パスで読むためディレクトリごとコピーする)</t>
         </is>
       </c>
       <c r="C95" s="3"/>
@@ -9007,12 +9007,12 @@
     <row r="96" ht="19.5" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">後始末でのボリューム削除</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+          <t xml:space="preserve">取得範囲 / --trace-report-lookback (既定 6h) と --trace-report-limit (既定 50。サービスごと)</t>
         </is>
       </c>
       <c r="C96" s="3"/>
@@ -9021,26 +9021,26 @@
     <row r="97" ht="33.0" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" ht="33.0" customHeight="1">
+    <row r="98" ht="49.5" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">5.4-2 デプロイエラー時の調査モード (既定) / --exit-on-deploy-error</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">対話の前 / 失敗した起動ログを表示し、WAR デプロイ時 Java 例外解析を先に済ませる (画面へ出すのは --deploy-exception-display 指定時。既定では全量レポート [10] へ残すだけ)</t>
         </is>
       </c>
       <c r="C98" s="3"/>
@@ -9049,47 +9049,117 @@
     <row r="99" ht="33.0" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" ht="33.0" customHeight="1">
+    <row r="100" ht="49.5" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">原因</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
         </is>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" ht="33.0" customHeight="1">
+    <row r="101" ht="19.5" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
         </is>
       </c>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
     </row>
+    <row r="102" ht="33.0" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2 出力ファイル</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+        </is>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+    </row>
+    <row r="103" ht="33.0" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+        </is>
+      </c>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+    </row>
+    <row r="104" ht="33.0" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+    </row>
+    <row r="105" ht="33.0" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+    </row>
+    <row r="106" ht="33.0" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="37">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -9122,6 +9192,11 @@
     <mergeCell ref="B99:D99"/>
     <mergeCell ref="B100:D100"/>
     <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="B106:D106"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-24 03:37:59</t>
+          <t xml:space="preserve">2026-08-29 22:04:17</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="181.5" customHeight="1">
+    <row r="23" ht="214.5" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
@@ -731,11 +731,11 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(起動確認時に自動。結果は全量レポート [10] へ。画面表示は --deploy-exception-display 指定時のみ、Excel 出力は --deploy-exception-excel 指定時のみ、テキスト出力は --deploy-exception-text 指定時のみ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="132.0" customHeight="1">
+          <t xml:space="preserve">(起動確認時に自動。画面表示は --deploy-exception-display 指定時のみ、全量レポート [10] への記載は --deploy-exception-report 指定時のみ、Excel 出力は --deploy-exception-excel 指定時のみ、テキスト出力は --deploy-exception-text 指定時のみ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="231.0" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
@@ -748,7 +748,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定で自動。無効化は --no-readonly-analysis。ファイル出力は --report-dir / --readonly-analysis-excel / --readonly-analysis-text 指定時)</t>
+          <t xml:space="preserve">(既定で自動。無効化は --no-readonly-analysis。画面表示は --readonly-analysis-display 指定時のみ、全量レポート [11] への記載は --readonly-analysis-report 指定時のみ。ファイル出力は --report-dir / --readonly-analysis-excel / --readonly-analysis-text 指定時)</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="115.5" customHeight="1">
+    <row r="84" ht="165.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析</t>
@@ -1645,11 +1645,11 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、出力先の要否判定、画面表示 (--deploy-exception-display 指定時) と Excel / テキスト出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="181.5" customHeight="1">
+          <t xml:space="preserve">デプロイ処理ログの収集、解析ヘルパーの実行、出力先の要否判定、画面表示 (--deploy-exception-display 指定時)、全量レポートへの記載 (--deploy-exception-report 指定時)、Excel / テキスト出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="264.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用 FS 分析</t>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyze_readonly_filesystem / readonly_collect_compose_facts / readonly_collect_dockerfile_facts / readonly_parse_dockerfile / readonly_shell_write_targets / readonly_scan_context_script / readonly_collect_runtime_facts / readonly_container_probe / readonly_collect_container_scripts / show_readonly_filesystem_analysis / append_readonly_analysis_report</t>
+          <t xml:space="preserve">analyze_readonly_filesystem / readonly_collect_compose_facts / readonly_collect_dockerfile_facts / readonly_parse_dockerfile / readonly_shell_write_targets / readonly_scan_context_script / readonly_collect_runtime_facts / readonly_container_probe / readonly_collect_container_scripts / show_readonly_filesystem_analysis / show_readonly_analysis_outputs / append_readonly_analysis_report</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose.yml の read_only / tmpfs / volumes の解析、Dockerfile からのビルド時の書き込み先の収集、起動スクリプトからの実行時の書き込み先の収集、コンテナの書き込み状況の収集、判定結果の表示と Excel / テキスト出力</t>
+          <t xml:space="preserve">compose.yml の read_only / tmpfs / volumes の解析、Dockerfile からのビルド時の書き込み先の収集、起動スクリプトからの実行時の書き込み先の収集、コンテナの書き込み状況の収集、判定結果の表示 (--readonly-analysis-display 指定時)、全量レポートへの記載 (--readonly-analysis-report 指定時)、Excel / テキスト出力</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正、--copy-artifact-path / --copy-artifact-search-dir が絶対パスでない、--remove-volumes と --keep-volumes の同時指定</t>
+          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、--readonly-analysis-display と --no-readonly-analysis の同時指定、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正、--copy-artifact-path / --copy-artifact-search-dir が絶対パスでない、--remove-volumes と --keep-volumes の同時指定</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-report</t>
+          <t xml:space="preserve">--cwagent-verify-display</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4379,7 +4379,7 @@
       <c r="E49" s="7"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
+          <t xml:space="preserve">ビルド・デプロイ後の「CloudWatch Agent の送信状況チェック」「cwagent の警告・エラー」「cwagent のログ送信検証」を画面へ表示する (既定では表示しない)</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-delivery-report</t>
+          <t xml:space="preserve">--no-cwagent-verify-display</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4407,7 +4407,7 @@
       <c r="E50" s="7"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達レポートを行わない (既定)</t>
+          <t xml:space="preserve">上記 3 つを画面へ表示しない (既定)</t>
         </is>
       </c>
     </row>
@@ -4419,23 +4419,23 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E51" s="7"/>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
         </is>
       </c>
     </row>
@@ -4447,23 +4447,23 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--no-cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達レポートを行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -4475,27 +4475,27 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="49.5" customHeight="1">
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="33.0" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
@@ -4503,23 +4503,23 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -4531,27 +4531,27 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-required</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="E55" s="7"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="33.0" customHeight="1">
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="49.5" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
@@ -4559,23 +4559,23 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
         </is>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-required</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -4597,30 +4597,30 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
+          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
         </is>
       </c>
     </row>
     <row r="58" ht="33.0" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-startup</t>
+          <t xml:space="preserve">--cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -4628,46 +4628,38 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
+      <c r="E58" s="7"/>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
+          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="33.0" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--no-cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(対象全体)</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E59" s="7"/>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
         </is>
       </c>
     </row>
@@ -4679,27 +4671,27 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--verify-startup</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">拡張正規表現</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
         </is>
       </c>
     </row>
@@ -4711,27 +4703,27 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4743,17 +4735,17 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">拡張正規表現</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -4763,7 +4755,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -4775,17 +4767,17 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
@@ -4795,7 +4787,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -4807,27 +4799,27 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-healthy</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -4839,17 +4831,17 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -4859,7 +4851,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -4871,27 +4863,27 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--allow-service-exit NAME</t>
+          <t xml:space="preserve">--wait-healthy</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
+          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
         </is>
       </c>
     </row>
@@ -4903,27 +4895,27 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-pull-images</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4935,27 +4927,27 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--allow-service-exit NAME</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
         </is>
       </c>
     </row>
@@ -4967,27 +4959,27 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--no-pull-images</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4991,7 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -5009,7 +5001,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -5019,7 +5011,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -5031,27 +5023,27 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-up-retry</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5055,7 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -5073,7 +5065,7 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -5083,7 +5075,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5087,7 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--recreate-containers</t>
+          <t xml:space="preserve">--no-up-retry</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5115,7 +5107,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
+          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
         </is>
       </c>
     </row>
@@ -5127,27 +5119,27 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-recreate-containers</t>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
+          <t xml:space="preserve">compose up の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5151,7 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--recreate-containers</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -5179,7 +5171,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
         </is>
       </c>
     </row>
@@ -5191,27 +5183,27 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--no-recreate-containers</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5215,7 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--suppress-startup-logs</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -5243,7 +5235,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
         </is>
       </c>
     </row>
@@ -5255,27 +5247,27 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
         </is>
       </c>
     </row>
@@ -5287,83 +5279,91 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="33.0" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="19.5" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E80" s="7"/>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="19.5" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E81" s="7"/>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -5375,23 +5375,23 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-method METHOD</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
+          <t xml:space="preserve">URL</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストメソッド</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -5403,23 +5403,23 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIME タイプ</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動)</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E83" s="7"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -5431,23 +5431,23 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">HTTP メソッド</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -5459,23 +5459,23 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">MIME タイプ</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -5487,23 +5487,23 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">JSON 文字列</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E86" s="7"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
@@ -5515,23 +5515,23 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">key=value&amp;...</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
         </is>
       </c>
     </row>
@@ -5543,83 +5543,83 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E88" s="7"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="89" ht="19.5" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="19.5" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
-        </is>
-      </c>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E90" s="7"/>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="33.0" customHeight="1">
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="19.5" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5627,23 +5627,23 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -5655,23 +5655,23 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="E92" s="7"/>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
@@ -5683,27 +5683,27 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-after-interaction</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
         </is>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="33.0" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--remove-volumes</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5727,7 +5727,7 @@
       <c r="E94" s="7"/>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-volumes</t>
+          <t xml:space="preserve">--keep-container-after-interaction</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5755,7 +5755,7 @@
       <c r="E95" s="7"/>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
+          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
         </is>
       </c>
     </row>
@@ -5767,27 +5767,27 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--usage-check-script PATH</t>
+          <t xml:space="preserve">--remove-volumes</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動解決)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E96" s="7"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="19.5" customHeight="1">
+          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="33.0" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5795,119 +5795,111 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-free-path DIR</t>
+          <t xml:space="preserve">--keep-volumes</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(既定の 7 か所)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="33.0" customHeight="1">
+          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="E98" s="7"/>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
         </is>
       </c>
     </row>
     <row r="99" ht="19.5" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-free-path DIR</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="E99" s="7"/>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="33.0" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="19.5" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
         </is>
       </c>
     </row>
@@ -5919,17 +5911,17 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--env-list-file FILE</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5939,7 +5931,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5943,7 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5961,7 +5953,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非出力)</t>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -5971,7 +5963,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
         </is>
       </c>
     </row>
@@ -5983,91 +5975,91 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-directory-tree</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="19.5" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="33.0" customHeight="1">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B104" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="33.0" customHeight="1">
-      <c r="A105" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B105" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -6079,31 +6071,31 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="66.0" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="33.0" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6111,17 +6103,17 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
@@ -6131,7 +6123,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -6143,59 +6135,59 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="82.5" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="19.5" customHeight="1">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B109" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -6207,17 +6199,17 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--deploy-exception-display</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -6227,11 +6219,11 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="33.0" customHeight="1">
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="19.5" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6239,17 +6231,17 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -6259,11 +6251,11 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="19.5" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="33.0" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6271,17 +6263,17 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--deploy-exception-report</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
@@ -6291,7 +6283,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6295,7 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--no-deploy-exception-report</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -6313,7 +6305,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -6323,7 +6315,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
+          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6327,7 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -6355,7 +6347,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6359,7 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -6377,7 +6369,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -6387,7 +6379,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -6399,59 +6391,59 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="33.0" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E116" s="7" t="inlineStr">
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="49.5" customHeight="1">
-      <c r="A117" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B117" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6463,17 +6455,17 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--readonly-analysis-display</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
@@ -6483,11 +6475,11 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="19.5" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="33.0" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6495,7 +6487,7 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--no-readonly-analysis-display</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -6505,7 +6497,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
@@ -6515,11 +6507,11 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="33.0" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="49.5" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6527,17 +6519,17 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--readonly-analysis-report</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
@@ -6547,7 +6539,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6551,7 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--no-readonly-analysis-report</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -6569,241 +6561,253 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="33.0" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="33.0" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="19.5" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-readonly-analysis</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E121" s="7" t="inlineStr">
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="19.5" customHeight="1">
-      <c r="A122" s="11" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="49.5" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="19.5" customHeight="1">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B123" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="33.0" customHeight="1">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B124" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="19.5" customHeight="1">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B125" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="126" ht="33.0" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="19.5" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E126" s="7"/>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="33.0" customHeight="1">
-      <c r="A127" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B127" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(オプション不要)</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E127" s="7"/>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
     <row r="128" ht="33.0" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E128" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="129" ht="33.0" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--undertow-analysis-display</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -6816,50 +6820,58 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E129" s="7"/>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="130" ht="33.0" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E130" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="33.0" customHeight="1">
+          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="19.5" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -6872,222 +6884,354 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E131" s="7"/>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
         </is>
       </c>
     </row>
     <row r="132" ht="19.5" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C132" s="3"/>
-      <c r="D132" s="3"/>
-      <c r="E132" s="7"/>
+          <t xml:space="preserve">--no-undertow-analysis</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="133" ht="33.0" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C133" s="3"/>
-      <c r="D133" s="3"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="3"/>
-    </row>
-    <row r="134" ht="33.0" customHeight="1">
+          <t xml:space="preserve">--cert-check-text FILE</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="19.5" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
-        </is>
-      </c>
-      <c r="C134" s="3"/>
-      <c r="D134" s="3"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="3"/>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="33.0" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
-        </is>
-      </c>
-      <c r="C135" s="3"/>
-      <c r="D135" s="3"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="3"/>
-    </row>
-    <row r="136" ht="33.0" customHeight="1">
+          <t xml:space="preserve">--jboss-module-list-text FILE</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="19.5" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
-        </is>
-      </c>
-      <c r="C136" s="3"/>
-      <c r="D136" s="3"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="3"/>
+          <t xml:space="preserve">--no-jboss-module-list-text</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="33.0" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
-        </is>
-      </c>
-      <c r="C137" s="3"/>
-      <c r="D137" s="3"/>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E137" s="7"/>
-      <c r="F137" s="3"/>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="33.0" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C138" s="3"/>
-      <c r="D138" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E138" s="7"/>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="139" ht="33.0" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C139" s="3"/>
-      <c r="D139" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E139" s="7"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="140" ht="33.0" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C140" s="3"/>
-      <c r="D140" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E140" s="7"/>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="141" ht="33.0" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C141" s="3"/>
-      <c r="D141" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E141" s="7"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="142" ht="33.0" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C142" s="3"/>
-      <c r="D142" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E142" s="7"/>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="19.5" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C143" s="3"/>
@@ -7095,92 +7239,292 @@
       <c r="E143" s="7"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
     <row r="144" ht="33.0" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="7"/>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F144" s="3"/>
     </row>
     <row r="145" ht="33.0" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="7"/>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
-        </is>
-      </c>
+      <c r="F145" s="3"/>
     </row>
     <row r="146" ht="33.0" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="7"/>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F146" s="3"/>
     </row>
     <row r="147" ht="33.0" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="7"/>
-      <c r="F147" s="3" t="inlineStr">
+      <c r="F147" s="3"/>
+    </row>
+    <row r="148" ht="33.0" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--noreport</t>
+        </is>
+      </c>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="3"/>
+    </row>
+    <row r="149" ht="33.0" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="33.0" customHeight="1">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="33.0" customHeight="1">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree</t>
+        </is>
+      </c>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="33.0" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="7"/>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="33.0" customHeight="1">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="33.0" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="33.0" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="33.0" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="33.0" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="33.0" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F147"/>
+  <autoFilter ref="A4:F158"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -7366,7 +7710,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(起動確認時に自動。結果は全量レポート [10] へ。画面表示は --deploy-exception-display 指定時のみ、Excel 出力は --deploy-exception-excel 指定時のみ、テキスト出力は --deploy-exception-text 指定時のみ)</t>
+          <t xml:space="preserve">(起動確認時に自動。画面表示は --deploy-exception-display 指定時のみ、全量レポート [10] への記載は --deploy-exception-report 指定時のみ、Excel 出力は --deploy-exception-excel 指定時のみ、テキスト出力は --deploy-exception-text 指定時のみ)</t>
         </is>
       </c>
       <c r="C14" s="10"/>
@@ -7380,7 +7724,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定で自動。無効化は --no-readonly-analysis。ファイル出力は --report-dir / --readonly-analysis-excel / --readonly-analysis-text 指定時)</t>
+          <t xml:space="preserve">(既定で自動。無効化は --no-readonly-analysis。画面表示は --readonly-analysis-display 指定時のみ、全量レポート [11] への記載は --readonly-analysis-report 指定時のみ。ファイル出力は --report-dir / --readonly-analysis-excel / --readonly-analysis-text 指定時)</t>
         </is>
       </c>
       <c r="C15" s="10"/>
@@ -8823,7 +9167,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -8835,17 +9179,17 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--deploy-exception-report</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -8857,154 +9201,186 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
     <row r="86" ht="33.0" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--readonly-analysis-display</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="9.0" customHeight="1">
-      <c r="A87" s="0"/>
-    </row>
-    <row r="88" ht="24.0" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
-        </is>
-      </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-    </row>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">記載箇所</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="49.5" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-report</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="33.0" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="33.0" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="33.0" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
-        </is>
-      </c>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-    </row>
-    <row r="91" ht="19.5" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">保護の対象</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">イメージ / compose の image: 指定。無ければ Compose の既定名 &lt;プロジェクト&gt;-&lt;サービス&gt; / &lt;プロジェクト&gt;_&lt;サービス&gt;</t>
-        </is>
-      </c>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-    </row>
-    <row r="92" ht="33.0" customHeight="1">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">logs モードで選べる操作</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">設定の取得 / --config (file: / env: / yaml: の URI 形式も解釈) → 設定注入用の環境変数 (AOT_CONFIG_CONTENT 等) → 既定パス の順に探し、docker cp で取り出す (distroless でシェルが無くても読める)。取り出せない場合は bind mount 元のホストファイルを読む</t>
-        </is>
-      </c>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-    </row>
-    <row r="93" ht="33.0" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">logs モードで選べる操作</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実行時の裏取り / Collector の内部テレメトリ (既定 8888/tcp) の otelcol_exporter_sent_spans / otelcol_exporter_send_failed_spans と、Collector ログの送信失敗・AWS 認証エラー</t>
-        </is>
-      </c>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="9.0" customHeight="1">
+      <c r="A91" s="0"/>
+    </row>
+    <row r="92" ht="24.0" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
+        </is>
+      </c>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">記載箇所</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内容</t>
+        </is>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
     </row>
     <row r="94" ht="33.0" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">logs モードで選べる操作</t>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主な WARN 判定 / 未参照の定義、memory_limiter が processors の先頭にない、receiver の endpoint 未指定 (v0.104 以降は既定が localhost)、ecs 検出器が有効なのに ECS_CONTAINER_METADATA_URI_V4 が無い、indexed_attributes が空 (X-Ray で注釈検索ができない)</t>
+          <t xml:space="preserve">前半 / 既定値 / ビルド / 起動確認 / URL 確認 / 対話操作 / 環境変数一覧 / ツリー / レポートの各既定値</t>
         </is>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
     </row>
-    <row r="95" ht="33.0" customHeight="1">
+    <row r="95" ht="19.5" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">logs モードで選べる操作</t>
+          <t xml:space="preserve">保護の対象</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力形式 / --trace-report-format single (既定) は .htm 1 ファイルへ HTML・CSS・JS・データを埋め込む。files は index.html / trace-report.css / trace-report.js / trace-data.js をディレクトリへ出力する (相対パスで読むためディレクトリごとコピーする)</t>
+          <t xml:space="preserve">イメージ / compose の image: 指定。無ければ Compose の既定名 &lt;プロジェクト&gt;-&lt;サービス&gt; / &lt;プロジェクト&gt;_&lt;サービス&gt;</t>
         </is>
       </c>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
     </row>
-    <row r="96" ht="19.5" customHeight="1">
+    <row r="96" ht="33.0" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">logs モードで選べる操作</t>
@@ -9012,7 +9388,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得範囲 / --trace-report-lookback (既定 6h) と --trace-report-limit (既定 50。サービスごと)</t>
+          <t xml:space="preserve">設定の取得 / --config (file: / env: / yaml: の URI 形式も解釈) → 設定注入用の環境変数 (AOT_CONFIG_CONTENT 等) → 既定パス の順に探し、docker cp で取り出す (distroless でシェルが無くても読める)。取り出せない場合は bind mount 元のホストファイルを読む</t>
         </is>
       </c>
       <c r="C96" s="3"/>
@@ -9021,26 +9397,26 @@
     <row r="97" ht="33.0" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
+          <t xml:space="preserve">実行時の裏取り / Collector の内部テレメトリ (既定 8888/tcp) の otelcol_exporter_sent_spans / otelcol_exporter_send_failed_spans と、Collector ログの送信失敗・AWS 認証エラー</t>
         </is>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" ht="49.5" customHeight="1">
+    <row r="98" ht="33.0" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-2 デプロイエラー時の調査モード (既定) / --exit-on-deploy-error</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話の前 / 失敗した起動ログを表示し、WAR デプロイ時 Java 例外解析を先に済ませる (画面へ出すのは --deploy-exception-display 指定時。既定では全量レポート [10] へ残すだけ)</t>
+          <t xml:space="preserve">主な WARN 判定 / 未参照の定義、memory_limiter が processors の先頭にない、receiver の endpoint 未指定 (v0.104 以降は既定が localhost)、ecs 検出器が有効なのに ECS_CONTAINER_METADATA_URI_V4 が無い、indexed_attributes が空 (X-Ray で注釈検索ができない)</t>
         </is>
       </c>
       <c r="C98" s="3"/>
@@ -9049,40 +9425,40 @@
     <row r="99" ht="33.0" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+          <t xml:space="preserve">出力形式 / --trace-report-format single (既定) は .htm 1 ファイルへ HTML・CSS・JS・データを埋め込む。files は index.html / trace-report.css / trace-report.js / trace-data.js をディレクトリへ出力する (相対パスで読むためディレクトリごとコピーする)</t>
         </is>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" ht="49.5" customHeight="1">
+    <row r="100" ht="19.5" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">原因</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+          <t xml:space="preserve">取得範囲 / --trace-report-lookback (既定 6h) と --trace-report-limit (既定 50。サービスごと)</t>
         </is>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" ht="19.5" customHeight="1">
+    <row r="101" ht="33.0" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">後始末でのボリューム削除</t>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C101" s="3"/>
@@ -9091,12 +9467,12 @@
     <row r="102" ht="33.0" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">JBoss モジュール一覧 (module-loading:module-info)</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+          <t xml:space="preserve">JBOSS_HOME の検出 / 環境変数 JBOSS_HOME / JBOSS_EAP_HOME → 既定の候補 (/opt/jboss-eap / /opt/eap / /opt/jboss / /opt/wildfly ほか) の順に、bin と modules を持つディレクトリを探す</t>
         </is>
       </c>
       <c r="C102" s="3"/>
@@ -9105,12 +9481,12 @@
     <row r="103" ht="33.0" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C103" s="3"/>
@@ -9119,47 +9495,145 @@
     <row r="104" ht="33.0" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
         </is>
       </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" ht="33.0" customHeight="1">
+    <row r="105" ht="49.5" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">原因</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
         </is>
       </c>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
     </row>
-    <row r="106" ht="33.0" customHeight="1">
+    <row r="106" ht="19.5" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
         </is>
       </c>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
     </row>
+    <row r="107" ht="33.0" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2 出力ファイル</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+        </is>
+      </c>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+    </row>
+    <row r="108" ht="33.0" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実行タイミングと前提</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
+        </is>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+    </row>
+    <row r="109" ht="19.5" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実行タイミングと前提</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
+        </is>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+    </row>
+    <row r="110" ht="33.0" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+        </is>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+    </row>
+    <row r="111" ht="33.0" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+        </is>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+    </row>
+    <row r="112" ht="33.0" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+    </row>
+    <row r="113" ht="33.0" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="40">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -9178,11 +9652,7 @@
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B91:D91"/>
-    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="A92:D92"/>
     <mergeCell ref="B93:D93"/>
     <mergeCell ref="B94:D94"/>
     <mergeCell ref="B95:D95"/>
@@ -9197,6 +9667,13 @@
     <mergeCell ref="B104:D104"/>
     <mergeCell ref="B105:D105"/>
     <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="B110:D110"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="B113:D113"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9791,7 +10268,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="82.5" customHeight="1">
+    <row r="35" ht="115.5" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -9799,35 +10276,38 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイ結果ファイルへ Java 例外解析を残す
+          <t xml:space="preserve">全量レポートへ Java 例外解析を残す
 (reports/build_and_verify_&lt;日時&gt;.txt … [10] に例外解析の全文。
-画面表示も Excel / テキストの出力も行わない ← 既定)</t>
+--deploy-exception-report が無ければ [10] へは記載しない ← 既定。
+画面表示も Excel / テキストの出力も行わない)</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
-    --compose-service app --startup-service app \
-    --report-dir ./reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="66.0" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-2</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">解析結果を画面でも読む (既定は非表示)</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
     --report-dir ./reports \
+    --deploy-exception-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="82.5" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-2</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">解析結果を画面でも読む (既定は非表示)</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --report-dir ./reports \
+    --deploy-exception-report \
     --deploy-exception-display</t>
         </is>
       </c>
@@ -9870,7 +10350,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="148.5" customHeight="1">
+    <row r="39" ht="181.5" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-5</t>
@@ -9881,6 +10361,7 @@
           <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
 既定で毎回実行される。--report-dir があれば
 reports/build_and_verify_&lt;日時&gt;_readonly_filesystem.xlsx / .txt も出力される
+(全量レポート [11] へ載せるには --readonly-analysis-report を併用する)
 Dockerfile のビルド時に書くだけのディレクトリは「ビルド時のみ」として
 対象から外し、entrypoint.sh などが起動のたびに書く場所を「要対応」に挙げる</t>
         </is>
@@ -9889,7 +10370,8 @@
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
-    --report-dir ./reports</t>
+    --report-dir ./reports \
+    --readonly-analysis-report</t>
         </is>
       </c>
     </row>
@@ -9913,7 +10395,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="33.0" customHeight="1">
+    <row r="41" ht="66.0" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-7</t>
@@ -9921,45 +10403,65 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面でも読む
+既定では画面へ出さず、Excel / テキストへ残すだけ</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --readonly-analysis-display</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="33.0" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-8</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの分析を行わない</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-readonly-analysis</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="66.0" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="43" ht="66.0" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
 進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="33.0" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="44" ht="33.0" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
         </is>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 22:04:17</t>
+          <t xml:space="preserve">2026-08-30 15:18:45</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9380,7 @@
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
     </row>
-    <row r="96" ht="33.0" customHeight="1">
+    <row r="96" ht="49.5" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">logs モードで選べる操作</t>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定の取得 / --config (file: / env: / yaml: の URI 形式も解釈) → 設定注入用の環境変数 (AOT_CONFIG_CONTENT 等) → 既定パス の順に探し、docker cp で取り出す (distroless でシェルが無くても読める)。取り出せない場合は bind mount 元のホストファイルを読む</t>
+          <t xml:space="preserve">root ユーザで bash へ接続 / bash 接続と同じ対話セッションを docker exec -u 0:0 で開く。コンテナの既定ユーザーが非 root (JBoss EAP の jboss ユーザー等) で、権限不足により読めないファイルの確認やパッケージ導入を調べたいときに使う / 接続先に /bin/bash (root 実行を禁止する設定では接続できない)</t>
         </is>
       </c>
       <c r="C96" s="3"/>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行時の裏取り / Collector の内部テレメトリ (既定 8888/tcp) の otelcol_exporter_sent_spans / otelcol_exporter_send_failed_spans と、Collector ログの送信失敗・AWS 認証エラー</t>
+          <t xml:space="preserve">設定の取得 / --config (file: / env: / yaml: の URI 形式も解釈) → 設定注入用の環境変数 (AOT_CONFIG_CONTENT 等) → 既定パス の順に探し、docker cp で取り出す (distroless でシェルが無くても読める)。取り出せない場合は bind mount 元のホストファイルを読む</t>
         </is>
       </c>
       <c r="C97" s="3"/>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主な WARN 判定 / 未参照の定義、memory_limiter が processors の先頭にない、receiver の endpoint 未指定 (v0.104 以降は既定が localhost)、ecs 検出器が有効なのに ECS_CONTAINER_METADATA_URI_V4 が無い、indexed_attributes が空 (X-Ray で注釈検索ができない)</t>
+          <t xml:space="preserve">実行時の裏取り / Collector の内部テレメトリ (既定 8888/tcp) の otelcol_exporter_sent_spans / otelcol_exporter_send_failed_spans と、Collector ログの送信失敗・AWS 認証エラー</t>
         </is>
       </c>
       <c r="C98" s="3"/>
@@ -9430,13 +9430,13 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力形式 / --trace-report-format single (既定) は .htm 1 ファイルへ HTML・CSS・JS・データを埋め込む。files は index.html / trace-report.css / trace-report.js / trace-data.js をディレクトリへ出力する (相対パスで読むためディレクトリごとコピーする)</t>
+          <t xml:space="preserve">主な WARN 判定 / 未参照の定義、memory_limiter が processors の先頭にない、receiver の endpoint 未指定 (v0.104 以降は既定が localhost)、ecs 検出器が有効なのに ECS_CONTAINER_METADATA_URI_V4 が無い、indexed_attributes が空 (X-Ray で注釈検索ができない)</t>
         </is>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" ht="19.5" customHeight="1">
+    <row r="100" ht="33.0" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">logs モードで選べる操作</t>
@@ -9444,21 +9444,21 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得範囲 / --trace-report-lookback (既定 6h) と --trace-report-limit (既定 50。サービスごと)</t>
+          <t xml:space="preserve">出力形式 / --trace-report-format single (既定) は .htm 1 ファイルへ HTML・CSS・JS・データを埋め込む。files は index.html / trace-report.css / trace-report.js / trace-data.js をディレクトリへ出力する (相対パスで読むためディレクトリごとコピーする)</t>
         </is>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" ht="33.0" customHeight="1">
+    <row r="101" ht="19.5" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
+          <t xml:space="preserve">logs モードで選べる操作</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
+          <t xml:space="preserve">取得範囲 / --trace-report-lookback (既定 6h) と --trace-report-limit (既定 50。サービスごと)</t>
         </is>
       </c>
       <c r="C101" s="3"/>
@@ -9467,12 +9467,12 @@
     <row r="102" ht="33.0" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss モジュール一覧 (module-loading:module-info)</t>
+          <t xml:space="preserve">ALB ヘルスチェック確認 (ステータスコード / 成功失敗判定)</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_HOME の検出 / 環境変数 JBOSS_HOME / JBOSS_EAP_HOME → 既定の候補 (/opt/jboss-eap / /opt/eap / /opt/jboss / /opt/wildfly ほか) の順に、bin と modules を持つディレクトリを探す</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 ALB_HEALTHCHECK_CLI → 既定 /opt/alb-healthcheck/healthcheck.py。インタプリタ (python3 / python) もコンテナ内で解決するため、ホスト側に Python は不要</t>
         </is>
       </c>
       <c r="C102" s="3"/>
@@ -9481,12 +9481,12 @@
     <row r="103" ht="33.0" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">JBoss モジュール一覧 (module-loading:module-info)</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+          <t xml:space="preserve">JBOSS_HOME の検出 / 環境変数 JBOSS_HOME / JBOSS_EAP_HOME → 既定の候補 (/opt/jboss-eap / /opt/eap / /opt/jboss / /opt/wildfly ほか) の順に、bin と modules を持つディレクトリを探す</t>
         </is>
       </c>
       <c r="C103" s="3"/>
@@ -9500,49 +9500,49 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" ht="49.5" customHeight="1">
+    <row r="105" ht="33.0" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">原因</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
         </is>
       </c>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
     </row>
-    <row r="106" ht="19.5" customHeight="1">
+    <row r="106" ht="49.5" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">後始末でのボリューム削除</t>
+          <t xml:space="preserve">原因</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
         </is>
       </c>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
     </row>
-    <row r="107" ht="33.0" customHeight="1">
+    <row r="107" ht="19.5" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
         </is>
       </c>
       <c r="C107" s="3"/>
@@ -9551,18 +9551,18 @@
     <row r="108" ht="33.0" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">6.2 出力ファイル</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
         </is>
       </c>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" ht="19.5" customHeight="1">
+    <row r="109" ht="33.0" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">実行タイミングと前提</t>
@@ -9570,21 +9570,21 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
+          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
         </is>
       </c>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" ht="33.0" customHeight="1">
+    <row r="110" ht="19.5" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">実行タイミングと前提</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
         </is>
       </c>
       <c r="C110" s="3"/>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
       <c r="C111" s="3"/>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
       <c r="C112" s="3"/>
@@ -9621,19 +9621,33 @@
     <row r="113" ht="33.0" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
         </is>
       </c>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
     </row>
+    <row r="114" ht="33.0" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="41">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -9674,6 +9688,7 @@
     <mergeCell ref="B111:D111"/>
     <mergeCell ref="B112:D112"/>
     <mergeCell ref="B113:D113"/>
+    <mergeCell ref="B114:D114"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-30 15:18:45</t>
+          <t xml:space="preserve">2026-08-31 22:38:36</t>
         </is>
       </c>
     </row>
@@ -7058,68 +7058,76 @@
     <row r="137" ht="33.0" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--truststore-inventory-text FILE</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E137" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="138" ht="33.0" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-truststore-inventory-text</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E138" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="139" ht="33.0" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -7135,7 +7143,7 @@
       <c r="E139" s="7"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -7147,23 +7155,23 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E140" s="7"/>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -7175,23 +7183,23 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E141" s="7"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7211,7 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--prune-build-cache</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -7219,61 +7227,85 @@
       <c r="E142" s="7"/>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="19.5" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="33.0" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C143" s="3"/>
-      <c r="D143" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E143" s="7"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="144" ht="33.0" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C144" s="3"/>
-      <c r="D144" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E144" s="7"/>
-      <c r="F144" s="3"/>
-    </row>
-    <row r="145" ht="33.0" customHeight="1">
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="19.5" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="7"/>
-      <c r="F145" s="3"/>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="33.0" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
@@ -7283,7 +7315,7 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C146" s="3"/>
@@ -7299,7 +7331,7 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C147" s="3"/>
@@ -7315,7 +7347,7 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C148" s="3"/>
@@ -7326,42 +7358,34 @@
     <row r="149" ht="33.0" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="7"/>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
+      <c r="F149" s="3"/>
     </row>
     <row r="150" ht="33.0" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="7"/>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
-        </is>
-      </c>
+      <c r="F150" s="3"/>
     </row>
     <row r="151" ht="33.0" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
@@ -7371,7 +7395,7 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C151" s="3"/>
@@ -7379,7 +7403,7 @@
       <c r="E151" s="7"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7415,7 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C152" s="3"/>
@@ -7399,7 +7423,7 @@
       <c r="E152" s="7"/>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7435,7 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C153" s="3"/>
@@ -7419,7 +7443,7 @@
       <c r="E153" s="7"/>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -7431,7 +7455,7 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C154" s="3"/>
@@ -7439,7 +7463,7 @@
       <c r="E154" s="7"/>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7475,7 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C155" s="3"/>
@@ -7459,7 +7483,7 @@
       <c r="E155" s="7"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7495,7 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C156" s="3"/>
@@ -7479,7 +7503,7 @@
       <c r="E156" s="7"/>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7515,7 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-file-limit N</t>
         </is>
       </c>
       <c r="C157" s="3"/>
@@ -7499,7 +7523,7 @@
       <c r="E157" s="7"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7535,7 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--directory-file-limit all</t>
         </is>
       </c>
       <c r="C158" s="3"/>
@@ -7519,12 +7543,52 @@
       <c r="E158" s="7"/>
       <c r="F158" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="33.0" customHeight="1">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="33.0" customHeight="1">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F158"/>
+  <autoFilter ref="A4:F160"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -9388,7 +9452,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">root ユーザで bash へ接続 / bash 接続と同じ対話セッションを docker exec -u 0:0 で開く。コンテナの既定ユーザーが非 root (JBoss EAP の jboss ユーザー等) で、権限不足により読めないファイルの確認やパッケージ導入を調べたいときに使う / 接続先に /bin/bash (root 実行を禁止する設定では接続できない)</t>
+          <t xml:space="preserve">root ユーザで bash へ接続 / bash 接続と同じ対話セッションを docker exec -u 0:0 で開く。コンテナの既定ユーザーが非 root (JBoss EAP の jboss ユーザー等) で、権限不足により読めないファイルの確認やパッケージ導入を調べたいときに使う / 接続先に対話シェル (root 実行を禁止する設定では接続できない)</t>
         </is>
       </c>
       <c r="C96" s="3"/>
@@ -9481,26 +9545,26 @@
     <row r="103" ht="33.0" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss モジュール一覧 (module-loading:module-info)</t>
+          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_HOME の検出 / 環境変数 JBOSS_HOME / JBOSS_EAP_HOME → 既定の候補 (/opt/jboss-eap / /opt/eap / /opt/jboss / /opt/wildfly ほか) の順に、bin と modules を持つディレクトリを探す</t>
+          <t xml:space="preserve">CLI の解決 / コンテナの環境変数 BATCH_MOCK_CLI → 既定 /opt/batch-mock/efs-propagation.sh。CLI はコンテナ内の POSIX sh で動くため、ホスト側にも コンテナ側にも Python は不要 (alpine でそのまま動く)</t>
         </is>
       </c>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
     </row>
-    <row r="104" ht="33.0" customHeight="1">
+    <row r="104" ht="49.5" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">EFS マウント伝播確認 (偽装バッチサーバー経由)</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
+          <t xml:space="preserve">(1) 偽装バッチサーバーの状態 / 起動状態・自身の healthcheck・連続失敗回数・再起動回数・起動時刻・実行 uid:gid・EFS マウント (マウント先 / rw ro / ボリューム名)。running でない / unhealthy / uid:gid が BATCH_MOCK_EFS_UID_GID (既定 6301:6302) と違うときは警告する</t>
         </is>
       </c>
       <c r="C104" s="3"/>
@@ -9509,82 +9573,82 @@
     <row r="105" ht="33.0" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
+          <t xml:space="preserve">JBoss モジュール一覧 (module-loading:module-info)</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
+          <t xml:space="preserve">JBOSS_HOME の検出 / 環境変数 JBOSS_HOME / JBOSS_EAP_HOME → 既定の候補 (/opt/jboss-eap / /opt/eap / /opt/jboss / /opt/wildfly ほか) の順に、bin と modules を持つディレクトリを探す</t>
         </is>
       </c>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
     </row>
-    <row r="106" ht="49.5" customHeight="1">
+    <row r="106" ht="33.0" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">原因</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
+          <t xml:space="preserve">ツリー・デプロイ構造 / [3] [4] は既定では見出しだけを残し、中身は出力しない。--directory-tree-report を併用したときだけ全深度・全ファイル名で保存する</t>
         </is>
       </c>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
     </row>
-    <row r="107" ht="19.5" customHeight="1">
+    <row r="107" ht="33.0" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">後始末でのボリューム削除</t>
+          <t xml:space="preserve">5.7 --report-dir (全量レポート)</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
+          <t xml:space="preserve">Java 例外解析・read_only 分析 / [10] [11] も既定では見出しと未出力である旨だけを残す。--deploy-exception-report / --readonly-analysis-report を併用したときだけ解析・分析結果を全量で保存する</t>
         </is>
       </c>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
     </row>
-    <row r="108" ht="33.0" customHeight="1">
+    <row r="108" ht="49.5" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 出力ファイル</t>
+          <t xml:space="preserve">原因</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
+          <t xml:space="preserve">A / 名前付きボリュームがデプロイ先を覆っている (最も多い) / Docker がイメージ側の内容をボリュームへ複製するのは、そのボリュームを新規作成した (中身が空の) 1 回目だけ。2 回目以降は既存の中身が優先され、イメージへ焼いた新しい WAR はコンテナから一切見えない。compose down は既定でボリュームを削除しないため、消すまで直らない</t>
         </is>
       </c>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" ht="33.0" customHeight="1">
+    <row r="109" ht="19.5" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">後始末でのボリューム削除</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作を「0) 対話操作を終了」まで進めた実行 (終了コード 0) / 削除する (既定。従来は残していた)</t>
         </is>
       </c>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" ht="19.5" customHeight="1">
+    <row r="110" ht="33.0" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行タイミングと前提</t>
+          <t xml:space="preserve">6.2 出力ファイル</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
+          <t xml:space="preserve">[12] JBoss EAP Undertow バーチャルホスト (default-host) の分析 / subsystem の既定値、server とリスナー、バーチャルホストと受け付けるホスト名、Host ヘッダーごとの振り分け、実リクエストによる確認、要確認 / 「未取得」として理由を記録</t>
         </is>
       </c>
       <c r="C110" s="3"/>
@@ -9593,26 +9657,26 @@
     <row r="111" ht="33.0" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">実行タイミングと前提</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
+          <t xml:space="preserve">画面表示 / 既定では行わない。--readonly-analysis-display 指定時のみ (--no-readonly-analysis-display で打ち消せる)。分析と Excel / テキスト出力は指定が無くても行う</t>
         </is>
       </c>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
     </row>
-    <row r="112" ht="33.0" customHeight="1">
+    <row r="112" ht="19.5" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">実行タイミングと前提</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
+          <t xml:space="preserve">全量レポート [11] への記載 / 既定では行わない。--readonly-analysis-report 指定時のみ (--no-readonly-analysis-report で打ち消せる)</t>
         </is>
       </c>
       <c r="C112" s="3"/>
@@ -9626,7 +9690,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION / --region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
       <c r="C113" s="3"/>
@@ -9635,19 +9699,47 @@
     <row r="114" ht="33.0" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
     </row>
+    <row r="115" ht="33.0" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
+        </is>
+      </c>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+    </row>
+    <row r="116" ht="33.0" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぐ</t>
+        </is>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="43">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -9689,6 +9781,8 @@
     <mergeCell ref="B112:D112"/>
     <mergeCell ref="B113:D113"/>
     <mergeCell ref="B114:D114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="B116:D116"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/build_and_verify_guide.xlsx
+++ b/docs/build_and_verify_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31 22:38:36</t>
+          <t xml:space="preserve">2026-09-01 02:31:49</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="33.0" customHeight="1">
+    <row r="106" ht="49.5" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6071,17 +6071,17 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--directory-tree-excel</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -6091,11 +6091,11 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ディレクトリのみのツリーを Excel ブック (.xlsx) へ追加出力する。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6103,17 +6103,17 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">上記の Excel 出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6135,12 +6135,12 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -6150,16 +6150,16 @@
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="82.5" customHeight="1">
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する。指定すると Excel 出力を有効にする (--report-dir が無くても出力できる)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="33.0" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6167,17 +6167,17 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -6199,17 +6199,17 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -6219,11 +6219,11 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="19.5" customHeight="1">
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="33.0" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6231,59 +6231,59 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="99.0" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="33.0" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B112" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-report</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリのみのツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-report</t>
+          <t xml:space="preserve">--deploy-exception-display</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -6303,51 +6303,51 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="19.5" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="E113" s="7" t="inlineStr">
+      <c r="E114" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="33.0" customHeight="1">
-      <c r="A114" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B114" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -6359,17 +6359,17 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-report</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -6379,11 +6379,11 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="19.5" customHeight="1">
+          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="33.0" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6391,17 +6391,17 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--no-deploy-exception-report</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -6423,17 +6423,17 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6455,91 +6455,91 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-display</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="19.5" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="33.0" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="33.0" customHeight="1">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis-display</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="49.5" customHeight="1">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B120" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-report</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis-report</t>
+          <t xml:space="preserve">--readonly-analysis-display</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -6559,9 +6559,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6583,123 +6583,123 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-readonly-analysis-display</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+     